--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -40553,6 +40553,52 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1748" t="n">
+        <v>0</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>3</v>
+      </c>
+      <c r="G1748" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1749" t="n">
+        <v>1500</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="G1749" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -40599,6 +40599,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1750" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G1750" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -40622,6 +40622,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -40463,22 +40463,22 @@
     </row>
     <row r="1744">
       <c r="A1744" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1744" t="n">
         <v>1500</v>
       </c>
       <c r="C1744" t="n">
-        <v>3.03999996185303</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="D1744" t="n">
-        <v>3.03999996185303</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="E1744" t="n">
-        <v>3.03999996185303</v>
+        <v>3.05999994277954</v>
       </c>
       <c r="F1744" t="n">
-        <v>3.03999996185303</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="G1744" t="s">
         <v>7</v>
@@ -40486,19 +40486,19 @@
     </row>
     <row r="1745">
       <c r="A1745" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1745" t="n">
-        <v>6750</v>
+        <v>1500</v>
       </c>
       <c r="C1745" t="n">
-        <v>3.09999990463257</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="D1745" t="n">
-        <v>3.00999999046326</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="E1745" t="n">
-        <v>3.00999999046326</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="F1745" t="n">
         <v>3.03999996185303</v>
@@ -40509,19 +40509,19 @@
     </row>
     <row r="1746">
       <c r="A1746" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1746" t="n">
-        <v>0</v>
+        <v>6750</v>
       </c>
       <c r="C1746" t="n">
-        <v>3.03999996185303</v>
+        <v>3.09999990463257</v>
       </c>
       <c r="D1746" t="n">
-        <v>3.03999996185303</v>
+        <v>3.00999999046326</v>
       </c>
       <c r="E1746" t="n">
-        <v>3.03999996185303</v>
+        <v>3.00999999046326</v>
       </c>
       <c r="F1746" t="n">
         <v>3.03999996185303</v>
@@ -40532,22 +40532,22 @@
     </row>
     <row r="1747">
       <c r="A1747" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1747" t="n">
-        <v>3750</v>
+        <v>0</v>
       </c>
       <c r="C1747" t="n">
-        <v>3.04999995231628</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="D1747" t="n">
-        <v>3</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="E1747" t="n">
-        <v>3.04999995231628</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="F1747" t="n">
-        <v>3</v>
+        <v>3.03999996185303</v>
       </c>
       <c r="G1747" t="s">
         <v>7</v>
@@ -40555,19 +40555,19 @@
     </row>
     <row r="1748">
       <c r="A1748" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1748" t="n">
-        <v>0</v>
+        <v>3750</v>
       </c>
       <c r="C1748" t="n">
-        <v>3</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="D1748" t="n">
         <v>3</v>
       </c>
       <c r="E1748" t="n">
-        <v>3</v>
+        <v>3.04999995231628</v>
       </c>
       <c r="F1748" t="n">
         <v>3</v>
@@ -40578,22 +40578,22 @@
     </row>
     <row r="1749">
       <c r="A1749" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1749" t="n">
-        <v>1500</v>
+        <v>0</v>
       </c>
       <c r="C1749" t="n">
-        <v>3.00999999046326</v>
+        <v>3</v>
       </c>
       <c r="D1749" t="n">
-        <v>3.00999999046326</v>
+        <v>3</v>
       </c>
       <c r="E1749" t="n">
-        <v>3.00999999046326</v>
+        <v>3</v>
       </c>
       <c r="F1749" t="n">
-        <v>3.00999999046326</v>
+        <v>3</v>
       </c>
       <c r="G1749" t="s">
         <v>7</v>
@@ -40601,22 +40601,22 @@
     </row>
     <row r="1750">
       <c r="A1750" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1750" t="n">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="C1750" t="n">
-        <v>3.03999996185303</v>
+        <v>3.00999999046326</v>
       </c>
       <c r="D1750" t="n">
-        <v>3.03999996185303</v>
+        <v>3.00999999046326</v>
       </c>
       <c r="E1750" t="n">
-        <v>3.03999996185303</v>
+        <v>3.00999999046326</v>
       </c>
       <c r="F1750" t="n">
-        <v>3.03999996185303</v>
+        <v>3.00999999046326</v>
       </c>
       <c r="G1750" t="s">
         <v>7</v>
@@ -40624,24 +40624,47 @@
     </row>
     <row r="1751">
       <c r="A1751" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1751" t="n">
-        <v>2250</v>
+        <v>750</v>
       </c>
       <c r="C1751" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1751" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="E1751" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="G1751" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1752" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1752" t="n">
         <v>3.05999994277954</v>
       </c>
-      <c r="D1751" t="n">
-        <v>3.04999995231628</v>
-      </c>
-      <c r="E1751" t="n">
-        <v>3.04999995231628</v>
-      </c>
-      <c r="F1751" t="n">
+      <c r="D1752" t="n">
         <v>3.05999994277954</v>
       </c>
-      <c r="G1751" t="s">
+      <c r="E1752" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G1752" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189449310303</v>
+        <v>2.73189425468445</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722755432129</v>
+        <v>2.86722779273987</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.50550007820129</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80716872215271</v>
+        <v>2.80716848373413</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.70586848258972</v>
+        <v>2.7058687210083</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.38949990272522</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71427702903748</v>
+        <v>2.7142767906189</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.36050009727478</v>
       </c>
       <c r="G12" t="n">
-        <v>2.69105386734009</v>
+        <v>2.69105434417725</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -707,7 +707,7 @@
         <v>3.36450004577637</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6942572593689</v>
+        <v>2.69425702095032</v>
       </c>
       <c r="H13" t="s">
         <v>8</v>
@@ -733,7 +733,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72228479385376</v>
+        <v>2.72228455543518</v>
       </c>
       <c r="H14" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558554649353</v>
+        <v>3.63558530807495</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.96390914916992</v>
+        <v>3.96390891075134</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G21" t="n">
-        <v>3.60515546798706</v>
+        <v>3.60515570640564</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51226425170898</v>
+        <v>3.51226401329041</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43698954582214</v>
+        <v>3.43698930740356</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4914436340332</v>
+        <v>3.49144387245178</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.38350009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>3.51026201248169</v>
+        <v>3.51026225090027</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.24350023269653</v>
       </c>
       <c r="G27" t="n">
-        <v>3.39815139770508</v>
+        <v>3.39815187454224</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.20050001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>3.36371731758118</v>
+        <v>3.36371755599976</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048462867737</v>
+        <v>3.33048439025879</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.28724193572998</v>
+        <v>3.28724217414856</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.04700517654419</v>
+        <v>3.04700493812561</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.97093033790588</v>
+        <v>2.9709300994873</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1435,7 +1435,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H41" t="s">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H42" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9909496307373</v>
+        <v>2.99094986915588</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1643,7 +1643,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H49" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507225036621</v>
+        <v>3.11507248878479</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702470779419</v>
+        <v>3.06702494621277</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507225036621</v>
+        <v>3.11507248878479</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505248069763</v>
+        <v>3.09505271911621</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>2.90686702728271</v>
+        <v>2.90686726570129</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280371665955</v>
+        <v>2.84280347824097</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670910835266</v>
+        <v>2.74670886993408</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467757225037</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>2.83879995346069</v>
+        <v>2.83879947662354</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2345,7 +2345,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H76" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80676865577698</v>
+        <v>2.80676817893982</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866156578064</v>
+        <v>2.69866132736206</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049612045288</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185596466064</v>
+        <v>1.88185584545135</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556377887726</v>
+        <v>1.58556389808655</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161908626556</v>
+        <v>1.64161896705627</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771393299103</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G106" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771393299103</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.89787173271179</v>
+        <v>1.8978716135025</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205342292786</v>
+        <v>2.08205318450928</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049612045288</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79475617408752</v>
+        <v>2.7947564125061</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>2.66663002967834</v>
+        <v>2.66662979125977</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467757225037</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.79475617408752</v>
+        <v>2.7947564125061</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.78674840927124</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78674840927124</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G132" t="n">
-        <v>2.61057472229004</v>
+        <v>2.61057448387146</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856295585632</v>
+        <v>2.59856271743774</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71868133544922</v>
+        <v>2.71868109703064</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>2.76272487640381</v>
+        <v>2.76272463798523</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G164" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3</v>
       </c>
       <c r="G168" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3</v>
       </c>
       <c r="G169" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G179" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3</v>
       </c>
       <c r="G180" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3</v>
       </c>
       <c r="G181" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3</v>
       </c>
       <c r="G184" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3</v>
       </c>
       <c r="G185" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3</v>
       </c>
       <c r="G186" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3</v>
       </c>
       <c r="G187" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.05100893974304</v>
+        <v>3.0510094165802</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258625030518</v>
+        <v>2.62258696556091</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258625030518</v>
+        <v>2.62258696556091</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3</v>
       </c>
       <c r="G219" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.49446034431458</v>
+        <v>2.49445986747742</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6193,7 +6193,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H224" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29025888442993</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.29025888442993</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G241" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G244" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3</v>
       </c>
       <c r="G245" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3</v>
       </c>
       <c r="G246" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3</v>
       </c>
       <c r="G255" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.18615627288818</v>
+        <v>2.1861560344696</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834548950195</v>
+        <v>2.37834572792053</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G304" t="n">
-        <v>2.73069334030151</v>
+        <v>2.73069357872009</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>2.60657095909119</v>
+        <v>2.60657072067261</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039703369141</v>
+        <v>2.43039679527283</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045634269714</v>
+        <v>2.49045610427856</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>2.36633372306824</v>
+        <v>2.36633348464966</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3</v>
       </c>
       <c r="G322" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8819,7 +8819,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H325" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G328" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G331" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9027,7 +9027,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H333" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3</v>
       </c>
       <c r="G335" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.43840479850769</v>
+        <v>2.43840503692627</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3</v>
       </c>
       <c r="G344" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G347" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049612045288</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>2.67063403129578</v>
+        <v>2.6706337928772</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>2.66663002967834</v>
+        <v>2.66662979125977</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266580581665</v>
+        <v>2.70266556739807</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467757225037</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.77473640441895</v>
+        <v>2.77473664283752</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.5</v>
       </c>
       <c r="G366" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G369" t="n">
-        <v>3.23519039154053</v>
+        <v>3.23519062995911</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10041,7 +10041,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H372" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07503294944763</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10275,7 +10275,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H381" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G383" t="n">
-        <v>3.07503294944763</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>3.07503294944763</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G389" t="n">
-        <v>3.07503294944763</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G390" t="n">
-        <v>3.07503294944763</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10535,7 +10535,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G391" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H391" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.17112755775452</v>
+        <v>3.1711277961731</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G400" t="n">
-        <v>3.07503294944763</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>3.42738056182861</v>
+        <v>3.42738032341003</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4</v>
       </c>
       <c r="G424" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G435" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11887,7 +11887,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H443" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12043,7 +12043,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H449" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>3.04300141334534</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12147,7 +12147,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H453" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12225,7 +12225,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G456" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H456" t="s">
         <v>8</v>
@@ -12251,7 +12251,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H457" t="s">
         <v>8</v>
@@ -12277,7 +12277,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H458" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12407,7 +12407,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H463" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12511,7 +12511,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H467" t="s">
         <v>8</v>
@@ -12537,7 +12537,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G468" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H468" t="s">
         <v>8</v>
@@ -12563,7 +12563,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H469" t="s">
         <v>8</v>
@@ -12589,7 +12589,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H470" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>3.07503294944763</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12693,7 +12693,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H474" t="s">
         <v>8</v>
@@ -12719,7 +12719,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H475" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12823,7 +12823,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H479" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13057,7 +13057,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H488" t="s">
         <v>8</v>
@@ -13109,7 +13109,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G490" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H490" t="s">
         <v>8</v>
@@ -13135,7 +13135,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H491" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G493" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G495" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G498" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G499" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G505" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.5</v>
       </c>
       <c r="G517" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846386909485</v>
+        <v>2.49846410751343</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G529" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14149,7 +14149,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H530" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3</v>
       </c>
       <c r="G540" t="n">
-        <v>2.40236949920654</v>
+        <v>2.40236926078796</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>2.29025888442993</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15475,7 +15475,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213226318359</v>
+        <v>2.16213250160217</v>
       </c>
       <c r="H581" t="s">
         <v>8</v>
@@ -15579,7 +15579,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G585" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H585" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400588035583</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15631,7 +15631,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G587" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H587" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.17814803123474</v>
+        <v>2.1781485080719</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G589" t="n">
-        <v>2.1301007270813</v>
+        <v>2.13010096549988</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15709,7 +15709,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G590" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H590" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.05002188682556</v>
+        <v>2.05002164840698</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400588035583</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587961673737</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2</v>
       </c>
       <c r="G600" t="n">
-        <v>1.60157954692841</v>
+        <v>1.6015796661377</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G602" t="n">
-        <v>1.53751647472382</v>
+        <v>1.53751623630524</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2</v>
       </c>
       <c r="G603" t="n">
-        <v>1.60157954692841</v>
+        <v>1.6015796661377</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61759519577026</v>
+        <v>1.61759531497955</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376924037933</v>
+        <v>1.79376912117004</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587961673737</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.9539270401001</v>
+        <v>1.95392715930939</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.80978488922119</v>
+        <v>1.80978500843048</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962697029114</v>
+        <v>1.64962673187256</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568227767944</v>
+        <v>1.70568215847015</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376924037933</v>
+        <v>1.79376912117004</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771393299103</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568227767944</v>
+        <v>1.70568215847015</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779277324677</v>
+        <v>1.81779265403748</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779277324677</v>
+        <v>1.81779265403748</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G647" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.85018181800842</v>
+        <v>1.850182056427</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.80106210708618</v>
+        <v>1.80106198787689</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836863517761</v>
+        <v>1.85836839675903</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836863517761</v>
+        <v>1.85836839675903</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650225162506</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650225162506</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G661" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.83380877971649</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G664" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.83380877971649</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G669" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G671" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G676" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G677" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G697" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G722" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G723" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G739" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G748" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.50224947929382</v>
+        <v>1.50224959850311</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634288787842</v>
+        <v>1.50634276866913</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634288787842</v>
+        <v>1.50634276866913</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359609603882</v>
+        <v>1.47359621524811</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G756" t="n">
-        <v>1.48996949195862</v>
+        <v>1.48996961116791</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>1.60458254814148</v>
+        <v>1.60458266735077</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G774" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.60458254814148</v>
+        <v>1.60458266735077</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>1.80106210708618</v>
+        <v>1.80106198787689</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G789" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.80924880504608</v>
+        <v>1.8092485666275</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G794" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G795" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G802" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G811" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650225162506</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80106210708618</v>
+        <v>1.80106198787689</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842171669006</v>
+        <v>1.94842183589935</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21845,7 +21845,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H826" t="s">
         <v>8</v>
@@ -21871,7 +21871,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G827" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H827" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21975,7 +21975,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H831" t="s">
         <v>8</v>
@@ -22105,7 +22105,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H836" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22183,7 +22183,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H839" t="s">
         <v>8</v>
@@ -22287,7 +22287,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H843" t="s">
         <v>8</v>
@@ -22313,7 +22313,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H844" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>2.05484795570374</v>
+        <v>2.05484819412231</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.05484795570374</v>
+        <v>2.05484819412231</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22599,7 +22599,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H855" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22677,7 +22677,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G858" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H858" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935508728027</v>
+        <v>1.98935496807098</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204820156097</v>
+        <v>1.93204832077026</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479511260986</v>
+        <v>1.96479487419128</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930152893066</v>
+        <v>1.89930188655853</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930152893066</v>
+        <v>1.89930188655853</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.83380877971649</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>2.05484795570374</v>
+        <v>2.05484819412231</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G901" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G904" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993092536926</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993092536926</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G918" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G919" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G935" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G940" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993092536926</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G954" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G956" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G958" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G984" t="n">
-        <v>1.74206173419952</v>
+        <v>1.74206161499023</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.34070432186127</v>
+        <v>1.34070444107056</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362520694733</v>
+        <v>1.32362532615662</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.34070432186127</v>
+        <v>1.34070444107056</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.33216488361359</v>
+        <v>1.3321647644043</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.33216488361359</v>
+        <v>1.3321647644043</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.75</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.49441564083099</v>
+        <v>1.49441576004028</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.51149463653564</v>
+        <v>1.51149475574493</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958752155304</v>
+        <v>1.63958728313446</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.74206173419952</v>
+        <v>1.74206161499023</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.59688997268677</v>
+        <v>1.59688985347748</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.59688997268677</v>
+        <v>1.59688985347748</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958752155304</v>
+        <v>1.63958728313446</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -46028,6 +46028,32 @@
         <v>3.09999990463257</v>
       </c>
       <c r="H1756" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1757" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G1757" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="H1757" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189425468445</v>
+        <v>2.73189449310303</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -447,7 +447,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722779273987</v>
+        <v>2.86722755432129</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -499,7 +499,7 @@
         <v>3.33400011062622</v>
       </c>
       <c r="G5" t="n">
-        <v>2.66983318328857</v>
+        <v>2.66983294487</v>
       </c>
       <c r="H5" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7058687210083</v>
+        <v>2.70586848258972</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64260625839233</v>
+        <v>2.64260601997375</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69065356254578</v>
+        <v>2.69065380096436</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -681,7 +681,7 @@
         <v>3.36050009727478</v>
       </c>
       <c r="G12" t="n">
-        <v>2.69105434417725</v>
+        <v>2.69105386734009</v>
       </c>
       <c r="H12" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558530807495</v>
+        <v>3.63558578491211</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.96390891075134</v>
+        <v>3.9639093875885</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -889,7 +889,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578300476074</v>
+        <v>3.83578276634216</v>
       </c>
       <c r="H20" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G21" t="n">
-        <v>3.60515570640564</v>
+        <v>3.60515522956848</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -993,7 +993,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43698930740356</v>
+        <v>3.43698978424072</v>
       </c>
       <c r="H24" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.49144387245178</v>
+        <v>3.4914436340332</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1071,7 +1071,7 @@
         <v>4.24350023269653</v>
       </c>
       <c r="G27" t="n">
-        <v>3.39815187454224</v>
+        <v>3.39815139770508</v>
       </c>
       <c r="H27" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.20050001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>3.36371755599976</v>
+        <v>3.36371731758118</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128523826599</v>
+        <v>3.33128547668457</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048439025879</v>
+        <v>3.33048462867737</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.28724217414856</v>
+        <v>3.28724193572998</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.625</v>
       </c>
       <c r="G33" t="n">
-        <v>2.9028627872467</v>
+        <v>2.90286302566528</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1487,7 +1487,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>3.03499317169189</v>
+        <v>3.03499293327332</v>
       </c>
       <c r="H43" t="s">
         <v>8</v>
@@ -1513,7 +1513,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>3.03499317169189</v>
+        <v>3.03499293327332</v>
       </c>
       <c r="H44" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694562911987</v>
+        <v>2.98694586753845</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694562911987</v>
+        <v>2.98694586753845</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.625</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9028627872467</v>
+        <v>2.90286302566528</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505271911621</v>
+        <v>3.09505248069763</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>2.90686726570129</v>
+        <v>2.90686702728271</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280347824097</v>
+        <v>2.84280371665955</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670886993408</v>
+        <v>2.74670934677124</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>2.83879947662354</v>
+        <v>2.83879995346069</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88684725761414</v>
+        <v>2.88684701919556</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.88684725761414</v>
+        <v>2.88684701919556</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2579,7 +2579,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80676817893982</v>
+        <v>2.8067684173584</v>
       </c>
       <c r="H85" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.59055495262146</v>
+        <v>2.59055519104004</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.53049612045288</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2761,7 +2761,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H92" t="s">
         <v>8</v>
@@ -2787,7 +2787,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H93" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556389808655</v>
+        <v>1.58556377887726</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2969,7 +2969,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161896705627</v>
+        <v>1.64161884784698</v>
       </c>
       <c r="H100" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.67765462398529</v>
+        <v>1.677654504776</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75773346424103</v>
+        <v>1.75773358345032</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8978716135025</v>
+        <v>1.89787173271179</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205318450928</v>
+        <v>2.08205342292786</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.53049612045288</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3255,7 +3255,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H111" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>2.81878018379211</v>
+        <v>2.81877994537354</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664956092834</v>
+        <v>2.68664979934692</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>2.66662979125977</v>
+        <v>2.66663002967834</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>2.75071263313293</v>
+        <v>2.75071287155151</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.78674817085266</v>
+        <v>2.78674840927124</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78674817085266</v>
+        <v>2.78674840927124</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856271743774</v>
+        <v>2.59856295585632</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>2.52248764038086</v>
+        <v>2.52248787879944</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>2.52248764038086</v>
+        <v>2.52248787879944</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4087,7 +4087,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H143" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71868109703064</v>
+        <v>2.71868133544922</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4217,7 +4217,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.8267879486084</v>
+        <v>2.82678771018982</v>
       </c>
       <c r="H148" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G150" t="n">
-        <v>2.69065356254578</v>
+        <v>2.69065380096436</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G151" t="n">
-        <v>2.69065356254578</v>
+        <v>2.69065380096436</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G152" t="n">
-        <v>2.71067357063293</v>
+        <v>2.71067333221436</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G153" t="n">
-        <v>2.64260625839233</v>
+        <v>2.64260601997375</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.63459825515747</v>
+        <v>2.63459801673889</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>2.52248764038086</v>
+        <v>2.52248787879944</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G164" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3</v>
       </c>
       <c r="G168" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3</v>
       </c>
       <c r="G169" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3</v>
       </c>
       <c r="G180" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3</v>
       </c>
       <c r="G181" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3</v>
       </c>
       <c r="G184" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3</v>
       </c>
       <c r="G185" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3</v>
       </c>
       <c r="G186" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3</v>
       </c>
       <c r="G187" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5283,7 +5283,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H189" t="s">
         <v>8</v>
@@ -5309,7 +5309,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H190" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.0510094165802</v>
+        <v>3.05100893974304</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.81878018379211</v>
+        <v>2.81877994537354</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G202" t="n">
-        <v>2.69065356254578</v>
+        <v>2.69065380096436</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258696556091</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258696556091</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>2.52248764038086</v>
+        <v>2.52248787879944</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5907,7 +5907,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H213" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34631395339966</v>
+        <v>2.34631443023682</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -5985,7 +5985,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H216" t="s">
         <v>8</v>
@@ -6011,7 +6011,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H217" t="s">
         <v>8</v>
@@ -6037,7 +6037,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H218" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3</v>
       </c>
       <c r="G219" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6089,7 +6089,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H220" t="s">
         <v>8</v>
@@ -6141,7 +6141,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.49445986747742</v>
+        <v>2.494460105896</v>
       </c>
       <c r="H222" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6219,7 +6219,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H225" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.52248764038086</v>
+        <v>2.52248787879944</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.52248764038086</v>
+        <v>2.52248787879944</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6349,7 +6349,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H230" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>2.34631395339966</v>
+        <v>2.34631443023682</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6427,7 +6427,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H233" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6609,7 +6609,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H240" t="s">
         <v>8</v>
@@ -6635,7 +6635,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G241" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H241" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3</v>
       </c>
       <c r="G245" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3</v>
       </c>
       <c r="G246" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3</v>
       </c>
       <c r="G255" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7129,7 +7129,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G260" t="n">
-        <v>2.21418380737305</v>
+        <v>2.21418356895447</v>
       </c>
       <c r="H260" t="s">
         <v>8</v>
@@ -7155,7 +7155,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21418380737305</v>
+        <v>2.21418356895447</v>
       </c>
       <c r="H261" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21018004417419</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820757865906</v>
+        <v>2.23820734024048</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7441,7 +7441,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H272" t="s">
         <v>8</v>
@@ -7467,7 +7467,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H273" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21018004417419</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G304" t="n">
-        <v>2.73069357872009</v>
+        <v>2.73069310188293</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8377,7 +8377,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H308" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039679527283</v>
+        <v>2.43039703369141</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8585,7 +8585,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>2.36633348464966</v>
+        <v>2.36633372306824</v>
       </c>
       <c r="H316" t="s">
         <v>8</v>
@@ -8663,7 +8663,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H319" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430218696594</v>
+        <v>2.33430242538452</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3</v>
       </c>
       <c r="G322" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8923,7 +8923,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H329" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.52248764038086</v>
+        <v>2.52248787879944</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3</v>
       </c>
       <c r="G335" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9261,7 +9261,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H342" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3</v>
       </c>
       <c r="G344" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.53049612045288</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9573,7 +9573,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G354" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H354" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>2.66662979125977</v>
+        <v>2.66663002967834</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.5</v>
       </c>
       <c r="G366" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G382" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G383" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G389" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G390" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.1711277961731</v>
+        <v>3.17112755775452</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G400" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4</v>
       </c>
       <c r="G424" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G440" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G451" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G454" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G459" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G460" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G476" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G478" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G480" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G481" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G487" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495410919189</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G489" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G493" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G495" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G496" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G498" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G499" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G505" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.5</v>
       </c>
       <c r="G517" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14071,7 +14071,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H527" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846410751343</v>
+        <v>2.49846434593201</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3</v>
       </c>
       <c r="G540" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14513,7 +14513,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H544" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14825,7 +14825,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H556" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G562" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21018004417419</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.1781485080719</v>
+        <v>2.17814826965332</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G589" t="n">
-        <v>2.13010096549988</v>
+        <v>2.1301007270813</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587985515594</v>
+        <v>1.90587973594666</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2</v>
       </c>
       <c r="G600" t="n">
-        <v>1.6015796661377</v>
+        <v>1.60157954692841</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G601" t="n">
-        <v>1.49747693538666</v>
+        <v>1.49747705459595</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G602" t="n">
-        <v>1.53751623630524</v>
+        <v>1.53751635551453</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2</v>
       </c>
       <c r="G603" t="n">
-        <v>1.6015796661377</v>
+        <v>1.60157954692841</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.6336110830307</v>
+        <v>1.63361120223999</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564273834229</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376912117004</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587985515594</v>
+        <v>1.90587973594666</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.80978500843048</v>
+        <v>1.8097847700119</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16567,7 +16567,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962673187256</v>
+        <v>1.64962685108185</v>
       </c>
       <c r="H623" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564273834229</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970604896545</v>
+        <v>1.72970592975616</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970604896545</v>
+        <v>1.72970592975616</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376912117004</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779289245605</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779289245605</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17061,7 +17061,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75372970104218</v>
+        <v>1.75372958183289</v>
       </c>
       <c r="H642" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.83380854129791</v>
+        <v>1.83380842208862</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G647" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.850182056427</v>
+        <v>1.85018169879913</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17503,7 +17503,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H659" t="s">
         <v>8</v>
@@ -17555,7 +17555,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G661" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H661" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G664" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17685,7 +17685,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H666" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G669" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17815,7 +17815,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G671" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H671" t="s">
         <v>8</v>
@@ -18049,7 +18049,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H680" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18283,7 +18283,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H689" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19323,7 +19323,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>1.6455157995224</v>
+        <v>1.64551568031311</v>
       </c>
       <c r="H729" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G747" t="n">
-        <v>1.51452946662903</v>
+        <v>1.51452934741974</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19843,7 +19843,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.56364929676056</v>
+        <v>1.56364917755127</v>
       </c>
       <c r="H749" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19921,7 +19921,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.50224959850311</v>
+        <v>1.50224947929382</v>
       </c>
       <c r="H752" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359621524811</v>
+        <v>1.47359609603882</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20025,7 +20025,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G756" t="n">
-        <v>1.48996961116791</v>
+        <v>1.48996949195862</v>
       </c>
       <c r="H756" t="s">
         <v>8</v>
@@ -20129,7 +20129,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>1.60458266735077</v>
+        <v>1.60458254814148</v>
       </c>
       <c r="H760" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20337,7 +20337,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G768" t="n">
-        <v>1.56364929676056</v>
+        <v>1.56364917755127</v>
       </c>
       <c r="H768" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G771" t="n">
-        <v>1.51452946662903</v>
+        <v>1.51452934741974</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20545,7 +20545,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.60458266735077</v>
+        <v>1.60458254814148</v>
       </c>
       <c r="H776" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20649,7 +20649,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H780" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.8092485666275</v>
+        <v>1.80924868583679</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G794" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G795" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21143,7 +21143,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H799" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21221,7 +21221,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G802" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H802" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842183589935</v>
+        <v>1.94842171669006</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G818" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22053,7 +22053,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847455978394</v>
       </c>
       <c r="H834" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.99754166603088</v>
+        <v>1.99754154682159</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22443,7 +22443,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G849" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847455978394</v>
       </c>
       <c r="H849" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.10396790504456</v>
+        <v>2.10396766662598</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22703,7 +22703,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935496807098</v>
+        <v>1.98935508728027</v>
       </c>
       <c r="H859" t="s">
         <v>8</v>
@@ -22729,7 +22729,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847455978394</v>
       </c>
       <c r="H860" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>2.0139148235321</v>
+        <v>2.01391506195068</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930176734924</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930176734924</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G872" t="n">
-        <v>1.91567492485046</v>
+        <v>1.91567504405975</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G901" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G904" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993092536926</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993092536926</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G918" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G919" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G935" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G940" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993092536926</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G954" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G956" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G958" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G984" t="n">
-        <v>1.74206161499023</v>
+        <v>1.74206173419952</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -25979,7 +25979,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H985" t="s">
         <v>8</v>
@@ -26031,7 +26031,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H987" t="s">
         <v>8</v>
@@ -26707,7 +26707,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1013" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27253,7 +27253,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.34070444107056</v>
+        <v>1.34070432186127</v>
       </c>
       <c r="H1034" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362532615662</v>
+        <v>1.32362520694733</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27331,7 +27331,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.34070444107056</v>
+        <v>1.34070432186127</v>
       </c>
       <c r="H1037" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.3321647644043</v>
+        <v>1.33216488361359</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.3321647644043</v>
+        <v>1.33216488361359</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27825,7 +27825,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1056" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.75</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.49441576004028</v>
+        <v>1.49441564083099</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28865,7 +28865,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1096" t="s">
         <v>8</v>
@@ -28891,7 +28891,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1097" t="s">
         <v>8</v>
@@ -28917,7 +28917,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1098" t="s">
         <v>8</v>
@@ -29047,7 +29047,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1103" t="s">
         <v>8</v>
@@ -29151,7 +29151,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.51149475574493</v>
+        <v>1.51149463653564</v>
       </c>
       <c r="H1107" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958728313446</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.74206161499023</v>
+        <v>1.74206173419952</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29593,7 +29593,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1124" t="s">
         <v>8</v>
@@ -29905,7 +29905,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1136" t="s">
         <v>8</v>
@@ -29931,7 +29931,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1137" t="s">
         <v>8</v>
@@ -30009,7 +30009,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H1140" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.59688985347748</v>
+        <v>1.59688997268677</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.59688985347748</v>
+        <v>1.59688997268677</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958728313446</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -46054,6 +46054,32 @@
         <v>3.11999988555908</v>
       </c>
       <c r="H1757" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1758" t="n">
+        <v>6000</v>
+      </c>
+      <c r="C1758" t="n">
+        <v>3.17000007629395</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="G1758" t="n">
+        <v>3.14000010490417</v>
+      </c>
+      <c r="H1758" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722755432129</v>
+        <v>2.86722779273987</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.70586848258972</v>
+        <v>2.7058687210083</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -577,7 +577,7 @@
         <v>3.38949990272522</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7142767906189</v>
+        <v>2.71427702903748</v>
       </c>
       <c r="H8" t="s">
         <v>8</v>
@@ -655,7 +655,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H11" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.43449997901917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7503125667572</v>
+        <v>2.75031232833862</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.32327771186829</v>
+        <v>3.32327747344971</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -915,7 +915,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G21" t="n">
-        <v>3.60515546798706</v>
+        <v>3.60515570640564</v>
       </c>
       <c r="H21" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>3.4353883266449</v>
+        <v>3.43538808822632</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51226377487183</v>
+        <v>3.51226425170898</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329771995544</v>
+        <v>3.34329748153687</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1123,7 +1123,7 @@
         <v>4.20050001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>3.36371731758118</v>
+        <v>3.3637170791626</v>
       </c>
       <c r="H29" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128547668457</v>
+        <v>3.33128523826599</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1201,7 +1201,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.28724217414856</v>
+        <v>3.28724241256714</v>
       </c>
       <c r="H32" t="s">
         <v>8</v>
@@ -1227,7 +1227,7 @@
         <v>3.625</v>
       </c>
       <c r="G33" t="n">
-        <v>2.90286302566528</v>
+        <v>2.9028627872467</v>
       </c>
       <c r="H33" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.04700517654419</v>
+        <v>3.04700541496277</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03098964691162</v>
+        <v>3.03098940849304</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.9709300994873</v>
+        <v>2.97092986106873</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1409,7 +1409,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H40" t="s">
         <v>8</v>
@@ -1591,7 +1591,7 @@
         <v>3.625</v>
       </c>
       <c r="G47" t="n">
-        <v>2.90286302566528</v>
+        <v>2.9028627872467</v>
       </c>
       <c r="H47" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99094986915588</v>
+        <v>2.9909496307373</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.07903695106506</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1825,7 +1825,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H56" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702518463135</v>
+        <v>3.06702470779419</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1903,7 +1903,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H59" t="s">
         <v>8</v>
@@ -1955,7 +1955,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H61" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505271911621</v>
+        <v>3.09505248069763</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G63" t="n">
-        <v>3.03098964691162</v>
+        <v>3.03098940849304</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087079048157</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2085,7 +2085,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>2.90686726570129</v>
+        <v>2.90686702728271</v>
       </c>
       <c r="H66" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280395507812</v>
+        <v>2.84280371665955</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83479571342468</v>
+        <v>2.8347954750061</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2293,7 +2293,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H74" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>2.83879995346069</v>
+        <v>2.83879971504211</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>3.07903695106506</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087079048157</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2527,7 +2527,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88684725761414</v>
+        <v>2.88684749603271</v>
       </c>
       <c r="H83" t="s">
         <v>8</v>
@@ -2553,7 +2553,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.88684725761414</v>
+        <v>2.88684749603271</v>
       </c>
       <c r="H84" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.59055495262146</v>
+        <v>2.59055471420288</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049564361572</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2735,7 +2735,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H91" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185572624207</v>
+        <v>1.88185596466064</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.66163885593414</v>
+        <v>1.66163873672485</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66163885593414</v>
+        <v>1.66163873672485</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.67765462398529</v>
+        <v>1.677654504776</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G106" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205318450928</v>
+        <v>2.08205342292786</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049564361572</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3463,7 +3463,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H119" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664979934692</v>
+        <v>2.68664956092834</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3541,7 +3541,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>2.66663002967834</v>
+        <v>2.66662979125977</v>
       </c>
       <c r="H122" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3671,7 +3671,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H127" t="s">
         <v>8</v>
@@ -3697,7 +3697,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.78674864768982</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H128" t="s">
         <v>8</v>
@@ -3723,7 +3723,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78674864768982</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H129" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G132" t="n">
-        <v>2.61057448387146</v>
+        <v>2.61057472229004</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -4009,7 +4009,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H140" t="s">
         <v>8</v>
@@ -4035,7 +4035,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H141" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047563552856</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4269,7 +4269,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G150" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H150" t="s">
         <v>8</v>
@@ -4295,7 +4295,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G151" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H151" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.63459849357605</v>
+        <v>2.63459825515747</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4451,7 +4451,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>2.76272463798523</v>
+        <v>2.76272487640381</v>
       </c>
       <c r="H157" t="s">
         <v>8</v>
@@ -4581,7 +4581,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H162" t="s">
         <v>8</v>
@@ -4633,7 +4633,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G164" t="n">
-        <v>2.48244833946228</v>
+        <v>2.48244786262512</v>
       </c>
       <c r="H164" t="s">
         <v>8</v>
@@ -4659,7 +4659,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>2.48244833946228</v>
+        <v>2.48244786262512</v>
       </c>
       <c r="H165" t="s">
         <v>8</v>
@@ -4685,7 +4685,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>2.48244833946228</v>
+        <v>2.48244786262512</v>
       </c>
       <c r="H166" t="s">
         <v>8</v>
@@ -4737,7 +4737,7 @@
         <v>3</v>
       </c>
       <c r="G168" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H168" t="s">
         <v>8</v>
@@ -4763,7 +4763,7 @@
         <v>3</v>
       </c>
       <c r="G169" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H169" t="s">
         <v>8</v>
@@ -4789,7 +4789,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H170" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5049,7 +5049,7 @@
         <v>3</v>
       </c>
       <c r="G180" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H180" t="s">
         <v>8</v>
@@ -5075,7 +5075,7 @@
         <v>3</v>
       </c>
       <c r="G181" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H181" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5127,7 +5127,7 @@
         <v>3</v>
       </c>
       <c r="G183" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H183" t="s">
         <v>8</v>
@@ -5153,7 +5153,7 @@
         <v>3</v>
       </c>
       <c r="G184" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H184" t="s">
         <v>8</v>
@@ -5179,7 +5179,7 @@
         <v>3</v>
       </c>
       <c r="G185" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H185" t="s">
         <v>8</v>
@@ -5205,7 +5205,7 @@
         <v>3</v>
       </c>
       <c r="G186" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H186" t="s">
         <v>8</v>
@@ -5231,7 +5231,7 @@
         <v>3</v>
       </c>
       <c r="G187" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H187" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.05100917816162</v>
+        <v>3.05100893974304</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>2.83479571342468</v>
+        <v>2.8347954750061</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5621,7 +5621,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G202" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H202" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451941490173</v>
+        <v>2.55451965332031</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5777,7 +5777,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H208" t="s">
         <v>8</v>
@@ -5803,7 +5803,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.48244833946228</v>
+        <v>2.48244786262512</v>
       </c>
       <c r="H209" t="s">
         <v>8</v>
@@ -5829,7 +5829,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>2.48244833946228</v>
+        <v>2.48244786262512</v>
       </c>
       <c r="H210" t="s">
         <v>8</v>
@@ -5855,7 +5855,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>2.48244833946228</v>
+        <v>2.48244786262512</v>
       </c>
       <c r="H211" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047563552856</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -6063,7 +6063,7 @@
         <v>3</v>
       </c>
       <c r="G219" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H219" t="s">
         <v>8</v>
@@ -6245,7 +6245,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H226" t="s">
         <v>8</v>
@@ -6271,7 +6271,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H227" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>2.35031819343567</v>
+        <v>2.35031795501709</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6375,7 +6375,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H231" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G234" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6505,7 +6505,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H236" t="s">
         <v>8</v>
@@ -6531,7 +6531,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H237" t="s">
         <v>8</v>
@@ -6739,7 +6739,7 @@
         <v>3</v>
       </c>
       <c r="G245" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H245" t="s">
         <v>8</v>
@@ -6765,7 +6765,7 @@
         <v>3</v>
       </c>
       <c r="G246" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H246" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6999,7 +6999,7 @@
         <v>3</v>
       </c>
       <c r="G255" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H255" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7077,7 +7077,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H258" t="s">
         <v>8</v>
@@ -7103,7 +7103,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H259" t="s">
         <v>8</v>
@@ -7207,7 +7207,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225111961365</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H263" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.18615627288818</v>
+        <v>2.1861560344696</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7311,7 +7311,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820757865906</v>
+        <v>2.23820734024048</v>
       </c>
       <c r="H267" t="s">
         <v>8</v>
@@ -7337,7 +7337,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225111961365</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H268" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7415,7 +7415,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H271" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834596633911</v>
+        <v>2.37834572792053</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7701,7 +7701,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H282" t="s">
         <v>8</v>
@@ -7727,7 +7727,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H283" t="s">
         <v>8</v>
@@ -7753,7 +7753,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H284" t="s">
         <v>8</v>
@@ -7883,7 +7883,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225111961365</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H289" t="s">
         <v>8</v>
@@ -7909,7 +7909,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225111961365</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H290" t="s">
         <v>8</v>
@@ -7935,7 +7935,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225111961365</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H291" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8143,7 +8143,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225111961365</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H299" t="s">
         <v>8</v>
@@ -8169,7 +8169,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225111961365</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H300" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047563552856</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8429,7 +8429,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39035749435425</v>
+        <v>2.39035725593567</v>
       </c>
       <c r="H310" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045634269714</v>
+        <v>2.49045610427856</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41838526725769</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8689,7 +8689,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430218696594</v>
+        <v>2.33430194854736</v>
       </c>
       <c r="H320" t="s">
         <v>8</v>
@@ -8715,7 +8715,7 @@
         <v>3</v>
       </c>
       <c r="G321" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H321" t="s">
         <v>8</v>
@@ -8741,7 +8741,7 @@
         <v>3</v>
       </c>
       <c r="G322" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H322" t="s">
         <v>8</v>
@@ -8793,7 +8793,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39436149597168</v>
+        <v>2.3943612575531</v>
       </c>
       <c r="H324" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.41838526725769</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8949,7 +8949,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H330" t="s">
         <v>8</v>
@@ -9079,7 +9079,7 @@
         <v>3</v>
       </c>
       <c r="G335" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H335" t="s">
         <v>8</v>
@@ -9105,7 +9105,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39436149597168</v>
+        <v>2.3943612575531</v>
       </c>
       <c r="H336" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9287,7 +9287,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G343" t="n">
-        <v>2.39035749435425</v>
+        <v>2.39035725593567</v>
       </c>
       <c r="H343" t="s">
         <v>8</v>
@@ -9313,7 +9313,7 @@
         <v>3</v>
       </c>
       <c r="G344" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H344" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9391,7 +9391,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G347" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H347" t="s">
         <v>8</v>
@@ -9417,7 +9417,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H348" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9469,7 +9469,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H350" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451941490173</v>
+        <v>2.55451965332031</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049564361572</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9651,7 +9651,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>2.66663002967834</v>
+        <v>2.66662979125977</v>
       </c>
       <c r="H357" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9911,7 +9911,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H367" t="s">
         <v>8</v>
@@ -9963,7 +9963,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G369" t="n">
-        <v>3.23519062995911</v>
+        <v>3.23519039154053</v>
       </c>
       <c r="H369" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315885543823</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10119,7 +10119,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H375" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10223,7 +10223,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H379" t="s">
         <v>8</v>
@@ -10249,7 +10249,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H380" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G382" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G383" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G389" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G390" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10743,7 +10743,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H399" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G400" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10873,7 +10873,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H404" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>3.42738032341003</v>
+        <v>3.42738056182861</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G408" t="n">
-        <v>3.34730100631714</v>
+        <v>3.34730124473572</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11003,7 +11003,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H409" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315885543823</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11081,7 +11081,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H412" t="s">
         <v>8</v>
@@ -11107,7 +11107,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H413" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315885543823</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4</v>
       </c>
       <c r="G424" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315885543823</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G427" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11653,7 +11653,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H434" t="s">
         <v>8</v>
@@ -11679,7 +11679,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G435" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H435" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11731,7 +11731,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H437" t="s">
         <v>8</v>
@@ -11861,7 +11861,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H442" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12121,7 +12121,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H452" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G454" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G459" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12485,7 +12485,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H466" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G476" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G478" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12927,7 +12927,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.91487455368042</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H483" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292185783386</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G489" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13187,7 +13187,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G493" t="n">
-        <v>2.91487455368042</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H493" t="s">
         <v>8</v>
@@ -13213,7 +13213,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H494" t="s">
         <v>8</v>
@@ -13239,7 +13239,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G495" t="n">
-        <v>2.91487455368042</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H495" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G496" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13317,7 +13317,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G498" t="n">
-        <v>2.91487455368042</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H498" t="s">
         <v>8</v>
@@ -13343,7 +13343,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G499" t="n">
-        <v>2.91487455368042</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H499" t="s">
         <v>8</v>
@@ -13369,7 +13369,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H500" t="s">
         <v>8</v>
@@ -13395,7 +13395,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H501" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13499,7 +13499,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G505" t="n">
-        <v>2.91487455368042</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H505" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13551,7 +13551,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H507" t="s">
         <v>8</v>
@@ -13577,7 +13577,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H508" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13733,7 +13733,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H514" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.83479571342468</v>
+        <v>2.8347954750061</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G529" t="n">
-        <v>2.41838526725769</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14305,7 +14305,7 @@
         <v>3</v>
       </c>
       <c r="G536" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H536" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14409,7 +14409,7 @@
         <v>3</v>
       </c>
       <c r="G540" t="n">
-        <v>2.40236926078796</v>
+        <v>2.40236902236938</v>
       </c>
       <c r="H540" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14617,7 +14617,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H548" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14773,7 +14773,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H554" t="s">
         <v>8</v>
@@ -14799,7 +14799,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H555" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -14929,7 +14929,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H560" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G562" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>2.41838526725769</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15137,7 +15137,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H568" t="s">
         <v>8</v>
@@ -15163,7 +15163,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H569" t="s">
         <v>8</v>
@@ -15189,7 +15189,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H570" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15501,7 +15501,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H582" t="s">
         <v>8</v>
@@ -15527,7 +15527,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G583" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H583" t="s">
         <v>8</v>
@@ -15553,7 +15553,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H584" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400588035583</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G589" t="n">
-        <v>2.13010096549988</v>
+        <v>2.1301007270813</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400588035583</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98595857620239</v>
+        <v>1.98595881462097</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G598" t="n">
-        <v>1.77775323390961</v>
+        <v>1.77775311470032</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2</v>
       </c>
       <c r="G600" t="n">
-        <v>1.60157954692841</v>
+        <v>1.60157942771912</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G602" t="n">
-        <v>1.53751623630524</v>
+        <v>1.53751635551453</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2</v>
       </c>
       <c r="G603" t="n">
-        <v>1.60157954692841</v>
+        <v>1.60157942771912</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>1.69767427444458</v>
+        <v>1.697674036026</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>1.69767427444458</v>
+        <v>1.697674036026</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16203,7 +16203,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61759531497955</v>
+        <v>1.61759519577026</v>
       </c>
       <c r="H609" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>1.69767427444458</v>
+        <v>1.697674036026</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.69767427444458</v>
+        <v>1.697674036026</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G616" t="n">
-        <v>1.77775323390961</v>
+        <v>1.77775311470032</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.9539270401001</v>
+        <v>1.95392692089081</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.72169804573059</v>
+        <v>1.72169816493988</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970581054688</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970581054688</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.72169804573059</v>
+        <v>1.72169816493988</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.83380842208862</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81743538379669</v>
+        <v>1.8174352645874</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.25</v>
       </c>
       <c r="G646" t="n">
-        <v>1.8419953584671</v>
+        <v>1.84199523925781</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G647" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.850182056427</v>
+        <v>1.85018193721771</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17399,7 +17399,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H655" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G664" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17711,7 +17711,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H667" t="s">
         <v>8</v>
@@ -17737,7 +17737,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H668" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17893,7 +17893,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H674" t="s">
         <v>8</v>
@@ -17945,7 +17945,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G676" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H676" t="s">
         <v>8</v>
@@ -17971,7 +17971,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G677" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H677" t="s">
         <v>8</v>
@@ -17997,7 +17997,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H678" t="s">
         <v>8</v>
@@ -18023,7 +18023,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G679" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H679" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18101,7 +18101,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H682" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18309,7 +18309,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H690" t="s">
         <v>8</v>
@@ -18335,7 +18335,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H691" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18439,7 +18439,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H695" t="s">
         <v>8</v>
@@ -18491,7 +18491,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G697" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H697" t="s">
         <v>8</v>
@@ -18517,7 +18517,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H698" t="s">
         <v>8</v>
@@ -18621,7 +18621,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H702" t="s">
         <v>8</v>
@@ -18647,7 +18647,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H703" t="s">
         <v>8</v>
@@ -18673,7 +18673,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H704" t="s">
         <v>8</v>
@@ -18699,7 +18699,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H705" t="s">
         <v>8</v>
@@ -18725,7 +18725,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H706" t="s">
         <v>8</v>
@@ -18751,7 +18751,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H707" t="s">
         <v>8</v>
@@ -18777,7 +18777,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H708" t="s">
         <v>8</v>
@@ -18803,7 +18803,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H709" t="s">
         <v>8</v>
@@ -18829,7 +18829,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H710" t="s">
         <v>8</v>
@@ -18855,7 +18855,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H711" t="s">
         <v>8</v>
@@ -18881,7 +18881,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H712" t="s">
         <v>8</v>
@@ -18907,7 +18907,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H713" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18959,7 +18959,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H715" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19011,7 +19011,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H717" t="s">
         <v>8</v>
@@ -19037,7 +19037,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H718" t="s">
         <v>8</v>
@@ -19063,7 +19063,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H719" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G722" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G723" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19219,7 +19219,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H725" t="s">
         <v>8</v>
@@ -19245,7 +19245,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H726" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G732" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G733" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19583,7 +19583,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G739" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H739" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19765,7 +19765,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H746" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G747" t="n">
-        <v>1.51452946662903</v>
+        <v>1.51452934741974</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19817,7 +19817,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G748" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H748" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20051,7 +20051,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H757" t="s">
         <v>8</v>
@@ -20155,7 +20155,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H761" t="s">
         <v>8</v>
@@ -20181,7 +20181,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H762" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G771" t="n">
-        <v>1.51452946662903</v>
+        <v>1.51452934741974</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20493,7 +20493,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G774" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H774" t="s">
         <v>8</v>
@@ -20519,7 +20519,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H775" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20675,7 +20675,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H781" t="s">
         <v>8</v>
@@ -20753,7 +20753,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H784" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G789" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -20987,7 +20987,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.8092485666275</v>
+        <v>1.80924880504608</v>
       </c>
       <c r="H793" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21169,7 +21169,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G800" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H800" t="s">
         <v>8</v>
@@ -21195,7 +21195,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H801" t="s">
         <v>8</v>
@@ -21247,7 +21247,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H803" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G811" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21481,7 +21481,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G812" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H812" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G818" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034106254578</v>
+        <v>2.12034130096436</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22391,7 +22391,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H847" t="s">
         <v>8</v>
@@ -22417,7 +22417,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H848" t="s">
         <v>8</v>
@@ -22547,7 +22547,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.10396814346313</v>
+        <v>2.10396790504456</v>
       </c>
       <c r="H853" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22755,7 +22755,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>2.01391458511353</v>
+        <v>2.0139148235321</v>
       </c>
       <c r="H861" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479475498199</v>
+        <v>1.96479499340057</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G872" t="n">
-        <v>1.91567516326904</v>
+        <v>1.91567492485046</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23145,7 +23145,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H876" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037759780884</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G981" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037759780884</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>1.6225084066391</v>
+        <v>1.62250828742981</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362532615662</v>
+        <v>1.32362520694733</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.38340198993683</v>
+        <v>1.38340187072754</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.75</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.49441576004028</v>
+        <v>1.49441564083099</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.44317853450775</v>
+        <v>1.44317865371704</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.38340198993683</v>
+        <v>1.38340187072754</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.6225084066391</v>
+        <v>1.62250828742981</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -46132,6 +46132,32 @@
         <v>3.04999995231628</v>
       </c>
       <c r="H1760" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1761">
+      <c r="A1761" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1761" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C1761" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="D1761" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="E1761" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="F1761" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G1761" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="H1761" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -40937,8 +40937,31 @@
       <c r="E1764" t="n">
         <v>2.92000007629395</v>
       </c>
-      <c r="F1764"/>
+      <c r="F1764" t="n">
+        <v>2.88000011444092</v>
+      </c>
       <c r="G1764" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1765">
+      <c r="A1765" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1765" t="n">
+        <v>21000</v>
+      </c>
+      <c r="C1765" t="n">
+        <v>3.10999989509583</v>
+      </c>
+      <c r="D1765" t="n">
+        <v>2.84999990463257</v>
+      </c>
+      <c r="E1765" t="n">
+        <v>2.85999989509583</v>
+      </c>
+      <c r="F1765"/>
+      <c r="G1765" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -40960,8 +40960,31 @@
       <c r="E1765" t="n">
         <v>2.85999989509583</v>
       </c>
-      <c r="F1765"/>
+      <c r="F1765" t="n">
+        <v>3.10999989509583</v>
+      </c>
       <c r="G1765" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1766">
+      <c r="A1766" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1766" t="n">
+        <v>17250</v>
+      </c>
+      <c r="C1766" t="n">
+        <v>3.15000009536743</v>
+      </c>
+      <c r="D1766" t="n">
+        <v>2.94000005722046</v>
+      </c>
+      <c r="E1766" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="F1766"/>
+      <c r="G1766" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -40983,8 +40983,31 @@
       <c r="E1766" t="n">
         <v>3.11999988555908</v>
       </c>
-      <c r="F1766"/>
+      <c r="F1766" t="n">
+        <v>2.96000003814697</v>
+      </c>
       <c r="G1766" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1767">
+      <c r="A1767" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1767" t="n">
+        <v>16500</v>
+      </c>
+      <c r="C1767" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="D1767" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="E1767" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="F1767"/>
+      <c r="G1767" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -41006,7 +41006,9 @@
       <c r="E1767" t="n">
         <v>2.99000000953674</v>
       </c>
-      <c r="F1767"/>
+      <c r="F1767" t="n">
+        <v>3.09999990463257</v>
+      </c>
       <c r="G1767" t="s">
         <v>7</v>
       </c>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -41036,6 +41036,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1769">
+      <c r="A1769" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1769" t="n">
+        <v>2250</v>
+      </c>
+      <c r="C1769" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D1769" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E1769" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1769" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="G1769" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -421,7 +421,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189425468445</v>
+        <v>2.73189449310303</v>
       </c>
       <c r="H2" t="s">
         <v>8</v>
@@ -473,7 +473,7 @@
         <v>3.50550007820129</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80716896057129</v>
+        <v>2.80716872215271</v>
       </c>
       <c r="H4" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75111317634583</v>
+        <v>2.7511134147644</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -759,7 +759,7 @@
         <v>3.37150001525879</v>
       </c>
       <c r="G15" t="n">
-        <v>2.69986295700073</v>
+        <v>2.69986271858215</v>
       </c>
       <c r="H15" t="s">
         <v>8</v>
@@ -863,7 +863,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.96390914916992</v>
+        <v>3.9639093875885</v>
       </c>
       <c r="H19" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>3.43538784980774</v>
+        <v>3.43538808822632</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -1019,7 +1019,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.49144315719604</v>
+        <v>3.4914436340332</v>
       </c>
       <c r="H25" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.38350009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>3.51026225090027</v>
+        <v>3.51026248931885</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1097,7 +1097,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329724311829</v>
+        <v>3.34329748153687</v>
       </c>
       <c r="H28" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128547668457</v>
+        <v>3.33128523826599</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048439025879</v>
+        <v>3.33048462867737</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1253,7 +1253,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.04700517654419</v>
+        <v>3.04700493812561</v>
       </c>
       <c r="H34" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03098917007446</v>
+        <v>3.03098940849304</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1357,7 +1357,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H38" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1539,7 +1539,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H45" t="s">
         <v>8</v>
@@ -1565,7 +1565,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H46" t="s">
         <v>8</v>
@@ -1617,7 +1617,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9909496307373</v>
+        <v>2.99094986915588</v>
       </c>
       <c r="H48" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08304071426392</v>
+        <v>3.08304047584534</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H53" t="s">
         <v>8</v>
@@ -1773,7 +1773,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.07903671264648</v>
+        <v>3.07903695106506</v>
       </c>
       <c r="H54" t="s">
         <v>8</v>
@@ -1799,7 +1799,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H55" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702470779419</v>
+        <v>3.06702494621277</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -1981,7 +1981,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505271911621</v>
+        <v>3.09505248069763</v>
       </c>
       <c r="H62" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G63" t="n">
-        <v>3.03098917007446</v>
+        <v>3.03098940849304</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2033,7 +2033,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H64" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2163,7 +2163,7 @@
         <v>3.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H69" t="s">
         <v>8</v>
@@ -2189,7 +2189,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>2.8347954750061</v>
+        <v>2.83479571342468</v>
       </c>
       <c r="H70" t="s">
         <v>8</v>
@@ -2215,7 +2215,7 @@
         <v>3.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H71" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670886993408</v>
+        <v>2.74670910835266</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2267,7 +2267,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H73" t="s">
         <v>8</v>
@@ -2319,7 +2319,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>2.83879995346069</v>
+        <v>2.83879971504211</v>
       </c>
       <c r="H75" t="s">
         <v>8</v>
@@ -2371,7 +2371,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>3.07903671264648</v>
+        <v>3.07903695106506</v>
       </c>
       <c r="H77" t="s">
         <v>8</v>
@@ -2397,7 +2397,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G78" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H78" t="s">
         <v>8</v>
@@ -2423,7 +2423,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H79" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866180419922</v>
+        <v>2.69866132736206</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2631,7 +2631,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.5905544757843</v>
+        <v>2.59055495262146</v>
       </c>
       <c r="H87" t="s">
         <v>8</v>
@@ -2657,7 +2657,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H88" t="s">
         <v>8</v>
@@ -2683,7 +2683,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.53049564361572</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H89" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185584545135</v>
+        <v>1.88185572624207</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556389808655</v>
+        <v>1.58556377887726</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -3021,7 +3021,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.677654504776</v>
+        <v>1.67765462398529</v>
       </c>
       <c r="H102" t="s">
         <v>8</v>
@@ -3047,7 +3047,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771381378174</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H103" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75773334503174</v>
+        <v>1.75773358345032</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3099,7 +3099,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H105" t="s">
         <v>8</v>
@@ -3151,7 +3151,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771381378174</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H107" t="s">
         <v>8</v>
@@ -3177,7 +3177,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8978716135025</v>
+        <v>1.89787173271179</v>
       </c>
       <c r="H108" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205342292786</v>
+        <v>2.08205318450928</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3229,7 +3229,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.53049564361572</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H110" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3307,7 +3307,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H113" t="s">
         <v>8</v>
@@ -3333,7 +3333,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H114" t="s">
         <v>8</v>
@@ -3359,7 +3359,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H115" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3437,7 +3437,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H118" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664956092834</v>
+        <v>2.68664979934692</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3567,7 +3567,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>2.75071287155151</v>
+        <v>2.75071263313293</v>
       </c>
       <c r="H123" t="s">
         <v>8</v>
@@ -3593,7 +3593,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H124" t="s">
         <v>8</v>
@@ -3619,7 +3619,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H125" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G132" t="n">
-        <v>2.61057472229004</v>
+        <v>2.61057448387146</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3931,7 +3931,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H137" t="s">
         <v>8</v>
@@ -3957,7 +3957,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H138" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.44240880012512</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047563552856</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4139,7 +4139,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H145" t="s">
         <v>8</v>
@@ -4165,7 +4165,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71868133544922</v>
+        <v>2.71868109703064</v>
       </c>
       <c r="H146" t="s">
         <v>8</v>
@@ -4191,7 +4191,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H147" t="s">
         <v>8</v>
@@ -4373,7 +4373,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.63459849357605</v>
+        <v>2.63459825515747</v>
       </c>
       <c r="H154" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4477,7 +4477,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H158" t="s">
         <v>8</v>
@@ -4503,7 +4503,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H159" t="s">
         <v>8</v>
@@ -4529,7 +4529,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H160" t="s">
         <v>8</v>
@@ -4555,7 +4555,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H161" t="s">
         <v>8</v>
@@ -4711,7 +4711,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45842480659485</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H167" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4841,7 +4841,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H172" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G179" t="n">
-        <v>2.44240880012512</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5101,7 +5101,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H182" t="s">
         <v>8</v>
@@ -5257,7 +5257,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H188" t="s">
         <v>8</v>
@@ -5465,7 +5465,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G196" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H196" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.05100893974304</v>
+        <v>3.05100917816162</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5543,7 +5543,7 @@
         <v>3.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H199" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5595,7 +5595,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>2.8347954750061</v>
+        <v>2.83479571342468</v>
       </c>
       <c r="H201" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5699,7 +5699,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451965332031</v>
+        <v>2.55451941490173</v>
       </c>
       <c r="H205" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047563552856</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.44240880012512</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>2.44240880012512</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6167,7 +6167,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H223" t="s">
         <v>8</v>
@@ -6297,7 +6297,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H228" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G234" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6713,7 +6713,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G244" t="n">
-        <v>2.45842480659485</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H244" t="s">
         <v>8</v>
@@ -6791,7 +6791,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H247" t="s">
         <v>8</v>
@@ -6947,7 +6947,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H253" t="s">
         <v>8</v>
@@ -6973,7 +6973,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H254" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7181,7 +7181,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H262" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7493,7 +7493,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834572792053</v>
+        <v>2.37834548950195</v>
       </c>
       <c r="H274" t="s">
         <v>8</v>
@@ -7519,7 +7519,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H275" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7779,7 +7779,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H285" t="s">
         <v>8</v>
@@ -7805,7 +7805,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H286" t="s">
         <v>8</v>
@@ -7831,7 +7831,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H287" t="s">
         <v>8</v>
@@ -7857,7 +7857,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H288" t="s">
         <v>8</v>
@@ -7961,7 +7961,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.28625464439392</v>
+        <v>2.2862548828125</v>
       </c>
       <c r="H292" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8065,7 +8065,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H296" t="s">
         <v>8</v>
@@ -8221,7 +8221,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H302" t="s">
         <v>8</v>
@@ -8247,7 +8247,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H303" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471663475037</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8325,7 +8325,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>2.60657072067261</v>
+        <v>2.60657095909119</v>
       </c>
       <c r="H306" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047563552856</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039679527283</v>
+        <v>2.43039703369141</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.44240880012512</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045634269714</v>
+        <v>2.49045610427856</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8507,7 +8507,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H313" t="s">
         <v>8</v>
@@ -8611,7 +8611,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H317" t="s">
         <v>8</v>
@@ -8637,7 +8637,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H318" t="s">
         <v>8</v>
@@ -8845,7 +8845,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H326" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G328" t="n">
-        <v>2.44240880012512</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -8975,7 +8975,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G331" t="n">
-        <v>2.45842480659485</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H331" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.44240880012512</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9053,7 +9053,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H334" t="s">
         <v>8</v>
@@ -9131,7 +9131,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.43840503692627</v>
+        <v>2.43840479850769</v>
       </c>
       <c r="H337" t="s">
         <v>8</v>
@@ -9183,7 +9183,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H339" t="s">
         <v>8</v>
@@ -9235,7 +9235,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H341" t="s">
         <v>8</v>
@@ -9339,7 +9339,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>2.5505154132843</v>
+        <v>2.55051517486572</v>
       </c>
       <c r="H345" t="s">
         <v>8</v>
@@ -9365,7 +9365,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H346" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>2.62659025192261</v>
+        <v>2.62659049034119</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9521,7 +9521,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451965332031</v>
+        <v>2.55451941490173</v>
       </c>
       <c r="H352" t="s">
         <v>8</v>
@@ -9547,7 +9547,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.53049564361572</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H353" t="s">
         <v>8</v>
@@ -9625,7 +9625,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H356" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266556739807</v>
+        <v>2.70266580581665</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9729,7 +9729,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H360" t="s">
         <v>8</v>
@@ -9755,7 +9755,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.77473664283752</v>
+        <v>2.77473640441895</v>
       </c>
       <c r="H361" t="s">
         <v>8</v>
@@ -9781,7 +9781,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H362" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9885,7 +9885,7 @@
         <v>3.5</v>
       </c>
       <c r="G366" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H366" t="s">
         <v>8</v>
@@ -9937,7 +9937,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H368" t="s">
         <v>8</v>
@@ -10015,7 +10015,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G371" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H371" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10145,7 +10145,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H376" t="s">
         <v>8</v>
@@ -10197,7 +10197,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H378" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G382" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G383" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10353,7 +10353,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H384" t="s">
         <v>8</v>
@@ -10379,7 +10379,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H385" t="s">
         <v>8</v>
@@ -10431,7 +10431,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H387" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G389" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G390" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.1711277961731</v>
+        <v>3.17112755775452</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10613,7 +10613,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H394" t="s">
         <v>8</v>
@@ -10639,7 +10639,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H395" t="s">
         <v>8</v>
@@ -10665,7 +10665,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H396" t="s">
         <v>8</v>
@@ -10691,7 +10691,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H397" t="s">
         <v>8</v>
@@ -10717,7 +10717,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H398" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G400" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10795,7 +10795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H401" t="s">
         <v>8</v>
@@ -10821,7 +10821,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G402" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H402" t="s">
         <v>8</v>
@@ -10847,7 +10847,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H403" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -10977,7 +10977,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G408" t="n">
-        <v>3.34730100631714</v>
+        <v>3.34730124473572</v>
       </c>
       <c r="H408" t="s">
         <v>8</v>
@@ -11159,7 +11159,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H415" t="s">
         <v>8</v>
@@ -11237,7 +11237,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H418" t="s">
         <v>8</v>
@@ -11263,7 +11263,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G419" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H419" t="s">
         <v>8</v>
@@ -11367,7 +11367,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G423" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H423" t="s">
         <v>8</v>
@@ -11497,7 +11497,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G428" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H428" t="s">
         <v>8</v>
@@ -11523,7 +11523,7 @@
         <v>3.85999989509583</v>
       </c>
       <c r="G429" t="n">
-        <v>3.09104871749878</v>
+        <v>3.0910484790802</v>
       </c>
       <c r="H429" t="s">
         <v>8</v>
@@ -11549,7 +11549,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H430" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11601,7 +11601,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H432" t="s">
         <v>8</v>
@@ -11627,7 +11627,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H433" t="s">
         <v>8</v>
@@ -11705,7 +11705,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H436" t="s">
         <v>8</v>
@@ -11757,7 +11757,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H438" t="s">
         <v>8</v>
@@ -11783,7 +11783,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H439" t="s">
         <v>8</v>
@@ -11809,7 +11809,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G440" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H440" t="s">
         <v>8</v>
@@ -11835,7 +11835,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H441" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12069,7 +12069,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H450" t="s">
         <v>8</v>
@@ -12095,7 +12095,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G451" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H451" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G454" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G459" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12329,7 +12329,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G460" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H460" t="s">
         <v>8</v>
@@ -12355,7 +12355,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H461" t="s">
         <v>8</v>
@@ -12381,7 +12381,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H462" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G476" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G478" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12849,7 +12849,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G480" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H480" t="s">
         <v>8</v>
@@ -12875,7 +12875,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G481" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H481" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12953,7 +12953,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H484" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292185783386</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13031,7 +13031,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G487" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H487" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G489" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13161,7 +13161,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H492" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>2.88284277915955</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13785,7 +13785,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.8347954750061</v>
+        <v>2.83479571342468</v>
       </c>
       <c r="H516" t="s">
         <v>8</v>
@@ -13811,7 +13811,7 @@
         <v>3.5</v>
       </c>
       <c r="G517" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H517" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471663475037</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471663475037</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471663475037</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471663475037</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -13941,7 +13941,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H522" t="s">
         <v>8</v>
@@ -13967,7 +13967,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H523" t="s">
         <v>8</v>
@@ -13993,7 +13993,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H524" t="s">
         <v>8</v>
@@ -14019,7 +14019,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H525" t="s">
         <v>8</v>
@@ -14045,7 +14045,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H526" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846386909485</v>
+        <v>2.49846410751343</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14123,7 +14123,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G529" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H529" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14227,7 +14227,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H533" t="s">
         <v>8</v>
@@ -14279,7 +14279,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H535" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14461,7 +14461,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H542" t="s">
         <v>8</v>
@@ -14487,7 +14487,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H543" t="s">
         <v>8</v>
@@ -14565,7 +14565,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H546" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14669,7 +14669,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H550" t="s">
         <v>8</v>
@@ -14747,7 +14747,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H553" t="s">
         <v>8</v>
@@ -14955,7 +14955,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H561" t="s">
         <v>8</v>
@@ -14981,7 +14981,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G562" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H562" t="s">
         <v>8</v>
@@ -15033,7 +15033,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H564" t="s">
         <v>8</v>
@@ -15111,7 +15111,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H567" t="s">
         <v>8</v>
@@ -15215,7 +15215,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H571" t="s">
         <v>8</v>
@@ -15241,7 +15241,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H572" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15345,7 +15345,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H576" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.17814826965332</v>
+        <v>2.17814803123474</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15683,7 +15683,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G589" t="n">
-        <v>2.1301007270813</v>
+        <v>2.13010096549988</v>
       </c>
       <c r="H589" t="s">
         <v>8</v>
@@ -15735,7 +15735,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.05002164840698</v>
+        <v>2.05002188682556</v>
       </c>
       <c r="H591" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98595881462097</v>
+        <v>1.98595857620239</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986372947693</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587997436523</v>
+        <v>1.90587973594666</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G598" t="n">
-        <v>1.77775311470032</v>
+        <v>1.7777533531189</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15995,7 +15995,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G601" t="n">
-        <v>1.49747681617737</v>
+        <v>1.49747693538666</v>
       </c>
       <c r="H601" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G602" t="n">
-        <v>1.53751635551453</v>
+        <v>1.53751623630524</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16073,7 +16073,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.6336110830307</v>
+        <v>1.63361120223999</v>
       </c>
       <c r="H604" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16125,7 +16125,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H606" t="s">
         <v>8</v>
@@ -16151,7 +16151,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H607" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16281,7 +16281,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.74572157859802</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H612" t="s">
         <v>8</v>
@@ -16307,7 +16307,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H613" t="s">
         <v>8</v>
@@ -16333,7 +16333,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H614" t="s">
         <v>8</v>
@@ -16359,7 +16359,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H615" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G616" t="n">
-        <v>1.77775311470032</v>
+        <v>1.7777533531189</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16411,7 +16411,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H617" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376888275146</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587997436523</v>
+        <v>1.90587973594666</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986372947693</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.9539270401001</v>
+        <v>1.95392715930939</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16619,7 +16619,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H625" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970604896545</v>
+        <v>1.72970592975616</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970604896545</v>
+        <v>1.72970592975616</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376888275146</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16749,7 +16749,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H630" t="s">
         <v>8</v>
@@ -16801,7 +16801,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.74572157859802</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H632" t="s">
         <v>8</v>
@@ -16827,7 +16827,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.74572157859802</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H633" t="s">
         <v>8</v>
@@ -16853,7 +16853,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.74572157859802</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H634" t="s">
         <v>8</v>
@@ -16879,7 +16879,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.74572157859802</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H635" t="s">
         <v>8</v>
@@ -16931,7 +16931,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771381378174</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H637" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -16983,7 +16983,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H639" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.83380842208862</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81743514537811</v>
+        <v>1.81743538379669</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17165,7 +17165,7 @@
         <v>2.25</v>
       </c>
       <c r="G646" t="n">
-        <v>1.8419953584671</v>
+        <v>1.84199523925781</v>
       </c>
       <c r="H646" t="s">
         <v>8</v>
@@ -17269,7 +17269,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H650" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474191188812</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17373,7 +17373,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78468871116638</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H654" t="s">
         <v>8</v>
@@ -17425,7 +17425,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H656" t="s">
         <v>8</v>
@@ -17451,7 +17451,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H657" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474191188812</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.83380842208862</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.83380842208862</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17763,7 +17763,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G669" t="n">
-        <v>1.78468871116638</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H669" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G696" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18543,7 +18543,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H699" t="s">
         <v>8</v>
@@ -18569,7 +18569,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G700" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H700" t="s">
         <v>8</v>
@@ -18595,7 +18595,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G701" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H701" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.76831555366516</v>
+        <v>1.76831543445587</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G722" t="n">
-        <v>1.76831555366516</v>
+        <v>1.76831543445587</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G723" t="n">
-        <v>1.76831555366516</v>
+        <v>1.76831543445587</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19557,7 +19557,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G738" t="n">
-        <v>1.54318261146545</v>
+        <v>1.54318273067474</v>
       </c>
       <c r="H738" t="s">
         <v>8</v>
@@ -19609,7 +19609,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G740" t="n">
-        <v>1.58002269268036</v>
+        <v>1.58002257347107</v>
       </c>
       <c r="H740" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.57183599472046</v>
+        <v>1.57183587551117</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G747" t="n">
-        <v>1.51452934741974</v>
+        <v>1.51452946662903</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19947,7 +19947,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H753" t="s">
         <v>8</v>
@@ -19973,7 +19973,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H754" t="s">
         <v>8</v>
@@ -20077,7 +20077,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G758" t="n">
-        <v>1.58002269268036</v>
+        <v>1.58002257347107</v>
       </c>
       <c r="H758" t="s">
         <v>8</v>
@@ -20103,7 +20103,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.58002269268036</v>
+        <v>1.58002257347107</v>
       </c>
       <c r="H759" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G771" t="n">
-        <v>1.51452934741974</v>
+        <v>1.51452946662903</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57183599472046</v>
+        <v>1.57183587551117</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.57183599472046</v>
+        <v>1.57183587551117</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20857,7 +20857,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H788" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G789" t="n">
-        <v>1.76831555366516</v>
+        <v>1.76831543445587</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21013,7 +21013,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G794" t="n">
-        <v>1.78468871116638</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H794" t="s">
         <v>8</v>
@@ -21039,7 +21039,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G795" t="n">
-        <v>1.78468871116638</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H795" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>1.76831555366516</v>
+        <v>1.76831543445587</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21273,7 +21273,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H804" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21351,7 +21351,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G807" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H807" t="s">
         <v>8</v>
@@ -21377,7 +21377,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H808" t="s">
         <v>8</v>
@@ -21403,7 +21403,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H809" t="s">
         <v>8</v>
@@ -21429,7 +21429,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G810" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H810" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G811" t="n">
-        <v>1.76831555366516</v>
+        <v>1.76831543445587</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21507,7 +21507,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H813" t="s">
         <v>8</v>
@@ -21533,7 +21533,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H814" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842207431793</v>
+        <v>1.94842171669006</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G818" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.9975414276123</v>
+        <v>1.99754166603088</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116850852966</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>2.03028845787048</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>2.03028845787048</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>2.08759427070618</v>
+        <v>2.08759474754333</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116850852966</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204832077026</v>
+        <v>1.93204820156097</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479499340057</v>
+        <v>1.96479511260986</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930152893066</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930152893066</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.83380842208862</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23041,7 +23041,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G872" t="n">
-        <v>1.91567516326904</v>
+        <v>1.91567492485046</v>
       </c>
       <c r="H872" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>2.03028845787048</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G879" t="n">
-        <v>2.03028845787048</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>2.03028845787048</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>2.03028845787048</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116850852966</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G901" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G904" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993092536926</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993092536926</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24081,7 +24081,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H912" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G918" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G919" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G935" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G940" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G949" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993092536926</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25147,7 +25147,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H953" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G954" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G956" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G958" t="n">
-        <v>1.94701015949249</v>
+        <v>1.9470100402832</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2</v>
       </c>
       <c r="G961" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.8445360660553</v>
+        <v>1.84453594684601</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G984" t="n">
-        <v>1.74206161499023</v>
+        <v>1.74206173419952</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2</v>
       </c>
       <c r="G986" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G991" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27279,7 +27279,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362532615662</v>
+        <v>1.32362520694733</v>
       </c>
       <c r="H1035" t="s">
         <v>8</v>
@@ -27357,7 +27357,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1038" t="s">
         <v>8</v>
@@ -27383,7 +27383,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1039" t="s">
         <v>8</v>
@@ -27409,7 +27409,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1040" t="s">
         <v>8</v>
@@ -27435,7 +27435,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1041" t="s">
         <v>8</v>
@@ -27461,7 +27461,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1042" t="s">
         <v>8</v>
@@ -27487,7 +27487,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1043" t="s">
         <v>8</v>
@@ -27513,7 +27513,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1044" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.3321647644043</v>
+        <v>1.33216488361359</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.3321647644043</v>
+        <v>1.33216488361359</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27669,7 +27669,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1050" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27851,7 +27851,7 @@
         <v>1.75</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.49441576004028</v>
+        <v>1.49441564083099</v>
       </c>
       <c r="H1057" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29229,7 +29229,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1110" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.74206161499023</v>
+        <v>1.74206173419952</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>2</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>2</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>2</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.59688985347748</v>
+        <v>1.59688997268677</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.59688985347748</v>
+        <v>1.59688997268677</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30191,7 +30191,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1147" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.06746220588684</v>
+        <v>2.06746244430542</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.99555051326752</v>
+        <v>1.99555063247681</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -46418,6 +46418,32 @@
         <v>3.0699999332428</v>
       </c>
       <c r="H1771" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1772">
+      <c r="A1772" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1772" t="n">
+        <v>750</v>
+      </c>
+      <c r="C1772" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D1772" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1772" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="F1772" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G1772" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="H1772" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -447,7 +447,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722755432129</v>
+        <v>2.86722779273987</v>
       </c>
       <c r="H3" t="s">
         <v>8</v>
@@ -525,7 +525,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.70586848258972</v>
+        <v>2.7058687210083</v>
       </c>
       <c r="H6" t="s">
         <v>8</v>
@@ -551,7 +551,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64260625839233</v>
+        <v>2.64260601997375</v>
       </c>
       <c r="H7" t="s">
         <v>8</v>
@@ -603,7 +603,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7511134147644</v>
+        <v>2.75111317634583</v>
       </c>
       <c r="H9" t="s">
         <v>8</v>
@@ -629,7 +629,7 @@
         <v>3.43650007247925</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75191426277161</v>
+        <v>2.75191402435303</v>
       </c>
       <c r="H10" t="s">
         <v>8</v>
@@ -785,7 +785,7 @@
         <v>3.43449997901917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7503125667572</v>
+        <v>2.75031232833862</v>
       </c>
       <c r="H16" t="s">
         <v>8</v>
@@ -811,7 +811,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.32327771186829</v>
+        <v>3.32327747344971</v>
       </c>
       <c r="H17" t="s">
         <v>8</v>
@@ -837,7 +837,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558578491211</v>
+        <v>3.63558554649353</v>
       </c>
       <c r="H18" t="s">
         <v>8</v>
@@ -941,7 +941,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>3.43538808822632</v>
+        <v>3.43538784980774</v>
       </c>
       <c r="H22" t="s">
         <v>8</v>
@@ -967,7 +967,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51226425170898</v>
+        <v>3.51226401329041</v>
       </c>
       <c r="H23" t="s">
         <v>8</v>
@@ -1045,7 +1045,7 @@
         <v>4.38350009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>3.51026248931885</v>
+        <v>3.51026201248169</v>
       </c>
       <c r="H26" t="s">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128523826599</v>
+        <v>3.33128547668457</v>
       </c>
       <c r="H30" t="s">
         <v>8</v>
@@ -1175,7 +1175,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048462867737</v>
+        <v>3.33048439025879</v>
       </c>
       <c r="H31" t="s">
         <v>8</v>
@@ -1279,7 +1279,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03098940849304</v>
+        <v>3.03098917007446</v>
       </c>
       <c r="H35" t="s">
         <v>8</v>
@@ -1305,7 +1305,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.9709300994873</v>
+        <v>2.97092986106873</v>
       </c>
       <c r="H36" t="s">
         <v>8</v>
@@ -1331,7 +1331,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H37" t="s">
         <v>8</v>
@@ -1383,7 +1383,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H39" t="s">
         <v>8</v>
@@ -1669,7 +1669,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H50" t="s">
         <v>8</v>
@@ -1695,7 +1695,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H51" t="s">
         <v>8</v>
@@ -1721,7 +1721,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08304047584534</v>
+        <v>3.08304071426392</v>
       </c>
       <c r="H52" t="s">
         <v>8</v>
@@ -1851,7 +1851,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702494621277</v>
+        <v>3.06702470779419</v>
       </c>
       <c r="H57" t="s">
         <v>8</v>
@@ -1877,7 +1877,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H58" t="s">
         <v>8</v>
@@ -1929,7 +1929,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H60" t="s">
         <v>8</v>
@@ -2007,7 +2007,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G63" t="n">
-        <v>3.03098940849304</v>
+        <v>3.03098917007446</v>
       </c>
       <c r="H63" t="s">
         <v>8</v>
@@ -2059,7 +2059,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087055206299</v>
       </c>
       <c r="H65" t="s">
         <v>8</v>
@@ -2111,7 +2111,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H67" t="s">
         <v>8</v>
@@ -2137,7 +2137,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280371665955</v>
+        <v>2.84280347824097</v>
       </c>
       <c r="H68" t="s">
         <v>8</v>
@@ -2241,7 +2241,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670910835266</v>
+        <v>2.74670886993408</v>
       </c>
       <c r="H72" t="s">
         <v>8</v>
@@ -2449,7 +2449,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H80" t="s">
         <v>8</v>
@@ -2475,7 +2475,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H81" t="s">
         <v>8</v>
@@ -2501,7 +2501,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087055206299</v>
       </c>
       <c r="H82" t="s">
         <v>8</v>
@@ -2605,7 +2605,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866132736206</v>
+        <v>2.69866156578064</v>
       </c>
       <c r="H86" t="s">
         <v>8</v>
@@ -2709,7 +2709,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H90" t="s">
         <v>8</v>
@@ -2813,7 +2813,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185572624207</v>
+        <v>1.88185596466064</v>
       </c>
       <c r="H94" t="s">
         <v>8</v>
@@ -2839,7 +2839,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.57755589485168</v>
+        <v>1.5775557756424</v>
       </c>
       <c r="H95" t="s">
         <v>8</v>
@@ -2865,7 +2865,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H96" t="s">
         <v>8</v>
@@ -2891,7 +2891,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.66163885593414</v>
+        <v>1.66163873672485</v>
       </c>
       <c r="H97" t="s">
         <v>8</v>
@@ -2917,7 +2917,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66163885593414</v>
+        <v>1.66163873672485</v>
       </c>
       <c r="H98" t="s">
         <v>8</v>
@@ -2943,7 +2943,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556377887726</v>
+        <v>1.58556389808655</v>
       </c>
       <c r="H99" t="s">
         <v>8</v>
@@ -2995,7 +2995,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H101" t="s">
         <v>8</v>
@@ -3073,7 +3073,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75773358345032</v>
+        <v>1.75773346424103</v>
       </c>
       <c r="H104" t="s">
         <v>8</v>
@@ -3125,7 +3125,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G106" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H106" t="s">
         <v>8</v>
@@ -3203,7 +3203,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205318450928</v>
+        <v>2.08205342292786</v>
       </c>
       <c r="H109" t="s">
         <v>8</v>
@@ -3281,7 +3281,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>2.81878018379211</v>
+        <v>2.81877994537354</v>
       </c>
       <c r="H112" t="s">
         <v>8</v>
@@ -3385,7 +3385,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H116" t="s">
         <v>8</v>
@@ -3411,7 +3411,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H117" t="s">
         <v>8</v>
@@ -3489,7 +3489,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664979934692</v>
+        <v>2.68664956092834</v>
       </c>
       <c r="H120" t="s">
         <v>8</v>
@@ -3645,7 +3645,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H126" t="s">
         <v>8</v>
@@ -3749,7 +3749,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H130" t="s">
         <v>8</v>
@@ -3775,7 +3775,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H131" t="s">
         <v>8</v>
@@ -3801,7 +3801,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G132" t="n">
-        <v>2.61057448387146</v>
+        <v>2.61057472229004</v>
       </c>
       <c r="H132" t="s">
         <v>8</v>
@@ -3827,7 +3827,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H133" t="s">
         <v>8</v>
@@ -3853,7 +3853,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H134" t="s">
         <v>8</v>
@@ -3879,7 +3879,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H135" t="s">
         <v>8</v>
@@ -3905,7 +3905,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H136" t="s">
         <v>8</v>
@@ -3983,7 +3983,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856271743774</v>
+        <v>2.59856295585632</v>
       </c>
       <c r="H139" t="s">
         <v>8</v>
@@ -4061,7 +4061,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H142" t="s">
         <v>8</v>
@@ -4113,7 +4113,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H144" t="s">
         <v>8</v>
@@ -4321,7 +4321,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G152" t="n">
-        <v>2.71067357063293</v>
+        <v>2.71067333221436</v>
       </c>
       <c r="H152" t="s">
         <v>8</v>
@@ -4347,7 +4347,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G153" t="n">
-        <v>2.64260625839233</v>
+        <v>2.64260601997375</v>
       </c>
       <c r="H153" t="s">
         <v>8</v>
@@ -4399,7 +4399,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H155" t="s">
         <v>8</v>
@@ -4815,7 +4815,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.37434148788452</v>
+        <v>2.37434124946594</v>
       </c>
       <c r="H171" t="s">
         <v>8</v>
@@ -4867,7 +4867,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H173" t="s">
         <v>8</v>
@@ -4893,7 +4893,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H174" t="s">
         <v>8</v>
@@ -4919,7 +4919,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H175" t="s">
         <v>8</v>
@@ -4945,7 +4945,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G176" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H176" t="s">
         <v>8</v>
@@ -4971,7 +4971,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H177" t="s">
         <v>8</v>
@@ -4997,7 +4997,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H178" t="s">
         <v>8</v>
@@ -5023,7 +5023,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G179" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H179" t="s">
         <v>8</v>
@@ -5491,7 +5491,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H197" t="s">
         <v>8</v>
@@ -5517,7 +5517,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.05100917816162</v>
+        <v>3.05100893974304</v>
       </c>
       <c r="H198" t="s">
         <v>8</v>
@@ -5569,7 +5569,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.81878018379211</v>
+        <v>2.81877994537354</v>
       </c>
       <c r="H200" t="s">
         <v>8</v>
@@ -5647,7 +5647,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H203" t="s">
         <v>8</v>
@@ -5673,7 +5673,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H204" t="s">
         <v>8</v>
@@ -5725,7 +5725,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258648872375</v>
+        <v>2.62258672714233</v>
       </c>
       <c r="H206" t="s">
         <v>8</v>
@@ -5751,7 +5751,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258648872375</v>
+        <v>2.62258672714233</v>
       </c>
       <c r="H207" t="s">
         <v>8</v>
@@ -5881,7 +5881,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H212" t="s">
         <v>8</v>
@@ -5933,7 +5933,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H214" t="s">
         <v>8</v>
@@ -5959,7 +5959,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H215" t="s">
         <v>8</v>
@@ -6115,7 +6115,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H221" t="s">
         <v>8</v>
@@ -6323,7 +6323,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>2.35031771659851</v>
+        <v>2.35031795501709</v>
       </c>
       <c r="H229" t="s">
         <v>8</v>
@@ -6401,7 +6401,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H232" t="s">
         <v>8</v>
@@ -6453,7 +6453,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G234" t="n">
-        <v>2.37434148788452</v>
+        <v>2.37434124946594</v>
       </c>
       <c r="H234" t="s">
         <v>8</v>
@@ -6479,7 +6479,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>2.31428241729736</v>
+        <v>2.31428217887878</v>
       </c>
       <c r="H235" t="s">
         <v>8</v>
@@ -6895,7 +6895,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H251" t="s">
         <v>8</v>
@@ -6921,7 +6921,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H252" t="s">
         <v>8</v>
@@ -7051,7 +7051,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221158027649</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H257" t="s">
         <v>8</v>
@@ -7233,7 +7233,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H264" t="s">
         <v>8</v>
@@ -7259,7 +7259,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.1861560344696</v>
+        <v>2.18615627288818</v>
       </c>
       <c r="H265" t="s">
         <v>8</v>
@@ -7285,7 +7285,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H266" t="s">
         <v>8</v>
@@ -7389,7 +7389,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221158027649</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H270" t="s">
         <v>8</v>
@@ -7545,7 +7545,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H276" t="s">
         <v>8</v>
@@ -7571,7 +7571,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H277" t="s">
         <v>8</v>
@@ -7597,7 +7597,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H278" t="s">
         <v>8</v>
@@ -7623,7 +7623,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H279" t="s">
         <v>8</v>
@@ -7649,7 +7649,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H280" t="s">
         <v>8</v>
@@ -7675,7 +7675,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H281" t="s">
         <v>8</v>
@@ -7987,7 +7987,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H293" t="s">
         <v>8</v>
@@ -8013,7 +8013,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H294" t="s">
         <v>8</v>
@@ -8039,7 +8039,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H295" t="s">
         <v>8</v>
@@ -8091,7 +8091,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H297" t="s">
         <v>8</v>
@@ -8117,7 +8117,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H298" t="s">
         <v>8</v>
@@ -8195,7 +8195,7 @@
         <v>2.75</v>
       </c>
       <c r="G301" t="n">
-        <v>2.20217180252075</v>
+        <v>2.20217204093933</v>
       </c>
       <c r="H301" t="s">
         <v>8</v>
@@ -8273,7 +8273,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G304" t="n">
-        <v>2.73069334030151</v>
+        <v>2.73069357872009</v>
       </c>
       <c r="H304" t="s">
         <v>8</v>
@@ -8299,7 +8299,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H305" t="s">
         <v>8</v>
@@ -8351,7 +8351,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H307" t="s">
         <v>8</v>
@@ -8403,7 +8403,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039703369141</v>
+        <v>2.43039679527283</v>
       </c>
       <c r="H309" t="s">
         <v>8</v>
@@ -8455,7 +8455,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H311" t="s">
         <v>8</v>
@@ -8481,7 +8481,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045610427856</v>
+        <v>2.49045586585999</v>
       </c>
       <c r="H312" t="s">
         <v>8</v>
@@ -8533,7 +8533,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H314" t="s">
         <v>8</v>
@@ -8559,7 +8559,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H315" t="s">
         <v>8</v>
@@ -8897,7 +8897,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G328" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H328" t="s">
         <v>8</v>
@@ -9001,7 +9001,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.4424090385437</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H332" t="s">
         <v>8</v>
@@ -9157,7 +9157,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H338" t="s">
         <v>8</v>
@@ -9443,7 +9443,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H349" t="s">
         <v>8</v>
@@ -9495,7 +9495,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>2.62659049034119</v>
+        <v>2.62659025192261</v>
       </c>
       <c r="H351" t="s">
         <v>8</v>
@@ -9599,7 +9599,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>2.6706337928772</v>
+        <v>2.67063403129578</v>
       </c>
       <c r="H355" t="s">
         <v>8</v>
@@ -9677,7 +9677,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266580581665</v>
+        <v>2.70266556739807</v>
       </c>
       <c r="H358" t="s">
         <v>8</v>
@@ -9703,7 +9703,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H359" t="s">
         <v>8</v>
@@ -9807,7 +9807,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H363" t="s">
         <v>8</v>
@@ -9833,7 +9833,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H364" t="s">
         <v>8</v>
@@ -9859,7 +9859,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H365" t="s">
         <v>8</v>
@@ -9989,7 +9989,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H370" t="s">
         <v>8</v>
@@ -10067,7 +10067,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H373" t="s">
         <v>8</v>
@@ -10093,7 +10093,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H374" t="s">
         <v>8</v>
@@ -10171,7 +10171,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H377" t="s">
         <v>8</v>
@@ -10301,7 +10301,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G382" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H382" t="s">
         <v>8</v>
@@ -10327,7 +10327,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G383" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H383" t="s">
         <v>8</v>
@@ -10405,7 +10405,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H386" t="s">
         <v>8</v>
@@ -10457,7 +10457,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H388" t="s">
         <v>8</v>
@@ -10483,7 +10483,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G389" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H389" t="s">
         <v>8</v>
@@ -10509,7 +10509,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G390" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H390" t="s">
         <v>8</v>
@@ -10561,7 +10561,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H392" t="s">
         <v>8</v>
@@ -10587,7 +10587,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.17112755775452</v>
+        <v>3.1711277961731</v>
       </c>
       <c r="H393" t="s">
         <v>8</v>
@@ -10769,7 +10769,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G400" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H400" t="s">
         <v>8</v>
@@ -10899,7 +10899,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>3.42738032341003</v>
+        <v>3.42738056182861</v>
       </c>
       <c r="H405" t="s">
         <v>8</v>
@@ -10925,7 +10925,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>3.31526970863342</v>
+        <v>3.31526947021484</v>
       </c>
       <c r="H406" t="s">
         <v>8</v>
@@ -10951,7 +10951,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>3.31526970863342</v>
+        <v>3.31526947021484</v>
       </c>
       <c r="H407" t="s">
         <v>8</v>
@@ -11029,7 +11029,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511155128479</v>
       </c>
       <c r="H410" t="s">
         <v>8</v>
@@ -11055,7 +11055,7 @@
         <v>4</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H411" t="s">
         <v>8</v>
@@ -11133,7 +11133,7 @@
         <v>4</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H414" t="s">
         <v>8</v>
@@ -11185,7 +11185,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511155128479</v>
       </c>
       <c r="H416" t="s">
         <v>8</v>
@@ -11211,7 +11211,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H417" t="s">
         <v>8</v>
@@ -11289,7 +11289,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H420" t="s">
         <v>8</v>
@@ -11315,7 +11315,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H421" t="s">
         <v>8</v>
@@ -11341,7 +11341,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H422" t="s">
         <v>8</v>
@@ -11393,7 +11393,7 @@
         <v>4</v>
       </c>
       <c r="G424" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H424" t="s">
         <v>8</v>
@@ -11419,7 +11419,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511155128479</v>
       </c>
       <c r="H425" t="s">
         <v>8</v>
@@ -11445,7 +11445,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H426" t="s">
         <v>8</v>
@@ -11471,7 +11471,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G427" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H427" t="s">
         <v>8</v>
@@ -11575,7 +11575,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H431" t="s">
         <v>8</v>
@@ -11913,7 +11913,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H444" t="s">
         <v>8</v>
@@ -11939,7 +11939,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H445" t="s">
         <v>8</v>
@@ -11965,7 +11965,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H446" t="s">
         <v>8</v>
@@ -11991,7 +11991,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H447" t="s">
         <v>8</v>
@@ -12017,7 +12017,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H448" t="s">
         <v>8</v>
@@ -12173,7 +12173,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G454" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H454" t="s">
         <v>8</v>
@@ -12199,7 +12199,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H455" t="s">
         <v>8</v>
@@ -12303,7 +12303,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G459" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H459" t="s">
         <v>8</v>
@@ -12433,7 +12433,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H464" t="s">
         <v>8</v>
@@ -12459,7 +12459,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H465" t="s">
         <v>8</v>
@@ -12615,7 +12615,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H471" t="s">
         <v>8</v>
@@ -12641,7 +12641,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H472" t="s">
         <v>8</v>
@@ -12667,7 +12667,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H473" t="s">
         <v>8</v>
@@ -12745,7 +12745,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G476" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H476" t="s">
         <v>8</v>
@@ -12771,7 +12771,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H477" t="s">
         <v>8</v>
@@ -12797,7 +12797,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G478" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H478" t="s">
         <v>8</v>
@@ -12901,7 +12901,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H482" t="s">
         <v>8</v>
@@ -12979,7 +12979,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H485" t="s">
         <v>8</v>
@@ -13005,7 +13005,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H486" t="s">
         <v>8</v>
@@ -13083,7 +13083,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G489" t="n">
-        <v>3.01096940040588</v>
+        <v>3.01096963882446</v>
       </c>
       <c r="H489" t="s">
         <v>8</v>
@@ -13265,7 +13265,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H496" t="s">
         <v>8</v>
@@ -13291,7 +13291,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H497" t="s">
         <v>8</v>
@@ -13421,7 +13421,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H502" t="s">
         <v>8</v>
@@ -13447,7 +13447,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H503" t="s">
         <v>8</v>
@@ -13473,7 +13473,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H504" t="s">
         <v>8</v>
@@ -13525,7 +13525,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H506" t="s">
         <v>8</v>
@@ -13603,7 +13603,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H509" t="s">
         <v>8</v>
@@ -13629,7 +13629,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H510" t="s">
         <v>8</v>
@@ -13655,7 +13655,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H511" t="s">
         <v>8</v>
@@ -13681,7 +13681,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H512" t="s">
         <v>8</v>
@@ -13707,7 +13707,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H513" t="s">
         <v>8</v>
@@ -13759,7 +13759,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H515" t="s">
         <v>8</v>
@@ -13837,7 +13837,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H518" t="s">
         <v>8</v>
@@ -13863,7 +13863,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H519" t="s">
         <v>8</v>
@@ -13889,7 +13889,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H520" t="s">
         <v>8</v>
@@ -13915,7 +13915,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471663475037</v>
       </c>
       <c r="H521" t="s">
         <v>8</v>
@@ -14097,7 +14097,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846410751343</v>
+        <v>2.49846386909485</v>
       </c>
       <c r="H528" t="s">
         <v>8</v>
@@ -14175,7 +14175,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H531" t="s">
         <v>8</v>
@@ -14201,7 +14201,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H532" t="s">
         <v>8</v>
@@ -14253,7 +14253,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H534" t="s">
         <v>8</v>
@@ -14383,7 +14383,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H539" t="s">
         <v>8</v>
@@ -14435,7 +14435,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H541" t="s">
         <v>8</v>
@@ -14539,7 +14539,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H545" t="s">
         <v>8</v>
@@ -14591,7 +14591,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221158027649</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H547" t="s">
         <v>8</v>
@@ -14643,7 +14643,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H549" t="s">
         <v>8</v>
@@ -14695,7 +14695,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H551" t="s">
         <v>8</v>
@@ -14721,7 +14721,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H552" t="s">
         <v>8</v>
@@ -14851,7 +14851,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H557" t="s">
         <v>8</v>
@@ -14877,7 +14877,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H558" t="s">
         <v>8</v>
@@ -14903,7 +14903,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H559" t="s">
         <v>8</v>
@@ -15007,7 +15007,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H563" t="s">
         <v>8</v>
@@ -15267,7 +15267,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H573" t="s">
         <v>8</v>
@@ -15293,7 +15293,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H574" t="s">
         <v>8</v>
@@ -15319,7 +15319,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H575" t="s">
         <v>8</v>
@@ -15371,7 +15371,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221158027649</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H577" t="s">
         <v>8</v>
@@ -15397,7 +15397,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221158027649</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H578" t="s">
         <v>8</v>
@@ -15423,7 +15423,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221158027649</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H579" t="s">
         <v>8</v>
@@ -15449,7 +15449,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H580" t="s">
         <v>8</v>
@@ -15605,7 +15605,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400588035583</v>
+        <v>2.03400611877441</v>
       </c>
       <c r="H586" t="s">
         <v>8</v>
@@ -15657,7 +15657,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.17814803123474</v>
+        <v>2.17814779281616</v>
       </c>
       <c r="H588" t="s">
         <v>8</v>
@@ -15761,7 +15761,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400588035583</v>
+        <v>2.03400611877441</v>
       </c>
       <c r="H592" t="s">
         <v>8</v>
@@ -15787,7 +15787,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G593" t="n">
-        <v>2.01799035072327</v>
+        <v>2.01799011230469</v>
       </c>
       <c r="H593" t="s">
         <v>8</v>
@@ -15813,7 +15813,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98595857620239</v>
+        <v>1.98595869541168</v>
       </c>
       <c r="H594" t="s">
         <v>8</v>
@@ -15865,7 +15865,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986372947693</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H596" t="s">
         <v>8</v>
@@ -15891,7 +15891,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587973594666</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H597" t="s">
         <v>8</v>
@@ -15917,7 +15917,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G598" t="n">
-        <v>1.7777533531189</v>
+        <v>1.77775323390961</v>
       </c>
       <c r="H598" t="s">
         <v>8</v>
@@ -15943,7 +15943,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H599" t="s">
         <v>8</v>
@@ -15969,7 +15969,7 @@
         <v>2</v>
       </c>
       <c r="G600" t="n">
-        <v>1.60157954692841</v>
+        <v>1.6015796661377</v>
       </c>
       <c r="H600" t="s">
         <v>8</v>
@@ -16021,7 +16021,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G602" t="n">
-        <v>1.53751623630524</v>
+        <v>1.53751635551453</v>
       </c>
       <c r="H602" t="s">
         <v>8</v>
@@ -16047,7 +16047,7 @@
         <v>2</v>
       </c>
       <c r="G603" t="n">
-        <v>1.60157954692841</v>
+        <v>1.6015796661377</v>
       </c>
       <c r="H603" t="s">
         <v>8</v>
@@ -16099,7 +16099,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564273834229</v>
       </c>
       <c r="H605" t="s">
         <v>8</v>
@@ -16177,7 +16177,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H608" t="s">
         <v>8</v>
@@ -16229,7 +16229,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H610" t="s">
         <v>8</v>
@@ -16255,7 +16255,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H611" t="s">
         <v>8</v>
@@ -16385,7 +16385,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G616" t="n">
-        <v>1.7777533531189</v>
+        <v>1.77775323390961</v>
       </c>
       <c r="H616" t="s">
         <v>8</v>
@@ -16437,7 +16437,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376924037933</v>
+        <v>1.79376900196075</v>
       </c>
       <c r="H618" t="s">
         <v>8</v>
@@ -16463,7 +16463,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587973594666</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H619" t="s">
         <v>8</v>
@@ -16489,7 +16489,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986372947693</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H620" t="s">
         <v>8</v>
@@ -16515,7 +16515,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.95392715930939</v>
+        <v>1.95392692089081</v>
       </c>
       <c r="H621" t="s">
         <v>8</v>
@@ -16541,7 +16541,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.8097847700119</v>
+        <v>1.80978488922119</v>
       </c>
       <c r="H622" t="s">
         <v>8</v>
@@ -16593,7 +16593,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564273834229</v>
       </c>
       <c r="H624" t="s">
         <v>8</v>
@@ -16645,7 +16645,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.72169816493988</v>
+        <v>1.72169804573059</v>
       </c>
       <c r="H626" t="s">
         <v>8</v>
@@ -16671,7 +16671,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H627" t="s">
         <v>8</v>
@@ -16697,7 +16697,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H628" t="s">
         <v>8</v>
@@ -16723,7 +16723,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376924037933</v>
+        <v>1.79376900196075</v>
       </c>
       <c r="H629" t="s">
         <v>8</v>
@@ -16775,7 +16775,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.72169816493988</v>
+        <v>1.72169804573059</v>
       </c>
       <c r="H631" t="s">
         <v>8</v>
@@ -16905,7 +16905,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71369016170502</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H636" t="s">
         <v>8</v>
@@ -16957,7 +16957,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H638" t="s">
         <v>8</v>
@@ -17009,7 +17009,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779289245605</v>
+        <v>1.81779277324677</v>
       </c>
       <c r="H640" t="s">
         <v>8</v>
@@ -17035,7 +17035,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779289245605</v>
+        <v>1.81779277324677</v>
       </c>
       <c r="H641" t="s">
         <v>8</v>
@@ -17087,7 +17087,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380842208862</v>
       </c>
       <c r="H643" t="s">
         <v>8</v>
@@ -17113,7 +17113,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81743538379669</v>
+        <v>1.8174352645874</v>
       </c>
       <c r="H644" t="s">
         <v>8</v>
@@ -17139,7 +17139,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H645" t="s">
         <v>8</v>
@@ -17191,7 +17191,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G647" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H647" t="s">
         <v>8</v>
@@ -17217,7 +17217,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H648" t="s">
         <v>8</v>
@@ -17243,7 +17243,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.85018181800842</v>
+        <v>1.85018193721771</v>
       </c>
       <c r="H649" t="s">
         <v>8</v>
@@ -17295,7 +17295,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H651" t="s">
         <v>8</v>
@@ -17321,7 +17321,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836863517761</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H652" t="s">
         <v>8</v>
@@ -17347,7 +17347,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836863517761</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H653" t="s">
         <v>8</v>
@@ -17477,7 +17477,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H658" t="s">
         <v>8</v>
@@ -17529,7 +17529,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H660" t="s">
         <v>8</v>
@@ -17581,7 +17581,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H662" t="s">
         <v>8</v>
@@ -17607,7 +17607,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.83380877971649</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H663" t="s">
         <v>8</v>
@@ -17633,7 +17633,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G664" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H664" t="s">
         <v>8</v>
@@ -17659,7 +17659,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.83380877971649</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H665" t="s">
         <v>8</v>
@@ -17789,7 +17789,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H670" t="s">
         <v>8</v>
@@ -17841,7 +17841,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H672" t="s">
         <v>8</v>
@@ -17867,7 +17867,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H673" t="s">
         <v>8</v>
@@ -17919,7 +17919,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H675" t="s">
         <v>8</v>
@@ -18075,7 +18075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H681" t="s">
         <v>8</v>
@@ -18127,7 +18127,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H683" t="s">
         <v>8</v>
@@ -18153,7 +18153,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H684" t="s">
         <v>8</v>
@@ -18179,7 +18179,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H685" t="s">
         <v>8</v>
@@ -18231,7 +18231,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H687" t="s">
         <v>8</v>
@@ -18257,7 +18257,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H688" t="s">
         <v>8</v>
@@ -18361,7 +18361,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H692" t="s">
         <v>8</v>
@@ -18387,7 +18387,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H693" t="s">
         <v>8</v>
@@ -18413,7 +18413,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H694" t="s">
         <v>8</v>
@@ -18465,7 +18465,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G696" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H696" t="s">
         <v>8</v>
@@ -18933,7 +18933,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H714" t="s">
         <v>8</v>
@@ -18985,7 +18985,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H716" t="s">
         <v>8</v>
@@ -19089,7 +19089,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H720" t="s">
         <v>8</v>
@@ -19115,7 +19115,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H721" t="s">
         <v>8</v>
@@ -19141,7 +19141,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G722" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H722" t="s">
         <v>8</v>
@@ -19167,7 +19167,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G723" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H723" t="s">
         <v>8</v>
@@ -19193,7 +19193,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H724" t="s">
         <v>8</v>
@@ -19271,7 +19271,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H727" t="s">
         <v>8</v>
@@ -19297,7 +19297,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H728" t="s">
         <v>8</v>
@@ -19375,7 +19375,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H731" t="s">
         <v>8</v>
@@ -19401,7 +19401,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G732" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H732" t="s">
         <v>8</v>
@@ -19427,7 +19427,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G733" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H733" t="s">
         <v>8</v>
@@ -19453,7 +19453,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H734" t="s">
         <v>8</v>
@@ -19479,7 +19479,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H735" t="s">
         <v>8</v>
@@ -19505,7 +19505,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H736" t="s">
         <v>8</v>
@@ -19531,7 +19531,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H737" t="s">
         <v>8</v>
@@ -19635,7 +19635,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H741" t="s">
         <v>8</v>
@@ -19661,7 +19661,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H742" t="s">
         <v>8</v>
@@ -19687,7 +19687,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H743" t="s">
         <v>8</v>
@@ -19713,7 +19713,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H744" t="s">
         <v>8</v>
@@ -19791,7 +19791,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G747" t="n">
-        <v>1.51452946662903</v>
+        <v>1.51452934741974</v>
       </c>
       <c r="H747" t="s">
         <v>8</v>
@@ -19869,7 +19869,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H750" t="s">
         <v>8</v>
@@ -19895,7 +19895,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H751" t="s">
         <v>8</v>
@@ -19999,7 +19999,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359609603882</v>
+        <v>1.47359621524811</v>
       </c>
       <c r="H755" t="s">
         <v>8</v>
@@ -20207,7 +20207,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H763" t="s">
         <v>8</v>
@@ -20233,7 +20233,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H764" t="s">
         <v>8</v>
@@ -20259,7 +20259,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H765" t="s">
         <v>8</v>
@@ -20285,7 +20285,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H766" t="s">
         <v>8</v>
@@ -20311,7 +20311,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H767" t="s">
         <v>8</v>
@@ -20415,7 +20415,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G771" t="n">
-        <v>1.51452946662903</v>
+        <v>1.51452934741974</v>
       </c>
       <c r="H771" t="s">
         <v>8</v>
@@ -20441,7 +20441,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H772" t="s">
         <v>8</v>
@@ -20467,7 +20467,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H773" t="s">
         <v>8</v>
@@ -20571,7 +20571,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H777" t="s">
         <v>8</v>
@@ -20597,7 +20597,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H778" t="s">
         <v>8</v>
@@ -20623,7 +20623,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H779" t="s">
         <v>8</v>
@@ -20701,7 +20701,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H782" t="s">
         <v>8</v>
@@ -20727,7 +20727,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H783" t="s">
         <v>8</v>
@@ -20779,7 +20779,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H785" t="s">
         <v>8</v>
@@ -20805,7 +20805,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H786" t="s">
         <v>8</v>
@@ -20831,7 +20831,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H787" t="s">
         <v>8</v>
@@ -20883,7 +20883,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G789" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H789" t="s">
         <v>8</v>
@@ -20909,7 +20909,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H790" t="s">
         <v>8</v>
@@ -20935,7 +20935,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H791" t="s">
         <v>8</v>
@@ -20961,7 +20961,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H792" t="s">
         <v>8</v>
@@ -21065,7 +21065,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H796" t="s">
         <v>8</v>
@@ -21091,7 +21091,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H797" t="s">
         <v>8</v>
@@ -21117,7 +21117,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H798" t="s">
         <v>8</v>
@@ -21299,7 +21299,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H805" t="s">
         <v>8</v>
@@ -21325,7 +21325,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H806" t="s">
         <v>8</v>
@@ -21455,7 +21455,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G811" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H811" t="s">
         <v>8</v>
@@ -21559,7 +21559,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H815" t="s">
         <v>8</v>
@@ -21585,7 +21585,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842171669006</v>
+        <v>1.94842183589935</v>
       </c>
       <c r="H816" t="s">
         <v>8</v>
@@ -21611,7 +21611,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H817" t="s">
         <v>8</v>
@@ -21637,7 +21637,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G818" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H818" t="s">
         <v>8</v>
@@ -21663,7 +21663,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H819" t="s">
         <v>8</v>
@@ -21689,7 +21689,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H820" t="s">
         <v>8</v>
@@ -21715,7 +21715,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H821" t="s">
         <v>8</v>
@@ -21741,7 +21741,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H822" t="s">
         <v>8</v>
@@ -21767,7 +21767,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H823" t="s">
         <v>8</v>
@@ -21793,7 +21793,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H824" t="s">
         <v>8</v>
@@ -21819,7 +21819,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H825" t="s">
         <v>8</v>
@@ -21897,7 +21897,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H828" t="s">
         <v>8</v>
@@ -21923,7 +21923,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H829" t="s">
         <v>8</v>
@@ -21949,7 +21949,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H830" t="s">
         <v>8</v>
@@ -22001,7 +22001,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034106254578</v>
+        <v>2.12034130096436</v>
       </c>
       <c r="H832" t="s">
         <v>8</v>
@@ -22027,7 +22027,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H833" t="s">
         <v>8</v>
@@ -22079,7 +22079,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.99754166603088</v>
+        <v>1.9975414276123</v>
       </c>
       <c r="H835" t="s">
         <v>8</v>
@@ -22131,7 +22131,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H837" t="s">
         <v>8</v>
@@ -22157,7 +22157,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H838" t="s">
         <v>8</v>
@@ -22209,7 +22209,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H840" t="s">
         <v>8</v>
@@ -22235,7 +22235,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H841" t="s">
         <v>8</v>
@@ -22261,7 +22261,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H842" t="s">
         <v>8</v>
@@ -22339,7 +22339,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H845" t="s">
         <v>8</v>
@@ -22365,7 +22365,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H846" t="s">
         <v>8</v>
@@ -22469,7 +22469,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H850" t="s">
         <v>8</v>
@@ -22495,7 +22495,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>2.08759474754333</v>
+        <v>2.08759450912476</v>
       </c>
       <c r="H851" t="s">
         <v>8</v>
@@ -22521,7 +22521,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H852" t="s">
         <v>8</v>
@@ -22573,7 +22573,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H854" t="s">
         <v>8</v>
@@ -22625,7 +22625,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H856" t="s">
         <v>8</v>
@@ -22651,7 +22651,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H857" t="s">
         <v>8</v>
@@ -22781,7 +22781,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204820156097</v>
+        <v>1.93204832077026</v>
       </c>
       <c r="H862" t="s">
         <v>8</v>
@@ -22807,7 +22807,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479511260986</v>
+        <v>1.96479499340057</v>
       </c>
       <c r="H863" t="s">
         <v>8</v>
@@ -22833,7 +22833,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H864" t="s">
         <v>8</v>
@@ -22859,7 +22859,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930152893066</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H865" t="s">
         <v>8</v>
@@ -22885,7 +22885,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930152893066</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H866" t="s">
         <v>8</v>
@@ -22911,7 +22911,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H867" t="s">
         <v>8</v>
@@ -22937,7 +22937,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H868" t="s">
         <v>8</v>
@@ -22963,7 +22963,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H869" t="s">
         <v>8</v>
@@ -22989,7 +22989,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655497550964</v>
       </c>
       <c r="H870" t="s">
         <v>8</v>
@@ -23015,7 +23015,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.83380877971649</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H871" t="s">
         <v>8</v>
@@ -23067,7 +23067,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H873" t="s">
         <v>8</v>
@@ -23093,7 +23093,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292837142944</v>
       </c>
       <c r="H874" t="s">
         <v>8</v>
@@ -23171,7 +23171,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H877" t="s">
         <v>8</v>
@@ -23223,7 +23223,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G879" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H879" t="s">
         <v>8</v>
@@ -23249,7 +23249,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H880" t="s">
         <v>8</v>
@@ -23275,7 +23275,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H881" t="s">
         <v>8</v>
@@ -23301,7 +23301,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H882" t="s">
         <v>8</v>
@@ -23327,7 +23327,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H883" t="s">
         <v>8</v>
@@ -23353,7 +23353,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H884" t="s">
         <v>8</v>
@@ -23379,7 +23379,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H885" t="s">
         <v>8</v>
@@ -23405,7 +23405,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H886" t="s">
         <v>8</v>
@@ -23665,7 +23665,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H896" t="s">
         <v>8</v>
@@ -23717,7 +23717,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H898" t="s">
         <v>8</v>
@@ -23769,7 +23769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H900" t="s">
         <v>8</v>
@@ -23795,7 +23795,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G901" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H901" t="s">
         <v>8</v>
@@ -23847,7 +23847,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H903" t="s">
         <v>8</v>
@@ -23873,7 +23873,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G904" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H904" t="s">
         <v>8</v>
@@ -23899,7 +23899,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H905" t="s">
         <v>8</v>
@@ -23925,7 +23925,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993092536926</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H906" t="s">
         <v>8</v>
@@ -23951,7 +23951,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993092536926</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H907" t="s">
         <v>8</v>
@@ -23977,7 +23977,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91285216808319</v>
+        <v>1.9128520488739</v>
       </c>
       <c r="H908" t="s">
         <v>8</v>
@@ -24003,7 +24003,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H909" t="s">
         <v>8</v>
@@ -24237,7 +24237,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G918" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H918" t="s">
         <v>8</v>
@@ -24263,7 +24263,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G919" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H919" t="s">
         <v>8</v>
@@ -24289,7 +24289,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H920" t="s">
         <v>8</v>
@@ -24315,7 +24315,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H921" t="s">
         <v>8</v>
@@ -24341,7 +24341,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H922" t="s">
         <v>8</v>
@@ -24419,7 +24419,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H925" t="s">
         <v>8</v>
@@ -24471,7 +24471,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H927" t="s">
         <v>8</v>
@@ -24497,7 +24497,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H928" t="s">
         <v>8</v>
@@ -24523,7 +24523,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H929" t="s">
         <v>8</v>
@@ -24549,7 +24549,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H930" t="s">
         <v>8</v>
@@ -24575,7 +24575,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H931" t="s">
         <v>8</v>
@@ -24601,7 +24601,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H932" t="s">
         <v>8</v>
@@ -24627,7 +24627,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H933" t="s">
         <v>8</v>
@@ -24653,7 +24653,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H934" t="s">
         <v>8</v>
@@ -24679,7 +24679,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G935" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H935" t="s">
         <v>8</v>
@@ -24757,7 +24757,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H938" t="s">
         <v>8</v>
@@ -24783,7 +24783,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H939" t="s">
         <v>8</v>
@@ -24809,7 +24809,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G940" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H940" t="s">
         <v>8</v>
@@ -24887,7 +24887,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H943" t="s">
         <v>8</v>
@@ -24913,7 +24913,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H944" t="s">
         <v>8</v>
@@ -24939,7 +24939,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H945" t="s">
         <v>8</v>
@@ -24965,7 +24965,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H946" t="s">
         <v>8</v>
@@ -24991,7 +24991,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H947" t="s">
         <v>8</v>
@@ -25017,7 +25017,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H948" t="s">
         <v>8</v>
@@ -25043,7 +25043,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G949" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H949" t="s">
         <v>8</v>
@@ -25095,7 +25095,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.91285216808319</v>
+        <v>1.9128520488739</v>
       </c>
       <c r="H951" t="s">
         <v>8</v>
@@ -25121,7 +25121,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993092536926</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H952" t="s">
         <v>8</v>
@@ -25173,7 +25173,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G954" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H954" t="s">
         <v>8</v>
@@ -25199,7 +25199,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H955" t="s">
         <v>8</v>
@@ -25225,7 +25225,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G956" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H956" t="s">
         <v>8</v>
@@ -25251,7 +25251,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H957" t="s">
         <v>8</v>
@@ -25277,7 +25277,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G958" t="n">
-        <v>1.9470100402832</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H958" t="s">
         <v>8</v>
@@ -25329,7 +25329,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H960" t="s">
         <v>8</v>
@@ -25355,7 +25355,7 @@
         <v>2</v>
       </c>
       <c r="G961" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H961" t="s">
         <v>8</v>
@@ -25433,7 +25433,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H964" t="s">
         <v>8</v>
@@ -25459,7 +25459,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H965" t="s">
         <v>8</v>
@@ -25511,7 +25511,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H967" t="s">
         <v>8</v>
@@ -25537,7 +25537,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H968" t="s">
         <v>8</v>
@@ -25563,7 +25563,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H969" t="s">
         <v>8</v>
@@ -25589,7 +25589,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.84453594684601</v>
+        <v>1.8445360660553</v>
       </c>
       <c r="H970" t="s">
         <v>8</v>
@@ -25615,7 +25615,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H971" t="s">
         <v>8</v>
@@ -25641,7 +25641,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H972" t="s">
         <v>8</v>
@@ -25667,7 +25667,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H973" t="s">
         <v>8</v>
@@ -25693,7 +25693,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H974" t="s">
         <v>8</v>
@@ -25719,7 +25719,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H975" t="s">
         <v>8</v>
@@ -25745,7 +25745,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H976" t="s">
         <v>8</v>
@@ -25771,7 +25771,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H977" t="s">
         <v>8</v>
@@ -25797,7 +25797,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037759780884</v>
       </c>
       <c r="H978" t="s">
         <v>8</v>
@@ -25823,7 +25823,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H979" t="s">
         <v>8</v>
@@ -25849,7 +25849,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H980" t="s">
         <v>8</v>
@@ -25875,7 +25875,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G981" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037759780884</v>
       </c>
       <c r="H981" t="s">
         <v>8</v>
@@ -25901,7 +25901,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H982" t="s">
         <v>8</v>
@@ -25927,7 +25927,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H983" t="s">
         <v>8</v>
@@ -25953,7 +25953,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G984" t="n">
-        <v>1.74206173419952</v>
+        <v>1.74206161499023</v>
       </c>
       <c r="H984" t="s">
         <v>8</v>
@@ -26005,7 +26005,7 @@
         <v>2</v>
       </c>
       <c r="G986" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H986" t="s">
         <v>8</v>
@@ -26057,7 +26057,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>1.6225084066391</v>
+        <v>1.62250828742981</v>
       </c>
       <c r="H988" t="s">
         <v>8</v>
@@ -26083,7 +26083,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.58835029602051</v>
+        <v>1.5883504152298</v>
       </c>
       <c r="H989" t="s">
         <v>8</v>
@@ -26135,7 +26135,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G991" t="n">
-        <v>1.40048098564148</v>
+        <v>1.40048086643219</v>
       </c>
       <c r="H991" t="s">
         <v>8</v>
@@ -26265,7 +26265,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H996" t="s">
         <v>8</v>
@@ -26291,7 +26291,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H997" t="s">
         <v>8</v>
@@ -26317,7 +26317,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H998" t="s">
         <v>8</v>
@@ -26343,7 +26343,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H999" t="s">
         <v>8</v>
@@ -26369,7 +26369,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1000" t="s">
         <v>8</v>
@@ -26421,7 +26421,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1002" t="s">
         <v>8</v>
@@ -26447,7 +26447,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1003" t="s">
         <v>8</v>
@@ -26473,7 +26473,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1004" t="s">
         <v>8</v>
@@ -26733,7 +26733,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1014" t="s">
         <v>8</v>
@@ -26759,7 +26759,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1015" t="s">
         <v>8</v>
@@ -26811,7 +26811,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1017" t="s">
         <v>8</v>
@@ -26837,7 +26837,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1018" t="s">
         <v>8</v>
@@ -26889,7 +26889,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1020" t="s">
         <v>8</v>
@@ -26915,7 +26915,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1021" t="s">
         <v>8</v>
@@ -26941,7 +26941,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1022" t="s">
         <v>8</v>
@@ -27071,7 +27071,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1027" t="s">
         <v>8</v>
@@ -27149,7 +27149,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1030" t="s">
         <v>8</v>
@@ -27175,7 +27175,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1031" t="s">
         <v>8</v>
@@ -27201,7 +27201,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1032" t="s">
         <v>8</v>
@@ -27227,7 +27227,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1033" t="s">
         <v>8</v>
@@ -27539,7 +27539,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1045" t="n">
-        <v>1.33216488361359</v>
+        <v>1.3321647644043</v>
       </c>
       <c r="H1045" t="s">
         <v>8</v>
@@ -27565,7 +27565,7 @@
         <v>1.55999994277954</v>
       </c>
       <c r="G1046" t="n">
-        <v>1.33216488361359</v>
+        <v>1.3321647644043</v>
       </c>
       <c r="H1046" t="s">
         <v>8</v>
@@ -27617,7 +27617,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.38340198993683</v>
+        <v>1.38340187072754</v>
       </c>
       <c r="H1048" t="s">
         <v>8</v>
@@ -27643,7 +27643,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1049" t="s">
         <v>8</v>
@@ -27747,7 +27747,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1053" t="s">
         <v>8</v>
@@ -27773,7 +27773,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1054" t="s">
         <v>8</v>
@@ -27799,7 +27799,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1055" t="s">
         <v>8</v>
@@ -27877,7 +27877,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1058" t="s">
         <v>8</v>
@@ -27903,7 +27903,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1059" t="s">
         <v>8</v>
@@ -27929,7 +27929,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1060" t="s">
         <v>8</v>
@@ -27955,7 +27955,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1061" t="s">
         <v>8</v>
@@ -27981,7 +27981,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1062" t="s">
         <v>8</v>
@@ -28007,7 +28007,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1063" t="s">
         <v>8</v>
@@ -28033,7 +28033,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.40048098564148</v>
+        <v>1.40048086643219</v>
       </c>
       <c r="H1064" t="s">
         <v>8</v>
@@ -28137,7 +28137,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1068" t="s">
         <v>8</v>
@@ -28215,7 +28215,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1071" t="s">
         <v>8</v>
@@ -28267,7 +28267,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.44317853450775</v>
+        <v>1.44317865371704</v>
       </c>
       <c r="H1073" t="s">
         <v>8</v>
@@ -28397,7 +28397,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1078" t="s">
         <v>8</v>
@@ -28423,7 +28423,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1079" t="s">
         <v>8</v>
@@ -28449,7 +28449,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1080" t="s">
         <v>8</v>
@@ -28475,7 +28475,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1081" t="s">
         <v>8</v>
@@ -28527,7 +28527,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1083" t="s">
         <v>8</v>
@@ -28553,7 +28553,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1084" t="s">
         <v>8</v>
@@ -28579,7 +28579,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.38340198993683</v>
+        <v>1.38340187072754</v>
       </c>
       <c r="H1085" t="s">
         <v>8</v>
@@ -28605,7 +28605,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1086" t="s">
         <v>8</v>
@@ -28631,7 +28631,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1087" t="s">
         <v>8</v>
@@ -28683,7 +28683,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1089" t="s">
         <v>8</v>
@@ -28709,7 +28709,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1090" t="s">
         <v>8</v>
@@ -28735,7 +28735,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1091" t="s">
         <v>8</v>
@@ -28761,7 +28761,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1092" t="s">
         <v>8</v>
@@ -28787,7 +28787,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1093" t="s">
         <v>8</v>
@@ -28813,7 +28813,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1094" t="s">
         <v>8</v>
@@ -28839,7 +28839,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.58835029602051</v>
+        <v>1.5883504152298</v>
       </c>
       <c r="H1095" t="s">
         <v>8</v>
@@ -29099,7 +29099,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1105" t="s">
         <v>8</v>
@@ -29255,7 +29255,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1111" t="s">
         <v>8</v>
@@ -29281,7 +29281,7 @@
         <v>2</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1112" t="s">
         <v>8</v>
@@ -29307,7 +29307,7 @@
         <v>2</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1113" t="s">
         <v>8</v>
@@ -29411,7 +29411,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H1117" t="s">
         <v>8</v>
@@ -29437,7 +29437,7 @@
         <v>2</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1118" t="s">
         <v>8</v>
@@ -29463,7 +29463,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.74206173419952</v>
+        <v>1.74206161499023</v>
       </c>
       <c r="H1119" t="s">
         <v>8</v>
@@ -29489,7 +29489,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H1120" t="s">
         <v>8</v>
@@ -29515,7 +29515,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H1121" t="s">
         <v>8</v>
@@ -29541,7 +29541,7 @@
         <v>2</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1122" t="s">
         <v>8</v>
@@ -29567,7 +29567,7 @@
         <v>2</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1123" t="s">
         <v>8</v>
@@ -29619,7 +29619,7 @@
         <v>2</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1125" t="s">
         <v>8</v>
@@ -29645,7 +29645,7 @@
         <v>2</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1126" t="s">
         <v>8</v>
@@ -29671,7 +29671,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H1127" t="s">
         <v>8</v>
@@ -29697,7 +29697,7 @@
         <v>2</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1128" t="s">
         <v>8</v>
@@ -29723,7 +29723,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H1129" t="s">
         <v>8</v>
@@ -29749,7 +29749,7 @@
         <v>2</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1130" t="s">
         <v>8</v>
@@ -29775,7 +29775,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1131" t="s">
         <v>8</v>
@@ -29853,7 +29853,7 @@
         <v>2</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1134" t="s">
         <v>8</v>
@@ -29879,7 +29879,7 @@
         <v>2</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1135" t="s">
         <v>8</v>
@@ -30035,7 +30035,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.6225084066391</v>
+        <v>1.62250828742981</v>
       </c>
       <c r="H1141" t="s">
         <v>8</v>
@@ -30061,7 +30061,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1142" t="s">
         <v>8</v>
@@ -30087,7 +30087,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1143" t="s">
         <v>8</v>
@@ -30139,7 +30139,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1145" t="n">
-        <v>1.59688997268677</v>
+        <v>1.59688985347748</v>
       </c>
       <c r="H1145" t="s">
         <v>8</v>
@@ -30165,7 +30165,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G1146" t="n">
-        <v>1.59688997268677</v>
+        <v>1.59688985347748</v>
       </c>
       <c r="H1146" t="s">
         <v>8</v>
@@ -30217,7 +30217,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1148" t="s">
         <v>8</v>
@@ -30295,7 +30295,7 @@
         <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1151" t="s">
         <v>8</v>
@@ -30321,7 +30321,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1152" t="s">
         <v>8</v>
@@ -31153,7 +31153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1184" t="s">
         <v>8</v>
@@ -31231,7 +31231,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1187" t="s">
         <v>8</v>
@@ -31309,7 +31309,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1190" t="s">
         <v>8</v>
@@ -31335,7 +31335,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1191" t="s">
         <v>8</v>
@@ -31361,7 +31361,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1192" t="s">
         <v>8</v>
@@ -31387,7 +31387,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.06746244430542</v>
+        <v>2.06746220588684</v>
       </c>
       <c r="H1193" t="s">
         <v>8</v>
@@ -31413,7 +31413,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.99555063247681</v>
+        <v>1.99555051326752</v>
       </c>
       <c r="H1194" t="s">
         <v>8</v>
@@ -31439,7 +31439,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1195" t="s">
         <v>8</v>
@@ -31465,7 +31465,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1196" t="s">
         <v>8</v>
@@ -31491,7 +31491,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1197" t="s">
         <v>8</v>
@@ -31517,7 +31517,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1198" t="s">
         <v>8</v>
@@ -31543,7 +31543,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1199" t="s">
         <v>8</v>
@@ -31569,7 +31569,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1200" t="s">
         <v>8</v>
@@ -31595,7 +31595,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1201" t="s">
         <v>8</v>
@@ -31621,7 +31621,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1202" t="s">
         <v>8</v>
@@ -31647,7 +31647,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1203" t="s">
         <v>8</v>
@@ -31699,7 +31699,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1205" t="s">
         <v>8</v>
@@ -31725,7 +31725,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1206" t="s">
         <v>8</v>
@@ -31751,7 +31751,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1207" t="s">
         <v>8</v>
@@ -31777,7 +31777,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1208" t="s">
         <v>8</v>
@@ -32297,7 +32297,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1228" t="s">
         <v>8</v>
@@ -32323,7 +32323,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1229" t="s">
         <v>8</v>
@@ -32427,7 +32427,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1233" t="s">
         <v>8</v>
@@ -32453,7 +32453,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1234" t="s">
         <v>8</v>
@@ -32661,7 +32661,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1242" t="s">
         <v>8</v>
@@ -32713,7 +32713,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1244" t="s">
         <v>8</v>
@@ -32817,7 +32817,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1248" t="s">
         <v>8</v>
@@ -32999,7 +32999,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1255" t="s">
         <v>8</v>
@@ -33025,7 +33025,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1256" t="s">
         <v>8</v>
@@ -33077,7 +33077,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1258" t="s">
         <v>8</v>
@@ -33155,7 +33155,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1261" t="s">
         <v>8</v>
@@ -33207,7 +33207,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1263" t="s">
         <v>8</v>
@@ -33571,7 +33571,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1277" t="s">
         <v>8</v>
@@ -33597,7 +33597,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1278" t="s">
         <v>8</v>
@@ -33675,7 +33675,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1281" t="s">
         <v>8</v>
@@ -33727,7 +33727,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1283" t="s">
         <v>8</v>
@@ -33753,7 +33753,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1284" t="s">
         <v>8</v>
@@ -33909,7 +33909,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1290" t="s">
         <v>8</v>
@@ -33961,7 +33961,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1292" t="s">
         <v>8</v>
@@ -33987,7 +33987,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1293" t="s">
         <v>8</v>
@@ -34013,7 +34013,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1294" t="s">
         <v>8</v>
@@ -34065,7 +34065,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1296" t="s">
         <v>8</v>
@@ -34091,7 +34091,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1297" t="s">
         <v>8</v>
@@ -34143,7 +34143,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1299" t="s">
         <v>8</v>
@@ -34169,7 +34169,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1300" t="s">
         <v>8</v>
@@ -34195,7 +34195,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1301" t="s">
         <v>8</v>
@@ -34221,7 +34221,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1302" t="s">
         <v>8</v>
@@ -34429,7 +34429,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1310" t="s">
         <v>8</v>
@@ -35209,7 +35209,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1340" t="s">
         <v>8</v>
@@ -35235,7 +35235,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1341" t="s">
         <v>8</v>
@@ -35261,7 +35261,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1342" t="s">
         <v>8</v>
@@ -35287,7 +35287,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1343" t="s">
         <v>8</v>
@@ -35313,7 +35313,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1344" t="s">
         <v>8</v>
@@ -35365,7 +35365,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1346" t="s">
         <v>8</v>
@@ -35391,7 +35391,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1347" t="s">
         <v>8</v>
@@ -35911,7 +35911,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1367" t="s">
         <v>8</v>
@@ -35937,7 +35937,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1368" t="s">
         <v>8</v>
@@ -35963,7 +35963,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1369" t="s">
         <v>8</v>
@@ -35989,7 +35989,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1370" t="s">
         <v>8</v>
@@ -36015,7 +36015,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1371" t="s">
         <v>8</v>
@@ -36119,7 +36119,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1375" t="s">
         <v>8</v>
@@ -36145,7 +36145,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1376" t="s">
         <v>8</v>
@@ -36223,7 +36223,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1379" t="s">
         <v>8</v>
@@ -36249,7 +36249,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.03150629997253</v>
+        <v>2.03150653839111</v>
       </c>
       <c r="H1380" t="s">
         <v>8</v>
@@ -36275,7 +36275,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1381" t="s">
         <v>8</v>
@@ -36301,7 +36301,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1382" t="s">
         <v>8</v>
@@ -36327,7 +36327,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1383" t="s">
         <v>8</v>
@@ -36353,7 +36353,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1384" t="s">
         <v>8</v>
@@ -36405,7 +36405,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1386" t="s">
         <v>8</v>
@@ -36431,7 +36431,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1387" t="s">
         <v>8</v>
@@ -36457,7 +36457,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1388" t="s">
         <v>8</v>
@@ -36483,7 +36483,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1389" t="s">
         <v>8</v>
@@ -36509,7 +36509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1390" t="s">
         <v>8</v>
@@ -36535,7 +36535,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1391" t="s">
         <v>8</v>
@@ -36561,7 +36561,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.03150629997253</v>
+        <v>2.03150653839111</v>
       </c>
       <c r="H1392" t="s">
         <v>8</v>
@@ -36587,7 +36587,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.01352858543396</v>
+        <v>2.01352834701538</v>
       </c>
       <c r="H1393" t="s">
         <v>8</v>
@@ -36613,7 +36613,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.01352858543396</v>
+        <v>2.01352834701538</v>
       </c>
       <c r="H1394" t="s">
         <v>8</v>
@@ -36639,7 +36639,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1395" t="s">
         <v>8</v>
@@ -36665,7 +36665,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1396" t="s">
         <v>8</v>
@@ -36717,7 +36717,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1398" t="s">
         <v>8</v>
@@ -36769,7 +36769,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1400" t="s">
         <v>8</v>
@@ -36821,7 +36821,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1402" t="s">
         <v>8</v>
@@ -46444,6 +46444,32 @@
         <v>3.09999990463257</v>
       </c>
       <c r="H1772" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1773">
+      <c r="A1773" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1773" t="n">
+        <v>8250</v>
+      </c>
+      <c r="C1773" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D1773" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E1773" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F1773" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G1773" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H1773" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -485,7 +485,7 @@
         <v>3.50550007820129</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80716872215271</v>
+        <v>2.80716824531555</v>
       </c>
       <c r="H4" t="n">
         <v>86250</v>
@@ -717,7 +717,7 @@
         <v>3.36050009727478</v>
       </c>
       <c r="G12" t="n">
-        <v>2.69105410575867</v>
+        <v>2.69105386734009</v>
       </c>
       <c r="H12" t="n">
         <v>1500</v>
@@ -746,7 +746,7 @@
         <v>3.36450004577637</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6942572593689</v>
+        <v>2.69425702095032</v>
       </c>
       <c r="H13" t="n">
         <v>14250</v>
@@ -804,7 +804,7 @@
         <v>3.37150001525879</v>
       </c>
       <c r="G15" t="n">
-        <v>2.69986295700073</v>
+        <v>2.69986271858215</v>
       </c>
       <c r="H15" t="n">
         <v>21750</v>
@@ -833,7 +833,7 @@
         <v>3.43449997901917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7503125667572</v>
+        <v>2.75031232833862</v>
       </c>
       <c r="H16" t="n">
         <v>44250</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.32327795028687</v>
+        <v>3.32327771186829</v>
       </c>
       <c r="H17" t="n">
         <v>604500</v>
@@ -891,7 +891,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558530807495</v>
+        <v>3.63558578491211</v>
       </c>
       <c r="H18" t="n">
         <v>196500</v>
@@ -920,7 +920,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.96390914916992</v>
+        <v>3.96390891075134</v>
       </c>
       <c r="H19" t="n">
         <v>402000</v>
@@ -949,7 +949,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578300476074</v>
+        <v>3.83578276634216</v>
       </c>
       <c r="H20" t="n">
         <v>495750</v>
@@ -978,7 +978,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G21" t="n">
-        <v>3.60515570640564</v>
+        <v>3.60515546798706</v>
       </c>
       <c r="H21" t="n">
         <v>81000</v>
@@ -1036,7 +1036,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51226401329041</v>
+        <v>3.51226377487183</v>
       </c>
       <c r="H23" t="n">
         <v>94500</v>
@@ -1094,7 +1094,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.49144339561462</v>
+        <v>3.4914436340332</v>
       </c>
       <c r="H25" t="n">
         <v>20250</v>
@@ -1123,7 +1123,7 @@
         <v>4.38350009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>3.51026225090027</v>
+        <v>3.51026201248169</v>
       </c>
       <c r="H26" t="n">
         <v>24750</v>
@@ -1181,7 +1181,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329724311829</v>
+        <v>3.34329748153687</v>
       </c>
       <c r="H28" t="n">
         <v>18000</v>
@@ -1239,7 +1239,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128547668457</v>
+        <v>3.33128523826599</v>
       </c>
       <c r="H30" t="n">
         <v>9000</v>
@@ -1268,7 +1268,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048439025879</v>
+        <v>3.33048462867737</v>
       </c>
       <c r="H31" t="n">
         <v>6750</v>
@@ -1297,7 +1297,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.28724217414856</v>
+        <v>3.28724193572998</v>
       </c>
       <c r="H32" t="n">
         <v>2250</v>
@@ -1326,7 +1326,7 @@
         <v>3.625</v>
       </c>
       <c r="G33" t="n">
-        <v>2.9028627872467</v>
+        <v>2.90286302566528</v>
       </c>
       <c r="H33" t="n">
         <v>146250</v>
@@ -1355,7 +1355,7 @@
         <v>3.8050000667572</v>
       </c>
       <c r="G34" t="n">
-        <v>3.04700517654419</v>
+        <v>3.04700493812561</v>
       </c>
       <c r="H34" t="n">
         <v>91500</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H38" t="n">
         <v>27000</v>
@@ -1529,7 +1529,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H40" t="n">
         <v>3000</v>
@@ -1558,7 +1558,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H41" t="n">
         <v>9750</v>
@@ -1587,7 +1587,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.625</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9028627872467</v>
+        <v>2.90286302566528</v>
       </c>
       <c r="H47" t="n">
         <v>12000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1819,7 +1819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H50" t="n">
         <v>4500</v>
@@ -1848,7 +1848,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H51" t="n">
         <v>750</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08304071426392</v>
+        <v>3.08304047584534</v>
       </c>
       <c r="H52" t="n">
         <v>29250</v>
@@ -1906,7 +1906,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H53" t="n">
         <v>9000</v>
@@ -1935,7 +1935,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.07903695106506</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H54" t="n">
         <v>13500</v>
@@ -1964,7 +1964,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H55" t="n">
         <v>2250</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507225036621</v>
+        <v>3.11507248878479</v>
       </c>
       <c r="H56" t="n">
         <v>18750</v>
@@ -2022,7 +2022,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702494621277</v>
+        <v>3.06702470779419</v>
       </c>
       <c r="H57" t="n">
         <v>18750</v>
@@ -2080,7 +2080,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H59" t="n">
         <v>12000</v>
@@ -2138,7 +2138,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507225036621</v>
+        <v>3.11507248878479</v>
       </c>
       <c r="H61" t="n">
         <v>5250</v>
@@ -2167,7 +2167,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505295753479</v>
+        <v>3.09505248069763</v>
       </c>
       <c r="H62" t="n">
         <v>4500</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670886993408</v>
+        <v>2.74670910835266</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2515,7 +2515,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H74" t="n">
         <v>15000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>2.83879971504211</v>
+        <v>2.83879995346069</v>
       </c>
       <c r="H75" t="n">
         <v>12750</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H76" t="n">
         <v>24000</v>
@@ -2602,7 +2602,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>3.07903695106506</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H77" t="n">
         <v>26250</v>
@@ -2660,7 +2660,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H79" t="n">
         <v>7500</v>
@@ -2718,7 +2718,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2863,7 +2863,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866180419922</v>
+        <v>2.69866132736206</v>
       </c>
       <c r="H86" t="n">
         <v>7500</v>
@@ -2892,7 +2892,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.59055471420288</v>
+        <v>2.59055495262146</v>
       </c>
       <c r="H87" t="n">
         <v>14250</v>
@@ -2921,7 +2921,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H88" t="n">
         <v>3750</v>
@@ -3008,7 +3008,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H91" t="n">
         <v>27750</v>
@@ -3037,7 +3037,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H92" t="n">
         <v>16500</v>
@@ -3066,7 +3066,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H93" t="n">
         <v>9750</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185584545135</v>
+        <v>1.88185608386993</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3153,7 +3153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H96" t="n">
         <v>14250</v>
@@ -3182,7 +3182,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.66163897514343</v>
+        <v>1.66163885593414</v>
       </c>
       <c r="H97" t="n">
         <v>2250</v>
@@ -3211,7 +3211,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66163897514343</v>
+        <v>1.66163885593414</v>
       </c>
       <c r="H98" t="n">
         <v>750</v>
@@ -3240,7 +3240,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556389808655</v>
+        <v>1.58556377887726</v>
       </c>
       <c r="H99" t="n">
         <v>14250</v>
@@ -3269,7 +3269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161884784698</v>
+        <v>1.64161896705627</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3298,7 +3298,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71369004249573</v>
+        <v>1.7136904001236</v>
       </c>
       <c r="H101" t="n">
         <v>6750</v>
@@ -3327,7 +3327,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.67765462398529</v>
+        <v>1.677654504776</v>
       </c>
       <c r="H102" t="n">
         <v>11250</v>
@@ -3356,7 +3356,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H103" t="n">
         <v>12000</v>
@@ -3443,7 +3443,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G106" t="n">
-        <v>1.71369004249573</v>
+        <v>1.7136904001236</v>
       </c>
       <c r="H106" t="n">
         <v>2250</v>
@@ -3472,7 +3472,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H107" t="n">
         <v>750</v>
@@ -3501,7 +3501,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8978716135025</v>
+        <v>1.89787173271179</v>
       </c>
       <c r="H108" t="n">
         <v>15750</v>
@@ -3530,7 +3530,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205318450928</v>
+        <v>2.08205342292786</v>
       </c>
       <c r="H109" t="n">
         <v>8250</v>
@@ -3646,7 +3646,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H113" t="n">
         <v>28500</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3791,7 +3791,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H118" t="n">
         <v>6000</v>
@@ -3820,7 +3820,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475665092468</v>
       </c>
       <c r="H119" t="n">
         <v>8250</v>
@@ -3849,7 +3849,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664956092834</v>
+        <v>2.68664979934692</v>
       </c>
       <c r="H120" t="n">
         <v>11250</v>
@@ -3936,7 +3936,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>2.75071263313293</v>
+        <v>2.75071310997009</v>
       </c>
       <c r="H123" t="n">
         <v>5250</v>
@@ -3994,7 +3994,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H125" t="n">
         <v>4500</v>
@@ -4052,7 +4052,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475665092468</v>
       </c>
       <c r="H127" t="n">
         <v>2250</v>
@@ -4139,7 +4139,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H130" t="n">
         <v>3750</v>
@@ -4168,7 +4168,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H131" t="n">
         <v>750</v>
@@ -4226,7 +4226,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H133" t="n">
         <v>5250</v>
@@ -4255,7 +4255,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H134" t="n">
         <v>750</v>
@@ -4284,7 +4284,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H135" t="n">
         <v>750</v>
@@ -4313,7 +4313,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H137" t="n">
         <v>750</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856271743774</v>
+        <v>2.59856295585632</v>
       </c>
       <c r="H139" t="n">
         <v>1500</v>
@@ -4545,7 +4545,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H144" t="n">
         <v>1500</v>
@@ -4574,7 +4574,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H145" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4777,7 +4777,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G152" t="n">
-        <v>2.71067357063293</v>
+        <v>2.71067333221436</v>
       </c>
       <c r="H152" t="n">
         <v>750</v>
@@ -4835,7 +4835,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.63459849357605</v>
+        <v>2.63459825515747</v>
       </c>
       <c r="H154" t="n">
         <v>9000</v>
@@ -4864,7 +4864,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H155" t="n">
         <v>8250</v>
@@ -4893,7 +4893,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G156" t="n">
-        <v>2.5625274181366</v>
+        <v>2.56252765655518</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H161" t="n">
         <v>14250</v>
@@ -5096,7 +5096,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>2.50647187232971</v>
+        <v>2.50647211074829</v>
       </c>
       <c r="H163" t="n">
         <v>6750</v>
@@ -5125,7 +5125,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G164" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H164" t="n">
         <v>750</v>
@@ -5154,7 +5154,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H166" t="n">
         <v>6750</v>
@@ -5212,7 +5212,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H167" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H171" t="n">
         <v>3000</v>
@@ -5357,7 +5357,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H173" t="n">
         <v>2250</v>
@@ -5415,7 +5415,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G176" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H177" t="n">
         <v>3750</v>
@@ -5531,7 +5531,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5821,7 +5821,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H188" t="n">
         <v>750</v>
@@ -5850,7 +5850,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029818534851</v>
       </c>
       <c r="H189" t="n">
         <v>3750</v>
@@ -5879,7 +5879,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029818534851</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G191" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H191" t="n">
         <v>1500</v>
@@ -6082,7 +6082,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H197" t="n">
         <v>139500</v>
@@ -6111,7 +6111,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.05100917816162</v>
+        <v>3.05100893974304</v>
       </c>
       <c r="H198" t="n">
         <v>203250</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H204" t="n">
         <v>12000</v>
@@ -6430,7 +6430,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H209" t="n">
         <v>2250</v>
@@ -6459,7 +6459,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H210" t="n">
         <v>3750</v>
@@ -6488,7 +6488,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H211" t="n">
         <v>2250</v>
@@ -6517,7 +6517,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H212" t="n">
         <v>2250</v>
@@ -6633,7 +6633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830642700195</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6691,7 +6691,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029818534851</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6836,7 +6836,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H223" t="n">
         <v>5250</v>
@@ -6894,7 +6894,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H225" t="n">
         <v>5250</v>
@@ -6981,7 +6981,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H228" t="n">
         <v>15750</v>
@@ -7010,7 +7010,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>2.35031771659851</v>
+        <v>2.35031795501709</v>
       </c>
       <c r="H229" t="n">
         <v>18750</v>
@@ -7039,7 +7039,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H230" t="n">
         <v>750</v>
@@ -7126,7 +7126,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029818534851</v>
       </c>
       <c r="H233" t="n">
         <v>3750</v>
@@ -7155,7 +7155,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G234" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H234" t="n">
         <v>2250</v>
@@ -7213,7 +7213,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29025840759277</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H236" t="n">
         <v>2250</v>
@@ -7242,7 +7242,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.29025840759277</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H238" t="n">
         <v>1500</v>
@@ -7300,7 +7300,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G241" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G244" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H244" t="n">
         <v>4500</v>
@@ -7619,7 +7619,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G250" t="n">
-        <v>2.39836525917053</v>
+        <v>2.39836502075195</v>
       </c>
       <c r="H250" t="n">
         <v>3000</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H253" t="n">
         <v>1500</v>
@@ -7735,7 +7735,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G254" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H254" t="n">
         <v>5250</v>
@@ -7822,7 +7822,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H257" t="n">
         <v>1500</v>
@@ -7851,7 +7851,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H258" t="n">
         <v>750</v>
@@ -7880,7 +7880,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7909,7 +7909,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G260" t="n">
-        <v>2.21418380737305</v>
+        <v>2.21418356895447</v>
       </c>
       <c r="H260" t="n">
         <v>3000</v>
@@ -7938,7 +7938,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21418380737305</v>
+        <v>2.21418356895447</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H262" t="n">
         <v>2250</v>
@@ -7996,7 +7996,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H263" t="n">
         <v>750</v>
@@ -8025,7 +8025,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.1861560344696</v>
+        <v>2.18615627288818</v>
       </c>
       <c r="H265" t="n">
         <v>1500</v>
@@ -8112,7 +8112,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820757865906</v>
+        <v>2.23820734024048</v>
       </c>
       <c r="H267" t="n">
         <v>2250</v>
@@ -8141,7 +8141,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8170,7 +8170,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8199,7 +8199,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H270" t="n">
         <v>750</v>
@@ -8257,7 +8257,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830642700195</v>
       </c>
       <c r="H272" t="n">
         <v>2250</v>
@@ -8286,7 +8286,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830642700195</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8663,7 +8663,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G286" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H286" t="n">
         <v>2250</v>
@@ -8692,7 +8692,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G287" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H287" t="n">
         <v>750</v>
@@ -8721,7 +8721,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H289" t="n">
         <v>750</v>
@@ -8779,7 +8779,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H290" t="n">
         <v>750</v>
@@ -8808,7 +8808,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8895,7 +8895,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H294" t="n">
         <v>750</v>
@@ -8924,7 +8924,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H295" t="n">
         <v>6000</v>
@@ -8953,7 +8953,7 @@
         <v>2.92499995231628</v>
       </c>
       <c r="G296" t="n">
-        <v>2.34231019020081</v>
+        <v>2.34230995178223</v>
       </c>
       <c r="H296" t="n">
         <v>1500</v>
@@ -8982,7 +8982,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H297" t="n">
         <v>2250</v>
@@ -9011,7 +9011,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H298" t="n">
         <v>2250</v>
@@ -9040,7 +9040,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H299" t="n">
         <v>3000</v>
@@ -9069,7 +9069,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H300" t="n">
         <v>750</v>
@@ -9127,7 +9127,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H302" t="n">
         <v>3000</v>
@@ -9156,7 +9156,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H305" t="n">
         <v>148500</v>
@@ -9243,7 +9243,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>2.60657095909119</v>
+        <v>2.60657072067261</v>
       </c>
       <c r="H306" t="n">
         <v>45000</v>
@@ -9272,7 +9272,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H307" t="n">
         <v>32250</v>
@@ -9330,7 +9330,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039679527283</v>
+        <v>2.43039703369141</v>
       </c>
       <c r="H309" t="n">
         <v>17250</v>
@@ -9417,7 +9417,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045634269714</v>
+        <v>2.49045610427856</v>
       </c>
       <c r="H312" t="n">
         <v>5250</v>
@@ -9446,7 +9446,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838479042053</v>
       </c>
       <c r="H313" t="n">
         <v>5250</v>
@@ -9475,7 +9475,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H314" t="n">
         <v>1500</v>
@@ -9504,7 +9504,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>2.36633348464966</v>
+        <v>2.36633372306824</v>
       </c>
       <c r="H316" t="n">
         <v>3750</v>
@@ -9620,7 +9620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830642700195</v>
       </c>
       <c r="H319" t="n">
         <v>3750</v>
@@ -9823,7 +9823,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838479042053</v>
       </c>
       <c r="H326" t="n">
         <v>6750</v>
@@ -9968,7 +9968,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G331" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H331" t="n">
         <v>7500</v>
@@ -10055,7 +10055,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H334" t="n">
         <v>2250</v>
@@ -10142,7 +10142,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.43840503692627</v>
+        <v>2.43840479850769</v>
       </c>
       <c r="H337" t="n">
         <v>3750</v>
@@ -10171,7 +10171,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H338" t="n">
         <v>1500</v>
@@ -10200,7 +10200,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H339" t="n">
         <v>7500</v>
@@ -10229,7 +10229,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G340" t="n">
-        <v>2.50647187232971</v>
+        <v>2.50647211074829</v>
       </c>
       <c r="H340" t="n">
         <v>29250</v>
@@ -10258,7 +10258,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H341" t="n">
         <v>20250</v>
@@ -10374,7 +10374,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>2.5505154132843</v>
+        <v>2.55051517486572</v>
       </c>
       <c r="H345" t="n">
         <v>26250</v>
@@ -10403,7 +10403,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H346" t="n">
         <v>54000</v>
@@ -10432,7 +10432,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G347" t="n">
-        <v>2.66262602806091</v>
+        <v>2.66262626647949</v>
       </c>
       <c r="H347" t="n">
         <v>31500</v>
@@ -10461,7 +10461,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>2.66262602806091</v>
+        <v>2.66262626647949</v>
       </c>
       <c r="H348" t="n">
         <v>2250</v>
@@ -10490,7 +10490,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H349" t="n">
         <v>3750</v>
@@ -10519,7 +10519,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>2.66262602806091</v>
+        <v>2.66262626647949</v>
       </c>
       <c r="H350" t="n">
         <v>6000</v>
@@ -10635,7 +10635,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G354" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H354" t="n">
         <v>4500</v>
@@ -10693,7 +10693,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H356" t="n">
         <v>5250</v>
@@ -10751,7 +10751,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266556739807</v>
+        <v>2.70266532897949</v>
       </c>
       <c r="H358" t="n">
         <v>13500</v>
@@ -10780,7 +10780,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H359" t="n">
         <v>10500</v>
@@ -10867,7 +10867,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H362" t="n">
         <v>15750</v>
@@ -10896,7 +10896,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H363" t="n">
         <v>1500</v>
@@ -10925,7 +10925,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H364" t="n">
         <v>3000</v>
@@ -10954,7 +10954,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H365" t="n">
         <v>5250</v>
@@ -11012,7 +11012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H367" t="n">
         <v>172500</v>
@@ -11041,7 +11041,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>3.26722192764282</v>
+        <v>3.2672221660614</v>
       </c>
       <c r="H368" t="n">
         <v>210750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11186,7 +11186,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H373" t="n">
         <v>11250</v>
@@ -11215,7 +11215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H374" t="n">
         <v>20250</v>
@@ -11244,7 +11244,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H375" t="n">
         <v>3750</v>
@@ -11273,7 +11273,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H376" t="n">
         <v>39000</v>
@@ -11360,7 +11360,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H379" t="n">
         <v>24000</v>
@@ -11389,7 +11389,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11476,7 +11476,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G383" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H383" t="n">
         <v>25500</v>
@@ -11592,7 +11592,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H387" t="n">
         <v>3750</v>
@@ -11621,7 +11621,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H388" t="n">
         <v>6000</v>
@@ -11650,7 +11650,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G389" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H389" t="n">
         <v>12750</v>
@@ -11679,7 +11679,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G390" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11708,7 +11708,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G391" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11737,7 +11737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H392" t="n">
         <v>5250</v>
@@ -11766,7 +11766,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.1711277961731</v>
+        <v>3.17112755775452</v>
       </c>
       <c r="H393" t="n">
         <v>23250</v>
@@ -11911,7 +11911,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11969,7 +11969,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G400" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H400" t="n">
         <v>750</v>
@@ -12056,7 +12056,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.26722192764282</v>
+        <v>3.2672221660614</v>
       </c>
       <c r="H403" t="n">
         <v>38250</v>
@@ -12114,7 +12114,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>3.42738008499146</v>
+        <v>3.42738080024719</v>
       </c>
       <c r="H405" t="n">
         <v>54750</v>
@@ -12201,7 +12201,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G408" t="n">
-        <v>3.34730076789856</v>
+        <v>3.34730100631714</v>
       </c>
       <c r="H408" t="n">
         <v>10500</v>
@@ -12404,7 +12404,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H415" t="n">
         <v>2250</v>
@@ -12839,7 +12839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H430" t="n">
         <v>7500</v>
@@ -12868,7 +12868,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H431" t="n">
         <v>9000</v>
@@ -12897,7 +12897,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H432" t="n">
         <v>4500</v>
@@ -12926,7 +12926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H433" t="n">
         <v>1500</v>
@@ -12955,7 +12955,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H434" t="n">
         <v>750</v>
@@ -12984,7 +12984,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G435" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H436" t="n">
         <v>4500</v>
@@ -13042,7 +13042,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H437" t="n">
         <v>750</v>
@@ -13071,7 +13071,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13100,7 +13100,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H439" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G440" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H442" t="n">
         <v>750</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13419,7 +13419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H450" t="n">
         <v>1500</v>
@@ -13448,7 +13448,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G451" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13477,7 +13477,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>3.04300093650818</v>
+        <v>3.0430006980896</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H453" t="n">
         <v>1500</v>
@@ -13564,7 +13564,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H455" t="n">
         <v>2250</v>
@@ -13593,7 +13593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G456" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H456" t="n">
         <v>3750</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H458" t="n">
         <v>3750</v>
@@ -13709,7 +13709,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G460" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H460" t="n">
         <v>1500</v>
@@ -13738,7 +13738,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H461" t="n">
         <v>1500</v>
@@ -13767,7 +13767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H463" t="n">
         <v>3000</v>
@@ -13825,7 +13825,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H464" t="n">
         <v>4500</v>
@@ -13854,7 +13854,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H466" t="n">
         <v>9750</v>
@@ -13912,7 +13912,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H467" t="n">
         <v>750</v>
@@ -13941,7 +13941,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G468" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H469" t="n">
         <v>1500</v>
@@ -13999,7 +13999,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H470" t="n">
         <v>2250</v>
@@ -14028,7 +14028,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H471" t="n">
         <v>6750</v>
@@ -14057,7 +14057,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H472" t="n">
         <v>750</v>
@@ -14086,7 +14086,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>3.07503247261047</v>
+        <v>3.07503271102905</v>
       </c>
       <c r="H473" t="n">
         <v>12750</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14202,7 +14202,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H477" t="n">
         <v>6000</v>
@@ -14260,7 +14260,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H479" t="n">
         <v>6000</v>
@@ -14289,7 +14289,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G480" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H480" t="n">
         <v>3750</v>
@@ -14318,7 +14318,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G481" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H481" t="n">
         <v>750</v>
@@ -14347,7 +14347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H482" t="n">
         <v>750</v>
@@ -14405,7 +14405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H484" t="n">
         <v>2250</v>
@@ -14434,7 +14434,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H485" t="n">
         <v>750</v>
@@ -14463,7 +14463,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G487" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H487" t="n">
         <v>6000</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14579,7 +14579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G490" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H490" t="n">
         <v>750</v>
@@ -14608,7 +14608,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H492" t="n">
         <v>750</v>
@@ -14695,7 +14695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H494" t="n">
         <v>2250</v>
@@ -14869,7 +14869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H500" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H503" t="n">
         <v>5250</v>
@@ -14985,7 +14985,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H504" t="n">
         <v>750</v>
@@ -15043,7 +15043,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H506" t="n">
         <v>8250</v>
@@ -15072,7 +15072,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H508" t="n">
         <v>4500</v>
@@ -15275,7 +15275,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H514" t="n">
         <v>5250</v>
@@ -15304,7 +15304,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H515" t="n">
         <v>6750</v>
@@ -15391,7 +15391,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H518" t="n">
         <v>12750</v>
@@ -15420,7 +15420,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H519" t="n">
         <v>3750</v>
@@ -15449,7 +15449,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15623,7 +15623,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59455871582031</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H526" t="n">
         <v>17250</v>
@@ -15652,7 +15652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15681,7 +15681,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846386909485</v>
+        <v>2.49846410751343</v>
       </c>
       <c r="H528" t="n">
         <v>5250</v>
@@ -15710,7 +15710,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G529" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838479042053</v>
       </c>
       <c r="H529" t="n">
         <v>9000</v>
@@ -15768,7 +15768,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H531" t="n">
         <v>3000</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15826,7 +15826,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H533" t="n">
         <v>15000</v>
@@ -15855,7 +15855,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H534" t="n">
         <v>8250</v>
@@ -15884,7 +15884,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H535" t="n">
         <v>2250</v>
@@ -16000,7 +16000,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H539" t="n">
         <v>24750</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16087,7 +16087,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H542" t="n">
         <v>6750</v>
@@ -16116,7 +16116,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H543" t="n">
         <v>2250</v>
@@ -16145,7 +16145,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830642700195</v>
       </c>
       <c r="H544" t="n">
         <v>750</v>
@@ -16174,7 +16174,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H545" t="n">
         <v>7500</v>
@@ -16203,7 +16203,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H546" t="n">
         <v>8250</v>
@@ -16232,7 +16232,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H547" t="n">
         <v>6750</v>
@@ -16261,7 +16261,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>2.29025840759277</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H548" t="n">
         <v>6750</v>
@@ -16290,7 +16290,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H549" t="n">
         <v>5250</v>
@@ -16319,7 +16319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16348,7 +16348,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H551" t="n">
         <v>102750</v>
@@ -16377,7 +16377,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H552" t="n">
         <v>3750</v>
@@ -16406,7 +16406,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H553" t="n">
         <v>3000</v>
@@ -16493,7 +16493,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830642700195</v>
       </c>
       <c r="H556" t="n">
         <v>3750</v>
@@ -16522,7 +16522,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H557" t="n">
         <v>5250</v>
@@ -16551,7 +16551,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H558" t="n">
         <v>6000</v>
@@ -16580,7 +16580,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16638,7 +16638,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H561" t="n">
         <v>21750</v>
@@ -16667,7 +16667,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G562" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H562" t="n">
         <v>2250</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16725,7 +16725,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838479042053</v>
       </c>
       <c r="H564" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.35432171821594</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H567" t="n">
         <v>13500</v>
@@ -16928,7 +16928,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H571" t="n">
         <v>7500</v>
@@ -16957,7 +16957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H572" t="n">
         <v>3000</v>
@@ -17073,7 +17073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H576" t="n">
         <v>3000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H577" t="n">
         <v>12750</v>
@@ -17131,7 +17131,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H579" t="n">
         <v>6000</v>
@@ -17189,7 +17189,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H580" t="n">
         <v>3750</v>
@@ -17218,7 +17218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213250160217</v>
+        <v>2.16213274002075</v>
       </c>
       <c r="H581" t="n">
         <v>15750</v>
@@ -17247,7 +17247,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H582" t="n">
         <v>18000</v>
@@ -17276,7 +17276,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G583" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H583" t="n">
         <v>15750</v>
@@ -17305,7 +17305,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H584" t="n">
         <v>4500</v>
@@ -17363,7 +17363,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400611877441</v>
       </c>
       <c r="H586" t="n">
         <v>6000</v>
@@ -17421,7 +17421,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.1781485080719</v>
+        <v>2.17814826965332</v>
       </c>
       <c r="H588" t="n">
         <v>8250</v>
@@ -17450,7 +17450,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G589" t="n">
-        <v>2.1301007270813</v>
+        <v>2.13010096549988</v>
       </c>
       <c r="H589" t="n">
         <v>3000</v>
@@ -17537,7 +17537,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400611877441</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>2.00197434425354</v>
+        <v>2.00197410583496</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986361026764</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17740,7 +17740,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>1.71369004249573</v>
+        <v>1.7136904001236</v>
       </c>
       <c r="H599" t="n">
         <v>12000</v>
@@ -17798,7 +17798,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G601" t="n">
-        <v>1.49747681617737</v>
+        <v>1.49747693538666</v>
       </c>
       <c r="H601" t="n">
         <v>16500</v>
@@ -17827,7 +17827,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G602" t="n">
-        <v>1.53751623630524</v>
+        <v>1.53751635551453</v>
       </c>
       <c r="H602" t="n">
         <v>10500</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.63361096382141</v>
+        <v>1.6336110830307</v>
       </c>
       <c r="H604" t="n">
         <v>1500</v>
@@ -17914,7 +17914,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H605" t="n">
         <v>3750</v>
@@ -17943,7 +17943,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767415523529</v>
       </c>
       <c r="H606" t="n">
         <v>14250</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767415523529</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H608" t="n">
         <v>11250</v>
@@ -18059,7 +18059,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H610" t="n">
         <v>5250</v>
@@ -18088,7 +18088,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>1.71369004249573</v>
+        <v>1.7136904001236</v>
       </c>
       <c r="H611" t="n">
         <v>4500</v>
@@ -18117,7 +18117,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18175,7 +18175,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767415523529</v>
       </c>
       <c r="H614" t="n">
         <v>4500</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767415523529</v>
       </c>
       <c r="H615" t="n">
         <v>5250</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986361026764</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18378,7 +18378,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.9539270401001</v>
+        <v>1.95392715930939</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18436,7 +18436,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962673187256</v>
+        <v>1.64962697029114</v>
       </c>
       <c r="H623" t="n">
         <v>186750</v>
@@ -18465,7 +18465,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H624" t="n">
         <v>174750</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H625" t="n">
         <v>23250</v>
@@ -18523,7 +18523,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.72169804573059</v>
+        <v>1.7216979265213</v>
       </c>
       <c r="H626" t="n">
         <v>40500</v>
@@ -18552,7 +18552,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H627" t="n">
         <v>3750</v>
@@ -18581,7 +18581,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.72169804573059</v>
+        <v>1.7216979265213</v>
       </c>
       <c r="H631" t="n">
         <v>5250</v>
@@ -18697,7 +18697,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H632" t="n">
         <v>2250</v>
@@ -18726,7 +18726,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H633" t="n">
         <v>750</v>
@@ -18755,7 +18755,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H635" t="n">
         <v>5250</v>
@@ -18813,7 +18813,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71369004249573</v>
+        <v>1.7136904001236</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H637" t="n">
         <v>7500</v>
@@ -18871,7 +18871,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H638" t="n">
         <v>18000</v>
@@ -18900,7 +18900,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H639" t="n">
         <v>15750</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779289245605</v>
       </c>
       <c r="H640" t="n">
         <v>17250</v>
@@ -18958,7 +18958,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779289245605</v>
       </c>
       <c r="H641" t="n">
         <v>167250</v>
@@ -18987,7 +18987,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75372970104218</v>
+        <v>1.7537294626236</v>
       </c>
       <c r="H642" t="n">
         <v>8250</v>
@@ -19074,7 +19074,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H645" t="n">
         <v>6000</v>
@@ -19132,7 +19132,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G647" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H647" t="n">
         <v>11250</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H648" t="n">
         <v>47250</v>
@@ -19190,7 +19190,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.850182056427</v>
+        <v>1.85018193721771</v>
       </c>
       <c r="H649" t="n">
         <v>5250</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H651" t="n">
         <v>33750</v>
@@ -19277,7 +19277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H652" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836851596832</v>
       </c>
       <c r="H653" t="n">
         <v>4500</v>
@@ -19364,7 +19364,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287528991699</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194239616394</v>
       </c>
       <c r="H658" t="n">
         <v>11250</v>
@@ -19509,7 +19509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194239616394</v>
       </c>
       <c r="H660" t="n">
         <v>12000</v>
@@ -19567,7 +19567,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474167346954</v>
       </c>
       <c r="H662" t="n">
         <v>7500</v>
@@ -19625,7 +19625,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G664" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H664" t="n">
         <v>6750</v>
@@ -19683,7 +19683,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H666" t="n">
         <v>4500</v>
@@ -19712,7 +19712,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287528991699</v>
       </c>
       <c r="H667" t="n">
         <v>5250</v>
@@ -19741,7 +19741,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287528991699</v>
       </c>
       <c r="H668" t="n">
         <v>10500</v>
@@ -19857,7 +19857,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H672" t="n">
         <v>2250</v>
@@ -19886,7 +19886,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H673" t="n">
         <v>3000</v>
@@ -19915,7 +19915,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H674" t="n">
         <v>750</v>
@@ -19944,7 +19944,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H675" t="n">
         <v>3750</v>
@@ -20060,7 +20060,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G679" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H679" t="n">
         <v>5250</v>
@@ -20147,7 +20147,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H682" t="n">
         <v>1500</v>
@@ -20205,7 +20205,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H684" t="n">
         <v>6000</v>
@@ -20292,7 +20292,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194239616394</v>
       </c>
       <c r="H687" t="n">
         <v>34500</v>
@@ -20524,7 +20524,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H695" t="n">
         <v>750</v>
@@ -20553,7 +20553,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G696" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H696" t="n">
         <v>1500</v>
@@ -20640,7 +20640,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H699" t="n">
         <v>1500</v>
@@ -20669,7 +20669,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G700" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G701" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H701" t="n">
         <v>750</v>
@@ -20785,7 +20785,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H704" t="n">
         <v>1500</v>
@@ -20843,7 +20843,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287528991699</v>
       </c>
       <c r="H706" t="n">
         <v>750</v>
@@ -20872,7 +20872,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H707" t="n">
         <v>2250</v>
@@ -20901,7 +20901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H710" t="n">
         <v>15000</v>
@@ -20988,7 +20988,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -21104,7 +21104,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287528991699</v>
       </c>
       <c r="H715" t="n">
         <v>3000</v>
@@ -21133,7 +21133,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G716" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H716" t="n">
         <v>17250</v>
@@ -21162,7 +21162,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H717" t="n">
         <v>7500</v>
@@ -21191,7 +21191,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H718" t="n">
         <v>2250</v>
@@ -21220,7 +21220,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21307,7 +21307,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G722" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H722" t="n">
         <v>1500</v>
@@ -21336,7 +21336,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G723" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H723" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H727" t="n">
         <v>3750</v>
@@ -21481,7 +21481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -21510,7 +21510,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>1.6455157995224</v>
+        <v>1.64551568031311</v>
       </c>
       <c r="H729" t="n">
         <v>3000</v>
@@ -21539,7 +21539,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G730" t="n">
-        <v>1.6291424036026</v>
+        <v>1.62914252281189</v>
       </c>
       <c r="H730" t="n">
         <v>2250</v>
@@ -21568,7 +21568,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63732922077179</v>
+        <v>1.63732898235321</v>
       </c>
       <c r="H731" t="n">
         <v>3000</v>
@@ -21655,7 +21655,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H734" t="n">
         <v>750</v>
@@ -21684,7 +21684,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H737" t="n">
         <v>2250</v>
@@ -21800,7 +21800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G739" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546247959137</v>
       </c>
       <c r="H739" t="n">
         <v>11250</v>
@@ -21945,7 +21945,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H744" t="n">
         <v>1500</v>
@@ -22003,7 +22003,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546247959137</v>
       </c>
       <c r="H746" t="n">
         <v>6000</v>
@@ -22061,7 +22061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G748" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546247959137</v>
       </c>
       <c r="H748" t="n">
         <v>10500</v>
@@ -22206,7 +22206,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22235,7 +22235,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359621524811</v>
+        <v>1.47359609603882</v>
       </c>
       <c r="H755" t="n">
         <v>6000</v>
@@ -22322,7 +22322,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546247959137</v>
       </c>
       <c r="H757" t="n">
         <v>79500</v>
@@ -22409,7 +22409,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>1.60458254814148</v>
+        <v>1.60458266735077</v>
       </c>
       <c r="H760" t="n">
         <v>3750</v>
@@ -22670,7 +22670,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G769" t="n">
-        <v>1.52271604537964</v>
+        <v>1.52271616458893</v>
       </c>
       <c r="H769" t="n">
         <v>3750</v>
@@ -22699,7 +22699,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G770" t="n">
-        <v>1.52271604537964</v>
+        <v>1.52271616458893</v>
       </c>
       <c r="H770" t="n">
         <v>3750</v>
@@ -22757,7 +22757,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H772" t="n">
         <v>2250</v>
@@ -22786,7 +22786,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.57183587551117</v>
+        <v>1.57183599472046</v>
       </c>
       <c r="H773" t="n">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G774" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546247959137</v>
       </c>
       <c r="H774" t="n">
         <v>2250</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.60458254814148</v>
+        <v>1.60458266735077</v>
       </c>
       <c r="H776" t="n">
         <v>28500</v>
@@ -22902,7 +22902,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.63732922077179</v>
+        <v>1.63732898235321</v>
       </c>
       <c r="H777" t="n">
         <v>16500</v>
@@ -22931,7 +22931,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.63732922077179</v>
+        <v>1.63732898235321</v>
       </c>
       <c r="H778" t="n">
         <v>3000</v>
@@ -22960,7 +22960,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194239616394</v>
       </c>
       <c r="H779" t="n">
         <v>21750</v>
@@ -22989,7 +22989,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H780" t="n">
         <v>60000</v>
@@ -23018,7 +23018,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H781" t="n">
         <v>11250</v>
@@ -23105,7 +23105,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H784" t="n">
         <v>2250</v>
@@ -23134,7 +23134,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H785" t="n">
         <v>750</v>
@@ -23163,7 +23163,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H786" t="n">
         <v>2250</v>
@@ -23192,7 +23192,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282208919525</v>
       </c>
       <c r="H787" t="n">
         <v>16500</v>
@@ -23250,7 +23250,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G789" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H789" t="n">
         <v>1500</v>
@@ -23308,7 +23308,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194239616394</v>
       </c>
       <c r="H791" t="n">
         <v>8250</v>
@@ -23337,7 +23337,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194215774536</v>
+        <v>1.75194239616394</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.8092485666275</v>
+        <v>1.80924880504608</v>
       </c>
       <c r="H793" t="n">
         <v>7500</v>
@@ -23511,7 +23511,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G798" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H798" t="n">
         <v>5250</v>
@@ -23569,7 +23569,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G800" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H800" t="n">
         <v>21750</v>
@@ -23598,7 +23598,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H801" t="n">
         <v>12750</v>
@@ -23656,7 +23656,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H804" t="n">
         <v>9750</v>
@@ -23772,7 +23772,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G807" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H807" t="n">
         <v>2250</v>
@@ -23801,7 +23801,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H808" t="n">
         <v>750</v>
@@ -23830,7 +23830,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G810" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23888,7 +23888,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G811" t="n">
-        <v>1.76831543445587</v>
+        <v>1.76831555366516</v>
       </c>
       <c r="H811" t="n">
         <v>10500</v>
@@ -23917,7 +23917,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G812" t="n">
-        <v>1.72738206386566</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H812" t="n">
         <v>3000</v>
@@ -23946,7 +23946,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H813" t="n">
         <v>5250</v>
@@ -24004,7 +24004,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H815" t="n">
         <v>11250</v>
@@ -24033,7 +24033,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842183589935</v>
+        <v>1.94842171669006</v>
       </c>
       <c r="H816" t="n">
         <v>13500</v>
@@ -24062,7 +24062,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H817" t="n">
         <v>76500</v>
@@ -24091,7 +24091,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G818" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H818" t="n">
         <v>8250</v>
@@ -24120,7 +24120,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H819" t="n">
         <v>25500</v>
@@ -24149,7 +24149,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H820" t="n">
         <v>11250</v>
@@ -24178,7 +24178,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H821" t="n">
         <v>2250</v>
@@ -24207,7 +24207,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H822" t="n">
         <v>9000</v>
@@ -24236,7 +24236,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H823" t="n">
         <v>3750</v>
@@ -24265,7 +24265,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H824" t="n">
         <v>65250</v>
@@ -24294,7 +24294,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H825" t="n">
         <v>78000</v>
@@ -24323,7 +24323,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H826" t="n">
         <v>27000</v>
@@ -24352,7 +24352,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G827" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H827" t="n">
         <v>60000</v>
@@ -24381,7 +24381,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748846530914</v>
       </c>
       <c r="H828" t="n">
         <v>11250</v>
@@ -24410,7 +24410,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H829" t="n">
         <v>36000</v>
@@ -24439,7 +24439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H830" t="n">
         <v>53250</v>
@@ -24468,7 +24468,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H831" t="n">
         <v>31500</v>
@@ -24584,7 +24584,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.9975414276123</v>
+        <v>1.99754154682159</v>
       </c>
       <c r="H835" t="n">
         <v>6000</v>
@@ -24613,7 +24613,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H836" t="n">
         <v>7500</v>
@@ -24671,7 +24671,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H838" t="n">
         <v>23250</v>
@@ -24700,7 +24700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H839" t="n">
         <v>27750</v>
@@ -24729,7 +24729,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H840" t="n">
         <v>3750</v>
@@ -24758,7 +24758,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H841" t="n">
         <v>33000</v>
@@ -24787,7 +24787,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H842" t="n">
         <v>26250</v>
@@ -24816,7 +24816,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H843" t="n">
         <v>2250</v>
@@ -24845,7 +24845,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H846" t="n">
         <v>175500</v>
@@ -24932,7 +24932,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H847" t="n">
         <v>41250</v>
@@ -24961,7 +24961,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H848" t="n">
         <v>2250</v>
@@ -25019,7 +25019,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H850" t="n">
         <v>15000</v>
@@ -25077,7 +25077,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25106,7 +25106,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.10396814346313</v>
+        <v>2.10396790504456</v>
       </c>
       <c r="H853" t="n">
         <v>5250</v>
@@ -25164,7 +25164,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H855" t="n">
         <v>7500</v>
@@ -25222,7 +25222,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660829544067</v>
       </c>
       <c r="H857" t="n">
         <v>9750</v>
@@ -25251,7 +25251,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G858" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H858" t="n">
         <v>750</v>
@@ -25338,7 +25338,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>2.01391458511353</v>
+        <v>2.01391506195068</v>
       </c>
       <c r="H861" t="n">
         <v>6000</v>
@@ -25367,7 +25367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204832077026</v>
+        <v>1.93204808235168</v>
       </c>
       <c r="H862" t="n">
         <v>27000</v>
@@ -25396,7 +25396,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479475498199</v>
+        <v>1.96479511260986</v>
       </c>
       <c r="H863" t="n">
         <v>4500</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H864" t="n">
         <v>7500</v>
@@ -25512,7 +25512,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H867" t="n">
         <v>1500</v>
@@ -25541,7 +25541,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111495018005</v>
       </c>
       <c r="H868" t="n">
         <v>11250</v>
@@ -25570,7 +25570,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H869" t="n">
         <v>23250</v>
@@ -25599,7 +25599,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.86655509471893</v>
+        <v>1.86655521392822</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -25657,7 +25657,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G872" t="n">
-        <v>1.91567516326904</v>
+        <v>1.91567492485046</v>
       </c>
       <c r="H872" t="n">
         <v>17250</v>
@@ -25686,7 +25686,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H873" t="n">
         <v>4500</v>
@@ -25715,7 +25715,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H874" t="n">
         <v>9000</v>
@@ -25744,7 +25744,7 @@
         <v>2.5</v>
       </c>
       <c r="G875" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H875" t="n">
         <v>66750</v>
@@ -25773,7 +25773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H876" t="n">
         <v>54750</v>
@@ -25802,7 +25802,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H877" t="n">
         <v>15000</v>
@@ -25831,7 +25831,7 @@
         <v>2.5</v>
       </c>
       <c r="G878" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H878" t="n">
         <v>36000</v>
@@ -25860,7 +25860,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G879" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H879" t="n">
         <v>1500</v>
@@ -25889,7 +25889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H880" t="n">
         <v>6750</v>
@@ -25947,7 +25947,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H882" t="n">
         <v>3000</v>
@@ -26034,7 +26034,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H885" t="n">
         <v>1500</v>
@@ -26063,7 +26063,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H886" t="n">
         <v>4500</v>
@@ -26092,7 +26092,7 @@
         <v>2.5</v>
       </c>
       <c r="G887" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H887" t="n">
         <v>4500</v>
@@ -26121,7 +26121,7 @@
         <v>2.5</v>
       </c>
       <c r="G888" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H888" t="n">
         <v>2250</v>
@@ -26150,7 +26150,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H889" t="n">
         <v>7500</v>
@@ -26179,7 +26179,7 @@
         <v>2.5</v>
       </c>
       <c r="G890" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H890" t="n">
         <v>46500</v>
@@ -26208,7 +26208,7 @@
         <v>2.5</v>
       </c>
       <c r="G891" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>2.5</v>
       </c>
       <c r="G892" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H892" t="n">
         <v>5250</v>
@@ -26266,7 +26266,7 @@
         <v>2.5</v>
       </c>
       <c r="G893" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26295,7 +26295,7 @@
         <v>2.5</v>
       </c>
       <c r="G894" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H894" t="n">
         <v>288750</v>
@@ -26324,7 +26324,7 @@
         <v>2.5</v>
       </c>
       <c r="G895" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H895" t="n">
         <v>3000</v>
@@ -26353,7 +26353,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H896" t="n">
         <v>4500</v>
@@ -26382,7 +26382,7 @@
         <v>2.5</v>
       </c>
       <c r="G897" t="n">
-        <v>2.04666137695312</v>
+        <v>2.04666113853455</v>
       </c>
       <c r="H897" t="n">
         <v>750</v>
@@ -26817,7 +26817,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H912" t="n">
         <v>3000</v>
@@ -28006,7 +28006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H953" t="n">
         <v>3000</v>
@@ -28325,7 +28325,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H964" t="n">
         <v>1500</v>
@@ -28412,7 +28412,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H967" t="n">
         <v>6750</v>
@@ -28441,7 +28441,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H968" t="n">
         <v>2250</v>
@@ -28528,7 +28528,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H971" t="n">
         <v>2250</v>
@@ -28557,7 +28557,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28586,7 +28586,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -28615,7 +28615,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H974" t="n">
         <v>750</v>
@@ -28644,7 +28644,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28731,7 +28731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037759780884</v>
       </c>
       <c r="H978" t="n">
         <v>3000</v>
@@ -28789,7 +28789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H980" t="n">
         <v>11250</v>
@@ -28818,7 +28818,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G981" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037759780884</v>
       </c>
       <c r="H981" t="n">
         <v>27000</v>
@@ -28847,7 +28847,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H982" t="n">
         <v>9000</v>
@@ -29021,7 +29021,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>1.6225084066391</v>
+        <v>1.62250828742981</v>
       </c>
       <c r="H988" t="n">
         <v>40500</v>
@@ -29253,7 +29253,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H996" t="n">
         <v>12000</v>
@@ -29282,7 +29282,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H997" t="n">
         <v>16500</v>
@@ -29311,7 +29311,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H998" t="n">
         <v>750</v>
@@ -29340,7 +29340,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29427,7 +29427,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1002" t="n">
         <v>5250</v>
@@ -29456,7 +29456,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1003" t="n">
         <v>39000</v>
@@ -29485,7 +29485,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1004" t="n">
         <v>81000</v>
@@ -29775,7 +29775,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1014" t="n">
         <v>9000</v>
@@ -29804,7 +29804,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -29862,7 +29862,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1017" t="n">
         <v>18000</v>
@@ -29891,7 +29891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1018" t="n">
         <v>3750</v>
@@ -30007,7 +30007,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1022" t="n">
         <v>6000</v>
@@ -30152,7 +30152,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1027" t="n">
         <v>1500</v>
@@ -30239,7 +30239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1030" t="n">
         <v>1500</v>
@@ -30268,7 +30268,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -30384,7 +30384,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362532615662</v>
+        <v>1.32362520694733</v>
       </c>
       <c r="H1035" t="n">
         <v>6000</v>
@@ -30471,7 +30471,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1038" t="n">
         <v>23250</v>
@@ -30500,7 +30500,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1039" t="n">
         <v>12000</v>
@@ -30529,7 +30529,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1040" t="n">
         <v>750</v>
@@ -30558,7 +30558,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1041" t="n">
         <v>6750</v>
@@ -30587,7 +30587,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1042" t="n">
         <v>5250</v>
@@ -30616,7 +30616,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1044" t="n">
         <v>1500</v>
@@ -30761,7 +30761,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.38340198993683</v>
+        <v>1.38340187072754</v>
       </c>
       <c r="H1048" t="n">
         <v>1500</v>
@@ -30819,7 +30819,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1050" t="n">
         <v>2250</v>
@@ -30935,7 +30935,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1054" t="n">
         <v>31500</v>
@@ -30964,7 +30964,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1055" t="n">
         <v>21000</v>
@@ -31022,7 +31022,7 @@
         <v>1.75</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.49441576004028</v>
+        <v>1.49441564083099</v>
       </c>
       <c r="H1057" t="n">
         <v>750</v>
@@ -31051,7 +31051,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1058" t="n">
         <v>2250</v>
@@ -31341,7 +31341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1068" t="n">
         <v>6000</v>
@@ -31428,7 +31428,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1071" t="n">
         <v>750</v>
@@ -31486,7 +31486,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.44317853450775</v>
+        <v>1.44317865371704</v>
       </c>
       <c r="H1073" t="n">
         <v>15750</v>
@@ -31834,7 +31834,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.38340198993683</v>
+        <v>1.38340187072754</v>
       </c>
       <c r="H1085" t="n">
         <v>3750</v>
@@ -32066,7 +32066,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.46025764942169</v>
+        <v>1.4602575302124</v>
       </c>
       <c r="H1093" t="n">
         <v>49500</v>
@@ -32095,7 +32095,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1094" t="n">
         <v>45750</v>
@@ -32414,7 +32414,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1105" t="n">
         <v>3750</v>
@@ -32559,7 +32559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1110" t="n">
         <v>45000</v>
@@ -32588,7 +32588,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1111" t="n">
         <v>12000</v>
@@ -32849,7 +32849,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H1120" t="n">
         <v>9750</v>
@@ -33168,7 +33168,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1131" t="n">
         <v>46500</v>
@@ -33458,7 +33458,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.6225084066391</v>
+        <v>1.62250828742981</v>
       </c>
       <c r="H1141" t="n">
         <v>8250</v>
@@ -33487,7 +33487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1142" t="n">
         <v>6000</v>
@@ -33516,7 +33516,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.54565274715424</v>
+        <v>1.54565262794495</v>
       </c>
       <c r="H1143" t="n">
         <v>3000</v>
@@ -33632,7 +33632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958752155304</v>
       </c>
       <c r="H1147" t="n">
         <v>9750</v>
@@ -33661,7 +33661,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.69936406612396</v>
+        <v>1.69936418533325</v>
       </c>
       <c r="H1148" t="n">
         <v>7500</v>
@@ -51821,6 +51821,35 @@
         <v>2250</v>
       </c>
       <c r="I1774" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1775">
+      <c r="A1775" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1775" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1775" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1775" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="E1775" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F1775" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="G1775" t="n">
+        <v>3.0699999332428</v>
+      </c>
+      <c r="H1775" t="n">
+        <v>3750</v>
+      </c>
+      <c r="I1775" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722755432129</v>
+        <v>2.86722779273987</v>
       </c>
       <c r="H3" t="n">
         <v>428250</v>
@@ -485,7 +485,7 @@
         <v>3.50550007820129</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80716824531555</v>
+        <v>2.80716848373413</v>
       </c>
       <c r="H4" t="n">
         <v>86250</v>
@@ -543,7 +543,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.70586848258972</v>
+        <v>2.7058687210083</v>
       </c>
       <c r="H6" t="n">
         <v>35250</v>
@@ -601,7 +601,7 @@
         <v>3.38949990272522</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7142767906189</v>
+        <v>2.71427702903748</v>
       </c>
       <c r="H8" t="n">
         <v>111000</v>
@@ -630,7 +630,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75111317634583</v>
+        <v>2.7511134147644</v>
       </c>
       <c r="H9" t="n">
         <v>62250</v>
@@ -688,7 +688,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G11" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H11" t="n">
         <v>9000</v>
@@ -746,7 +746,7 @@
         <v>3.36450004577637</v>
       </c>
       <c r="G13" t="n">
-        <v>2.69425702095032</v>
+        <v>2.6942572593689</v>
       </c>
       <c r="H13" t="n">
         <v>14250</v>
@@ -775,7 +775,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72228455543518</v>
+        <v>2.72228479385376</v>
       </c>
       <c r="H14" t="n">
         <v>7500</v>
@@ -833,7 +833,7 @@
         <v>3.43449997901917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.75031232833862</v>
+        <v>2.7503125667572</v>
       </c>
       <c r="H16" t="n">
         <v>44250</v>
@@ -920,7 +920,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.96390891075134</v>
+        <v>3.96390914916992</v>
       </c>
       <c r="H19" t="n">
         <v>402000</v>
@@ -949,7 +949,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578276634216</v>
+        <v>3.83578300476074</v>
       </c>
       <c r="H20" t="n">
         <v>495750</v>
@@ -1007,7 +1007,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>3.43538808822632</v>
+        <v>3.43538784980774</v>
       </c>
       <c r="H22" t="n">
         <v>193500</v>
@@ -1036,7 +1036,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51226377487183</v>
+        <v>3.51226401329041</v>
       </c>
       <c r="H23" t="n">
         <v>94500</v>
@@ -1152,7 +1152,7 @@
         <v>4.24350023269653</v>
       </c>
       <c r="G27" t="n">
-        <v>3.39815163612366</v>
+        <v>3.39815139770508</v>
       </c>
       <c r="H27" t="n">
         <v>19500</v>
@@ -1239,7 +1239,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128523826599</v>
+        <v>3.33128499984741</v>
       </c>
       <c r="H30" t="n">
         <v>9000</v>
@@ -1268,7 +1268,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048462867737</v>
+        <v>3.33048439025879</v>
       </c>
       <c r="H31" t="n">
         <v>6750</v>
@@ -1297,7 +1297,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.28724193572998</v>
+        <v>3.28724217414856</v>
       </c>
       <c r="H32" t="n">
         <v>2250</v>
@@ -1413,7 +1413,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.9709300994873</v>
+        <v>2.97092986106873</v>
       </c>
       <c r="H36" t="n">
         <v>16500</v>
@@ -1442,7 +1442,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H37" t="n">
         <v>750</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H38" t="n">
         <v>27000</v>
@@ -1674,7 +1674,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H45" t="n">
         <v>13500</v>
@@ -1703,7 +1703,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H46" t="n">
         <v>3000</v>
@@ -1761,7 +1761,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G48" t="n">
-        <v>2.99094986915588</v>
+        <v>2.9909496307373</v>
       </c>
       <c r="H48" t="n">
         <v>3000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1819,7 +1819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H50" t="n">
         <v>4500</v>
@@ -1848,7 +1848,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H51" t="n">
         <v>750</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08304047584534</v>
+        <v>3.08304023742676</v>
       </c>
       <c r="H52" t="n">
         <v>29250</v>
@@ -1906,7 +1906,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H53" t="n">
         <v>9000</v>
@@ -2022,7 +2022,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702470779419</v>
+        <v>3.06702446937561</v>
       </c>
       <c r="H57" t="n">
         <v>18750</v>
@@ -2051,7 +2051,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H58" t="n">
         <v>3000</v>
@@ -2080,7 +2080,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H59" t="n">
         <v>12000</v>
@@ -2109,7 +2109,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087055206299</v>
       </c>
       <c r="H65" t="n">
         <v>9750</v>
@@ -2399,7 +2399,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>2.83479571342468</v>
+        <v>2.8347954750061</v>
       </c>
       <c r="H70" t="n">
         <v>1500</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670910835266</v>
+        <v>2.74670886993408</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2486,7 +2486,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H73" t="n">
         <v>17250</v>
@@ -2718,7 +2718,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2747,7 +2747,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087055206299</v>
       </c>
       <c r="H82" t="n">
         <v>7500</v>
@@ -2776,7 +2776,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88684725761414</v>
+        <v>2.88684701919556</v>
       </c>
       <c r="H83" t="n">
         <v>5250</v>
@@ -2805,7 +2805,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.88684725761414</v>
+        <v>2.88684701919556</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>2.8067684173584</v>
+        <v>2.80676817893982</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866132736206</v>
+        <v>2.69866156578064</v>
       </c>
       <c r="H86" t="n">
         <v>7500</v>
@@ -2950,7 +2950,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049564361572</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H90" t="n">
         <v>10500</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185608386993</v>
+        <v>1.88185596466064</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3269,7 +3269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161896705627</v>
+        <v>1.64161908626556</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3298,7 +3298,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G101" t="n">
-        <v>1.7136904001236</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H101" t="n">
         <v>6750</v>
@@ -3356,7 +3356,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771381378174</v>
       </c>
       <c r="H103" t="n">
         <v>12000</v>
@@ -3443,7 +3443,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G106" t="n">
-        <v>1.7136904001236</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H106" t="n">
         <v>2250</v>
@@ -3472,7 +3472,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771381378174</v>
       </c>
       <c r="H107" t="n">
         <v>750</v>
@@ -3501,7 +3501,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.89787173271179</v>
+        <v>1.89787185192108</v>
       </c>
       <c r="H108" t="n">
         <v>15750</v>
@@ -3530,7 +3530,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205342292786</v>
+        <v>2.08205318450928</v>
       </c>
       <c r="H109" t="n">
         <v>8250</v>
@@ -3559,7 +3559,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049564361572</v>
       </c>
       <c r="H110" t="n">
         <v>16500</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H116" t="n">
         <v>6750</v>
@@ -3762,7 +3762,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H117" t="n">
         <v>3750</v>
@@ -3820,7 +3820,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79475665092468</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H119" t="n">
         <v>8250</v>
@@ -3849,7 +3849,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664979934692</v>
+        <v>2.68664956092834</v>
       </c>
       <c r="H120" t="n">
         <v>11250</v>
@@ -3936,7 +3936,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>2.75071310997009</v>
+        <v>2.75071263313293</v>
       </c>
       <c r="H123" t="n">
         <v>5250</v>
@@ -3965,7 +3965,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -4023,7 +4023,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H126" t="n">
         <v>3750</v>
@@ -4052,7 +4052,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.79475665092468</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H127" t="n">
         <v>2250</v>
@@ -4400,7 +4400,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856295585632</v>
+        <v>2.59856271743774</v>
       </c>
       <c r="H139" t="n">
         <v>1500</v>
@@ -4574,7 +4574,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H145" t="n">
         <v>3000</v>
@@ -4603,7 +4603,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71868133544922</v>
+        <v>2.71868109703064</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4719,7 +4719,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G150" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H150" t="n">
         <v>1500</v>
@@ -4748,7 +4748,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G151" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H151" t="n">
         <v>1500</v>
@@ -4864,7 +4864,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H155" t="n">
         <v>8250</v>
@@ -4893,7 +4893,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G156" t="n">
-        <v>2.56252765655518</v>
+        <v>2.5625274181366</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -4922,7 +4922,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>2.76272463798523</v>
+        <v>2.76272487640381</v>
       </c>
       <c r="H157" t="n">
         <v>11250</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H161" t="n">
         <v>14250</v>
@@ -5212,7 +5212,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45842432975769</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H167" t="n">
         <v>15000</v>
@@ -5502,7 +5502,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H177" t="n">
         <v>3750</v>
@@ -5531,7 +5531,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H182" t="n">
         <v>750</v>
@@ -5937,7 +5937,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H192" t="n">
         <v>3000</v>
@@ -5966,7 +5966,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G194" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G195" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6198,7 +6198,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>2.83479571342468</v>
+        <v>2.8347954750061</v>
       </c>
       <c r="H201" t="n">
         <v>30000</v>
@@ -6227,7 +6227,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G202" t="n">
-        <v>2.69065356254578</v>
+        <v>2.6906533241272</v>
       </c>
       <c r="H202" t="n">
         <v>45000</v>
@@ -6256,7 +6256,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H203" t="n">
         <v>9750</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H204" t="n">
         <v>12000</v>
@@ -6314,7 +6314,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451941490173</v>
+        <v>2.55451917648315</v>
       </c>
       <c r="H205" t="n">
         <v>13500</v>
@@ -6343,7 +6343,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H206" t="n">
         <v>8250</v>
@@ -6372,7 +6372,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6604,7 +6604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H215" t="n">
         <v>5250</v>
@@ -6633,7 +6633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830642700195</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6836,7 +6836,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H223" t="n">
         <v>5250</v>
@@ -6865,7 +6865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6894,7 +6894,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H225" t="n">
         <v>5250</v>
@@ -6981,7 +6981,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238903045654</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H228" t="n">
         <v>15750</v>
@@ -7039,7 +7039,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H230" t="n">
         <v>750</v>
@@ -7097,7 +7097,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H232" t="n">
         <v>6000</v>
@@ -7184,7 +7184,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>2.31428265571594</v>
+        <v>2.31428241729736</v>
       </c>
       <c r="H235" t="n">
         <v>4500</v>
@@ -7329,7 +7329,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G241" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G244" t="n">
-        <v>2.45842432975769</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H244" t="n">
         <v>4500</v>
@@ -7532,7 +7532,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H247" t="n">
         <v>1500</v>
@@ -7561,7 +7561,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H248" t="n">
         <v>1500</v>
@@ -7590,7 +7590,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G249" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G250" t="n">
-        <v>2.39836502075195</v>
+        <v>2.39836525917053</v>
       </c>
       <c r="H250" t="n">
         <v>3000</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H256" t="n">
         <v>7500</v>
@@ -7909,7 +7909,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G260" t="n">
-        <v>2.21418356895447</v>
+        <v>2.21418380737305</v>
       </c>
       <c r="H260" t="n">
         <v>3000</v>
@@ -7938,7 +7938,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21418356895447</v>
+        <v>2.21418380737305</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H262" t="n">
         <v>2250</v>
@@ -7996,7 +7996,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H263" t="n">
         <v>750</v>
@@ -8141,7 +8141,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8257,7 +8257,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830642700195</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H272" t="n">
         <v>2250</v>
@@ -8286,7 +8286,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830642700195</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834596633911</v>
+        <v>2.37834572792053</v>
       </c>
       <c r="H274" t="n">
         <v>3750</v>
@@ -8344,7 +8344,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H275" t="n">
         <v>12000</v>
@@ -8373,7 +8373,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H276" t="n">
         <v>3000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H289" t="n">
         <v>750</v>
@@ -8779,7 +8779,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H290" t="n">
         <v>750</v>
@@ -8808,7 +8808,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H299" t="n">
         <v>3000</v>
@@ -9069,7 +9069,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H300" t="n">
         <v>750</v>
@@ -9127,7 +9127,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H302" t="n">
         <v>3000</v>
@@ -9156,7 +9156,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H305" t="n">
         <v>148500</v>
@@ -9359,7 +9359,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39035749435425</v>
+        <v>2.39035725593567</v>
       </c>
       <c r="H310" t="n">
         <v>3000</v>
@@ -9446,7 +9446,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41838479042053</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H313" t="n">
         <v>5250</v>
@@ -9562,7 +9562,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H317" t="n">
         <v>3750</v>
@@ -9591,7 +9591,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830642700195</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H319" t="n">
         <v>3750</v>
@@ -9649,7 +9649,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430218696594</v>
+        <v>2.33430194854736</v>
       </c>
       <c r="H320" t="n">
         <v>750</v>
@@ -9794,7 +9794,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H325" t="n">
         <v>13500</v>
@@ -9823,7 +9823,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.41838479042053</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H326" t="n">
         <v>6750</v>
@@ -9968,7 +9968,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G331" t="n">
-        <v>2.45842432975769</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H331" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H333" t="n">
         <v>9000</v>
@@ -10055,7 +10055,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238903045654</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H334" t="n">
         <v>2250</v>
@@ -10258,7 +10258,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238903045654</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H341" t="n">
         <v>20250</v>
@@ -10316,7 +10316,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G343" t="n">
-        <v>2.39035749435425</v>
+        <v>2.39035725593567</v>
       </c>
       <c r="H343" t="n">
         <v>6000</v>
@@ -10432,7 +10432,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G347" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H347" t="n">
         <v>31500</v>
@@ -10461,7 +10461,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H348" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H350" t="n">
         <v>6000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>2.62659025192261</v>
+        <v>2.62659049034119</v>
       </c>
       <c r="H351" t="n">
         <v>3750</v>
@@ -10577,7 +10577,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451941490173</v>
+        <v>2.55451917648315</v>
       </c>
       <c r="H352" t="n">
         <v>4500</v>
@@ -10606,7 +10606,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049564361572</v>
       </c>
       <c r="H353" t="n">
         <v>750</v>
@@ -10635,7 +10635,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G354" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H354" t="n">
         <v>4500</v>
@@ -10664,7 +10664,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>2.6706337928772</v>
+        <v>2.67063403129578</v>
       </c>
       <c r="H355" t="n">
         <v>14250</v>
@@ -10751,7 +10751,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266532897949</v>
+        <v>2.70266556739807</v>
       </c>
       <c r="H358" t="n">
         <v>13500</v>
@@ -10809,7 +10809,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H360" t="n">
         <v>10500</v>
@@ -10838,7 +10838,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.7747368812561</v>
+        <v>2.77473640441895</v>
       </c>
       <c r="H361" t="n">
         <v>13500</v>
@@ -11012,7 +11012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G367" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H367" t="n">
         <v>172500</v>
@@ -11070,7 +11070,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G369" t="n">
-        <v>3.23519062995911</v>
+        <v>3.23519039154053</v>
       </c>
       <c r="H369" t="n">
         <v>87750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11215,7 +11215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H374" t="n">
         <v>20250</v>
@@ -11244,7 +11244,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H375" t="n">
         <v>3750</v>
@@ -11273,7 +11273,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H376" t="n">
         <v>39000</v>
@@ -11302,7 +11302,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H377" t="n">
         <v>18000</v>
@@ -11331,7 +11331,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H378" t="n">
         <v>6000</v>
@@ -11360,7 +11360,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H379" t="n">
         <v>24000</v>
@@ -11389,7 +11389,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11505,7 +11505,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H384" t="n">
         <v>19500</v>
@@ -11534,7 +11534,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H385" t="n">
         <v>22500</v>
@@ -11563,7 +11563,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11592,7 +11592,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H387" t="n">
         <v>3750</v>
@@ -11737,7 +11737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H392" t="n">
         <v>5250</v>
@@ -11795,7 +11795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H394" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -11853,7 +11853,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H397" t="n">
         <v>750</v>
@@ -11940,7 +11940,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11998,7 +11998,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H401" t="n">
         <v>8250</v>
@@ -12085,7 +12085,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H404" t="n">
         <v>21000</v>
@@ -12114,7 +12114,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>3.42738080024719</v>
+        <v>3.42738056182861</v>
       </c>
       <c r="H405" t="n">
         <v>54750</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H409" t="n">
         <v>12750</v>
@@ -12317,7 +12317,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H412" t="n">
         <v>3000</v>
@@ -12346,7 +12346,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H413" t="n">
         <v>5250</v>
@@ -12404,7 +12404,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H415" t="n">
         <v>2250</v>
@@ -12462,7 +12462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H417" t="n">
         <v>3750</v>
@@ -12491,7 +12491,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H418" t="n">
         <v>8250</v>
@@ -12549,7 +12549,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H420" t="n">
         <v>2250</v>
@@ -12578,7 +12578,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H421" t="n">
         <v>3000</v>
@@ -12607,7 +12607,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H426" t="n">
         <v>5250</v>
@@ -12752,7 +12752,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G427" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12868,7 +12868,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H431" t="n">
         <v>9000</v>
@@ -12897,7 +12897,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H432" t="n">
         <v>4500</v>
@@ -12955,7 +12955,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H434" t="n">
         <v>750</v>
@@ -12984,7 +12984,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G435" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13042,7 +13042,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H437" t="n">
         <v>750</v>
@@ -13071,7 +13071,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13100,7 +13100,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H439" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G440" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13187,7 +13187,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H442" t="n">
         <v>750</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13419,7 +13419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H450" t="n">
         <v>1500</v>
@@ -13448,7 +13448,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G451" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13477,7 +13477,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>3.0430006980896</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13564,7 +13564,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H455" t="n">
         <v>2250</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13709,7 +13709,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G460" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H460" t="n">
         <v>1500</v>
@@ -13738,7 +13738,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H461" t="n">
         <v>1500</v>
@@ -13767,7 +13767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13825,7 +13825,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H464" t="n">
         <v>4500</v>
@@ -13854,7 +13854,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H466" t="n">
         <v>9750</v>
@@ -14028,7 +14028,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H471" t="n">
         <v>6750</v>
@@ -14057,7 +14057,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H472" t="n">
         <v>750</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14202,7 +14202,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H477" t="n">
         <v>6000</v>
@@ -14289,7 +14289,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G480" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H480" t="n">
         <v>3750</v>
@@ -14318,7 +14318,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G481" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H481" t="n">
         <v>750</v>
@@ -14347,7 +14347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H482" t="n">
         <v>750</v>
@@ -14405,7 +14405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H484" t="n">
         <v>2250</v>
@@ -14434,7 +14434,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H485" t="n">
         <v>750</v>
@@ -14463,7 +14463,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14492,7 +14492,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G487" t="n">
-        <v>2.99495387077332</v>
+        <v>2.99495363235474</v>
       </c>
       <c r="H487" t="n">
         <v>6000</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698493003845</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14637,7 +14637,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H492" t="n">
         <v>750</v>
@@ -14869,7 +14869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H500" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089032173157</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.83479571342468</v>
+        <v>2.8347954750061</v>
       </c>
       <c r="H516" t="n">
         <v>1500</v>
@@ -15391,7 +15391,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H518" t="n">
         <v>12750</v>
@@ -15420,7 +15420,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H519" t="n">
         <v>3750</v>
@@ -15449,7 +15449,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15652,7 +15652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15681,7 +15681,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846410751343</v>
+        <v>2.49846386909485</v>
       </c>
       <c r="H528" t="n">
         <v>5250</v>
@@ -15710,7 +15710,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G529" t="n">
-        <v>2.41838479042053</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H529" t="n">
         <v>9000</v>
@@ -15739,7 +15739,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H530" t="n">
         <v>5250</v>
@@ -15768,7 +15768,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H531" t="n">
         <v>3000</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15826,7 +15826,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H533" t="n">
         <v>15000</v>
@@ -16000,7 +16000,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H539" t="n">
         <v>24750</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16145,7 +16145,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830642700195</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H544" t="n">
         <v>750</v>
@@ -16203,7 +16203,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H546" t="n">
         <v>8250</v>
@@ -16319,7 +16319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16493,7 +16493,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830642700195</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H556" t="n">
         <v>3750</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16725,7 +16725,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>2.41838479042053</v>
+        <v>2.41838502883911</v>
       </c>
       <c r="H564" t="n">
         <v>3000</v>
@@ -16928,7 +16928,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H571" t="n">
         <v>7500</v>
@@ -16957,7 +16957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H572" t="n">
         <v>3000</v>
@@ -17073,7 +17073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H576" t="n">
         <v>3000</v>
@@ -17218,7 +17218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213274002075</v>
+        <v>2.16213226318359</v>
       </c>
       <c r="H581" t="n">
         <v>15750</v>
@@ -17421,7 +17421,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.17814826965332</v>
+        <v>2.17814803123474</v>
       </c>
       <c r="H588" t="n">
         <v>8250</v>
@@ -17508,7 +17508,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.05002164840698</v>
+        <v>2.05002188682556</v>
       </c>
       <c r="H591" t="n">
         <v>11250</v>
@@ -17682,7 +17682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587973594666</v>
+        <v>1.90587961673737</v>
       </c>
       <c r="H597" t="n">
         <v>7500</v>
@@ -17711,7 +17711,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G598" t="n">
-        <v>1.7777533531189</v>
+        <v>1.77775323390961</v>
       </c>
       <c r="H598" t="n">
         <v>15000</v>
@@ -17740,7 +17740,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>1.7136904001236</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H599" t="n">
         <v>12000</v>
@@ -17798,7 +17798,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G601" t="n">
-        <v>1.49747693538666</v>
+        <v>1.49747681617737</v>
       </c>
       <c r="H601" t="n">
         <v>16500</v>
@@ -17914,7 +17914,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564249992371</v>
       </c>
       <c r="H605" t="n">
         <v>3750</v>
@@ -18030,7 +18030,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61759531497955</v>
+        <v>1.61759519577026</v>
       </c>
       <c r="H609" t="n">
         <v>5250</v>
@@ -18088,7 +18088,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>1.7136904001236</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H611" t="n">
         <v>4500</v>
@@ -18233,7 +18233,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G616" t="n">
-        <v>1.7777533531189</v>
+        <v>1.77775323390961</v>
       </c>
       <c r="H616" t="n">
         <v>3750</v>
@@ -18320,7 +18320,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587973594666</v>
+        <v>1.90587961673737</v>
       </c>
       <c r="H619" t="n">
         <v>75000</v>
@@ -18378,7 +18378,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.95392715930939</v>
+        <v>1.95392727851868</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.80978500843048</v>
+        <v>1.80978488922119</v>
       </c>
       <c r="H622" t="n">
         <v>48750</v>
@@ -18436,7 +18436,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962697029114</v>
+        <v>1.64962685108185</v>
       </c>
       <c r="H623" t="n">
         <v>186750</v>
@@ -18465,7 +18465,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564249992371</v>
       </c>
       <c r="H624" t="n">
         <v>174750</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568227767944</v>
+        <v>1.70568215847015</v>
       </c>
       <c r="H625" t="n">
         <v>23250</v>
@@ -18813,7 +18813,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>1.7136904001236</v>
+        <v>1.71369028091431</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771381378174</v>
       </c>
       <c r="H637" t="n">
         <v>7500</v>
@@ -18900,7 +18900,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568227767944</v>
+        <v>1.70568215847015</v>
       </c>
       <c r="H639" t="n">
         <v>15750</v>
@@ -19045,7 +19045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81743538379669</v>
+        <v>1.8174352645874</v>
       </c>
       <c r="H644" t="n">
         <v>18000</v>
@@ -19074,7 +19074,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H645" t="n">
         <v>6000</v>
@@ -19103,7 +19103,7 @@
         <v>2.25</v>
       </c>
       <c r="G646" t="n">
-        <v>1.8419953584671</v>
+        <v>1.84199523925781</v>
       </c>
       <c r="H646" t="n">
         <v>12750</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111495018005</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H648" t="n">
         <v>47250</v>
@@ -19219,7 +19219,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H650" t="n">
         <v>12000</v>
@@ -19277,7 +19277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836851596832</v>
+        <v>1.85836863517761</v>
       </c>
       <c r="H652" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836851596832</v>
+        <v>1.85836863517761</v>
       </c>
       <c r="H653" t="n">
         <v>4500</v>
@@ -19393,7 +19393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194239616394</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H658" t="n">
         <v>11250</v>
@@ -19509,7 +19509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194239616394</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H660" t="n">
         <v>12000</v>
@@ -19596,7 +19596,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H663" t="n">
         <v>21750</v>
@@ -19654,7 +19654,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H665" t="n">
         <v>15750</v>
@@ -19683,7 +19683,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.8256219625473</v>
+        <v>1.82562208175659</v>
       </c>
       <c r="H666" t="n">
         <v>4500</v>
@@ -19799,7 +19799,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H670" t="n">
         <v>15750</v>
@@ -19973,7 +19973,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G676" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H676" t="n">
         <v>750</v>
@@ -20002,7 +20002,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G677" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20118,7 +20118,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H681" t="n">
         <v>750</v>
@@ -20147,7 +20147,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H682" t="n">
         <v>1500</v>
@@ -20176,7 +20176,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H683" t="n">
         <v>8250</v>
@@ -20234,7 +20234,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H685" t="n">
         <v>4500</v>
@@ -20292,7 +20292,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194239616394</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H687" t="n">
         <v>34500</v>
@@ -20437,7 +20437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H695" t="n">
         <v>750</v>
@@ -20582,7 +20582,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G697" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H697" t="n">
         <v>4500</v>
@@ -20611,7 +20611,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H703" t="n">
         <v>2250</v>
@@ -20814,7 +20814,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H705" t="n">
         <v>750</v>
@@ -20959,7 +20959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H710" t="n">
         <v>15000</v>
@@ -20988,7 +20988,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21365,7 +21365,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21539,7 +21539,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G730" t="n">
-        <v>1.62914252281189</v>
+        <v>1.6291424036026</v>
       </c>
       <c r="H730" t="n">
         <v>2250</v>
@@ -21568,7 +21568,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63732898235321</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H731" t="n">
         <v>3000</v>
@@ -21597,7 +21597,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G732" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H732" t="n">
         <v>2250</v>
@@ -21626,7 +21626,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G733" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H734" t="n">
         <v>750</v>
@@ -21684,7 +21684,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H737" t="n">
         <v>2250</v>
@@ -21800,7 +21800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G739" t="n">
-        <v>1.55546247959137</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H739" t="n">
         <v>11250</v>
@@ -21858,7 +21858,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H741" t="n">
         <v>2250</v>
@@ -21887,7 +21887,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H742" t="n">
         <v>7500</v>
@@ -21916,7 +21916,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -21945,7 +21945,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G744" t="n">
-        <v>1.57183599472046</v>
+        <v>1.57183587551117</v>
       </c>
       <c r="H744" t="n">
         <v>1500</v>
@@ -22003,7 +22003,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="n">
-        <v>1.55546247959137</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H746" t="n">
         <v>6000</v>
@@ -22061,7 +22061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G748" t="n">
-        <v>1.55546247959137</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H748" t="n">
         <v>10500</v>
@@ -22090,7 +22090,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.56364929676056</v>
+        <v>1.56364941596985</v>
       </c>
       <c r="H749" t="n">
         <v>6750</v>
@@ -22119,7 +22119,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H751" t="n">
         <v>4500</v>
@@ -22206,7 +22206,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634288787842</v>
+        <v>1.50634276866913</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22235,7 +22235,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634288787842</v>
+        <v>1.50634276866913</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359609603882</v>
+        <v>1.47359621524811</v>
       </c>
       <c r="H755" t="n">
         <v>6000</v>
@@ -22322,7 +22322,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.55546247959137</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H757" t="n">
         <v>79500</v>
@@ -22409,7 +22409,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>1.60458266735077</v>
+        <v>1.60458254814148</v>
       </c>
       <c r="H760" t="n">
         <v>3750</v>
@@ -22438,7 +22438,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H761" t="n">
         <v>6000</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H763" t="n">
         <v>3750</v>
@@ -22525,7 +22525,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -22612,7 +22612,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G768" t="n">
-        <v>1.56364929676056</v>
+        <v>1.56364941596985</v>
       </c>
       <c r="H768" t="n">
         <v>1500</v>
@@ -22757,7 +22757,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G772" t="n">
-        <v>1.57183599472046</v>
+        <v>1.57183587551117</v>
       </c>
       <c r="H772" t="n">
         <v>2250</v>
@@ -22786,7 +22786,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G773" t="n">
-        <v>1.57183599472046</v>
+        <v>1.57183587551117</v>
       </c>
       <c r="H773" t="n">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G774" t="n">
-        <v>1.55546247959137</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H774" t="n">
         <v>2250</v>
@@ -22844,7 +22844,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H775" t="n">
         <v>4500</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.60458266735077</v>
+        <v>1.60458254814148</v>
       </c>
       <c r="H776" t="n">
         <v>28500</v>
@@ -22902,7 +22902,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.63732898235321</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H777" t="n">
         <v>16500</v>
@@ -22931,7 +22931,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.63732898235321</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H778" t="n">
         <v>3000</v>
@@ -22960,7 +22960,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194239616394</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H779" t="n">
         <v>21750</v>
@@ -22989,7 +22989,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.8256219625473</v>
+        <v>1.82562208175659</v>
       </c>
       <c r="H780" t="n">
         <v>60000</v>
@@ -23221,7 +23221,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H788" t="n">
         <v>35250</v>
@@ -23279,7 +23279,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23308,7 +23308,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194239616394</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H791" t="n">
         <v>8250</v>
@@ -23337,7 +23337,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194239616394</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
@@ -23656,7 +23656,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23714,7 +23714,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H805" t="n">
         <v>45750</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H806" t="n">
         <v>3000</v>
@@ -23946,7 +23946,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H813" t="n">
         <v>5250</v>
@@ -23975,7 +23975,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80106198787689</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H814" t="n">
         <v>9000</v>
@@ -24091,7 +24091,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G818" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H818" t="n">
         <v>8250</v>
@@ -24120,7 +24120,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H819" t="n">
         <v>25500</v>
@@ -24149,7 +24149,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111495018005</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H820" t="n">
         <v>11250</v>
@@ -24207,7 +24207,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H822" t="n">
         <v>9000</v>
@@ -24323,7 +24323,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>1.94023489952087</v>
+        <v>1.94023501873016</v>
       </c>
       <c r="H826" t="n">
         <v>27000</v>
@@ -24352,7 +24352,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G827" t="n">
-        <v>1.94023489952087</v>
+        <v>1.94023501873016</v>
       </c>
       <c r="H827" t="n">
         <v>60000</v>
@@ -24497,7 +24497,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034106254578</v>
+        <v>2.12034130096436</v>
       </c>
       <c r="H832" t="n">
         <v>2250</v>
@@ -24584,7 +24584,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.99754154682159</v>
+        <v>1.99754166603088</v>
       </c>
       <c r="H835" t="n">
         <v>6000</v>
@@ -24613,7 +24613,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210164070129</v>
+        <v>2.02210140228271</v>
       </c>
       <c r="H836" t="n">
         <v>7500</v>
@@ -24642,7 +24642,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H837" t="n">
         <v>3750</v>
@@ -24671,7 +24671,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H838" t="n">
         <v>23250</v>
@@ -24700,7 +24700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210164070129</v>
+        <v>2.02210140228271</v>
       </c>
       <c r="H839" t="n">
         <v>27750</v>
@@ -24729,7 +24729,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H840" t="n">
         <v>3750</v>
@@ -24758,7 +24758,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H841" t="n">
         <v>33000</v>
@@ -24787,7 +24787,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H842" t="n">
         <v>26250</v>
@@ -25019,7 +25019,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H850" t="n">
         <v>15000</v>
@@ -25077,7 +25077,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25106,7 +25106,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.10396790504456</v>
+        <v>2.10396766662598</v>
       </c>
       <c r="H853" t="n">
         <v>5250</v>
@@ -25164,7 +25164,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>1.97298169136047</v>
+        <v>1.97298157215118</v>
       </c>
       <c r="H855" t="n">
         <v>7500</v>
@@ -25193,7 +25193,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H856" t="n">
         <v>2250</v>
@@ -25251,7 +25251,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G858" t="n">
-        <v>1.97298169136047</v>
+        <v>1.97298157215118</v>
       </c>
       <c r="H858" t="n">
         <v>750</v>
@@ -25280,7 +25280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935508728027</v>
+        <v>1.98935484886169</v>
       </c>
       <c r="H859" t="n">
         <v>53250</v>
@@ -25338,7 +25338,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>2.01391506195068</v>
+        <v>2.01391458511353</v>
       </c>
       <c r="H861" t="n">
         <v>6000</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H864" t="n">
         <v>7500</v>
@@ -25454,7 +25454,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H865" t="n">
         <v>6750</v>
@@ -25483,7 +25483,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H867" t="n">
         <v>1500</v>
@@ -25541,7 +25541,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111495018005</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H868" t="n">
         <v>11250</v>
@@ -25628,7 +25628,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H871" t="n">
         <v>3750</v>
@@ -25686,7 +25686,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H873" t="n">
         <v>4500</v>
@@ -25715,7 +25715,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.88292849063873</v>
+        <v>1.88292860984802</v>
       </c>
       <c r="H874" t="n">
         <v>9000</v>
@@ -25744,7 +25744,7 @@
         <v>2.5</v>
       </c>
       <c r="G875" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H875" t="n">
         <v>66750</v>
@@ -25802,7 +25802,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H877" t="n">
         <v>15000</v>
@@ -25831,7 +25831,7 @@
         <v>2.5</v>
       </c>
       <c r="G878" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H878" t="n">
         <v>36000</v>
@@ -25860,7 +25860,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G879" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H879" t="n">
         <v>1500</v>
@@ -25889,7 +25889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H880" t="n">
         <v>6750</v>
@@ -26092,7 +26092,7 @@
         <v>2.5</v>
       </c>
       <c r="G887" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H887" t="n">
         <v>4500</v>
@@ -26121,7 +26121,7 @@
         <v>2.5</v>
       </c>
       <c r="G888" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H888" t="n">
         <v>2250</v>
@@ -26150,7 +26150,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H889" t="n">
         <v>7500</v>
@@ -26179,7 +26179,7 @@
         <v>2.5</v>
       </c>
       <c r="G890" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H890" t="n">
         <v>46500</v>
@@ -26208,7 +26208,7 @@
         <v>2.5</v>
       </c>
       <c r="G891" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>2.5</v>
       </c>
       <c r="G892" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H892" t="n">
         <v>5250</v>
@@ -26266,7 +26266,7 @@
         <v>2.5</v>
       </c>
       <c r="G893" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26295,7 +26295,7 @@
         <v>2.5</v>
       </c>
       <c r="G894" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H894" t="n">
         <v>288750</v>
@@ -26324,7 +26324,7 @@
         <v>2.5</v>
       </c>
       <c r="G895" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H895" t="n">
         <v>3000</v>
@@ -26353,7 +26353,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H896" t="n">
         <v>4500</v>
@@ -26382,7 +26382,7 @@
         <v>2.5</v>
       </c>
       <c r="G897" t="n">
-        <v>2.04666113853455</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H897" t="n">
         <v>750</v>
@@ -26411,7 +26411,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H898" t="n">
         <v>10500</v>
@@ -26498,7 +26498,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G901" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H901" t="n">
         <v>20250</v>
@@ -26527,7 +26527,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G902" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H902" t="n">
         <v>3750</v>
@@ -26614,7 +26614,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285192966461</v>
       </c>
       <c r="H908" t="n">
         <v>21000</v>
@@ -26730,7 +26730,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H909" t="n">
         <v>12750</v>
@@ -26759,7 +26759,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G910" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H910" t="n">
         <v>5250</v>
@@ -26788,7 +26788,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G911" t="n">
-        <v>1.86161506175995</v>
+        <v>1.86161494255066</v>
       </c>
       <c r="H911" t="n">
         <v>3750</v>
@@ -26817,7 +26817,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869393825531</v>
+        <v>1.8786940574646</v>
       </c>
       <c r="H912" t="n">
         <v>3000</v>
@@ -26846,7 +26846,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G913" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H913" t="n">
         <v>750</v>
@@ -26875,7 +26875,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G914" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H914" t="n">
         <v>2250</v>
@@ -26904,7 +26904,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G915" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G916" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G917" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G918" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H918" t="n">
         <v>6000</v>
@@ -27020,7 +27020,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G919" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H920" t="n">
         <v>5250</v>
@@ -27078,7 +27078,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H921" t="n">
         <v>6750</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H925" t="n">
         <v>8250</v>
@@ -27281,7 +27281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H928" t="n">
         <v>3000</v>
@@ -27310,7 +27310,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H929" t="n">
         <v>6750</v>
@@ -27339,7 +27339,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H930" t="n">
         <v>750</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824714660645</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27426,7 +27426,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H933" t="n">
         <v>20250</v>
@@ -27455,7 +27455,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H934" t="n">
         <v>12000</v>
@@ -27571,7 +27571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H938" t="n">
         <v>14250</v>
@@ -27600,7 +27600,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H939" t="n">
         <v>2250</v>
@@ -27629,7 +27629,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G940" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -27658,7 +27658,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H941" t="n">
         <v>4500</v>
@@ -27687,7 +27687,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G942" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -27716,7 +27716,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H943" t="n">
         <v>2250</v>
@@ -27745,7 +27745,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H944" t="n">
         <v>750</v>
@@ -27774,7 +27774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H945" t="n">
         <v>1500</v>
@@ -27803,7 +27803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H948" t="n">
         <v>2250</v>
@@ -27890,7 +27890,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G949" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H949" t="n">
         <v>9000</v>
@@ -27919,7 +27919,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G950" t="n">
-        <v>1.89577305316925</v>
+        <v>1.89577293395996</v>
       </c>
       <c r="H950" t="n">
         <v>6750</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285192966461</v>
       </c>
       <c r="H951" t="n">
         <v>10500</v>
@@ -28006,7 +28006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869393825531</v>
+        <v>1.8786940574646</v>
       </c>
       <c r="H953" t="n">
         <v>3000</v>
@@ -28064,7 +28064,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H955" t="n">
         <v>6750</v>
@@ -28093,7 +28093,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G956" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -28122,7 +28122,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H957" t="n">
         <v>3000</v>
@@ -28151,7 +28151,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G958" t="n">
-        <v>1.94701015949249</v>
+        <v>1.94701027870178</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G959" t="n">
-        <v>1.86161506175995</v>
+        <v>1.86161494255066</v>
       </c>
       <c r="H959" t="n">
         <v>9000</v>
@@ -28209,7 +28209,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H960" t="n">
         <v>30750</v>
@@ -28238,7 +28238,7 @@
         <v>2</v>
       </c>
       <c r="G961" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H961" t="n">
         <v>28500</v>
@@ -28354,7 +28354,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H965" t="n">
         <v>3750</v>
@@ -28412,7 +28412,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H967" t="n">
         <v>6750</v>
@@ -28441,7 +28441,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H968" t="n">
         <v>2250</v>
@@ -28470,7 +28470,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H969" t="n">
         <v>3750</v>
@@ -28615,7 +28615,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H974" t="n">
         <v>750</v>
@@ -28644,7 +28644,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28760,7 +28760,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H979" t="n">
         <v>2250</v>
@@ -28789,7 +28789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H980" t="n">
         <v>11250</v>
@@ -28876,7 +28876,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -28905,7 +28905,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G984" t="n">
-        <v>1.74206161499023</v>
+        <v>1.74206173419952</v>
       </c>
       <c r="H984" t="n">
         <v>750</v>
@@ -28963,7 +28963,7 @@
         <v>2</v>
       </c>
       <c r="G986" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H986" t="n">
         <v>8250</v>
@@ -28992,7 +28992,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H987" t="n">
         <v>52500</v>
@@ -29108,7 +29108,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G991" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H991" t="n">
         <v>120750</v>
@@ -29166,7 +29166,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G993" t="n">
-        <v>1.53711318969727</v>
+        <v>1.53711330890656</v>
       </c>
       <c r="H993" t="n">
         <v>46500</v>
@@ -29224,7 +29224,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G995" t="n">
-        <v>1.53711318969727</v>
+        <v>1.53711330890656</v>
       </c>
       <c r="H995" t="n">
         <v>6000</v>
@@ -29311,7 +29311,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H998" t="n">
         <v>750</v>
@@ -29340,7 +29340,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29369,7 +29369,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1000" t="n">
         <v>16500</v>
@@ -29456,7 +29456,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1003" t="n">
         <v>39000</v>
@@ -29485,7 +29485,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1004" t="n">
         <v>81000</v>
@@ -29746,7 +29746,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1013" t="n">
         <v>8250</v>
@@ -29775,7 +29775,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1014" t="n">
         <v>9000</v>
@@ -29804,7 +29804,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -29949,7 +29949,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1020" t="n">
         <v>24750</v>
@@ -29978,7 +29978,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1021" t="n">
         <v>4500</v>
@@ -30152,7 +30152,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1027" t="n">
         <v>1500</v>
@@ -30326,7 +30326,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1033" t="n">
         <v>3000</v>
@@ -30384,7 +30384,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362520694733</v>
+        <v>1.32362532615662</v>
       </c>
       <c r="H1035" t="n">
         <v>6000</v>
@@ -30906,7 +30906,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1053" t="n">
         <v>3750</v>
@@ -30935,7 +30935,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1054" t="n">
         <v>31500</v>
@@ -30964,7 +30964,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1055" t="n">
         <v>21000</v>
@@ -30993,7 +30993,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1056" t="n">
         <v>18000</v>
@@ -31051,7 +31051,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1058" t="n">
         <v>2250</v>
@@ -31138,7 +31138,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1061" t="n">
         <v>5250</v>
@@ -31167,7 +31167,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31196,7 +31196,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1063" t="n">
         <v>14250</v>
@@ -31225,7 +31225,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H1064" t="n">
         <v>8250</v>
@@ -31428,7 +31428,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1071" t="n">
         <v>750</v>
@@ -31486,7 +31486,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.44317865371704</v>
+        <v>1.44317853450775</v>
       </c>
       <c r="H1073" t="n">
         <v>15750</v>
@@ -31718,7 +31718,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1081" t="n">
         <v>4500</v>
@@ -31776,7 +31776,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1083" t="n">
         <v>12750</v>
@@ -31950,7 +31950,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1089" t="n">
         <v>6750</v>
@@ -31979,7 +31979,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1090" t="n">
         <v>15750</v>
@@ -32008,7 +32008,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1091" t="n">
         <v>4500</v>
@@ -32037,7 +32037,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.40902054309845</v>
+        <v>1.40902042388916</v>
       </c>
       <c r="H1092" t="n">
         <v>1500</v>
@@ -32182,7 +32182,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1097" t="n">
         <v>9750</v>
@@ -32298,7 +32298,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.53711318969727</v>
+        <v>1.53711330890656</v>
       </c>
       <c r="H1101" t="n">
         <v>11250</v>
@@ -32327,7 +32327,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.53711318969727</v>
+        <v>1.53711330890656</v>
       </c>
       <c r="H1102" t="n">
         <v>5250</v>
@@ -32443,7 +32443,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.53711318969727</v>
+        <v>1.53711330890656</v>
       </c>
       <c r="H1106" t="n">
         <v>3000</v>
@@ -32530,7 +32530,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.53711318969727</v>
+        <v>1.53711330890656</v>
       </c>
       <c r="H1109" t="n">
         <v>3750</v>
@@ -32617,7 +32617,7 @@
         <v>2</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1112" t="n">
         <v>37500</v>
@@ -32646,7 +32646,7 @@
         <v>2</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1113" t="n">
         <v>2250</v>
@@ -32762,7 +32762,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1117" t="n">
         <v>3000</v>
@@ -32791,7 +32791,7 @@
         <v>2</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1118" t="n">
         <v>32250</v>
@@ -32820,7 +32820,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.74206161499023</v>
+        <v>1.74206173419952</v>
       </c>
       <c r="H1119" t="n">
         <v>96750</v>
@@ -32878,7 +32878,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1121" t="n">
         <v>3000</v>
@@ -32907,7 +32907,7 @@
         <v>2</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1122" t="n">
         <v>1500</v>
@@ -32936,7 +32936,7 @@
         <v>2</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1123" t="n">
         <v>750</v>
@@ -32994,7 +32994,7 @@
         <v>2</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1125" t="n">
         <v>27750</v>
@@ -33023,7 +33023,7 @@
         <v>2</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1126" t="n">
         <v>82500</v>
@@ -33052,7 +33052,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1127" t="n">
         <v>1500</v>
@@ -33081,7 +33081,7 @@
         <v>2</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1128" t="n">
         <v>19500</v>
@@ -33110,7 +33110,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1129" t="n">
         <v>3000</v>
@@ -33139,7 +33139,7 @@
         <v>2</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1130" t="n">
         <v>12750</v>
@@ -33255,7 +33255,7 @@
         <v>2</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1134" t="n">
         <v>2250</v>
@@ -33284,7 +33284,7 @@
         <v>2</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H1140" t="n">
         <v>8250</v>
@@ -33545,7 +33545,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.53711318969727</v>
+        <v>1.53711330890656</v>
       </c>
       <c r="H1144" t="n">
         <v>17250</v>
@@ -33748,7 +33748,7 @@
         <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1151" t="n">
         <v>18000</v>
@@ -51850,6 +51850,35 @@
         <v>3750</v>
       </c>
       <c r="I1775" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1776">
+      <c r="A1776" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1776" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1776" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1776" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E1776" t="n">
+        <v>3</v>
+      </c>
+      <c r="F1776" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="G1776" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="H1776" t="n">
+        <v>6750</v>
+      </c>
+      <c r="I1776" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -456,7 +456,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722779273987</v>
+        <v>2.86722755432129</v>
       </c>
       <c r="H3" t="n">
         <v>428250</v>
@@ -572,7 +572,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64260625839233</v>
+        <v>2.64260649681091</v>
       </c>
       <c r="H7" t="n">
         <v>76500</v>
@@ -833,7 +833,7 @@
         <v>3.43449997901917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7503125667572</v>
+        <v>2.75031232833862</v>
       </c>
       <c r="H16" t="n">
         <v>44250</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.32327771186829</v>
+        <v>3.32327795028687</v>
       </c>
       <c r="H17" t="n">
         <v>604500</v>
@@ -891,7 +891,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558578491211</v>
+        <v>3.63558554649353</v>
       </c>
       <c r="H18" t="n">
         <v>196500</v>
@@ -1181,7 +1181,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329748153687</v>
+        <v>3.34329771995544</v>
       </c>
       <c r="H28" t="n">
         <v>18000</v>
@@ -1326,7 +1326,7 @@
         <v>3.625</v>
       </c>
       <c r="G33" t="n">
-        <v>2.90286302566528</v>
+        <v>2.90286326408386</v>
       </c>
       <c r="H33" t="n">
         <v>146250</v>
@@ -1413,7 +1413,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.97092986106873</v>
+        <v>2.9709300994873</v>
       </c>
       <c r="H36" t="n">
         <v>16500</v>
@@ -1442,7 +1442,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H37" t="n">
         <v>750</v>
@@ -1500,7 +1500,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H39" t="n">
         <v>15000</v>
@@ -1674,7 +1674,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694562911987</v>
+        <v>2.98694586753845</v>
       </c>
       <c r="H45" t="n">
         <v>13500</v>
@@ -1703,7 +1703,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694562911987</v>
+        <v>2.98694586753845</v>
       </c>
       <c r="H46" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>3.625</v>
       </c>
       <c r="G47" t="n">
-        <v>2.90286302566528</v>
+        <v>2.90286326408386</v>
       </c>
       <c r="H47" t="n">
         <v>12000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1819,7 +1819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H50" t="n">
         <v>4500</v>
@@ -1848,7 +1848,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H51" t="n">
         <v>750</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08304023742676</v>
+        <v>3.08304047584534</v>
       </c>
       <c r="H52" t="n">
         <v>29250</v>
@@ -1935,7 +1935,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.07903671264648</v>
+        <v>3.07903695106506</v>
       </c>
       <c r="H54" t="n">
         <v>13500</v>
@@ -2051,7 +2051,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H58" t="n">
         <v>3000</v>
@@ -2080,7 +2080,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H59" t="n">
         <v>12000</v>
@@ -2109,7 +2109,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2312,7 +2312,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H67" t="n">
         <v>7500</v>
@@ -2399,7 +2399,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G70" t="n">
-        <v>2.8347954750061</v>
+        <v>2.83479571342468</v>
       </c>
       <c r="H70" t="n">
         <v>1500</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670886993408</v>
+        <v>2.74670910835266</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2602,7 +2602,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>3.07903671264648</v>
+        <v>3.07903695106506</v>
       </c>
       <c r="H77" t="n">
         <v>26250</v>
@@ -2718,7 +2718,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2863,7 +2863,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866156578064</v>
+        <v>2.69866180419922</v>
       </c>
       <c r="H86" t="n">
         <v>7500</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185596466064</v>
+        <v>1.88185608386993</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3153,7 +3153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H96" t="n">
         <v>14250</v>
@@ -3182,7 +3182,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.66163885593414</v>
+        <v>1.66163897514343</v>
       </c>
       <c r="H97" t="n">
         <v>2250</v>
@@ -3211,7 +3211,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66163885593414</v>
+        <v>1.66163897514343</v>
       </c>
       <c r="H98" t="n">
         <v>750</v>
@@ -3327,7 +3327,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.677654504776</v>
+        <v>1.67765462398529</v>
       </c>
       <c r="H102" t="n">
         <v>11250</v>
@@ -3414,7 +3414,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H105" t="n">
         <v>6750</v>
@@ -3530,7 +3530,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205318450928</v>
+        <v>2.08205342292786</v>
       </c>
       <c r="H109" t="n">
         <v>8250</v>
@@ -3588,7 +3588,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H111" t="n">
         <v>28500</v>
@@ -3733,7 +3733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H116" t="n">
         <v>6750</v>
@@ -3762,7 +3762,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H117" t="n">
         <v>3750</v>
@@ -3820,7 +3820,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79475617408752</v>
+        <v>2.7947564125061</v>
       </c>
       <c r="H119" t="n">
         <v>8250</v>
@@ -4023,7 +4023,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H126" t="n">
         <v>3750</v>
@@ -4052,7 +4052,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.79475617408752</v>
+        <v>2.7947564125061</v>
       </c>
       <c r="H127" t="n">
         <v>2250</v>
@@ -4487,7 +4487,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.44240856170654</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H142" t="n">
         <v>750</v>
@@ -4516,7 +4516,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4545,7 +4545,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H144" t="n">
         <v>1500</v>
@@ -4574,7 +4574,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H145" t="n">
         <v>3000</v>
@@ -4603,7 +4603,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71868109703064</v>
+        <v>2.71868133544922</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4661,7 +4661,7 @@
         <v>3.52999997138977</v>
       </c>
       <c r="G148" t="n">
-        <v>2.82678771018982</v>
+        <v>2.8267879486084</v>
       </c>
       <c r="H148" t="n">
         <v>2250</v>
@@ -4806,7 +4806,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G153" t="n">
-        <v>2.64260625839233</v>
+        <v>2.64260649681091</v>
       </c>
       <c r="H153" t="n">
         <v>10500</v>
@@ -4864,7 +4864,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H155" t="n">
         <v>8250</v>
@@ -4893,7 +4893,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G156" t="n">
-        <v>2.5625274181366</v>
+        <v>2.56252765655518</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -5038,7 +5038,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H161" t="n">
         <v>14250</v>
@@ -5125,7 +5125,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G164" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H164" t="n">
         <v>750</v>
@@ -5154,7 +5154,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H166" t="n">
         <v>6750</v>
@@ -5328,7 +5328,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.37434148788452</v>
+        <v>2.3743417263031</v>
       </c>
       <c r="H171" t="n">
         <v>3000</v>
@@ -5357,7 +5357,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5386,7 +5386,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H173" t="n">
         <v>2250</v>
@@ -5415,7 +5415,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G176" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G179" t="n">
-        <v>2.44240856170654</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H179" t="n">
         <v>2250</v>
@@ -5821,7 +5821,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H188" t="n">
         <v>750</v>
@@ -5908,7 +5908,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G191" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H191" t="n">
         <v>1500</v>
@@ -5937,7 +5937,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826664924622</v>
       </c>
       <c r="H192" t="n">
         <v>3000</v>
@@ -5966,7 +5966,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826664924622</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G194" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826664924622</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G195" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826664924622</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.61858248710632</v>
+        <v>2.6185827255249</v>
       </c>
       <c r="H197" t="n">
         <v>139500</v>
@@ -6198,7 +6198,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G201" t="n">
-        <v>2.8347954750061</v>
+        <v>2.83479571342468</v>
       </c>
       <c r="H201" t="n">
         <v>30000</v>
@@ -6256,7 +6256,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H203" t="n">
         <v>9750</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H204" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258648872375</v>
+        <v>2.62258672714233</v>
       </c>
       <c r="H206" t="n">
         <v>8250</v>
@@ -6372,7 +6372,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258648872375</v>
+        <v>2.62258672714233</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6430,7 +6430,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H209" t="n">
         <v>2250</v>
@@ -6459,7 +6459,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H210" t="n">
         <v>3750</v>
@@ -6488,7 +6488,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>2.4824481010437</v>
+        <v>2.48244833946228</v>
       </c>
       <c r="H211" t="n">
         <v>2250</v>
@@ -6517,7 +6517,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H212" t="n">
         <v>2250</v>
@@ -6546,7 +6546,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.42639303207397</v>
+        <v>2.42639327049255</v>
       </c>
       <c r="H213" t="n">
         <v>10500</v>
@@ -6575,7 +6575,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.44240856170654</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H214" t="n">
         <v>8250</v>
@@ -6604,7 +6604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34631395339966</v>
+        <v>2.34631419181824</v>
       </c>
       <c r="H215" t="n">
         <v>5250</v>
@@ -6662,7 +6662,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.42639303207397</v>
+        <v>2.42639327049255</v>
       </c>
       <c r="H217" t="n">
         <v>11250</v>
@@ -6749,7 +6749,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.42639303207397</v>
+        <v>2.42639327049255</v>
       </c>
       <c r="H220" t="n">
         <v>750</v>
@@ -6778,7 +6778,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>2.44240856170654</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H221" t="n">
         <v>1500</v>
@@ -6836,7 +6836,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H223" t="n">
         <v>5250</v>
@@ -7097,7 +7097,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>2.34631395339966</v>
+        <v>2.34631419181824</v>
       </c>
       <c r="H232" t="n">
         <v>6000</v>
@@ -7155,7 +7155,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G234" t="n">
-        <v>2.37434148788452</v>
+        <v>2.3743417263031</v>
       </c>
       <c r="H234" t="n">
         <v>2250</v>
@@ -7271,7 +7271,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H238" t="n">
         <v>1500</v>
@@ -7300,7 +7300,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7561,7 +7561,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826664924622</v>
       </c>
       <c r="H248" t="n">
         <v>1500</v>
@@ -7590,7 +7590,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G249" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826664924622</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H253" t="n">
         <v>1500</v>
@@ -7793,7 +7793,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826664924622</v>
       </c>
       <c r="H256" t="n">
         <v>7500</v>
@@ -8083,7 +8083,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H266" t="n">
         <v>2250</v>
@@ -8112,7 +8112,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820734024048</v>
+        <v>2.23820757865906</v>
       </c>
       <c r="H267" t="n">
         <v>2250</v>
@@ -8170,7 +8170,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8837,7 +8837,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.2862548828125</v>
+        <v>2.28625512123108</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8924,7 +8924,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H295" t="n">
         <v>6000</v>
@@ -8982,7 +8982,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H297" t="n">
         <v>2250</v>
@@ -9011,7 +9011,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H298" t="n">
         <v>2250</v>
@@ -9098,7 +9098,7 @@
         <v>2.75</v>
       </c>
       <c r="G301" t="n">
-        <v>2.20217180252075</v>
+        <v>2.20217204093933</v>
       </c>
       <c r="H301" t="n">
         <v>9000</v>
@@ -9272,7 +9272,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H307" t="n">
         <v>32250</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42639303207397</v>
+        <v>2.42639327049255</v>
       </c>
       <c r="H308" t="n">
         <v>6750</v>
@@ -9388,7 +9388,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.44240856170654</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H311" t="n">
         <v>5250</v>
@@ -9475,7 +9475,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H314" t="n">
         <v>1500</v>
@@ -9504,7 +9504,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9533,7 +9533,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>2.36633372306824</v>
+        <v>2.36633396148682</v>
       </c>
       <c r="H316" t="n">
         <v>3750</v>
@@ -9765,7 +9765,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39436149597168</v>
+        <v>2.39436173439026</v>
       </c>
       <c r="H324" t="n">
         <v>7500</v>
@@ -9881,7 +9881,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G328" t="n">
-        <v>2.44240856170654</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H328" t="n">
         <v>9750</v>
@@ -9910,7 +9910,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H329" t="n">
         <v>2250</v>
@@ -9997,7 +9997,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.44240856170654</v>
+        <v>2.44240880012512</v>
       </c>
       <c r="H332" t="n">
         <v>4500</v>
@@ -10113,7 +10113,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39436149597168</v>
+        <v>2.39436173439026</v>
       </c>
       <c r="H336" t="n">
         <v>2250</v>
@@ -10171,7 +10171,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H338" t="n">
         <v>1500</v>
@@ -10200,7 +10200,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H339" t="n">
         <v>7500</v>
@@ -10287,7 +10287,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.42639303207397</v>
+        <v>2.42639327049255</v>
       </c>
       <c r="H342" t="n">
         <v>1500</v>
@@ -10432,7 +10432,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G347" t="n">
-        <v>2.66262602806091</v>
+        <v>2.66262626647949</v>
       </c>
       <c r="H347" t="n">
         <v>31500</v>
@@ -10461,7 +10461,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>2.66262602806091</v>
+        <v>2.66262626647949</v>
       </c>
       <c r="H348" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>2.66262602806091</v>
+        <v>2.66262626647949</v>
       </c>
       <c r="H350" t="n">
         <v>6000</v>
@@ -10780,7 +10780,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.61858248710632</v>
+        <v>2.6185827255249</v>
       </c>
       <c r="H359" t="n">
         <v>10500</v>
@@ -11012,7 +11012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H367" t="n">
         <v>172500</v>
@@ -11070,7 +11070,7 @@
         <v>4.03999996185303</v>
       </c>
       <c r="G369" t="n">
-        <v>3.23519039154053</v>
+        <v>3.23519062995911</v>
       </c>
       <c r="H369" t="n">
         <v>87750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11215,7 +11215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H374" t="n">
         <v>20250</v>
@@ -11302,7 +11302,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H377" t="n">
         <v>18000</v>
@@ -11331,7 +11331,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H378" t="n">
         <v>6000</v>
@@ -11360,7 +11360,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H379" t="n">
         <v>24000</v>
@@ -11389,7 +11389,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11505,7 +11505,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H384" t="n">
         <v>19500</v>
@@ -11534,7 +11534,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H385" t="n">
         <v>22500</v>
@@ -11563,7 +11563,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11737,7 +11737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H392" t="n">
         <v>5250</v>
@@ -11795,7 +11795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H394" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -11853,7 +11853,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H397" t="n">
         <v>750</v>
@@ -11911,7 +11911,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11998,7 +11998,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H401" t="n">
         <v>8250</v>
@@ -12085,7 +12085,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H404" t="n">
         <v>21000</v>
@@ -12143,7 +12143,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H406" t="n">
         <v>72750</v>
@@ -12172,7 +12172,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H407" t="n">
         <v>13500</v>
@@ -12201,7 +12201,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G408" t="n">
-        <v>3.34730100631714</v>
+        <v>3.34730124473572</v>
       </c>
       <c r="H408" t="n">
         <v>10500</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H409" t="n">
         <v>12750</v>
@@ -12317,7 +12317,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H412" t="n">
         <v>3000</v>
@@ -12346,7 +12346,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H413" t="n">
         <v>5250</v>
@@ -12462,7 +12462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H417" t="n">
         <v>3750</v>
@@ -12491,7 +12491,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H418" t="n">
         <v>8250</v>
@@ -12549,7 +12549,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H420" t="n">
         <v>2250</v>
@@ -12578,7 +12578,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H421" t="n">
         <v>3000</v>
@@ -12607,7 +12607,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H426" t="n">
         <v>5250</v>
@@ -12752,7 +12752,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G427" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H430" t="n">
         <v>7500</v>
@@ -12868,7 +12868,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H431" t="n">
         <v>9000</v>
@@ -12926,7 +12926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H433" t="n">
         <v>1500</v>
@@ -12955,7 +12955,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H434" t="n">
         <v>750</v>
@@ -12984,7 +12984,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G435" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901694297791</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H436" t="n">
         <v>4500</v>
@@ -13042,7 +13042,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H437" t="n">
         <v>750</v>
@@ -13187,7 +13187,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H442" t="n">
         <v>750</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13477,7 +13477,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13564,7 +13564,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H455" t="n">
         <v>2250</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13825,7 +13825,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H464" t="n">
         <v>4500</v>
@@ -13854,7 +13854,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -14028,7 +14028,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H471" t="n">
         <v>6750</v>
@@ -14057,7 +14057,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H472" t="n">
         <v>750</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14202,7 +14202,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H477" t="n">
         <v>6000</v>
@@ -14347,7 +14347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H482" t="n">
         <v>750</v>
@@ -14434,7 +14434,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H485" t="n">
         <v>750</v>
@@ -14463,7 +14463,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698493003845</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14753,7 +14753,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G496" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H496" t="n">
         <v>4500</v>
@@ -14782,7 +14782,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H497" t="n">
         <v>750</v>
@@ -14927,7 +14927,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H502" t="n">
         <v>3750</v>
@@ -15130,7 +15130,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H509" t="n">
         <v>4500</v>
@@ -15159,7 +15159,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H510" t="n">
         <v>9000</v>
@@ -15188,7 +15188,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15246,7 +15246,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>2.88284301757812</v>
+        <v>2.8828432559967</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -15333,7 +15333,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G516" t="n">
-        <v>2.8347954750061</v>
+        <v>2.83479571342468</v>
       </c>
       <c r="H516" t="n">
         <v>1500</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15855,7 +15855,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H534" t="n">
         <v>8250</v>
@@ -15884,7 +15884,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H535" t="n">
         <v>2250</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16087,7 +16087,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H542" t="n">
         <v>6750</v>
@@ -16116,7 +16116,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H543" t="n">
         <v>2250</v>
@@ -16174,7 +16174,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H545" t="n">
         <v>7500</v>
@@ -16290,7 +16290,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H549" t="n">
         <v>5250</v>
@@ -16348,7 +16348,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H551" t="n">
         <v>102750</v>
@@ -16377,7 +16377,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H552" t="n">
         <v>3750</v>
@@ -16406,7 +16406,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H553" t="n">
         <v>3000</v>
@@ -16522,7 +16522,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H557" t="n">
         <v>5250</v>
@@ -16551,7 +16551,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H558" t="n">
         <v>6000</v>
@@ -16580,7 +16580,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16638,7 +16638,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H561" t="n">
         <v>21750</v>
@@ -16667,7 +16667,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G562" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H562" t="n">
         <v>2250</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.35432195663452</v>
+        <v>2.3543221950531</v>
       </c>
       <c r="H567" t="n">
         <v>13500</v>
@@ -16986,7 +16986,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H573" t="n">
         <v>6750</v>
@@ -17015,7 +17015,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822734832764</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17218,7 +17218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213226318359</v>
+        <v>2.16213250160217</v>
       </c>
       <c r="H581" t="n">
         <v>15750</v>
@@ -17421,7 +17421,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.17814803123474</v>
+        <v>2.17814826965332</v>
       </c>
       <c r="H588" t="n">
         <v>8250</v>
@@ -17508,7 +17508,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.05002188682556</v>
+        <v>2.05002164840698</v>
       </c>
       <c r="H591" t="n">
         <v>11250</v>
@@ -17595,7 +17595,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98595857620239</v>
+        <v>1.98595881462097</v>
       </c>
       <c r="H594" t="n">
         <v>6000</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>2.00197410583496</v>
+        <v>2.00197434425354</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986361026764</v>
+        <v>1.88986349105835</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17682,7 +17682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587961673737</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H597" t="n">
         <v>7500</v>
@@ -18001,7 +18001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H608" t="n">
         <v>11250</v>
@@ -18030,7 +18030,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G609" t="n">
-        <v>1.61759519577026</v>
+        <v>1.61759531497955</v>
       </c>
       <c r="H609" t="n">
         <v>5250</v>
@@ -18059,7 +18059,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H610" t="n">
         <v>5250</v>
@@ -18146,7 +18146,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H613" t="n">
         <v>4500</v>
@@ -18262,7 +18262,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H617" t="n">
         <v>5250</v>
@@ -18320,7 +18320,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587961673737</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H619" t="n">
         <v>75000</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986361026764</v>
+        <v>1.88986349105835</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H625" t="n">
         <v>23250</v>
@@ -18523,7 +18523,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.7216979265213</v>
+        <v>1.72169804573059</v>
       </c>
       <c r="H626" t="n">
         <v>40500</v>
@@ -18639,7 +18639,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H630" t="n">
         <v>14250</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.7216979265213</v>
+        <v>1.72169804573059</v>
       </c>
       <c r="H631" t="n">
         <v>5250</v>
@@ -18871,7 +18871,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H638" t="n">
         <v>18000</v>
@@ -18900,7 +18900,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H639" t="n">
         <v>15750</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779289245605</v>
+        <v>1.81779277324677</v>
       </c>
       <c r="H640" t="n">
         <v>17250</v>
@@ -18958,7 +18958,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779289245605</v>
+        <v>1.81779277324677</v>
       </c>
       <c r="H641" t="n">
         <v>167250</v>
@@ -51879,6 +51879,35 @@
         <v>6750</v>
       </c>
       <c r="I1776" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1777">
+      <c r="A1777" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1777" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1777" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1777" t="n">
+        <v>3.04999995231628</v>
+      </c>
+      <c r="E1777" t="n">
+        <v>3.00999999046326</v>
+      </c>
+      <c r="F1777" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="G1777" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="H1777" t="n">
+        <v>9000</v>
+      </c>
+      <c r="I1777" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189425468445</v>
+        <v>2.73189449310303</v>
       </c>
       <c r="H2" t="n">
         <v>893250</v>
@@ -485,7 +485,7 @@
         <v>3.50550007820129</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80716848373413</v>
+        <v>2.80716872215271</v>
       </c>
       <c r="H4" t="n">
         <v>86250</v>
@@ -543,7 +543,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7058687210083</v>
+        <v>2.70586848258972</v>
       </c>
       <c r="H6" t="n">
         <v>35250</v>
@@ -572,7 +572,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G7" t="n">
-        <v>2.64260649681091</v>
+        <v>2.64260625839233</v>
       </c>
       <c r="H7" t="n">
         <v>76500</v>
@@ -601,7 +601,7 @@
         <v>3.38949990272522</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71427702903748</v>
+        <v>2.7142767906189</v>
       </c>
       <c r="H8" t="n">
         <v>111000</v>
@@ -630,7 +630,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G9" t="n">
-        <v>2.7511134147644</v>
+        <v>2.75111317634583</v>
       </c>
       <c r="H9" t="n">
         <v>62250</v>
@@ -659,7 +659,7 @@
         <v>3.43650007247925</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75191426277161</v>
+        <v>2.75191402435303</v>
       </c>
       <c r="H10" t="n">
         <v>33750</v>
@@ -688,7 +688,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G11" t="n">
-        <v>2.6906533241272</v>
+        <v>2.69065356254578</v>
       </c>
       <c r="H11" t="n">
         <v>9000</v>
@@ -775,7 +775,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72228479385376</v>
+        <v>2.72228455543518</v>
       </c>
       <c r="H14" t="n">
         <v>7500</v>
@@ -833,7 +833,7 @@
         <v>3.43449997901917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.75031232833862</v>
+        <v>2.7503125667572</v>
       </c>
       <c r="H16" t="n">
         <v>44250</v>
@@ -862,7 +862,7 @@
         <v>4.15000009536743</v>
       </c>
       <c r="G17" t="n">
-        <v>3.32327795028687</v>
+        <v>3.32327771186829</v>
       </c>
       <c r="H17" t="n">
         <v>604500</v>
@@ -949,7 +949,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578300476074</v>
+        <v>3.83578324317932</v>
       </c>
       <c r="H20" t="n">
         <v>495750</v>
@@ -1007,7 +1007,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>3.43538784980774</v>
+        <v>3.43538808822632</v>
       </c>
       <c r="H22" t="n">
         <v>193500</v>
@@ -1181,7 +1181,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329771995544</v>
+        <v>3.34329748153687</v>
       </c>
       <c r="H28" t="n">
         <v>18000</v>
@@ -1239,7 +1239,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128499984741</v>
+        <v>3.33128523826599</v>
       </c>
       <c r="H30" t="n">
         <v>9000</v>
@@ -1268,7 +1268,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048439025879</v>
+        <v>3.33048462867737</v>
       </c>
       <c r="H31" t="n">
         <v>6750</v>
@@ -1326,7 +1326,7 @@
         <v>3.625</v>
       </c>
       <c r="G33" t="n">
-        <v>2.90286326408386</v>
+        <v>2.90286302566528</v>
       </c>
       <c r="H33" t="n">
         <v>146250</v>
@@ -1413,7 +1413,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.9709300994873</v>
+        <v>2.97093033790588</v>
       </c>
       <c r="H36" t="n">
         <v>16500</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H38" t="n">
         <v>27000</v>
@@ -1529,7 +1529,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H40" t="n">
         <v>3000</v>
@@ -1558,7 +1558,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H41" t="n">
         <v>9750</v>
@@ -1587,7 +1587,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1732,7 +1732,7 @@
         <v>3.625</v>
       </c>
       <c r="G47" t="n">
-        <v>2.90286326408386</v>
+        <v>2.90286302566528</v>
       </c>
       <c r="H47" t="n">
         <v>12000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1906,7 +1906,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H53" t="n">
         <v>9000</v>
@@ -1935,7 +1935,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.07903695106506</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H54" t="n">
         <v>13500</v>
@@ -1964,7 +1964,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H55" t="n">
         <v>2250</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507201194763</v>
       </c>
       <c r="H56" t="n">
         <v>18750</v>
@@ -2022,7 +2022,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702446937561</v>
+        <v>3.06702470779419</v>
       </c>
       <c r="H57" t="n">
         <v>18750</v>
@@ -2138,7 +2138,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507201194763</v>
       </c>
       <c r="H61" t="n">
         <v>5250</v>
@@ -2167,7 +2167,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505248069763</v>
+        <v>3.09505224227905</v>
       </c>
       <c r="H62" t="n">
         <v>4500</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087055206299</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H65" t="n">
         <v>9750</v>
@@ -2370,7 +2370,7 @@
         <v>3.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276393890381</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2428,7 +2428,7 @@
         <v>3.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276393890381</v>
       </c>
       <c r="H71" t="n">
         <v>750</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670910835266</v>
+        <v>2.74670886993408</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2486,7 +2486,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467709541321</v>
       </c>
       <c r="H73" t="n">
         <v>17250</v>
@@ -2515,7 +2515,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H74" t="n">
         <v>15000</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H76" t="n">
         <v>24000</v>
@@ -2602,7 +2602,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>3.07903695106506</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H77" t="n">
         <v>26250</v>
@@ -2660,7 +2660,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H79" t="n">
         <v>7500</v>
@@ -2747,7 +2747,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087055206299</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H82" t="n">
         <v>7500</v>
@@ -2776,7 +2776,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G83" t="n">
-        <v>2.88684701919556</v>
+        <v>2.88684725761414</v>
       </c>
       <c r="H83" t="n">
         <v>5250</v>
@@ -2805,7 +2805,7 @@
         <v>3.60500001907349</v>
       </c>
       <c r="G84" t="n">
-        <v>2.88684701919556</v>
+        <v>2.88684725761414</v>
       </c>
       <c r="H84" t="n">
         <v>0</v>
@@ -2834,7 +2834,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80676817893982</v>
+        <v>2.8067684173584</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2863,7 +2863,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866180419922</v>
+        <v>2.69866132736206</v>
       </c>
       <c r="H86" t="n">
         <v>7500</v>
@@ -2950,7 +2950,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.53049564361572</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H90" t="n">
         <v>10500</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185608386993</v>
+        <v>1.88185584545135</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3124,7 +3124,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.57755589485168</v>
+        <v>1.5775557756424</v>
       </c>
       <c r="H95" t="n">
         <v>9000</v>
@@ -3153,7 +3153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H96" t="n">
         <v>14250</v>
@@ -3182,7 +3182,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G97" t="n">
-        <v>1.66163897514343</v>
+        <v>1.66163885593414</v>
       </c>
       <c r="H97" t="n">
         <v>2250</v>
@@ -3211,7 +3211,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G98" t="n">
-        <v>1.66163897514343</v>
+        <v>1.66163885593414</v>
       </c>
       <c r="H98" t="n">
         <v>750</v>
@@ -3269,7 +3269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161908626556</v>
+        <v>1.64161896705627</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3298,7 +3298,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G101" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H101" t="n">
         <v>6750</v>
@@ -3356,7 +3356,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771381378174</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H103" t="n">
         <v>12000</v>
@@ -3385,7 +3385,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75773346424103</v>
+        <v>1.75773334503174</v>
       </c>
       <c r="H104" t="n">
         <v>12000</v>
@@ -3414,7 +3414,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H105" t="n">
         <v>6750</v>
@@ -3443,7 +3443,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G106" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H106" t="n">
         <v>2250</v>
@@ -3472,7 +3472,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771381378174</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H107" t="n">
         <v>750</v>
@@ -3559,7 +3559,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.53049564361572</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H110" t="n">
         <v>16500</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H116" t="n">
         <v>6750</v>
@@ -3762,7 +3762,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H117" t="n">
         <v>3750</v>
@@ -3878,7 +3878,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G121" t="n">
-        <v>2.74270486831665</v>
+        <v>2.74270462989807</v>
       </c>
       <c r="H121" t="n">
         <v>750</v>
@@ -3907,7 +3907,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>2.66662979125977</v>
+        <v>2.66663002967834</v>
       </c>
       <c r="H122" t="n">
         <v>3750</v>
@@ -3965,7 +3965,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467709541321</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -4023,7 +4023,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H126" t="n">
         <v>3750</v>
@@ -4197,7 +4197,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G132" t="n">
-        <v>2.61057448387146</v>
+        <v>2.61057472229004</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4400,7 +4400,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856271743774</v>
+        <v>2.59856295585632</v>
       </c>
       <c r="H139" t="n">
         <v>1500</v>
@@ -4545,7 +4545,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H144" t="n">
         <v>1500</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4690,7 +4690,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74270486831665</v>
+        <v>2.74270462989807</v>
       </c>
       <c r="H149" t="n">
         <v>3750</v>
@@ -4719,7 +4719,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G150" t="n">
-        <v>2.6906533241272</v>
+        <v>2.69065356254578</v>
       </c>
       <c r="H150" t="n">
         <v>1500</v>
@@ -4748,7 +4748,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G151" t="n">
-        <v>2.6906533241272</v>
+        <v>2.69065356254578</v>
       </c>
       <c r="H151" t="n">
         <v>1500</v>
@@ -4806,7 +4806,7 @@
         <v>3.29999995231628</v>
       </c>
       <c r="G153" t="n">
-        <v>2.64260649681091</v>
+        <v>2.64260625839233</v>
       </c>
       <c r="H153" t="n">
         <v>10500</v>
@@ -4893,7 +4893,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G156" t="n">
-        <v>2.56252765655518</v>
+        <v>2.56252717971802</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -4922,7 +4922,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>2.76272487640381</v>
+        <v>2.76272463798523</v>
       </c>
       <c r="H157" t="n">
         <v>11250</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>2.50647211074829</v>
+        <v>2.50647187232971</v>
       </c>
       <c r="H163" t="n">
         <v>6750</v>
@@ -5212,7 +5212,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H167" t="n">
         <v>15000</v>
@@ -5328,7 +5328,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H171" t="n">
         <v>3000</v>
@@ -5357,7 +5357,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G172" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H172" t="n">
         <v>4500</v>
@@ -5502,7 +5502,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H177" t="n">
         <v>3750</v>
@@ -5531,7 +5531,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5647,7 +5647,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H182" t="n">
         <v>750</v>
@@ -5821,7 +5821,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G188" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H188" t="n">
         <v>750</v>
@@ -5850,7 +5850,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.33029818534851</v>
+        <v>2.33029794692993</v>
       </c>
       <c r="H189" t="n">
         <v>3750</v>
@@ -5879,7 +5879,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33029818534851</v>
+        <v>2.33029794692993</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G191" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H191" t="n">
         <v>1500</v>
@@ -5937,7 +5937,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H192" t="n">
         <v>3000</v>
@@ -5966,7 +5966,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G194" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G195" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6140,7 +6140,7 @@
         <v>3.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276393890381</v>
       </c>
       <c r="H199" t="n">
         <v>148500</v>
@@ -6227,7 +6227,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G202" t="n">
-        <v>2.6906533241272</v>
+        <v>2.69065356254578</v>
       </c>
       <c r="H202" t="n">
         <v>45000</v>
@@ -6256,7 +6256,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264532089233</v>
       </c>
       <c r="H203" t="n">
         <v>9750</v>
@@ -6314,7 +6314,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451917648315</v>
+        <v>2.55451965332031</v>
       </c>
       <c r="H205" t="n">
         <v>13500</v>
@@ -6343,7 +6343,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H206" t="n">
         <v>8250</v>
@@ -6372,7 +6372,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H212" t="n">
         <v>2250</v>
@@ -6546,7 +6546,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.42639327049255</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H213" t="n">
         <v>10500</v>
@@ -6604,7 +6604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H215" t="n">
         <v>5250</v>
@@ -6633,7 +6633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6662,7 +6662,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.42639327049255</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H217" t="n">
         <v>11250</v>
@@ -6691,7 +6691,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>2.33029818534851</v>
+        <v>2.33029794692993</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.42639327049255</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H220" t="n">
         <v>750</v>
@@ -6807,7 +6807,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.494460105896</v>
+        <v>2.49446034431458</v>
       </c>
       <c r="H222" t="n">
         <v>6750</v>
@@ -6865,7 +6865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6894,7 +6894,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H225" t="n">
         <v>5250</v>
@@ -7010,7 +7010,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>2.35031795501709</v>
+        <v>2.35031771659851</v>
       </c>
       <c r="H229" t="n">
         <v>18750</v>
@@ -7039,7 +7039,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832571983337</v>
       </c>
       <c r="H230" t="n">
         <v>750</v>
@@ -7097,7 +7097,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H232" t="n">
         <v>6000</v>
@@ -7126,7 +7126,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.33029818534851</v>
+        <v>2.33029794692993</v>
       </c>
       <c r="H233" t="n">
         <v>3750</v>
@@ -7155,7 +7155,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G234" t="n">
-        <v>2.3743417263031</v>
+        <v>2.37434148788452</v>
       </c>
       <c r="H234" t="n">
         <v>2250</v>
@@ -7271,7 +7271,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H238" t="n">
         <v>1500</v>
@@ -7300,7 +7300,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832571983337</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G241" t="n">
-        <v>2.35832595825195</v>
+        <v>2.35832571983337</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G244" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H244" t="n">
         <v>4500</v>
@@ -7532,7 +7532,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H247" t="n">
         <v>1500</v>
@@ -7561,7 +7561,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H248" t="n">
         <v>1500</v>
@@ -7590,7 +7590,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G249" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G250" t="n">
-        <v>2.39836525917053</v>
+        <v>2.39836502075195</v>
       </c>
       <c r="H250" t="n">
         <v>3000</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635325431824</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635325431824</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7706,7 +7706,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G253" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H253" t="n">
         <v>1500</v>
@@ -7793,7 +7793,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.29826664924622</v>
+        <v>2.29826641082764</v>
       </c>
       <c r="H256" t="n">
         <v>7500</v>
@@ -7967,7 +7967,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H262" t="n">
         <v>2250</v>
@@ -7996,7 +7996,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H263" t="n">
         <v>750</v>
@@ -8083,7 +8083,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H266" t="n">
         <v>2250</v>
@@ -8112,7 +8112,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820757865906</v>
+        <v>2.23820734024048</v>
       </c>
       <c r="H267" t="n">
         <v>2250</v>
@@ -8141,7 +8141,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8170,7 +8170,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.26623511314392</v>
+        <v>2.26623487472534</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8257,7 +8257,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H272" t="n">
         <v>2250</v>
@@ -8286,7 +8286,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8344,7 +8344,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H275" t="n">
         <v>12000</v>
@@ -8373,7 +8373,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H276" t="n">
         <v>3000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H289" t="n">
         <v>750</v>
@@ -8779,7 +8779,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H290" t="n">
         <v>750</v>
@@ -8808,7 +8808,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.28625512123108</v>
+        <v>2.28625464439392</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -9040,7 +9040,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H299" t="n">
         <v>3000</v>
@@ -9069,7 +9069,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H300" t="n">
         <v>750</v>
@@ -9127,7 +9127,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H302" t="n">
         <v>3000</v>
@@ -9156,7 +9156,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G304" t="n">
-        <v>2.73069334030151</v>
+        <v>2.73069310188293</v>
       </c>
       <c r="H304" t="n">
         <v>120750</v>
@@ -9243,7 +9243,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>2.60657072067261</v>
+        <v>2.60657095909119</v>
       </c>
       <c r="H306" t="n">
         <v>45000</v>
@@ -9272,7 +9272,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H307" t="n">
         <v>32250</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42639327049255</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H308" t="n">
         <v>6750</v>
@@ -9330,7 +9330,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039703369141</v>
+        <v>2.43039727210999</v>
       </c>
       <c r="H309" t="n">
         <v>17250</v>
@@ -9417,7 +9417,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045610427856</v>
+        <v>2.49045634269714</v>
       </c>
       <c r="H312" t="n">
         <v>5250</v>
@@ -9533,7 +9533,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>2.36633396148682</v>
+        <v>2.36633372306824</v>
       </c>
       <c r="H316" t="n">
         <v>3750</v>
@@ -9562,7 +9562,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H317" t="n">
         <v>3750</v>
@@ -9591,7 +9591,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H319" t="n">
         <v>3750</v>
@@ -9649,7 +9649,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430194854736</v>
+        <v>2.33430218696594</v>
       </c>
       <c r="H320" t="n">
         <v>750</v>
@@ -9765,7 +9765,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G324" t="n">
-        <v>2.39436173439026</v>
+        <v>2.39436149597168</v>
       </c>
       <c r="H324" t="n">
         <v>7500</v>
@@ -9794,7 +9794,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H325" t="n">
         <v>13500</v>
@@ -9968,7 +9968,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G331" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H331" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H333" t="n">
         <v>9000</v>
@@ -10113,7 +10113,7 @@
         <v>2.99000000953674</v>
       </c>
       <c r="G336" t="n">
-        <v>2.39436173439026</v>
+        <v>2.39436149597168</v>
       </c>
       <c r="H336" t="n">
         <v>2250</v>
@@ -10142,7 +10142,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.43840479850769</v>
+        <v>2.43840503692627</v>
       </c>
       <c r="H337" t="n">
         <v>3750</v>
@@ -10200,7 +10200,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G339" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H339" t="n">
         <v>7500</v>
@@ -10229,7 +10229,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G340" t="n">
-        <v>2.50647211074829</v>
+        <v>2.50647187232971</v>
       </c>
       <c r="H340" t="n">
         <v>29250</v>
@@ -10287,7 +10287,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.42639327049255</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H342" t="n">
         <v>1500</v>
@@ -10374,7 +10374,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>2.55051517486572</v>
+        <v>2.5505154132843</v>
       </c>
       <c r="H345" t="n">
         <v>26250</v>
@@ -10432,7 +10432,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G347" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H347" t="n">
         <v>31500</v>
@@ -10461,7 +10461,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G348" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H348" t="n">
         <v>2250</v>
@@ -10519,7 +10519,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G350" t="n">
-        <v>2.66262626647949</v>
+        <v>2.66262602806091</v>
       </c>
       <c r="H350" t="n">
         <v>6000</v>
@@ -10577,7 +10577,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451917648315</v>
+        <v>2.55451965332031</v>
       </c>
       <c r="H352" t="n">
         <v>4500</v>
@@ -10606,7 +10606,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.53049564361572</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H353" t="n">
         <v>750</v>
@@ -10635,7 +10635,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G354" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H354" t="n">
         <v>4500</v>
@@ -10664,7 +10664,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>2.67063403129578</v>
+        <v>2.6706337928772</v>
       </c>
       <c r="H355" t="n">
         <v>14250</v>
@@ -10722,7 +10722,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>2.66662979125977</v>
+        <v>2.66663002967834</v>
       </c>
       <c r="H357" t="n">
         <v>4500</v>
@@ -10809,7 +10809,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467709541321</v>
       </c>
       <c r="H360" t="n">
         <v>10500</v>
@@ -10983,7 +10983,7 @@
         <v>3.5</v>
       </c>
       <c r="G366" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276393890381</v>
       </c>
       <c r="H366" t="n">
         <v>25500</v>
@@ -11041,7 +11041,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H368" t="n">
         <v>210750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11244,7 +11244,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H375" t="n">
         <v>3750</v>
@@ -11273,7 +11273,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H376" t="n">
         <v>39000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11592,7 +11592,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H387" t="n">
         <v>3750</v>
@@ -11708,7 +11708,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G391" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11911,7 +11911,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -12056,7 +12056,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H403" t="n">
         <v>38250</v>
@@ -12114,7 +12114,7 @@
         <v>4.28000020980835</v>
       </c>
       <c r="G405" t="n">
-        <v>3.42738056182861</v>
+        <v>3.42738032341003</v>
       </c>
       <c r="H405" t="n">
         <v>54750</v>
@@ -12259,7 +12259,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511155128479</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12404,7 +12404,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.13909578323364</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H415" t="n">
         <v>2250</v>
@@ -12433,7 +12433,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511155128479</v>
       </c>
       <c r="H416" t="n">
         <v>3750</v>
@@ -12694,7 +12694,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511155128479</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12839,7 +12839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H430" t="n">
         <v>7500</v>
@@ -12897,7 +12897,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G432" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H432" t="n">
         <v>4500</v>
@@ -12926,7 +12926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H433" t="n">
         <v>1500</v>
@@ -13013,7 +13013,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H436" t="n">
         <v>4500</v>
@@ -13071,7 +13071,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G438" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H438" t="n">
         <v>7500</v>
@@ -13100,7 +13100,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G439" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H439" t="n">
         <v>3000</v>
@@ -13129,7 +13129,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G440" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H440" t="n">
         <v>0</v>
@@ -13158,7 +13158,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G441" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H441" t="n">
         <v>0</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13419,7 +13419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H450" t="n">
         <v>1500</v>
@@ -13448,7 +13448,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G451" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H451" t="n">
         <v>3000</v>
@@ -13506,7 +13506,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H453" t="n">
         <v>1500</v>
@@ -13593,7 +13593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G456" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H456" t="n">
         <v>3750</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H458" t="n">
         <v>3750</v>
@@ -13709,7 +13709,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G460" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H460" t="n">
         <v>1500</v>
@@ -13738,7 +13738,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H461" t="n">
         <v>1500</v>
@@ -13767,7 +13767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H463" t="n">
         <v>3000</v>
@@ -13883,7 +13883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H466" t="n">
         <v>9750</v>
@@ -13912,7 +13912,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H467" t="n">
         <v>750</v>
@@ -13941,7 +13941,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G468" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H469" t="n">
         <v>1500</v>
@@ -13999,7 +13999,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H470" t="n">
         <v>2250</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14260,7 +14260,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H479" t="n">
         <v>6000</v>
@@ -14289,7 +14289,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G480" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H480" t="n">
         <v>3750</v>
@@ -14318,7 +14318,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G481" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H481" t="n">
         <v>750</v>
@@ -14405,7 +14405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H484" t="n">
         <v>2250</v>
@@ -14492,7 +14492,7 @@
         <v>3.74000000953674</v>
       </c>
       <c r="G487" t="n">
-        <v>2.99495363235474</v>
+        <v>2.99495387077332</v>
       </c>
       <c r="H487" t="n">
         <v>6000</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14579,7 +14579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G490" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H490" t="n">
         <v>750</v>
@@ -14608,7 +14608,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H492" t="n">
         <v>750</v>
@@ -14695,7 +14695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H494" t="n">
         <v>2250</v>
@@ -14869,7 +14869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H500" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089032173157</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H508" t="n">
         <v>4500</v>
@@ -15275,7 +15275,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H514" t="n">
         <v>5250</v>
@@ -15362,7 +15362,7 @@
         <v>3.5</v>
       </c>
       <c r="G517" t="n">
-        <v>2.80276417732239</v>
+        <v>2.80276393890381</v>
       </c>
       <c r="H517" t="n">
         <v>6750</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15652,7 +15652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15681,7 +15681,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846386909485</v>
+        <v>2.49846434593201</v>
       </c>
       <c r="H528" t="n">
         <v>5250</v>
@@ -15739,7 +15739,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H530" t="n">
         <v>5250</v>
@@ -15768,7 +15768,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H531" t="n">
         <v>3000</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635325431824</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15826,7 +15826,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H533" t="n">
         <v>15000</v>
@@ -15884,7 +15884,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G535" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H535" t="n">
         <v>2250</v>
@@ -16000,7 +16000,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H539" t="n">
         <v>24750</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635325431824</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16087,7 +16087,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G542" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H542" t="n">
         <v>6750</v>
@@ -16116,7 +16116,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G543" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H543" t="n">
         <v>2250</v>
@@ -16145,7 +16145,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H544" t="n">
         <v>750</v>
@@ -16203,7 +16203,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H546" t="n">
         <v>8250</v>
@@ -16319,7 +16319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16406,7 +16406,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G553" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H553" t="n">
         <v>3000</v>
@@ -16493,7 +16493,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H556" t="n">
         <v>3750</v>
@@ -16638,7 +16638,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G561" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H561" t="n">
         <v>21750</v>
@@ -16667,7 +16667,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G562" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H562" t="n">
         <v>2250</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635325431824</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16812,7 +16812,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G567" t="n">
-        <v>2.3543221950531</v>
+        <v>2.35432195663452</v>
       </c>
       <c r="H567" t="n">
         <v>13500</v>
@@ -16928,7 +16928,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H571" t="n">
         <v>7500</v>
@@ -16957,7 +16957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H572" t="n">
         <v>3000</v>
@@ -16986,7 +16986,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H573" t="n">
         <v>6750</v>
@@ -17015,7 +17015,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822734832764</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H576" t="n">
         <v>3000</v>
@@ -17218,7 +17218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213250160217</v>
+        <v>2.16213226318359</v>
       </c>
       <c r="H581" t="n">
         <v>15750</v>
@@ -17247,7 +17247,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.09806895256042</v>
+        <v>2.098069190979</v>
       </c>
       <c r="H582" t="n">
         <v>18000</v>
@@ -17276,7 +17276,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G583" t="n">
-        <v>2.09806895256042</v>
+        <v>2.098069190979</v>
       </c>
       <c r="H583" t="n">
         <v>15750</v>
@@ -17305,7 +17305,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.09806895256042</v>
+        <v>2.098069190979</v>
       </c>
       <c r="H584" t="n">
         <v>4500</v>
@@ -17334,7 +17334,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G585" t="n">
-        <v>2.11408495903015</v>
+        <v>2.11408519744873</v>
       </c>
       <c r="H585" t="n">
         <v>6000</v>
@@ -17363,7 +17363,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400611877441</v>
+        <v>2.03400564193726</v>
       </c>
       <c r="H586" t="n">
         <v>6000</v>
@@ -17392,7 +17392,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G587" t="n">
-        <v>2.11408495903015</v>
+        <v>2.11408519744873</v>
       </c>
       <c r="H587" t="n">
         <v>3000</v>
@@ -17479,7 +17479,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G590" t="n">
-        <v>2.11408495903015</v>
+        <v>2.11408519744873</v>
       </c>
       <c r="H590" t="n">
         <v>10500</v>
@@ -17537,7 +17537,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400611877441</v>
+        <v>2.03400564193726</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17595,7 +17595,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98595881462097</v>
+        <v>1.98595857620239</v>
       </c>
       <c r="H594" t="n">
         <v>6000</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986349105835</v>
+        <v>1.8898640871048</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17740,7 +17740,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G599" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H599" t="n">
         <v>12000</v>
@@ -17798,7 +17798,7 @@
         <v>1.87000000476837</v>
       </c>
       <c r="G601" t="n">
-        <v>1.49747681617737</v>
+        <v>1.49747693538666</v>
       </c>
       <c r="H601" t="n">
         <v>16500</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.6336110830307</v>
+        <v>1.63361120223999</v>
       </c>
       <c r="H604" t="n">
         <v>1500</v>
@@ -17914,7 +17914,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.66564249992371</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H605" t="n">
         <v>3750</v>
@@ -17943,7 +17943,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H606" t="n">
         <v>14250</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H608" t="n">
         <v>11250</v>
@@ -18059,7 +18059,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H610" t="n">
         <v>5250</v>
@@ -18088,7 +18088,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G611" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H611" t="n">
         <v>4500</v>
@@ -18146,7 +18146,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H613" t="n">
         <v>4500</v>
@@ -18175,7 +18175,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H614" t="n">
         <v>4500</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.69767415523529</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H615" t="n">
         <v>5250</v>
@@ -18262,7 +18262,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H617" t="n">
         <v>5250</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986349105835</v>
+        <v>1.8898640871048</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18378,7 +18378,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.95392727851868</v>
+        <v>1.9539270401001</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18436,7 +18436,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962685108185</v>
+        <v>1.64962697029114</v>
       </c>
       <c r="H623" t="n">
         <v>186750</v>
@@ -18465,7 +18465,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66564249992371</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H624" t="n">
         <v>174750</v>
@@ -18639,7 +18639,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H630" t="n">
         <v>14250</v>
@@ -18813,7 +18813,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G636" t="n">
-        <v>1.71369028091431</v>
+        <v>1.71369016170502</v>
       </c>
       <c r="H636" t="n">
         <v>1500</v>
@@ -18842,7 +18842,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771381378174</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H637" t="n">
         <v>7500</v>
@@ -18871,7 +18871,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H638" t="n">
         <v>18000</v>
@@ -18987,7 +18987,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.7537294626236</v>
+        <v>1.75372958183289</v>
       </c>
       <c r="H642" t="n">
         <v>8250</v>
@@ -19016,7 +19016,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.83380842208862</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H643" t="n">
         <v>15000</v>
@@ -19045,7 +19045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>1.8174352645874</v>
+        <v>1.81743538379669</v>
       </c>
       <c r="H644" t="n">
         <v>18000</v>
@@ -19190,7 +19190,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.85018193721771</v>
+        <v>1.85018181800842</v>
       </c>
       <c r="H649" t="n">
         <v>5250</v>
@@ -19219,7 +19219,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.80106210708618</v>
+        <v>1.80106198787689</v>
       </c>
       <c r="H650" t="n">
         <v>12000</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474167346954</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H651" t="n">
         <v>33750</v>
@@ -19277,7 +19277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836863517761</v>
+        <v>1.8583687543869</v>
       </c>
       <c r="H652" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836863517761</v>
+        <v>1.8583687543869</v>
       </c>
       <c r="H653" t="n">
         <v>4500</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H654" t="n">
         <v>9750</v>
@@ -19364,7 +19364,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79287528991699</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194203853607</v>
       </c>
       <c r="H658" t="n">
         <v>11250</v>
@@ -19509,7 +19509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194203853607</v>
       </c>
       <c r="H660" t="n">
         <v>12000</v>
@@ -19567,7 +19567,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474167346954</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H662" t="n">
         <v>7500</v>
@@ -19596,7 +19596,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.83380854129791</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H663" t="n">
         <v>21750</v>
@@ -19654,7 +19654,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.83380854129791</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H665" t="n">
         <v>15750</v>
@@ -19683,7 +19683,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.82562208175659</v>
+        <v>1.82562184333801</v>
       </c>
       <c r="H666" t="n">
         <v>4500</v>
@@ -19712,7 +19712,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>1.79287528991699</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H667" t="n">
         <v>5250</v>
@@ -19741,7 +19741,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>1.79287528991699</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H668" t="n">
         <v>10500</v>
@@ -19770,7 +19770,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G669" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H669" t="n">
         <v>6750</v>
@@ -19799,7 +19799,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H670" t="n">
         <v>15750</v>
@@ -20118,7 +20118,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H681" t="n">
         <v>750</v>
@@ -20176,7 +20176,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H683" t="n">
         <v>8250</v>
@@ -20234,7 +20234,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H685" t="n">
         <v>4500</v>
@@ -20292,7 +20292,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194203853607</v>
       </c>
       <c r="H687" t="n">
         <v>34500</v>
@@ -20321,7 +20321,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H688" t="n">
         <v>19500</v>
@@ -20437,7 +20437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H699" t="n">
         <v>1500</v>
@@ -20669,7 +20669,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G700" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G701" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H701" t="n">
         <v>750</v>
@@ -20843,7 +20843,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.79287528991699</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H706" t="n">
         <v>750</v>
@@ -20872,7 +20872,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H707" t="n">
         <v>2250</v>
@@ -20901,7 +20901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21104,7 +21104,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79287528991699</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H715" t="n">
         <v>3000</v>
@@ -21162,7 +21162,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H717" t="n">
         <v>7500</v>
@@ -21191,7 +21191,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H718" t="n">
         <v>2250</v>
@@ -21220,7 +21220,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H720" t="n">
         <v>3000</v>
@@ -21278,7 +21278,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21510,7 +21510,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G729" t="n">
-        <v>1.64551568031311</v>
+        <v>1.6455157995224</v>
       </c>
       <c r="H729" t="n">
         <v>3000</v>
@@ -21597,7 +21597,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G732" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H732" t="n">
         <v>2250</v>
@@ -21626,7 +21626,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G733" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21771,7 +21771,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G738" t="n">
-        <v>1.54318273067474</v>
+        <v>1.54318261146545</v>
       </c>
       <c r="H738" t="n">
         <v>12750</v>
@@ -22090,7 +22090,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.56364941596985</v>
+        <v>1.56364929676056</v>
       </c>
       <c r="H749" t="n">
         <v>6750</v>
@@ -22206,7 +22206,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22235,7 +22235,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -22264,7 +22264,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359621524811</v>
+        <v>1.47359609603882</v>
       </c>
       <c r="H755" t="n">
         <v>6000</v>
@@ -22641,7 +22641,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G768" t="n">
-        <v>1.56364941596985</v>
+        <v>1.56364929676056</v>
       </c>
       <c r="H768" t="n">
         <v>1500</v>
@@ -22670,7 +22670,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G769" t="n">
-        <v>1.52271616458893</v>
+        <v>1.52271604537964</v>
       </c>
       <c r="H769" t="n">
         <v>3750</v>
@@ -22699,7 +22699,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G770" t="n">
-        <v>1.52271616458893</v>
+        <v>1.52271604537964</v>
       </c>
       <c r="H770" t="n">
         <v>3750</v>
@@ -22960,7 +22960,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194203853607</v>
       </c>
       <c r="H779" t="n">
         <v>21750</v>
@@ -22989,7 +22989,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.82562208175659</v>
+        <v>1.82562184333801</v>
       </c>
       <c r="H780" t="n">
         <v>60000</v>
@@ -23018,7 +23018,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H781" t="n">
         <v>11250</v>
@@ -23047,7 +23047,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H782" t="n">
         <v>7500</v>
@@ -23076,7 +23076,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H784" t="n">
         <v>2250</v>
@@ -23221,7 +23221,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>1.80106210708618</v>
+        <v>1.80106198787689</v>
       </c>
       <c r="H788" t="n">
         <v>35250</v>
@@ -23279,7 +23279,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23308,7 +23308,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194203853607</v>
       </c>
       <c r="H791" t="n">
         <v>8250</v>
@@ -23337,7 +23337,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194203853607</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G794" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H794" t="n">
         <v>750</v>
@@ -23424,7 +23424,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G795" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H795" t="n">
         <v>750</v>
@@ -23453,7 +23453,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H796" t="n">
         <v>1500</v>
@@ -23482,7 +23482,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H797" t="n">
         <v>2250</v>
@@ -23598,7 +23598,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H801" t="n">
         <v>12750</v>
@@ -23685,7 +23685,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H804" t="n">
         <v>9750</v>
@@ -23714,7 +23714,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H805" t="n">
         <v>45750</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H806" t="n">
         <v>3000</v>
@@ -23772,7 +23772,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G807" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H807" t="n">
         <v>2250</v>
@@ -23801,7 +23801,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H808" t="n">
         <v>750</v>
@@ -23830,7 +23830,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G810" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23946,7 +23946,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H813" t="n">
         <v>5250</v>
@@ -23975,7 +23975,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80106210708618</v>
+        <v>1.80106198787689</v>
       </c>
       <c r="H814" t="n">
         <v>9000</v>
@@ -24033,7 +24033,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842171669006</v>
+        <v>1.94842183589935</v>
       </c>
       <c r="H816" t="n">
         <v>13500</v>
@@ -24062,7 +24062,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748858451843</v>
       </c>
       <c r="H817" t="n">
         <v>76500</v>
@@ -24178,7 +24178,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748858451843</v>
       </c>
       <c r="H821" t="n">
         <v>2250</v>
@@ -24265,7 +24265,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H824" t="n">
         <v>65250</v>
@@ -24294,7 +24294,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H825" t="n">
         <v>78000</v>
@@ -24323,7 +24323,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H826" t="n">
         <v>27000</v>
@@ -24352,7 +24352,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G827" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H827" t="n">
         <v>60000</v>
@@ -24381,7 +24381,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748846530914</v>
+        <v>1.90748858451843</v>
       </c>
       <c r="H828" t="n">
         <v>11250</v>
@@ -24410,7 +24410,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H829" t="n">
         <v>36000</v>
@@ -24439,7 +24439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H830" t="n">
         <v>53250</v>
@@ -24497,7 +24497,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034130096436</v>
+        <v>2.12034106254578</v>
       </c>
       <c r="H832" t="n">
         <v>2250</v>
@@ -24526,7 +24526,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H833" t="n">
         <v>6750</v>
@@ -24555,7 +24555,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847455978394</v>
       </c>
       <c r="H834" t="n">
         <v>3000</v>
@@ -24584,7 +24584,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.99754166603088</v>
+        <v>1.9975414276123</v>
       </c>
       <c r="H835" t="n">
         <v>6000</v>
@@ -24671,7 +24671,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H838" t="n">
         <v>23250</v>
@@ -24729,7 +24729,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H840" t="n">
         <v>3750</v>
@@ -24874,7 +24874,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H845" t="n">
         <v>16500</v>
@@ -24903,7 +24903,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H846" t="n">
         <v>175500</v>
@@ -24990,7 +24990,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G849" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847455978394</v>
       </c>
       <c r="H849" t="n">
         <v>8250</v>
@@ -25019,7 +25019,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H850" t="n">
         <v>15000</v>
@@ -25077,7 +25077,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25106,7 +25106,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G853" t="n">
-        <v>2.10396766662598</v>
+        <v>2.10396790504456</v>
       </c>
       <c r="H853" t="n">
         <v>5250</v>
@@ -25135,7 +25135,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H854" t="n">
         <v>42000</v>
@@ -25164,7 +25164,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H855" t="n">
         <v>7500</v>
@@ -25222,7 +25222,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660829544067</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H857" t="n">
         <v>9750</v>
@@ -25251,7 +25251,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G858" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H858" t="n">
         <v>750</v>
@@ -25280,7 +25280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935484886169</v>
+        <v>1.9893547296524</v>
       </c>
       <c r="H859" t="n">
         <v>53250</v>
@@ -25309,7 +25309,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847455978394</v>
       </c>
       <c r="H860" t="n">
         <v>6750</v>
@@ -25338,7 +25338,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>2.01391458511353</v>
+        <v>2.0139148235321</v>
       </c>
       <c r="H861" t="n">
         <v>6000</v>
@@ -25367,7 +25367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204808235168</v>
+        <v>1.93204843997955</v>
       </c>
       <c r="H862" t="n">
         <v>27000</v>
@@ -25628,7 +25628,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.83380854129791</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H871" t="n">
         <v>3750</v>
@@ -25802,7 +25802,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H877" t="n">
         <v>15000</v>
@@ -25860,7 +25860,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G879" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H879" t="n">
         <v>1500</v>
@@ -25889,7 +25889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H880" t="n">
         <v>6750</v>
@@ -25918,7 +25918,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H881" t="n">
         <v>7500</v>
@@ -25947,7 +25947,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H882" t="n">
         <v>3000</v>
@@ -25976,7 +25976,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H883" t="n">
         <v>6000</v>
@@ -26005,7 +26005,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.06303477287292</v>
+        <v>2.06303453445435</v>
       </c>
       <c r="H884" t="n">
         <v>4500</v>
@@ -26034,7 +26034,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H885" t="n">
         <v>1500</v>
@@ -26063,7 +26063,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H886" t="n">
         <v>4500</v>
@@ -26353,7 +26353,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H896" t="n">
         <v>4500</v>
@@ -26469,7 +26469,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H900" t="n">
         <v>1500</v>
@@ -26498,7 +26498,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G901" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H901" t="n">
         <v>20250</v>
@@ -26527,7 +26527,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G902" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H902" t="n">
         <v>3750</v>
@@ -26556,7 +26556,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H903" t="n">
         <v>11250</v>
@@ -26585,7 +26585,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G904" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26643,7 +26643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993104457855</v>
       </c>
       <c r="H906" t="n">
         <v>750</v>
@@ -26672,7 +26672,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993104457855</v>
       </c>
       <c r="H907" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91285192966461</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H908" t="n">
         <v>21000</v>
@@ -26730,7 +26730,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H909" t="n">
         <v>12750</v>
@@ -26759,7 +26759,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G910" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H910" t="n">
         <v>5250</v>
@@ -26788,7 +26788,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G911" t="n">
-        <v>1.86161494255066</v>
+        <v>1.86161506175995</v>
       </c>
       <c r="H911" t="n">
         <v>3750</v>
@@ -26817,7 +26817,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.8786940574646</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H912" t="n">
         <v>3000</v>
@@ -26846,7 +26846,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G913" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H913" t="n">
         <v>750</v>
@@ -26875,7 +26875,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G914" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H914" t="n">
         <v>2250</v>
@@ -26904,7 +26904,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G915" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H915" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G916" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H916" t="n">
         <v>0</v>
@@ -26962,7 +26962,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G917" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H917" t="n">
         <v>0</v>
@@ -26991,7 +26991,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G918" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H918" t="n">
         <v>6000</v>
@@ -27020,7 +27020,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G919" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H919" t="n">
         <v>0</v>
@@ -27049,7 +27049,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H920" t="n">
         <v>5250</v>
@@ -27078,7 +27078,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H921" t="n">
         <v>6750</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27281,7 +27281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H928" t="n">
         <v>3000</v>
@@ -27310,7 +27310,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H929" t="n">
         <v>6750</v>
@@ -27339,7 +27339,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H930" t="n">
         <v>750</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824714660645</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H932" t="n">
         <v>2250</v>
@@ -27426,7 +27426,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H933" t="n">
         <v>20250</v>
@@ -27455,7 +27455,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H934" t="n">
         <v>12000</v>
@@ -27484,7 +27484,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G935" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H935" t="n">
         <v>5250</v>
@@ -27571,7 +27571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H938" t="n">
         <v>14250</v>
@@ -27600,7 +27600,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G939" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H939" t="n">
         <v>2250</v>
@@ -27629,7 +27629,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G940" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H940" t="n">
         <v>0</v>
@@ -27658,7 +27658,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G941" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H941" t="n">
         <v>4500</v>
@@ -27687,7 +27687,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G942" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H942" t="n">
         <v>0</v>
@@ -27716,7 +27716,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H943" t="n">
         <v>2250</v>
@@ -27745,7 +27745,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H944" t="n">
         <v>750</v>
@@ -27774,7 +27774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H945" t="n">
         <v>1500</v>
@@ -27803,7 +27803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H948" t="n">
         <v>2250</v>
@@ -27919,7 +27919,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G950" t="n">
-        <v>1.89577293395996</v>
+        <v>1.89577305316925</v>
       </c>
       <c r="H950" t="n">
         <v>6750</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.91285192966461</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H951" t="n">
         <v>10500</v>
@@ -27977,7 +27977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993104457855</v>
       </c>
       <c r="H952" t="n">
         <v>9750</v>
@@ -28006,7 +28006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.8786940574646</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H953" t="n">
         <v>3000</v>
@@ -28035,7 +28035,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G954" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H954" t="n">
         <v>6750</v>
@@ -28064,7 +28064,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G955" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H955" t="n">
         <v>6750</v>
@@ -28093,7 +28093,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G956" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H956" t="n">
         <v>0</v>
@@ -28122,7 +28122,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G957" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H957" t="n">
         <v>3000</v>
@@ -28151,7 +28151,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G958" t="n">
-        <v>1.94701027870178</v>
+        <v>1.94701015949249</v>
       </c>
       <c r="H958" t="n">
         <v>0</v>
@@ -28180,7 +28180,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G959" t="n">
-        <v>1.86161494255066</v>
+        <v>1.86161506175995</v>
       </c>
       <c r="H959" t="n">
         <v>9000</v>
@@ -28325,7 +28325,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G964" t="n">
-        <v>1.69936418533325</v>
+        <v>1.69936406612396</v>
       </c>
       <c r="H964" t="n">
         <v>1500</v>
@@ -28412,7 +28412,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H967" t="n">
         <v>6750</v>
@@ -28441,7 +28441,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H968" t="n">
         <v>2250</v>
@@ -28499,7 +28499,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.8445360660553</v>
+        <v>1.84453594684601</v>
       </c>
       <c r="H970" t="n">
         <v>2250</v>
@@ -28528,7 +28528,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H971" t="n">
         <v>2250</v>
@@ -28557,7 +28557,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28586,7 +28586,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -28615,7 +28615,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H974" t="n">
         <v>750</v>
@@ -28644,7 +28644,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28731,7 +28731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>1.81037759780884</v>
+        <v>1.81037771701813</v>
       </c>
       <c r="H978" t="n">
         <v>3000</v>
@@ -28789,7 +28789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H980" t="n">
         <v>11250</v>
@@ -28818,7 +28818,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G981" t="n">
-        <v>1.81037759780884</v>
+        <v>1.81037771701813</v>
       </c>
       <c r="H981" t="n">
         <v>27000</v>
@@ -28847,7 +28847,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H982" t="n">
         <v>9000</v>
@@ -28905,7 +28905,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G984" t="n">
-        <v>1.74206173419952</v>
+        <v>1.74206161499023</v>
       </c>
       <c r="H984" t="n">
         <v>750</v>
@@ -28992,7 +28992,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H987" t="n">
         <v>52500</v>
@@ -29021,7 +29021,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G988" t="n">
-        <v>1.62250828742981</v>
+        <v>1.6225084066391</v>
       </c>
       <c r="H988" t="n">
         <v>40500</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H989" t="n">
         <v>18000</v>
@@ -29166,7 +29166,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G993" t="n">
-        <v>1.53711330890656</v>
+        <v>1.53711318969727</v>
       </c>
       <c r="H993" t="n">
         <v>46500</v>
@@ -29224,7 +29224,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G995" t="n">
-        <v>1.53711330890656</v>
+        <v>1.53711318969727</v>
       </c>
       <c r="H995" t="n">
         <v>6000</v>
@@ -29253,7 +29253,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G996" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H996" t="n">
         <v>12000</v>
@@ -29282,7 +29282,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G997" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H997" t="n">
         <v>16500</v>
@@ -29311,7 +29311,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H998" t="n">
         <v>750</v>
@@ -29340,7 +29340,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1001" t="n">
         <v>8250</v>
@@ -29427,7 +29427,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1002" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1002" t="n">
         <v>5250</v>
@@ -29456,7 +29456,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1003" t="n">
         <v>39000</v>
@@ -29485,7 +29485,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1004" t="n">
         <v>81000</v>
@@ -29514,7 +29514,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1005" t="n">
         <v>9000</v>
@@ -29543,7 +29543,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1006" t="n">
         <v>10500</v>
@@ -29572,7 +29572,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1007" t="n">
         <v>18750</v>
@@ -29601,7 +29601,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1008" t="n">
         <v>9000</v>
@@ -29630,7 +29630,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1010" t="n">
         <v>12000</v>
@@ -29688,7 +29688,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1011" t="n">
         <v>6000</v>
@@ -29717,7 +29717,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1012" t="n">
         <v>6000</v>
@@ -29775,7 +29775,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1014" t="n">
         <v>9000</v>
@@ -29804,7 +29804,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -29862,7 +29862,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1017" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1017" t="n">
         <v>18000</v>
@@ -29891,7 +29891,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1018" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1018" t="n">
         <v>3750</v>
@@ -30007,7 +30007,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1022" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1022" t="n">
         <v>6000</v>
@@ -30152,7 +30152,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1027" t="n">
         <v>1500</v>
@@ -30181,7 +30181,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1028" t="n">
         <v>1500</v>
@@ -30210,7 +30210,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30239,7 +30239,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1030" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1030" t="n">
         <v>1500</v>
@@ -30268,7 +30268,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1031" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1031" t="n">
         <v>0</v>
@@ -30297,7 +30297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1032" t="n">
         <v>4500</v>
@@ -30326,7 +30326,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1033" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1033" t="n">
         <v>3000</v>
@@ -30384,7 +30384,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362532615662</v>
+        <v>1.32362520694733</v>
       </c>
       <c r="H1035" t="n">
         <v>6000</v>
@@ -30413,7 +30413,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.2638486623764</v>
+        <v>1.26384878158569</v>
       </c>
       <c r="H1036" t="n">
         <v>95250</v>
@@ -30761,7 +30761,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1048" t="n">
-        <v>1.38340187072754</v>
+        <v>1.38340198993683</v>
       </c>
       <c r="H1048" t="n">
         <v>1500</v>
@@ -30790,7 +30790,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1049" t="n">
         <v>9000</v>
@@ -30935,7 +30935,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1054" t="n">
         <v>31500</v>
@@ -30964,7 +30964,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1055" t="n">
         <v>21000</v>
@@ -31022,7 +31022,7 @@
         <v>1.75</v>
       </c>
       <c r="G1057" t="n">
-        <v>1.49441564083099</v>
+        <v>1.49441576004028</v>
       </c>
       <c r="H1057" t="n">
         <v>750</v>
@@ -31051,7 +31051,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1058" t="n">
         <v>2250</v>
@@ -31080,7 +31080,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1059" t="n">
         <v>99750</v>
@@ -31109,7 +31109,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1060" t="n">
         <v>4500</v>
@@ -31196,7 +31196,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1063" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1063" t="n">
         <v>14250</v>
@@ -31341,7 +31341,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1068" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1068" t="n">
         <v>6000</v>
@@ -31399,7 +31399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1070" t="n">
         <v>3750</v>
@@ -31428,7 +31428,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1071" t="n">
         <v>750</v>
@@ -31486,7 +31486,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.44317853450775</v>
+        <v>1.44317865371704</v>
       </c>
       <c r="H1073" t="n">
         <v>15750</v>
@@ -31631,7 +31631,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1078" t="n">
         <v>2250</v>
@@ -31660,7 +31660,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1079" t="n">
         <v>2250</v>
@@ -31689,7 +31689,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -31718,7 +31718,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1081" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1081" t="n">
         <v>4500</v>
@@ -31776,7 +31776,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1083" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1083" t="n">
         <v>12750</v>
@@ -31805,7 +31805,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1084" t="n">
         <v>19500</v>
@@ -31834,7 +31834,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G1085" t="n">
-        <v>1.38340187072754</v>
+        <v>1.38340198993683</v>
       </c>
       <c r="H1085" t="n">
         <v>3750</v>
@@ -31863,7 +31863,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1086" t="n">
         <v>3000</v>
@@ -31892,7 +31892,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1087" t="n">
         <v>6000</v>
@@ -31950,7 +31950,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1089" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1089" t="n">
         <v>6750</v>
@@ -32008,7 +32008,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1091" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1091" t="n">
         <v>4500</v>
@@ -32037,7 +32037,7 @@
         <v>1.64999997615814</v>
       </c>
       <c r="G1092" t="n">
-        <v>1.40902042388916</v>
+        <v>1.40902054309845</v>
       </c>
       <c r="H1092" t="n">
         <v>1500</v>
@@ -32066,7 +32066,7 @@
         <v>1.71000003814697</v>
       </c>
       <c r="G1093" t="n">
-        <v>1.4602575302124</v>
+        <v>1.46025764942169</v>
       </c>
       <c r="H1093" t="n">
         <v>49500</v>
@@ -32095,7 +32095,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1094" t="n">
-        <v>1.54565262794495</v>
+        <v>1.54565274715424</v>
       </c>
       <c r="H1094" t="n">
         <v>45750</v>
@@ -32124,7 +32124,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H1095" t="n">
         <v>20250</v>
@@ -32298,7 +32298,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1101" t="n">
-        <v>1.53711330890656</v>
+        <v>1.53711318969727</v>
       </c>
       <c r="H1101" t="n">
         <v>11250</v>
@@ -32327,7 +32327,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1102" t="n">
-        <v>1.53711330890656</v>
+        <v>1.53711318969727</v>
       </c>
       <c r="H1102" t="n">
         <v>5250</v>
@@ -32414,7 +32414,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1105" t="n">
-        <v>1.54565262794495</v>
+        <v>1.54565274715424</v>
       </c>
       <c r="H1105" t="n">
         <v>3750</v>
@@ -32443,7 +32443,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1106" t="n">
-        <v>1.53711330890656</v>
+        <v>1.53711318969727</v>
       </c>
       <c r="H1106" t="n">
         <v>3000</v>
@@ -32530,7 +32530,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1109" t="n">
-        <v>1.53711330890656</v>
+        <v>1.53711318969727</v>
       </c>
       <c r="H1109" t="n">
         <v>3750</v>
@@ -32559,7 +32559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958752155304</v>
+        <v>1.63958740234375</v>
       </c>
       <c r="H1110" t="n">
         <v>45000</v>
@@ -32588,7 +32588,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1111" t="n">
-        <v>1.69936418533325</v>
+        <v>1.69936406612396</v>
       </c>
       <c r="H1111" t="n">
         <v>12000</v>
@@ -32820,7 +32820,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1119" t="n">
-        <v>1.74206173419952</v>
+        <v>1.74206161499023</v>
       </c>
       <c r="H1119" t="n">
         <v>96750</v>
@@ -32849,7 +32849,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H1120" t="n">
         <v>9750</v>
@@ -33168,7 +33168,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1131" t="n">
-        <v>1.69936418533325</v>
+        <v>1.69936406612396</v>
       </c>
       <c r="H1131" t="n">
         <v>46500</v>
@@ -33429,7 +33429,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H1140" t="n">
         <v>8250</v>
@@ -33458,7 +33458,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1141" t="n">
-        <v>1.62250828742981</v>
+        <v>1.6225084066391</v>
       </c>
       <c r="H1141" t="n">
         <v>8250</v>
@@ -33487,7 +33487,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1142" t="n">
-        <v>1.54565262794495</v>
+        <v>1.54565274715424</v>
       </c>
       <c r="H1142" t="n">
         <v>6000</v>
@@ -33516,7 +33516,7 @@
         <v>1.80999994277954</v>
       </c>
       <c r="G1143" t="n">
-        <v>1.54565262794495</v>
+        <v>1.54565274715424</v>
       </c>
       <c r="H1143" t="n">
         <v>3000</v>
@@ -33545,7 +33545,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G1144" t="n">
-        <v>1.53711330890656</v>
+        <v>1.53711318969727</v>
       </c>
       <c r="H1144" t="n">
         <v>17250</v>
@@ -33632,7 +33632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958752155304</v>
+        <v>1.63958740234375</v>
       </c>
       <c r="H1147" t="n">
         <v>9750</v>
@@ -33661,7 +33661,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1148" t="n">
-        <v>1.69936418533325</v>
+        <v>1.69936406612396</v>
       </c>
       <c r="H1148" t="n">
         <v>7500</v>
@@ -33777,7 +33777,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1152" t="n">
         <v>122250</v>
@@ -34705,7 +34705,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1184" t="n">
         <v>84000</v>
@@ -34792,7 +34792,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1187" t="n">
         <v>18000</v>
@@ -34879,7 +34879,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1190" t="n">
         <v>57000</v>
@@ -34908,7 +34908,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1191" t="n">
         <v>43500</v>
@@ -34937,7 +34937,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1192" t="n">
         <v>75750</v>
@@ -34966,7 +34966,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.06746220588684</v>
+        <v>2.06746244430542</v>
       </c>
       <c r="H1193" t="n">
         <v>28500</v>
@@ -34995,7 +34995,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.99555051326752</v>
+        <v>1.99555063247681</v>
       </c>
       <c r="H1194" t="n">
         <v>24000</v>
@@ -35024,7 +35024,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1195" t="n">
         <v>12000</v>
@@ -35053,7 +35053,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1196" t="n">
         <v>12000</v>
@@ -35082,7 +35082,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1197" t="n">
         <v>2250</v>
@@ -35111,7 +35111,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1198" t="n">
         <v>30000</v>
@@ -35140,7 +35140,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1199" t="n">
         <v>3750</v>
@@ -35169,7 +35169,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1200" t="n">
         <v>0</v>
@@ -35198,7 +35198,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1201" t="n">
         <v>750</v>
@@ -35227,7 +35227,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1202" t="n">
         <v>6000</v>
@@ -35256,7 +35256,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1203" t="n">
         <v>9000</v>
@@ -35314,7 +35314,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1205" t="n">
         <v>21000</v>
@@ -35343,7 +35343,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1206" t="n">
         <v>24750</v>
@@ -35372,7 +35372,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1207" t="n">
         <v>3750</v>
@@ -35401,7 +35401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1208" t="n">
         <v>3750</v>
@@ -35981,7 +35981,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1228" t="n">
         <v>12750</v>
@@ -36010,7 +36010,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1229" t="n">
         <v>9750</v>
@@ -36126,7 +36126,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1233" t="n">
         <v>1500</v>
@@ -36155,7 +36155,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1234" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1242" t="n">
         <v>27000</v>
@@ -36445,7 +36445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1244" t="n">
         <v>2250</v>
@@ -36561,7 +36561,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1248" t="n">
         <v>3000</v>
@@ -36764,7 +36764,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1255" t="n">
         <v>7500</v>
@@ -36793,7 +36793,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1256" t="n">
         <v>11250</v>
@@ -36851,7 +36851,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1258" t="n">
         <v>20250</v>
@@ -36938,7 +36938,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1261" t="n">
         <v>12750</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1263" t="n">
         <v>32250</v>
@@ -37402,7 +37402,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1277" t="n">
         <v>5250</v>
@@ -37431,7 +37431,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1278" t="n">
         <v>4500</v>
@@ -37518,7 +37518,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1281" t="n">
         <v>6000</v>
@@ -37576,7 +37576,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1283" t="n">
         <v>2250</v>
@@ -37605,7 +37605,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1284" t="n">
         <v>8250</v>
@@ -37779,7 +37779,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1290" t="n">
         <v>14250</v>
@@ -37837,7 +37837,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1292" t="n">
         <v>750</v>
@@ -37866,7 +37866,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1293" t="n">
         <v>750</v>
@@ -37895,7 +37895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1294" t="n">
         <v>0</v>
@@ -37953,7 +37953,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1296" t="n">
         <v>4500</v>
@@ -37982,7 +37982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1297" t="n">
         <v>3000</v>
@@ -38040,7 +38040,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1299" t="n">
         <v>7500</v>
@@ -38069,7 +38069,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1300" t="n">
         <v>3000</v>
@@ -38098,7 +38098,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1301" t="n">
         <v>6750</v>
@@ -38127,7 +38127,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1302" t="n">
         <v>6000</v>
@@ -38359,7 +38359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1310" t="n">
         <v>7500</v>
@@ -39229,7 +39229,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1340" t="n">
         <v>5250</v>
@@ -39258,7 +39258,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1341" t="n">
         <v>2250</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1342" t="n">
         <v>12000</v>
@@ -39316,7 +39316,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1343" t="n">
         <v>13500</v>
@@ -39345,7 +39345,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1344" t="n">
         <v>5250</v>
@@ -39403,7 +39403,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1346" t="n">
         <v>6000</v>
@@ -39432,7 +39432,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1347" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1367" t="n">
         <v>2250</v>
@@ -40041,7 +40041,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1368" t="n">
         <v>42750</v>
@@ -40070,7 +40070,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1369" t="n">
         <v>4500</v>
@@ -40099,7 +40099,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1370" t="n">
         <v>0</v>
@@ -40128,7 +40128,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1371" t="n">
         <v>1500</v>
@@ -40244,7 +40244,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1375" t="n">
         <v>750</v>
@@ -40273,7 +40273,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1376" t="n">
         <v>0</v>
@@ -40360,7 +40360,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1379" t="n">
         <v>5250</v>
@@ -40389,7 +40389,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1380" t="n">
         <v>114750</v>
@@ -40418,7 +40418,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1381" t="n">
         <v>12750</v>
@@ -40447,7 +40447,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1382" t="n">
         <v>4500</v>
@@ -40476,7 +40476,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1383" t="n">
         <v>1500</v>
@@ -40505,7 +40505,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1384" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1386" t="n">
         <v>15000</v>
@@ -40592,7 +40592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1387" t="n">
         <v>3000</v>
@@ -40621,7 +40621,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1388" t="n">
         <v>2250</v>
@@ -40650,7 +40650,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1389" t="n">
         <v>1500</v>
@@ -40679,7 +40679,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1391" t="n">
         <v>1500</v>
@@ -40737,7 +40737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1392" t="n">
         <v>60750</v>
@@ -40766,7 +40766,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1393" t="n">
         <v>5250</v>
@@ -40795,7 +40795,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1394" t="n">
         <v>13500</v>
@@ -40824,7 +40824,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1395" t="n">
         <v>11250</v>
@@ -40853,7 +40853,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1396" t="n">
         <v>21000</v>
@@ -40911,7 +40911,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1398" t="n">
         <v>15750</v>
@@ -40969,7 +40969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1400" t="n">
         <v>22500</v>
@@ -41027,7 +41027,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1402" t="n">
         <v>9000</v>
@@ -51908,6 +51908,35 @@
         <v>9000</v>
       </c>
       <c r="I1777" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1778">
+      <c r="A1778" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1778" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1778" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="D1778" t="n">
+        <v>3.08999991416931</v>
+      </c>
+      <c r="E1778" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="F1778" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="G1778" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="H1778" t="n">
+        <v>6000</v>
+      </c>
+      <c r="I1778" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -717,7 +717,7 @@
         <v>3.36050009727478</v>
       </c>
       <c r="G12" t="n">
-        <v>2.69105386734009</v>
+        <v>2.69105410575867</v>
       </c>
       <c r="H12" t="n">
         <v>1500</v>
@@ -775,7 +775,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72228455543518</v>
+        <v>2.72228479385376</v>
       </c>
       <c r="H14" t="n">
         <v>7500</v>
@@ -1007,7 +1007,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>3.43538808822632</v>
+        <v>3.4353883266449</v>
       </c>
       <c r="H22" t="n">
         <v>193500</v>
@@ -1094,7 +1094,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4914436340332</v>
+        <v>3.49144339561462</v>
       </c>
       <c r="H25" t="n">
         <v>20250</v>
@@ -1152,7 +1152,7 @@
         <v>4.24350023269653</v>
       </c>
       <c r="G27" t="n">
-        <v>3.39815139770508</v>
+        <v>3.39815163612366</v>
       </c>
       <c r="H27" t="n">
         <v>19500</v>
@@ -1239,7 +1239,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128523826599</v>
+        <v>3.33128547668457</v>
       </c>
       <c r="H30" t="n">
         <v>9000</v>
@@ -1268,7 +1268,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048462867737</v>
+        <v>3.33048486709595</v>
       </c>
       <c r="H31" t="n">
         <v>6750</v>
@@ -1442,7 +1442,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H37" t="n">
         <v>750</v>
@@ -1761,7 +1761,7 @@
         <v>3.73499989509583</v>
       </c>
       <c r="G48" t="n">
-        <v>2.9909496307373</v>
+        <v>2.99094986915588</v>
       </c>
       <c r="H48" t="n">
         <v>3000</v>
@@ -1906,7 +1906,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H53" t="n">
         <v>9000</v>
@@ -1964,7 +1964,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H55" t="n">
         <v>2250</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507201194763</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H56" t="n">
         <v>18750</v>
@@ -2051,7 +2051,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H58" t="n">
         <v>3000</v>
@@ -2109,7 +2109,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507201194763</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H61" t="n">
         <v>5250</v>
@@ -2167,7 +2167,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505224227905</v>
+        <v>3.09505248069763</v>
       </c>
       <c r="H62" t="n">
         <v>4500</v>
@@ -2254,7 +2254,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087079048157</v>
       </c>
       <c r="H65" t="n">
         <v>9750</v>
@@ -2283,7 +2283,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>2.90686702728271</v>
+        <v>2.90686726570129</v>
       </c>
       <c r="H66" t="n">
         <v>3750</v>
@@ -2341,7 +2341,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280371665955</v>
+        <v>2.84280347824097</v>
       </c>
       <c r="H68" t="n">
         <v>8250</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670886993408</v>
+        <v>2.74670910835266</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2486,7 +2486,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467709541321</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H73" t="n">
         <v>17250</v>
@@ -2660,7 +2660,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H79" t="n">
         <v>7500</v>
@@ -2747,7 +2747,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087079048157</v>
       </c>
       <c r="H82" t="n">
         <v>7500</v>
@@ -2834,7 +2834,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>2.8067684173584</v>
+        <v>2.80676817893982</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2892,7 +2892,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.59055495262146</v>
+        <v>2.59055471420288</v>
       </c>
       <c r="H87" t="n">
         <v>14250</v>
@@ -2921,7 +2921,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H88" t="n">
         <v>3750</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H90" t="n">
         <v>10500</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185584545135</v>
+        <v>1.88185596466064</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3124,7 +3124,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.5775557756424</v>
+        <v>1.57755589485168</v>
       </c>
       <c r="H95" t="n">
         <v>9000</v>
@@ -3153,7 +3153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H96" t="n">
         <v>14250</v>
@@ -3240,7 +3240,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556377887726</v>
+        <v>1.58556365966797</v>
       </c>
       <c r="H99" t="n">
         <v>14250</v>
@@ -3269,7 +3269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161896705627</v>
+        <v>1.64161920547485</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3385,7 +3385,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75773334503174</v>
+        <v>1.75773358345032</v>
       </c>
       <c r="H104" t="n">
         <v>12000</v>
@@ -3414,7 +3414,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H105" t="n">
         <v>6750</v>
@@ -3501,7 +3501,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.89787185192108</v>
+        <v>1.8978716135025</v>
       </c>
       <c r="H108" t="n">
         <v>15750</v>
@@ -3588,7 +3588,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643209457397</v>
       </c>
       <c r="H111" t="n">
         <v>28500</v>
@@ -3646,7 +3646,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H113" t="n">
         <v>28500</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3791,7 +3791,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H118" t="n">
         <v>6000</v>
@@ -3820,7 +3820,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H119" t="n">
         <v>8250</v>
@@ -3878,7 +3878,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G121" t="n">
-        <v>2.74270462989807</v>
+        <v>2.74270486831665</v>
       </c>
       <c r="H121" t="n">
         <v>750</v>
@@ -3907,7 +3907,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G122" t="n">
-        <v>2.66663002967834</v>
+        <v>2.66662979125977</v>
       </c>
       <c r="H122" t="n">
         <v>3750</v>
@@ -3936,7 +3936,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>2.75071263313293</v>
+        <v>2.75071287155151</v>
       </c>
       <c r="H123" t="n">
         <v>5250</v>
@@ -3965,7 +3965,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467709541321</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -3994,7 +3994,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H125" t="n">
         <v>4500</v>
@@ -4052,7 +4052,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H127" t="n">
         <v>2250</v>
@@ -4081,7 +4081,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.78674840927124</v>
+        <v>2.78674864768982</v>
       </c>
       <c r="H128" t="n">
         <v>3000</v>
@@ -4110,7 +4110,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78674840927124</v>
+        <v>2.78674864768982</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H137" t="n">
         <v>750</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4516,7 +4516,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643209457397</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4690,7 +4690,7 @@
         <v>3.42499995231628</v>
       </c>
       <c r="G149" t="n">
-        <v>2.74270462989807</v>
+        <v>2.74270486831665</v>
       </c>
       <c r="H149" t="n">
         <v>3750</v>
@@ -4777,7 +4777,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G152" t="n">
-        <v>2.71067333221436</v>
+        <v>2.71067309379578</v>
       </c>
       <c r="H152" t="n">
         <v>750</v>
@@ -4864,7 +4864,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H155" t="n">
         <v>8250</v>
@@ -4893,7 +4893,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G156" t="n">
-        <v>2.56252717971802</v>
+        <v>2.5625274181366</v>
       </c>
       <c r="H156" t="n">
         <v>1500</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5096,7 +5096,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>2.50647187232971</v>
+        <v>2.50647234916687</v>
       </c>
       <c r="H163" t="n">
         <v>6750</v>
@@ -5212,7 +5212,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45842432975769</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H167" t="n">
         <v>15000</v>
@@ -5386,7 +5386,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H173" t="n">
         <v>2250</v>
@@ -5415,7 +5415,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G176" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.33029794692993</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H189" t="n">
         <v>3750</v>
@@ -5879,7 +5879,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33029794692993</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H197" t="n">
         <v>139500</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H204" t="n">
         <v>12000</v>
@@ -6343,7 +6343,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258648872375</v>
+        <v>2.62258672714233</v>
       </c>
       <c r="H206" t="n">
         <v>8250</v>
@@ -6372,7 +6372,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258648872375</v>
+        <v>2.62258672714233</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H213" t="n">
         <v>10500</v>
@@ -6633,7 +6633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6662,7 +6662,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H217" t="n">
         <v>11250</v>
@@ -6691,7 +6691,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>2.33029794692993</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H220" t="n">
         <v>750</v>
@@ -6807,7 +6807,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.49446034431458</v>
+        <v>2.494460105896</v>
       </c>
       <c r="H222" t="n">
         <v>6750</v>
@@ -6865,7 +6865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -7010,7 +7010,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>2.35031771659851</v>
+        <v>2.35031795501709</v>
       </c>
       <c r="H229" t="n">
         <v>18750</v>
@@ -7126,7 +7126,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.33029794692993</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H233" t="n">
         <v>3750</v>
@@ -7213,7 +7213,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H236" t="n">
         <v>2250</v>
@@ -7242,7 +7242,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G244" t="n">
-        <v>2.45842432975769</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H244" t="n">
         <v>4500</v>
@@ -7619,7 +7619,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G250" t="n">
-        <v>2.39836502075195</v>
+        <v>2.39836525917053</v>
       </c>
       <c r="H250" t="n">
         <v>3000</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.38635325431824</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.38635325431824</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H262" t="n">
         <v>2250</v>
@@ -8025,7 +8025,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21017980575562</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.18615627288818</v>
+        <v>2.1861560344696</v>
       </c>
       <c r="H265" t="n">
         <v>1500</v>
@@ -8257,7 +8257,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H272" t="n">
         <v>2250</v>
@@ -8286,7 +8286,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8373,7 +8373,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H276" t="n">
         <v>3000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.28625464439392</v>
+        <v>2.2862548828125</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8895,7 +8895,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21017980575562</v>
       </c>
       <c r="H294" t="n">
         <v>750</v>
@@ -8924,7 +8924,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H295" t="n">
         <v>6000</v>
@@ -8982,7 +8982,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H297" t="n">
         <v>2250</v>
@@ -9011,7 +9011,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H298" t="n">
         <v>2250</v>
@@ -9127,7 +9127,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H302" t="n">
         <v>3000</v>
@@ -9156,7 +9156,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H308" t="n">
         <v>6750</v>
@@ -9330,7 +9330,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039727210999</v>
+        <v>2.43039679527283</v>
       </c>
       <c r="H309" t="n">
         <v>17250</v>
@@ -9417,7 +9417,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045634269714</v>
+        <v>2.49045610427856</v>
       </c>
       <c r="H312" t="n">
         <v>5250</v>
@@ -9475,7 +9475,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H314" t="n">
         <v>1500</v>
@@ -9504,7 +9504,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H319" t="n">
         <v>3750</v>
@@ -9649,7 +9649,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430218696594</v>
+        <v>2.33430194854736</v>
       </c>
       <c r="H320" t="n">
         <v>750</v>
@@ -9794,7 +9794,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H325" t="n">
         <v>13500</v>
@@ -9910,7 +9910,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643209457397</v>
       </c>
       <c r="H329" t="n">
         <v>2250</v>
@@ -9968,7 +9968,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G331" t="n">
-        <v>2.45842432975769</v>
+        <v>2.45842456817627</v>
       </c>
       <c r="H331" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H333" t="n">
         <v>9000</v>
@@ -10142,7 +10142,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.43840503692627</v>
+        <v>2.43840479850769</v>
       </c>
       <c r="H337" t="n">
         <v>3750</v>
@@ -10171,7 +10171,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H338" t="n">
         <v>1500</v>
@@ -10229,7 +10229,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G340" t="n">
-        <v>2.50647187232971</v>
+        <v>2.50647234916687</v>
       </c>
       <c r="H340" t="n">
         <v>29250</v>
@@ -10287,7 +10287,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H342" t="n">
         <v>1500</v>
@@ -10403,7 +10403,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H346" t="n">
         <v>54000</v>
@@ -10693,7 +10693,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H356" t="n">
         <v>5250</v>
@@ -10722,7 +10722,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G357" t="n">
-        <v>2.66663002967834</v>
+        <v>2.66662979125977</v>
       </c>
       <c r="H357" t="n">
         <v>4500</v>
@@ -10780,7 +10780,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H359" t="n">
         <v>10500</v>
@@ -10809,7 +10809,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467709541321</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H360" t="n">
         <v>10500</v>
@@ -10867,7 +10867,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.7066695690155</v>
+        <v>2.70666933059692</v>
       </c>
       <c r="H362" t="n">
         <v>15750</v>
@@ -11186,7 +11186,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G373" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H373" t="n">
         <v>11250</v>
@@ -11244,7 +11244,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H375" t="n">
         <v>3750</v>
@@ -11273,7 +11273,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H376" t="n">
         <v>39000</v>
@@ -11476,7 +11476,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G383" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H383" t="n">
         <v>25500</v>
@@ -11592,7 +11592,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H387" t="n">
         <v>3750</v>
@@ -11621,7 +11621,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G388" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H388" t="n">
         <v>6000</v>
@@ -11650,7 +11650,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G389" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H389" t="n">
         <v>12750</v>
@@ -11679,7 +11679,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G390" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H390" t="n">
         <v>1500</v>
@@ -11766,7 +11766,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.17112755775452</v>
+        <v>3.17112731933594</v>
       </c>
       <c r="H393" t="n">
         <v>23250</v>
@@ -11969,7 +11969,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G400" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H400" t="n">
         <v>750</v>
@@ -12085,7 +12085,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H404" t="n">
         <v>21000</v>
@@ -12143,7 +12143,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>3.31526970863342</v>
+        <v>3.31526947021484</v>
       </c>
       <c r="H406" t="n">
         <v>72750</v>
@@ -12172,7 +12172,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>3.31526970863342</v>
+        <v>3.31526947021484</v>
       </c>
       <c r="H407" t="n">
         <v>13500</v>
@@ -12201,7 +12201,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G408" t="n">
-        <v>3.34730124473572</v>
+        <v>3.34730100631714</v>
       </c>
       <c r="H408" t="n">
         <v>10500</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H409" t="n">
         <v>12750</v>
@@ -12259,7 +12259,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.15511155128479</v>
+        <v>3.15511178970337</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12317,7 +12317,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H412" t="n">
         <v>3000</v>
@@ -12346,7 +12346,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917462348938</v>
       </c>
       <c r="H413" t="n">
         <v>5250</v>
@@ -12404,7 +12404,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.13909602165222</v>
+        <v>3.13909578323364</v>
       </c>
       <c r="H415" t="n">
         <v>2250</v>
@@ -12433,7 +12433,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15511155128479</v>
+        <v>3.15511178970337</v>
       </c>
       <c r="H416" t="n">
         <v>3750</v>
@@ -12694,7 +12694,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>3.15511155128479</v>
+        <v>3.15511178970337</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -13883,7 +13883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H466" t="n">
         <v>9750</v>
@@ -14086,7 +14086,7 @@
         <v>3.83999991416931</v>
       </c>
       <c r="G473" t="n">
-        <v>3.07503271102905</v>
+        <v>3.07503247261047</v>
       </c>
       <c r="H473" t="n">
         <v>12750</v>
@@ -14869,7 +14869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H500" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H503" t="n">
         <v>5250</v>
@@ -14985,7 +14985,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H504" t="n">
         <v>750</v>
@@ -15043,7 +15043,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H506" t="n">
         <v>8250</v>
@@ -15304,7 +15304,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H515" t="n">
         <v>6750</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15623,7 +15623,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H526" t="n">
         <v>17250</v>
@@ -15681,7 +15681,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846434593201</v>
+        <v>2.49846386909485</v>
       </c>
       <c r="H528" t="n">
         <v>5250</v>
@@ -15739,7 +15739,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H530" t="n">
         <v>5250</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.38635325431824</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15826,7 +15826,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H533" t="n">
         <v>15000</v>
@@ -15855,7 +15855,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H534" t="n">
         <v>8250</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.38635325431824</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16145,7 +16145,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H544" t="n">
         <v>750</v>
@@ -16174,7 +16174,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H545" t="n">
         <v>7500</v>
@@ -16203,7 +16203,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H546" t="n">
         <v>8250</v>
@@ -16261,7 +16261,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>2.29025864601135</v>
+        <v>2.29025888442993</v>
       </c>
       <c r="H548" t="n">
         <v>6750</v>
@@ -16290,7 +16290,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H549" t="n">
         <v>5250</v>
@@ -16319,7 +16319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16348,7 +16348,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H551" t="n">
         <v>102750</v>
@@ -16377,7 +16377,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H552" t="n">
         <v>3750</v>
@@ -16493,7 +16493,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H556" t="n">
         <v>3750</v>
@@ -16522,7 +16522,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H557" t="n">
         <v>5250</v>
@@ -16551,7 +16551,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H558" t="n">
         <v>6000</v>
@@ -16580,7 +16580,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.30627465248108</v>
+        <v>2.3062744140625</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.38635325431824</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16928,7 +16928,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H571" t="n">
         <v>7500</v>
@@ -16957,7 +16957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H572" t="n">
         <v>3000</v>
@@ -17073,7 +17073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424287796021</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H576" t="n">
         <v>3000</v>
@@ -17189,7 +17189,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21017980575562</v>
       </c>
       <c r="H580" t="n">
         <v>3750</v>
@@ -17363,7 +17363,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400611877441</v>
       </c>
       <c r="H586" t="n">
         <v>6000</v>
@@ -17537,7 +17537,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400611877441</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17595,7 +17595,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98595857620239</v>
+        <v>1.98595881462097</v>
       </c>
       <c r="H594" t="n">
         <v>6000</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.8898640871048</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17711,7 +17711,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G598" t="n">
-        <v>1.77775323390961</v>
+        <v>1.7777533531189</v>
       </c>
       <c r="H598" t="n">
         <v>15000</v>
@@ -17827,7 +17827,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G602" t="n">
-        <v>1.53751635551453</v>
+        <v>1.53751623630524</v>
       </c>
       <c r="H602" t="n">
         <v>10500</v>
@@ -17914,7 +17914,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564273834229</v>
       </c>
       <c r="H605" t="n">
         <v>3750</v>
@@ -18001,7 +18001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H608" t="n">
         <v>11250</v>
@@ -18059,7 +18059,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H610" t="n">
         <v>5250</v>
@@ -18117,7 +18117,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572169780731</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18146,7 +18146,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H613" t="n">
         <v>4500</v>
@@ -18233,7 +18233,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G616" t="n">
-        <v>1.77775323390961</v>
+        <v>1.7777533531189</v>
       </c>
       <c r="H616" t="n">
         <v>3750</v>
@@ -18262,7 +18262,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H617" t="n">
         <v>5250</v>
@@ -18291,7 +18291,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376912117004</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H618" t="n">
         <v>10500</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.8898640871048</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18378,7 +18378,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.9539270401001</v>
+        <v>1.95392727851868</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.80978488922119</v>
+        <v>1.8097847700119</v>
       </c>
       <c r="H622" t="n">
         <v>48750</v>
@@ -18465,7 +18465,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.665642619133</v>
+        <v>1.66564273834229</v>
       </c>
       <c r="H624" t="n">
         <v>174750</v>
@@ -18523,7 +18523,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.72169804573059</v>
+        <v>1.72169816493988</v>
       </c>
       <c r="H626" t="n">
         <v>40500</v>
@@ -18610,7 +18610,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376912117004</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H629" t="n">
         <v>18750</v>
@@ -18639,7 +18639,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H630" t="n">
         <v>14250</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.72169804573059</v>
+        <v>1.72169816493988</v>
       </c>
       <c r="H631" t="n">
         <v>5250</v>
@@ -18697,7 +18697,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572169780731</v>
       </c>
       <c r="H632" t="n">
         <v>2250</v>
@@ -18726,7 +18726,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572169780731</v>
       </c>
       <c r="H633" t="n">
         <v>750</v>
@@ -18755,7 +18755,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572169780731</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572169780731</v>
       </c>
       <c r="H635" t="n">
         <v>5250</v>
@@ -18871,7 +18871,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165862560272</v>
       </c>
       <c r="H638" t="n">
         <v>18000</v>
@@ -19045,7 +19045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81743538379669</v>
+        <v>1.81743514537811</v>
       </c>
       <c r="H644" t="n">
         <v>18000</v>
@@ -19074,7 +19074,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G645" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H645" t="n">
         <v>6000</v>
@@ -19277,7 +19277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.8583687543869</v>
+        <v>1.85836863517761</v>
       </c>
       <c r="H652" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.8583687543869</v>
+        <v>1.85836863517761</v>
       </c>
       <c r="H653" t="n">
         <v>4500</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H654" t="n">
         <v>9750</v>
@@ -19393,7 +19393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194203853607</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H658" t="n">
         <v>11250</v>
@@ -19509,7 +19509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194203853607</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H660" t="n">
         <v>12000</v>
@@ -19596,7 +19596,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.83380877971649</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H663" t="n">
         <v>21750</v>
@@ -19654,7 +19654,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.83380877971649</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H665" t="n">
         <v>15750</v>
@@ -19770,7 +19770,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G669" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H669" t="n">
         <v>6750</v>
@@ -19799,7 +19799,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H670" t="n">
         <v>15750</v>
@@ -19857,7 +19857,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H672" t="n">
         <v>2250</v>
@@ -19886,7 +19886,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H673" t="n">
         <v>3000</v>
@@ -19915,7 +19915,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.72738218307495</v>
+        <v>1.72738230228424</v>
       </c>
       <c r="H674" t="n">
         <v>750</v>
@@ -19944,7 +19944,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H675" t="n">
         <v>3750</v>
@@ -20060,7 +20060,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G679" t="n">
-        <v>1.72738218307495</v>
+        <v>1.72738230228424</v>
       </c>
       <c r="H679" t="n">
         <v>5250</v>
@@ -20118,7 +20118,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H681" t="n">
         <v>750</v>
@@ -20205,7 +20205,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H684" t="n">
         <v>6000</v>
@@ -20292,7 +20292,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194203853607</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H687" t="n">
         <v>34500</v>
@@ -20379,7 +20379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H690" t="n">
         <v>2250</v>
@@ -20408,7 +20408,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G696" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H696" t="n">
         <v>1500</v>
@@ -20640,7 +20640,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H699" t="n">
         <v>1500</v>
@@ -20669,7 +20669,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G700" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G701" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H701" t="n">
         <v>750</v>
@@ -20727,7 +20727,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H702" t="n">
         <v>750</v>
@@ -20785,7 +20785,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>1.72738218307495</v>
+        <v>1.72738230228424</v>
       </c>
       <c r="H704" t="n">
         <v>1500</v>
@@ -20872,7 +20872,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H707" t="n">
         <v>2250</v>
@@ -20901,7 +20901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -21017,7 +21017,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H712" t="n">
         <v>9000</v>
@@ -21046,7 +21046,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H713" t="n">
         <v>750</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21162,7 +21162,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H717" t="n">
         <v>7500</v>
@@ -21191,7 +21191,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H718" t="n">
         <v>2250</v>
@@ -21220,7 +21220,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21394,7 +21394,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H725" t="n">
         <v>8250</v>
@@ -21423,7 +21423,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67007565498352</v>
+        <v>1.67007577419281</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H727" t="n">
         <v>3750</v>
@@ -21481,7 +21481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -21800,7 +21800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G739" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H739" t="n">
         <v>11250</v>
@@ -21829,7 +21829,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G740" t="n">
-        <v>1.58002257347107</v>
+        <v>1.58002269268036</v>
       </c>
       <c r="H740" t="n">
         <v>2250</v>
@@ -22003,7 +22003,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H746" t="n">
         <v>6000</v>
@@ -22061,7 +22061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G748" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H748" t="n">
         <v>10500</v>
@@ -22177,7 +22177,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.50224947929382</v>
+        <v>1.50224959850311</v>
       </c>
       <c r="H752" t="n">
         <v>10500</v>
@@ -22206,7 +22206,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634288787842</v>
+        <v>1.50634276866913</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22235,7 +22235,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634288787842</v>
+        <v>1.50634276866913</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -22293,7 +22293,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G756" t="n">
-        <v>1.48996949195862</v>
+        <v>1.48996961116791</v>
       </c>
       <c r="H756" t="n">
         <v>16500</v>
@@ -22322,7 +22322,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H757" t="n">
         <v>79500</v>
@@ -22351,7 +22351,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G758" t="n">
-        <v>1.58002257347107</v>
+        <v>1.58002269268036</v>
       </c>
       <c r="H758" t="n">
         <v>6750</v>
@@ -22380,7 +22380,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.58002257347107</v>
+        <v>1.58002269268036</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>1.60458254814148</v>
+        <v>1.60458266735077</v>
       </c>
       <c r="H760" t="n">
         <v>3750</v>
@@ -22438,7 +22438,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727613925934</v>
       </c>
       <c r="H761" t="n">
         <v>6000</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727613925934</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22815,7 +22815,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G774" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H774" t="n">
         <v>2250</v>
@@ -22844,7 +22844,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727613925934</v>
       </c>
       <c r="H775" t="n">
         <v>4500</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.60458254814148</v>
+        <v>1.60458266735077</v>
       </c>
       <c r="H776" t="n">
         <v>28500</v>
@@ -22960,7 +22960,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194203853607</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H779" t="n">
         <v>21750</v>
@@ -23018,7 +23018,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H781" t="n">
         <v>11250</v>
@@ -23105,7 +23105,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H784" t="n">
         <v>2250</v>
@@ -23134,7 +23134,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H785" t="n">
         <v>750</v>
@@ -23163,7 +23163,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H786" t="n">
         <v>2250</v>
@@ -23192,7 +23192,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>1.70282208919525</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H787" t="n">
         <v>16500</v>
@@ -23279,7 +23279,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23308,7 +23308,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194203853607</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H791" t="n">
         <v>8250</v>
@@ -23337,7 +23337,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194203853607</v>
+        <v>1.75194227695465</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
@@ -23395,7 +23395,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G794" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H794" t="n">
         <v>750</v>
@@ -23424,7 +23424,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G795" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H795" t="n">
         <v>750</v>
@@ -23569,7 +23569,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G800" t="n">
-        <v>1.72738218307495</v>
+        <v>1.72738230228424</v>
       </c>
       <c r="H800" t="n">
         <v>21750</v>
@@ -23598,7 +23598,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556864261627</v>
       </c>
       <c r="H801" t="n">
         <v>12750</v>
@@ -23685,7 +23685,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H804" t="n">
         <v>9750</v>
@@ -23714,7 +23714,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H805" t="n">
         <v>45750</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919560432434</v>
       </c>
       <c r="H806" t="n">
         <v>3000</v>
@@ -23772,7 +23772,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G807" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H807" t="n">
         <v>2250</v>
@@ -23801,7 +23801,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H808" t="n">
         <v>750</v>
@@ -23830,7 +23830,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G810" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23917,7 +23917,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G812" t="n">
-        <v>1.72738218307495</v>
+        <v>1.72738230228424</v>
       </c>
       <c r="H812" t="n">
         <v>3000</v>
@@ -23946,7 +23946,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650201320648</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H813" t="n">
         <v>5250</v>
@@ -24033,7 +24033,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842183589935</v>
+        <v>1.94842195510864</v>
       </c>
       <c r="H816" t="n">
         <v>13500</v>
@@ -24062,7 +24062,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748858451843</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H817" t="n">
         <v>76500</v>
@@ -24091,7 +24091,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G818" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H818" t="n">
         <v>8250</v>
@@ -24120,7 +24120,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G819" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H819" t="n">
         <v>25500</v>
@@ -24178,7 +24178,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748858451843</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H821" t="n">
         <v>2250</v>
@@ -24207,7 +24207,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G822" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H822" t="n">
         <v>9000</v>
@@ -24265,7 +24265,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H824" t="n">
         <v>65250</v>
@@ -24294,7 +24294,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H825" t="n">
         <v>78000</v>
@@ -24381,7 +24381,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748858451843</v>
+        <v>1.90748834609985</v>
       </c>
       <c r="H828" t="n">
         <v>11250</v>
@@ -24410,7 +24410,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H829" t="n">
         <v>36000</v>
@@ -24439,7 +24439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H830" t="n">
         <v>53250</v>
@@ -24526,7 +24526,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G833" t="n">
-        <v>2.06303453445435</v>
+        <v>2.06303477287292</v>
       </c>
       <c r="H833" t="n">
         <v>6750</v>
@@ -24555,7 +24555,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.03847455978394</v>
+        <v>2.03847479820251</v>
       </c>
       <c r="H834" t="n">
         <v>3000</v>
@@ -24584,7 +24584,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.9975414276123</v>
+        <v>1.99754166603088</v>
       </c>
       <c r="H835" t="n">
         <v>6000</v>
@@ -24613,7 +24613,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H836" t="n">
         <v>7500</v>
@@ -24671,7 +24671,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H838" t="n">
         <v>23250</v>
@@ -24700,7 +24700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H839" t="n">
         <v>27750</v>
@@ -24729,7 +24729,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H840" t="n">
         <v>3750</v>
@@ -24758,7 +24758,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H841" t="n">
         <v>33000</v>
@@ -24787,7 +24787,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H842" t="n">
         <v>26250</v>
@@ -24874,7 +24874,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G845" t="n">
-        <v>2.06303453445435</v>
+        <v>2.06303477287292</v>
       </c>
       <c r="H845" t="n">
         <v>16500</v>
@@ -24903,7 +24903,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H846" t="n">
         <v>175500</v>
@@ -24990,7 +24990,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G849" t="n">
-        <v>2.03847455978394</v>
+        <v>2.03847479820251</v>
       </c>
       <c r="H849" t="n">
         <v>8250</v>
@@ -25019,7 +25019,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H850" t="n">
         <v>15000</v>
@@ -25077,7 +25077,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25135,7 +25135,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G854" t="n">
-        <v>2.06303453445435</v>
+        <v>2.06303477287292</v>
       </c>
       <c r="H854" t="n">
         <v>42000</v>
@@ -25222,7 +25222,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H857" t="n">
         <v>9750</v>
@@ -25280,7 +25280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.9893547296524</v>
+        <v>1.98935496807098</v>
       </c>
       <c r="H859" t="n">
         <v>53250</v>
@@ -25309,7 +25309,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03847455978394</v>
+        <v>2.03847479820251</v>
       </c>
       <c r="H860" t="n">
         <v>6750</v>
@@ -25367,7 +25367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204843997955</v>
+        <v>1.93204832077026</v>
       </c>
       <c r="H862" t="n">
         <v>27000</v>
@@ -25425,7 +25425,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G864" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H864" t="n">
         <v>7500</v>
@@ -25454,7 +25454,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930164813995</v>
+        <v>1.89930188655853</v>
       </c>
       <c r="H865" t="n">
         <v>6750</v>
@@ -25483,7 +25483,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930164813995</v>
+        <v>1.89930188655853</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25512,7 +25512,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G867" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H867" t="n">
         <v>1500</v>
@@ -25628,7 +25628,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.83380877971649</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H871" t="n">
         <v>3750</v>
@@ -25686,7 +25686,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G873" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H873" t="n">
         <v>4500</v>
@@ -25715,7 +25715,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G874" t="n">
-        <v>1.88292860984802</v>
+        <v>1.88292849063873</v>
       </c>
       <c r="H874" t="n">
         <v>9000</v>
@@ -25802,7 +25802,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H877" t="n">
         <v>15000</v>
@@ -25860,7 +25860,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G879" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H879" t="n">
         <v>1500</v>
@@ -25889,7 +25889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H880" t="n">
         <v>6750</v>
@@ -25918,7 +25918,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G881" t="n">
-        <v>2.06303453445435</v>
+        <v>2.06303477287292</v>
       </c>
       <c r="H881" t="n">
         <v>7500</v>
@@ -25947,7 +25947,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H882" t="n">
         <v>3000</v>
@@ -25976,7 +25976,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G883" t="n">
-        <v>2.06303453445435</v>
+        <v>2.06303477287292</v>
       </c>
       <c r="H883" t="n">
         <v>6000</v>
@@ -26005,7 +26005,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G884" t="n">
-        <v>2.06303453445435</v>
+        <v>2.06303477287292</v>
       </c>
       <c r="H884" t="n">
         <v>4500</v>
@@ -26034,7 +26034,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H885" t="n">
         <v>1500</v>
@@ -26063,7 +26063,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>2.07940793037415</v>
+        <v>2.07940816879272</v>
       </c>
       <c r="H886" t="n">
         <v>4500</v>
@@ -26353,7 +26353,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>2.03028798103333</v>
+        <v>2.0302882194519</v>
       </c>
       <c r="H896" t="n">
         <v>4500</v>
@@ -26469,7 +26469,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H900" t="n">
         <v>1500</v>
@@ -26556,7 +26556,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H903" t="n">
         <v>11250</v>
@@ -26585,7 +26585,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G904" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26643,7 +26643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993104457855</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H906" t="n">
         <v>750</v>
@@ -26672,7 +26672,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993104457855</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H907" t="n">
         <v>3000</v>
@@ -26730,7 +26730,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824726581573</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H909" t="n">
         <v>12750</v>
@@ -27049,7 +27049,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824726581573</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H920" t="n">
         <v>5250</v>
@@ -27078,7 +27078,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H921" t="n">
         <v>6750</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27252,7 +27252,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H927" t="n">
         <v>2250</v>
@@ -27281,7 +27281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824726581573</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H928" t="n">
         <v>3000</v>
@@ -27310,7 +27310,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H929" t="n">
         <v>6750</v>
@@ -27339,7 +27339,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824726581573</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H930" t="n">
         <v>750</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824726581573</v>
+        <v>1.99824702739716</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H932" t="n">
         <v>2250</v>
@@ -27426,7 +27426,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H933" t="n">
         <v>20250</v>
@@ -27455,7 +27455,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H934" t="n">
         <v>12000</v>
@@ -27484,7 +27484,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G935" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H935" t="n">
         <v>5250</v>
@@ -27571,7 +27571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H938" t="n">
         <v>14250</v>
@@ -27716,7 +27716,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H943" t="n">
         <v>2250</v>
@@ -27745,7 +27745,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H944" t="n">
         <v>750</v>
@@ -27774,7 +27774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H945" t="n">
         <v>1500</v>
@@ -27803,7 +27803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408927440643</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H948" t="n">
         <v>2250</v>
@@ -27977,7 +27977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993104457855</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H952" t="n">
         <v>9750</v>
@@ -28035,7 +28035,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G954" t="n">
-        <v>2.01532626152039</v>
+        <v>2.01532602310181</v>
       </c>
       <c r="H954" t="n">
         <v>6750</v>
@@ -28412,7 +28412,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H967" t="n">
         <v>6750</v>
@@ -28441,7 +28441,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H968" t="n">
         <v>2250</v>
@@ -28528,7 +28528,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H971" t="n">
         <v>2250</v>
@@ -28557,7 +28557,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28586,7 +28586,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -28615,7 +28615,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H974" t="n">
         <v>750</v>
@@ -28644,7 +28644,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28731,7 +28731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>1.81037771701813</v>
+        <v>1.81037783622742</v>
       </c>
       <c r="H978" t="n">
         <v>3000</v>
@@ -28789,7 +28789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>1.77621960639954</v>
+        <v>1.77621972560883</v>
       </c>
       <c r="H980" t="n">
         <v>11250</v>
@@ -28818,7 +28818,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G981" t="n">
-        <v>1.81037771701813</v>
+        <v>1.81037783622742</v>
       </c>
       <c r="H981" t="n">
         <v>27000</v>
@@ -28847,7 +28847,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H982" t="n">
         <v>9000</v>
@@ -28934,7 +28934,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H985" t="n">
         <v>4500</v>
@@ -28992,7 +28992,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H987" t="n">
         <v>52500</v>
@@ -29311,7 +29311,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H998" t="n">
         <v>750</v>
@@ -29340,7 +29340,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29398,7 +29398,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1001" t="n">
         <v>8250</v>
@@ -29456,7 +29456,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1003" t="n">
         <v>39000</v>
@@ -29485,7 +29485,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1004" t="n">
         <v>81000</v>
@@ -29514,7 +29514,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1005" t="n">
         <v>9000</v>
@@ -29543,7 +29543,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1006" t="n">
         <v>10500</v>
@@ -29572,7 +29572,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1007" t="n">
         <v>18750</v>
@@ -29601,7 +29601,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1008" t="n">
         <v>9000</v>
@@ -29630,7 +29630,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1010" t="n">
         <v>12000</v>
@@ -29688,7 +29688,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1011" t="n">
         <v>6000</v>
@@ -29717,7 +29717,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1012" t="n">
         <v>6000</v>
@@ -29775,7 +29775,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1014" t="n">
         <v>9000</v>
@@ -29804,7 +29804,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -30152,7 +30152,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1027" t="n">
         <v>1500</v>
@@ -30181,7 +30181,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1028" t="n">
         <v>1500</v>
@@ -30210,7 +30210,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30355,7 +30355,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.34070432186127</v>
+        <v>1.34070444107056</v>
       </c>
       <c r="H1034" t="n">
         <v>28500</v>
@@ -30384,7 +30384,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362520694733</v>
+        <v>1.32362532615662</v>
       </c>
       <c r="H1035" t="n">
         <v>6000</v>
@@ -30413,7 +30413,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.26384878158569</v>
+        <v>1.2638486623764</v>
       </c>
       <c r="H1036" t="n">
         <v>95250</v>
@@ -30442,7 +30442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.34070432186127</v>
+        <v>1.34070444107056</v>
       </c>
       <c r="H1037" t="n">
         <v>27000</v>
@@ -30587,7 +30587,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1042" t="n">
         <v>5250</v>
@@ -30616,7 +30616,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1044" t="n">
         <v>1500</v>
@@ -30819,7 +30819,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.35778343677521</v>
+        <v>1.35778331756592</v>
       </c>
       <c r="H1050" t="n">
         <v>2250</v>
@@ -30935,7 +30935,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1054" t="n">
         <v>31500</v>
@@ -30964,7 +30964,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1055" t="n">
         <v>21000</v>
@@ -31051,7 +31051,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1058" t="n">
         <v>2250</v>
@@ -31399,7 +31399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.45171821117401</v>
+        <v>1.45171809196472</v>
       </c>
       <c r="H1070" t="n">
         <v>3750</v>
@@ -31428,7 +31428,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.47733676433563</v>
+        <v>1.47733664512634</v>
       </c>
       <c r="H1071" t="n">
         <v>750</v>
@@ -31486,7 +31486,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.44317865371704</v>
+        <v>1.44317853450775</v>
       </c>
       <c r="H1073" t="n">
         <v>15750</v>
@@ -32153,7 +32153,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1096" t="n">
         <v>23250</v>
@@ -32211,7 +32211,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1098" t="n">
         <v>12750</v>
@@ -32356,7 +32356,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1103" t="n">
         <v>12000</v>
@@ -32472,7 +32472,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.51149463653564</v>
+        <v>1.51149475574493</v>
       </c>
       <c r="H1107" t="n">
         <v>6750</v>
@@ -32559,7 +32559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958728313446</v>
       </c>
       <c r="H1110" t="n">
         <v>45000</v>
@@ -32849,7 +32849,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H1120" t="n">
         <v>9750</v>
@@ -32965,7 +32965,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1124" t="n">
         <v>35250</v>
@@ -33313,7 +33313,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1136" t="n">
         <v>3750</v>
@@ -33342,7 +33342,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1137" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H1140" t="n">
         <v>8250</v>
@@ -33632,7 +33632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958728313446</v>
       </c>
       <c r="H1147" t="n">
         <v>9750</v>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189449310303</v>
+        <v>2.73189401626587</v>
       </c>
       <c r="H2" t="n">
         <v>893250</v>
@@ -456,7 +456,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722755432129</v>
+        <v>2.86722803115845</v>
       </c>
       <c r="H3" t="n">
         <v>428250</v>
@@ -543,7 +543,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.70586848258972</v>
+        <v>2.7058687210083</v>
       </c>
       <c r="H6" t="n">
         <v>35250</v>
@@ -601,7 +601,7 @@
         <v>3.38949990272522</v>
       </c>
       <c r="G8" t="n">
-        <v>2.7142767906189</v>
+        <v>2.71427655220032</v>
       </c>
       <c r="H8" t="n">
         <v>111000</v>
@@ -659,7 +659,7 @@
         <v>3.43650007247925</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75191402435303</v>
+        <v>2.75191426277161</v>
       </c>
       <c r="H10" t="n">
         <v>33750</v>
@@ -775,7 +775,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72228479385376</v>
+        <v>2.72228455543518</v>
       </c>
       <c r="H14" t="n">
         <v>7500</v>
@@ -891,7 +891,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558554649353</v>
+        <v>3.63558530807495</v>
       </c>
       <c r="H18" t="n">
         <v>196500</v>
@@ -920,7 +920,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.96390914916992</v>
+        <v>3.9639093875885</v>
       </c>
       <c r="H19" t="n">
         <v>402000</v>
@@ -949,7 +949,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578324317932</v>
+        <v>3.83578300476074</v>
       </c>
       <c r="H20" t="n">
         <v>495750</v>
@@ -978,7 +978,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G21" t="n">
-        <v>3.60515546798706</v>
+        <v>3.60515570640564</v>
       </c>
       <c r="H21" t="n">
         <v>81000</v>
@@ -1007,7 +1007,7 @@
         <v>4.28999996185303</v>
       </c>
       <c r="G22" t="n">
-        <v>3.4353883266449</v>
+        <v>3.43538808822632</v>
       </c>
       <c r="H22" t="n">
         <v>193500</v>
@@ -1094,7 +1094,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.49144339561462</v>
+        <v>3.4914436340332</v>
       </c>
       <c r="H25" t="n">
         <v>20250</v>
@@ -1123,7 +1123,7 @@
         <v>4.38350009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>3.51026201248169</v>
+        <v>3.51026225090027</v>
       </c>
       <c r="H26" t="n">
         <v>24750</v>
@@ -1152,7 +1152,7 @@
         <v>4.24350023269653</v>
       </c>
       <c r="G27" t="n">
-        <v>3.39815163612366</v>
+        <v>3.39815187454224</v>
       </c>
       <c r="H27" t="n">
         <v>19500</v>
@@ -1181,7 +1181,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329748153687</v>
+        <v>3.34329771995544</v>
       </c>
       <c r="H28" t="n">
         <v>18000</v>
@@ -1268,7 +1268,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048486709595</v>
+        <v>3.33048439025879</v>
       </c>
       <c r="H31" t="n">
         <v>6750</v>
@@ -1326,7 +1326,7 @@
         <v>3.625</v>
       </c>
       <c r="G33" t="n">
-        <v>2.90286302566528</v>
+        <v>2.9028627872467</v>
       </c>
       <c r="H33" t="n">
         <v>146250</v>
@@ -1413,7 +1413,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.97093033790588</v>
+        <v>2.9709300994873</v>
       </c>
       <c r="H36" t="n">
         <v>16500</v>
@@ -1442,7 +1442,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H37" t="n">
         <v>750</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H38" t="n">
         <v>27000</v>
@@ -1529,7 +1529,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H40" t="n">
         <v>3000</v>
@@ -1616,7 +1616,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>3.03499317169189</v>
+        <v>3.03499293327332</v>
       </c>
       <c r="H43" t="n">
         <v>3750</v>
@@ -1645,7 +1645,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>3.03499317169189</v>
+        <v>3.03499293327332</v>
       </c>
       <c r="H44" t="n">
         <v>750</v>
@@ -1674,7 +1674,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H45" t="n">
         <v>13500</v>
@@ -1703,7 +1703,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H46" t="n">
         <v>3000</v>
@@ -1732,7 +1732,7 @@
         <v>3.625</v>
       </c>
       <c r="G47" t="n">
-        <v>2.90286302566528</v>
+        <v>2.9028627872467</v>
       </c>
       <c r="H47" t="n">
         <v>12000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1906,7 +1906,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H53" t="n">
         <v>9000</v>
@@ -1964,7 +1964,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H55" t="n">
         <v>2250</v>
@@ -2022,7 +2022,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702470779419</v>
+        <v>3.06702494621277</v>
       </c>
       <c r="H57" t="n">
         <v>18750</v>
@@ -2051,7 +2051,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H58" t="n">
         <v>3000</v>
@@ -2080,7 +2080,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H59" t="n">
         <v>12000</v>
@@ -2109,7 +2109,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2167,7 +2167,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505248069763</v>
+        <v>3.09505271911621</v>
       </c>
       <c r="H62" t="n">
         <v>4500</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2283,7 +2283,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>2.90686726570129</v>
+        <v>2.90686702728271</v>
       </c>
       <c r="H66" t="n">
         <v>3750</v>
@@ -2370,7 +2370,7 @@
         <v>3.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2428,7 +2428,7 @@
         <v>3.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H71" t="n">
         <v>750</v>
@@ -2486,7 +2486,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467709541321</v>
       </c>
       <c r="H73" t="n">
         <v>17250</v>
@@ -2515,7 +2515,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H74" t="n">
         <v>15000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>2.83879995346069</v>
+        <v>2.83879947662354</v>
       </c>
       <c r="H75" t="n">
         <v>12750</v>
@@ -2660,7 +2660,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897740364075</v>
+        <v>3.01897764205933</v>
       </c>
       <c r="H79" t="n">
         <v>7500</v>
@@ -2892,7 +2892,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.59055471420288</v>
+        <v>2.59055495262146</v>
       </c>
       <c r="H87" t="n">
         <v>14250</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H90" t="n">
         <v>10500</v>
@@ -3008,7 +3008,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>2.25021910667419</v>
+        <v>2.25021934509277</v>
       </c>
       <c r="H91" t="n">
         <v>27750</v>
@@ -3037,7 +3037,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.0099823474884</v>
+        <v>2.00998258590698</v>
       </c>
       <c r="H92" t="n">
         <v>16500</v>
@@ -3066,7 +3066,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.0099823474884</v>
+        <v>2.00998258590698</v>
       </c>
       <c r="H93" t="n">
         <v>9750</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185596466064</v>
+        <v>1.88185572624207</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3153,7 +3153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H96" t="n">
         <v>14250</v>
@@ -3240,7 +3240,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556365966797</v>
+        <v>1.58556377887726</v>
       </c>
       <c r="H99" t="n">
         <v>14250</v>
@@ -3269,7 +3269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161920547485</v>
+        <v>1.64161896705627</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3327,7 +3327,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.67765462398529</v>
+        <v>1.677654504776</v>
       </c>
       <c r="H102" t="n">
         <v>11250</v>
@@ -3356,7 +3356,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771393299103</v>
       </c>
       <c r="H103" t="n">
         <v>12000</v>
@@ -3385,7 +3385,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G104" t="n">
-        <v>1.75773358345032</v>
+        <v>1.75773346424103</v>
       </c>
       <c r="H104" t="n">
         <v>12000</v>
@@ -3414,7 +3414,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H105" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771393299103</v>
       </c>
       <c r="H107" t="n">
         <v>750</v>
@@ -3501,7 +3501,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8978716135025</v>
+        <v>1.89787173271179</v>
       </c>
       <c r="H108" t="n">
         <v>15750</v>
@@ -3588,7 +3588,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>2.46643209457397</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H111" t="n">
         <v>28500</v>
@@ -3617,7 +3617,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H112" t="n">
         <v>15000</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H116" t="n">
         <v>6750</v>
@@ -3762,7 +3762,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H117" t="n">
         <v>3750</v>
@@ -3820,7 +3820,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79475617408752</v>
+        <v>2.7947564125061</v>
       </c>
       <c r="H119" t="n">
         <v>8250</v>
@@ -3849,7 +3849,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664956092834</v>
+        <v>2.68664979934692</v>
       </c>
       <c r="H120" t="n">
         <v>11250</v>
@@ -3936,7 +3936,7 @@
         <v>3.43499994277954</v>
       </c>
       <c r="G123" t="n">
-        <v>2.75071287155151</v>
+        <v>2.75071263313293</v>
       </c>
       <c r="H123" t="n">
         <v>5250</v>
@@ -3965,7 +3965,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467709541321</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -4023,7 +4023,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H126" t="n">
         <v>3750</v>
@@ -4052,7 +4052,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.79475617408752</v>
+        <v>2.7947564125061</v>
       </c>
       <c r="H127" t="n">
         <v>2250</v>
@@ -4081,7 +4081,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.78674864768982</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H128" t="n">
         <v>3000</v>
@@ -4110,7 +4110,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78674864768982</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4197,7 +4197,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G132" t="n">
-        <v>2.61057472229004</v>
+        <v>2.61057448387146</v>
       </c>
       <c r="H132" t="n">
         <v>1500</v>
@@ -4487,7 +4487,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.44240880012512</v>
+        <v>2.44240856170654</v>
       </c>
       <c r="H142" t="n">
         <v>750</v>
@@ -4516,7 +4516,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46643209457397</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4545,7 +4545,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H144" t="n">
         <v>1500</v>
@@ -4574,7 +4574,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H145" t="n">
         <v>3000</v>
@@ -4603,7 +4603,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71868133544922</v>
+        <v>2.71868109703064</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4777,7 +4777,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G152" t="n">
-        <v>2.71067309379578</v>
+        <v>2.71067333221436</v>
       </c>
       <c r="H152" t="n">
         <v>750</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H161" t="n">
         <v>14250</v>
@@ -5096,7 +5096,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>2.50647234916687</v>
+        <v>2.50647211074829</v>
       </c>
       <c r="H163" t="n">
         <v>6750</v>
@@ -5299,7 +5299,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H170" t="n">
         <v>18000</v>
@@ -5386,7 +5386,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H173" t="n">
         <v>2250</v>
@@ -5415,7 +5415,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G176" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H177" t="n">
         <v>3750</v>
@@ -5531,7 +5531,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G179" t="n">
-        <v>2.44240880012512</v>
+        <v>2.44240856170654</v>
       </c>
       <c r="H179" t="n">
         <v>2250</v>
@@ -5850,7 +5850,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H189" t="n">
         <v>3750</v>
@@ -5879,7 +5879,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -5908,7 +5908,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G191" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H191" t="n">
         <v>1500</v>
@@ -6111,7 +6111,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.05100893974304</v>
+        <v>3.05100917816162</v>
       </c>
       <c r="H198" t="n">
         <v>203250</v>
@@ -6140,7 +6140,7 @@
         <v>3.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H199" t="n">
         <v>148500</v>
@@ -6169,7 +6169,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H200" t="n">
         <v>47250</v>
@@ -6256,7 +6256,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264532089233</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H203" t="n">
         <v>9750</v>
@@ -6314,7 +6314,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451965332031</v>
+        <v>2.55451917648315</v>
       </c>
       <c r="H205" t="n">
         <v>13500</v>
@@ -6517,7 +6517,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H212" t="n">
         <v>2250</v>
@@ -6546,7 +6546,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H213" t="n">
         <v>10500</v>
@@ -6575,7 +6575,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.44240880012512</v>
+        <v>2.44240856170654</v>
       </c>
       <c r="H214" t="n">
         <v>8250</v>
@@ -6662,7 +6662,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H217" t="n">
         <v>11250</v>
@@ -6691,7 +6691,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H220" t="n">
         <v>750</v>
@@ -6778,7 +6778,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>2.44240880012512</v>
+        <v>2.44240856170654</v>
       </c>
       <c r="H221" t="n">
         <v>1500</v>
@@ -6836,7 +6836,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651141166687</v>
       </c>
       <c r="H223" t="n">
         <v>5250</v>
@@ -6865,7 +6865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6894,7 +6894,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H225" t="n">
         <v>5250</v>
@@ -6981,7 +6981,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H228" t="n">
         <v>15750</v>
@@ -7010,7 +7010,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>2.35031795501709</v>
+        <v>2.35031771659851</v>
       </c>
       <c r="H229" t="n">
         <v>18750</v>
@@ -7039,7 +7039,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.35832571983337</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H230" t="n">
         <v>750</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H231" t="n">
         <v>3000</v>
@@ -7126,7 +7126,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.33029842376709</v>
+        <v>2.33029866218567</v>
       </c>
       <c r="H233" t="n">
         <v>3750</v>
@@ -7213,7 +7213,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29025888442993</v>
+        <v>2.29025840759277</v>
       </c>
       <c r="H236" t="n">
         <v>2250</v>
@@ -7242,7 +7242,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.29025888442993</v>
+        <v>2.29025840759277</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7271,7 +7271,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G238" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H238" t="n">
         <v>1500</v>
@@ -7300,7 +7300,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G239" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -7329,7 +7329,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35832571983337</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G241" t="n">
-        <v>2.35832571983337</v>
+        <v>2.35832619667053</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7851,7 +7851,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>2.25021910667419</v>
+        <v>2.25021934509277</v>
       </c>
       <c r="H258" t="n">
         <v>750</v>
@@ -7880,7 +7880,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25021910667419</v>
+        <v>2.25021934509277</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H262" t="n">
         <v>2250</v>
@@ -7996,7 +7996,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H263" t="n">
         <v>750</v>
@@ -8054,7 +8054,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.1861560344696</v>
+        <v>2.18615627288818</v>
       </c>
       <c r="H265" t="n">
         <v>1500</v>
@@ -8141,7 +8141,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8170,7 +8170,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G269" t="n">
-        <v>2.26623487472534</v>
+        <v>2.26623511314392</v>
       </c>
       <c r="H269" t="n">
         <v>4500</v>
@@ -8228,7 +8228,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H271" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834572792053</v>
+        <v>2.37834548950195</v>
       </c>
       <c r="H274" t="n">
         <v>3750</v>
@@ -8373,7 +8373,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H276" t="n">
         <v>3000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H282" t="n">
         <v>3750</v>
@@ -8576,7 +8576,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8750,7 +8750,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H289" t="n">
         <v>750</v>
@@ -8779,7 +8779,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H290" t="n">
         <v>750</v>
@@ -8808,7 +8808,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -9040,7 +9040,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H299" t="n">
         <v>3000</v>
@@ -9069,7 +9069,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225064277649</v>
+        <v>2.28225088119507</v>
       </c>
       <c r="H300" t="n">
         <v>750</v>
@@ -9098,7 +9098,7 @@
         <v>2.75</v>
       </c>
       <c r="G301" t="n">
-        <v>2.20217204093933</v>
+        <v>2.20217180252075</v>
       </c>
       <c r="H301" t="n">
         <v>9000</v>
@@ -9127,7 +9127,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H302" t="n">
         <v>3000</v>
@@ -9156,7 +9156,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G304" t="n">
-        <v>2.73069310188293</v>
+        <v>2.73069357872009</v>
       </c>
       <c r="H304" t="n">
         <v>120750</v>
@@ -9272,7 +9272,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H307" t="n">
         <v>32250</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H308" t="n">
         <v>6750</v>
@@ -9359,7 +9359,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G310" t="n">
-        <v>2.39035725593567</v>
+        <v>2.39035749435425</v>
       </c>
       <c r="H310" t="n">
         <v>3000</v>
@@ -9388,7 +9388,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.44240880012512</v>
+        <v>2.44240856170654</v>
       </c>
       <c r="H311" t="n">
         <v>5250</v>
@@ -9446,7 +9446,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G313" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H313" t="n">
         <v>5250</v>
@@ -9475,7 +9475,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H314" t="n">
         <v>1500</v>
@@ -9504,7 +9504,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430194854736</v>
+        <v>2.33430218696594</v>
       </c>
       <c r="H320" t="n">
         <v>750</v>
@@ -9794,7 +9794,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H325" t="n">
         <v>13500</v>
@@ -9823,7 +9823,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G326" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H326" t="n">
         <v>6750</v>
@@ -9881,7 +9881,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G328" t="n">
-        <v>2.44240880012512</v>
+        <v>2.44240856170654</v>
       </c>
       <c r="H328" t="n">
         <v>9750</v>
@@ -9910,7 +9910,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>2.46643209457397</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H329" t="n">
         <v>2250</v>
@@ -9997,7 +9997,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.44240880012512</v>
+        <v>2.44240856170654</v>
       </c>
       <c r="H332" t="n">
         <v>4500</v>
@@ -10026,7 +10026,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H333" t="n">
         <v>9000</v>
@@ -10055,7 +10055,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H334" t="n">
         <v>2250</v>
@@ -10171,7 +10171,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.4063732624054</v>
+        <v>2.40637350082397</v>
       </c>
       <c r="H338" t="n">
         <v>1500</v>
@@ -10229,7 +10229,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G340" t="n">
-        <v>2.50647234916687</v>
+        <v>2.50647211074829</v>
       </c>
       <c r="H340" t="n">
         <v>29250</v>
@@ -10258,7 +10258,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238903045654</v>
       </c>
       <c r="H341" t="n">
         <v>20250</v>
@@ -10287,7 +10287,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H342" t="n">
         <v>1500</v>
@@ -10316,7 +10316,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G343" t="n">
-        <v>2.39035725593567</v>
+        <v>2.39035749435425</v>
       </c>
       <c r="H343" t="n">
         <v>6000</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>2.62659049034119</v>
+        <v>2.62659025192261</v>
       </c>
       <c r="H351" t="n">
         <v>3750</v>
@@ -10577,7 +10577,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451965332031</v>
+        <v>2.55451917648315</v>
       </c>
       <c r="H352" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G354" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H354" t="n">
         <v>4500</v>
@@ -10809,7 +10809,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467733383179</v>
+        <v>2.71467709541321</v>
       </c>
       <c r="H360" t="n">
         <v>10500</v>
@@ -10838,7 +10838,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.77473640441895</v>
+        <v>2.77473664283752</v>
       </c>
       <c r="H361" t="n">
         <v>13500</v>
@@ -10983,7 +10983,7 @@
         <v>3.5</v>
       </c>
       <c r="G366" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H366" t="n">
         <v>25500</v>
@@ -11012,7 +11012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H367" t="n">
         <v>172500</v>
@@ -11041,7 +11041,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>3.26722240447998</v>
+        <v>3.2672221660614</v>
       </c>
       <c r="H368" t="n">
         <v>210750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11244,7 +11244,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H375" t="n">
         <v>3750</v>
@@ -11273,7 +11273,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H376" t="n">
         <v>39000</v>
@@ -11302,7 +11302,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H377" t="n">
         <v>18000</v>
@@ -11331,7 +11331,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H378" t="n">
         <v>6000</v>
@@ -11360,7 +11360,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H379" t="n">
         <v>24000</v>
@@ -11389,7 +11389,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11505,7 +11505,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H384" t="n">
         <v>19500</v>
@@ -11534,7 +11534,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H385" t="n">
         <v>22500</v>
@@ -11563,7 +11563,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11592,7 +11592,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H387" t="n">
         <v>3750</v>
@@ -11766,7 +11766,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.17112731933594</v>
+        <v>3.17112755775452</v>
       </c>
       <c r="H393" t="n">
         <v>23250</v>
@@ -11795,7 +11795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H394" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -11853,7 +11853,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H397" t="n">
         <v>750</v>
@@ -11911,7 +11911,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -11998,7 +11998,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H401" t="n">
         <v>8250</v>
@@ -12056,7 +12056,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.26722240447998</v>
+        <v>3.2672221660614</v>
       </c>
       <c r="H403" t="n">
         <v>38250</v>
@@ -12085,7 +12085,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H404" t="n">
         <v>21000</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H409" t="n">
         <v>12750</v>
@@ -12317,7 +12317,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H412" t="n">
         <v>3000</v>
@@ -12346,7 +12346,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>3.21917462348938</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H413" t="n">
         <v>5250</v>
@@ -12404,7 +12404,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.13909578323364</v>
+        <v>3.1390962600708</v>
       </c>
       <c r="H415" t="n">
         <v>2250</v>
@@ -12462,7 +12462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H417" t="n">
         <v>3750</v>
@@ -12491,7 +12491,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H418" t="n">
         <v>8250</v>
@@ -12549,7 +12549,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H420" t="n">
         <v>2250</v>
@@ -12578,7 +12578,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H421" t="n">
         <v>3000</v>
@@ -12607,7 +12607,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12723,7 +12723,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H426" t="n">
         <v>5250</v>
@@ -12752,7 +12752,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G427" t="n">
-        <v>3.12308025360107</v>
+        <v>3.1230800151825</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H430" t="n">
         <v>7500</v>
@@ -12926,7 +12926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H433" t="n">
         <v>1500</v>
@@ -12955,7 +12955,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H434" t="n">
         <v>750</v>
@@ -12984,7 +12984,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G435" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H436" t="n">
         <v>4500</v>
@@ -13042,7 +13042,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H437" t="n">
         <v>750</v>
@@ -13187,7 +13187,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H442" t="n">
         <v>750</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13419,7 +13419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H450" t="n">
         <v>1500</v>
@@ -13477,7 +13477,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>3.04300117492676</v>
+        <v>3.04300093650818</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13738,7 +13738,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H461" t="n">
         <v>1500</v>
@@ -13767,7 +13767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H466" t="n">
         <v>9750</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14405,7 +14405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H484" t="n">
         <v>2250</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14637,7 +14637,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690656661987</v>
+        <v>2.94690632820129</v>
       </c>
       <c r="H492" t="n">
         <v>750</v>
@@ -14695,7 +14695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H494" t="n">
         <v>2250</v>
@@ -14869,7 +14869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H500" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H508" t="n">
         <v>4500</v>
@@ -15275,7 +15275,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H514" t="n">
         <v>5250</v>
@@ -15362,7 +15362,7 @@
         <v>3.5</v>
       </c>
       <c r="G517" t="n">
-        <v>2.80276393890381</v>
+        <v>2.80276441574097</v>
       </c>
       <c r="H517" t="n">
         <v>6750</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15652,7 +15652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15681,7 +15681,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846386909485</v>
+        <v>2.49846410751343</v>
       </c>
       <c r="H528" t="n">
         <v>5250</v>
@@ -15710,7 +15710,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G529" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H529" t="n">
         <v>9000</v>
@@ -15739,7 +15739,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H530" t="n">
         <v>5250</v>
@@ -15768,7 +15768,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H531" t="n">
         <v>3000</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15826,7 +15826,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H533" t="n">
         <v>15000</v>
@@ -16000,7 +16000,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041680335999</v>
+        <v>2.45041656494141</v>
       </c>
       <c r="H539" t="n">
         <v>24750</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16203,7 +16203,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H546" t="n">
         <v>8250</v>
@@ -16261,7 +16261,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>2.29025888442993</v>
+        <v>2.29025840759277</v>
       </c>
       <c r="H548" t="n">
         <v>6750</v>
@@ -16319,7 +16319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16435,7 +16435,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H555" t="n">
         <v>6000</v>
@@ -16609,7 +16609,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H560" t="n">
         <v>1500</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16725,7 +16725,7 @@
         <v>3.01999998092651</v>
       </c>
       <c r="G564" t="n">
-        <v>2.41838502883911</v>
+        <v>2.41838526725769</v>
       </c>
       <c r="H564" t="n">
         <v>3000</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H568" t="n">
         <v>6750</v>
@@ -16870,7 +16870,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H570" t="n">
         <v>750</v>
@@ -16928,7 +16928,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H571" t="n">
         <v>7500</v>
@@ -16957,7 +16957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H572" t="n">
         <v>3000</v>
@@ -17073,7 +17073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424311637878</v>
       </c>
       <c r="H576" t="n">
         <v>3000</v>
@@ -17218,7 +17218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213226318359</v>
+        <v>2.16213250160217</v>
       </c>
       <c r="H581" t="n">
         <v>15750</v>
@@ -17334,7 +17334,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G585" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H585" t="n">
         <v>6000</v>
@@ -17363,7 +17363,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400611877441</v>
+        <v>2.03400564193726</v>
       </c>
       <c r="H586" t="n">
         <v>6000</v>
@@ -17392,7 +17392,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G587" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H587" t="n">
         <v>3000</v>
@@ -17479,7 +17479,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G590" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H590" t="n">
         <v>10500</v>
@@ -17508,7 +17508,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.05002164840698</v>
+        <v>2.05002188682556</v>
       </c>
       <c r="H591" t="n">
         <v>11250</v>
@@ -17537,7 +17537,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400611877441</v>
+        <v>2.03400564193726</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17595,7 +17595,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G594" t="n">
-        <v>1.98595881462097</v>
+        <v>1.98595857620239</v>
       </c>
       <c r="H594" t="n">
         <v>6000</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>2.00197434425354</v>
+        <v>2.00197458267212</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986361026764</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.63361120223999</v>
+        <v>1.6336110830307</v>
       </c>
       <c r="H604" t="n">
         <v>1500</v>
@@ -17943,7 +17943,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H606" t="n">
         <v>14250</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H608" t="n">
         <v>11250</v>
@@ -18059,7 +18059,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H610" t="n">
         <v>5250</v>
@@ -18117,7 +18117,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18146,7 +18146,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H613" t="n">
         <v>4500</v>
@@ -18175,7 +18175,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H614" t="n">
         <v>4500</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.69767427444458</v>
+        <v>1.69767439365387</v>
       </c>
       <c r="H615" t="n">
         <v>5250</v>
@@ -18262,7 +18262,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H617" t="n">
         <v>5250</v>
@@ -18291,7 +18291,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376924037933</v>
+        <v>1.79376900196075</v>
       </c>
       <c r="H618" t="n">
         <v>10500</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986361026764</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18378,7 +18378,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.95392727851868</v>
+        <v>1.95392715930939</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.8097847700119</v>
+        <v>1.80978488922119</v>
       </c>
       <c r="H622" t="n">
         <v>48750</v>
@@ -18436,7 +18436,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962697029114</v>
+        <v>1.64962685108185</v>
       </c>
       <c r="H623" t="n">
         <v>186750</v>
@@ -18523,7 +18523,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.72169816493988</v>
+        <v>1.7216979265213</v>
       </c>
       <c r="H626" t="n">
         <v>40500</v>
@@ -18610,7 +18610,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376924037933</v>
+        <v>1.79376900196075</v>
       </c>
       <c r="H629" t="n">
         <v>18750</v>
@@ -18639,7 +18639,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173758506775</v>
+        <v>1.76173746585846</v>
       </c>
       <c r="H630" t="n">
         <v>14250</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.72169816493988</v>
+        <v>1.7216979265213</v>
       </c>
       <c r="H631" t="n">
         <v>5250</v>
@@ -18697,7 +18697,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H632" t="n">
         <v>2250</v>
@@ -18726,7 +18726,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H633" t="n">
         <v>750</v>
@@ -18755,7 +18755,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.74572169780731</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H635" t="n">
         <v>5250</v>
@@ -18842,7 +18842,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771369457245</v>
+        <v>1.73771393299103</v>
       </c>
       <c r="H637" t="n">
         <v>7500</v>
@@ -18871,7 +18871,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165862560272</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H638" t="n">
         <v>18000</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779277324677</v>
+        <v>1.81779265403748</v>
       </c>
       <c r="H640" t="n">
         <v>17250</v>
@@ -18958,7 +18958,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779277324677</v>
+        <v>1.81779265403748</v>
       </c>
       <c r="H641" t="n">
         <v>167250</v>
@@ -18987,7 +18987,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75372958183289</v>
+        <v>1.75372970104218</v>
       </c>
       <c r="H642" t="n">
         <v>8250</v>
@@ -19016,7 +19016,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.83380854129791</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H643" t="n">
         <v>15000</v>
@@ -19045,7 +19045,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G644" t="n">
-        <v>1.81743514537811</v>
+        <v>1.81743538379669</v>
       </c>
       <c r="H644" t="n">
         <v>18000</v>
@@ -19103,7 +19103,7 @@
         <v>2.25</v>
       </c>
       <c r="G646" t="n">
-        <v>1.84199523925781</v>
+        <v>1.8419953584671</v>
       </c>
       <c r="H646" t="n">
         <v>12750</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H648" t="n">
         <v>47250</v>
@@ -19190,7 +19190,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.85018181800842</v>
+        <v>1.85018193721771</v>
       </c>
       <c r="H649" t="n">
         <v>5250</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474191188812</v>
       </c>
       <c r="H651" t="n">
         <v>33750</v>
@@ -19277,7 +19277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836863517761</v>
+        <v>1.85836839675903</v>
       </c>
       <c r="H652" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836863517761</v>
+        <v>1.85836839675903</v>
       </c>
       <c r="H653" t="n">
         <v>4500</v>
@@ -19364,7 +19364,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650225162506</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650225162506</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19451,7 +19451,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G658" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H658" t="n">
         <v>11250</v>
@@ -19509,7 +19509,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G660" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H660" t="n">
         <v>12000</v>
@@ -19567,7 +19567,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474191188812</v>
       </c>
       <c r="H662" t="n">
         <v>7500</v>
@@ -19683,7 +19683,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H666" t="n">
         <v>4500</v>
@@ -19712,7 +19712,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H667" t="n">
         <v>5250</v>
@@ -19741,7 +19741,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H668" t="n">
         <v>10500</v>
@@ -19799,7 +19799,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H670" t="n">
         <v>15750</v>
@@ -19857,7 +19857,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H672" t="n">
         <v>2250</v>
@@ -19886,7 +19886,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H673" t="n">
         <v>3000</v>
@@ -19915,7 +19915,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G674" t="n">
-        <v>1.72738230228424</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H674" t="n">
         <v>750</v>
@@ -19944,7 +19944,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H675" t="n">
         <v>3750</v>
@@ -19973,7 +19973,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G676" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H676" t="n">
         <v>750</v>
@@ -20002,7 +20002,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G677" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20060,7 +20060,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G679" t="n">
-        <v>1.72738230228424</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H679" t="n">
         <v>5250</v>
@@ -20118,7 +20118,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H681" t="n">
         <v>750</v>
@@ -20176,7 +20176,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H683" t="n">
         <v>8250</v>
@@ -20205,7 +20205,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H684" t="n">
         <v>6000</v>
@@ -20234,7 +20234,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H685" t="n">
         <v>4500</v>
@@ -20292,7 +20292,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G687" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H687" t="n">
         <v>34500</v>
@@ -20321,7 +20321,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012873649597</v>
       </c>
       <c r="H688" t="n">
         <v>19500</v>
@@ -20379,7 +20379,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G690" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H690" t="n">
         <v>2250</v>
@@ -20408,7 +20408,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G691" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H691" t="n">
         <v>0</v>
@@ -20437,7 +20437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20553,7 +20553,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G696" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H696" t="n">
         <v>1500</v>
@@ -20582,7 +20582,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G697" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H697" t="n">
         <v>4500</v>
@@ -20611,7 +20611,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H699" t="n">
         <v>1500</v>
@@ -20669,7 +20669,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G700" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G701" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H701" t="n">
         <v>750</v>
@@ -20727,7 +20727,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G702" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H702" t="n">
         <v>750</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H703" t="n">
         <v>2250</v>
@@ -20785,7 +20785,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G704" t="n">
-        <v>1.72738230228424</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H704" t="n">
         <v>1500</v>
@@ -20814,7 +20814,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>1.71100890636444</v>
+        <v>1.71100878715515</v>
       </c>
       <c r="H705" t="n">
         <v>750</v>
@@ -20843,7 +20843,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H706" t="n">
         <v>750</v>
@@ -20872,7 +20872,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H707" t="n">
         <v>2250</v>
@@ -20901,7 +20901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -21017,7 +21017,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G712" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H712" t="n">
         <v>9000</v>
@@ -21046,7 +21046,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G713" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H713" t="n">
         <v>750</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21104,7 +21104,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79287540912628</v>
+        <v>1.79287552833557</v>
       </c>
       <c r="H715" t="n">
         <v>3000</v>
@@ -21162,7 +21162,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H717" t="n">
         <v>7500</v>
@@ -21191,7 +21191,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H718" t="n">
         <v>2250</v>
@@ -21220,7 +21220,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012873649597</v>
       </c>
       <c r="H720" t="n">
         <v>3000</v>
@@ -21278,7 +21278,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012873649597</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21394,7 +21394,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G725" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H725" t="n">
         <v>8250</v>
@@ -21423,7 +21423,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G726" t="n">
-        <v>1.67007577419281</v>
+        <v>1.67007565498352</v>
       </c>
       <c r="H726" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H727" t="n">
         <v>3750</v>
@@ -21481,7 +21481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H731" t="n">
         <v>3000</v>
@@ -21597,7 +21597,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G732" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H732" t="n">
         <v>2250</v>
@@ -21626,7 +21626,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G733" t="n">
-        <v>1.66188907623291</v>
+        <v>1.66188895702362</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H734" t="n">
         <v>750</v>
@@ -21684,7 +21684,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H737" t="n">
         <v>2250</v>
@@ -21771,7 +21771,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G738" t="n">
-        <v>1.54318261146545</v>
+        <v>1.54318273067474</v>
       </c>
       <c r="H738" t="n">
         <v>12750</v>
@@ -21800,7 +21800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G739" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H739" t="n">
         <v>11250</v>
@@ -21829,7 +21829,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G740" t="n">
-        <v>1.58002269268036</v>
+        <v>1.58002257347107</v>
       </c>
       <c r="H740" t="n">
         <v>2250</v>
@@ -21858,7 +21858,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H741" t="n">
         <v>2250</v>
@@ -21887,7 +21887,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H742" t="n">
         <v>7500</v>
@@ -21916,7 +21916,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H746" t="n">
         <v>6000</v>
@@ -22061,7 +22061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G748" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H748" t="n">
         <v>10500</v>
@@ -22090,7 +22090,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.56364929676056</v>
+        <v>1.56364941596985</v>
       </c>
       <c r="H749" t="n">
         <v>6750</v>
@@ -22119,7 +22119,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H751" t="n">
         <v>4500</v>
@@ -22177,7 +22177,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.50224959850311</v>
+        <v>1.50224947929382</v>
       </c>
       <c r="H752" t="n">
         <v>10500</v>
@@ -22264,7 +22264,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359609603882</v>
+        <v>1.47359621524811</v>
       </c>
       <c r="H755" t="n">
         <v>6000</v>
@@ -22293,7 +22293,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G756" t="n">
-        <v>1.48996961116791</v>
+        <v>1.48996949195862</v>
       </c>
       <c r="H756" t="n">
         <v>16500</v>
@@ -22322,7 +22322,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H757" t="n">
         <v>79500</v>
@@ -22351,7 +22351,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G758" t="n">
-        <v>1.58002269268036</v>
+        <v>1.58002257347107</v>
       </c>
       <c r="H758" t="n">
         <v>6750</v>
@@ -22380,7 +22380,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G759" t="n">
-        <v>1.58002269268036</v>
+        <v>1.58002257347107</v>
       </c>
       <c r="H759" t="n">
         <v>0</v>
@@ -22438,7 +22438,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727613925934</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H761" t="n">
         <v>6000</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727613925934</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H763" t="n">
         <v>3750</v>
@@ -22525,7 +22525,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -22612,7 +22612,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G768" t="n">
-        <v>1.56364929676056</v>
+        <v>1.56364941596985</v>
       </c>
       <c r="H768" t="n">
         <v>1500</v>
@@ -22815,7 +22815,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G774" t="n">
-        <v>1.55546271800995</v>
+        <v>1.55546259880066</v>
       </c>
       <c r="H774" t="n">
         <v>2250</v>
@@ -22844,7 +22844,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727613925934</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H775" t="n">
         <v>4500</v>
@@ -22902,7 +22902,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H777" t="n">
         <v>16500</v>
@@ -22931,7 +22931,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.63732922077179</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H778" t="n">
         <v>3000</v>
@@ -22960,7 +22960,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G779" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H779" t="n">
         <v>21750</v>
@@ -22989,7 +22989,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H780" t="n">
         <v>60000</v>
@@ -23018,7 +23018,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H781" t="n">
         <v>11250</v>
@@ -23047,7 +23047,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012873649597</v>
       </c>
       <c r="H782" t="n">
         <v>7500</v>
@@ -23076,7 +23076,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012873649597</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H784" t="n">
         <v>2250</v>
@@ -23134,7 +23134,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H785" t="n">
         <v>750</v>
@@ -23163,7 +23163,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H786" t="n">
         <v>2250</v>
@@ -23192,7 +23192,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>1.70282220840454</v>
+        <v>1.70282232761383</v>
       </c>
       <c r="H787" t="n">
         <v>16500</v>
@@ -23279,7 +23279,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23308,7 +23308,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G791" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H791" t="n">
         <v>8250</v>
@@ -23337,7 +23337,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G792" t="n">
-        <v>1.75194227695465</v>
+        <v>1.75194215774536</v>
       </c>
       <c r="H792" t="n">
         <v>0</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.80924880504608</v>
+        <v>1.80924868583679</v>
       </c>
       <c r="H793" t="n">
         <v>7500</v>
@@ -23453,7 +23453,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012873649597</v>
       </c>
       <c r="H796" t="n">
         <v>1500</v>
@@ -23482,7 +23482,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76012897491455</v>
+        <v>1.76012873649597</v>
       </c>
       <c r="H797" t="n">
         <v>2250</v>
@@ -23569,7 +23569,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G800" t="n">
-        <v>1.72738230228424</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H800" t="n">
         <v>21750</v>
@@ -23598,7 +23598,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556864261627</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H801" t="n">
         <v>12750</v>
@@ -23685,7 +23685,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H804" t="n">
         <v>9750</v>
@@ -23714,7 +23714,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H805" t="n">
         <v>45750</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919560432434</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H806" t="n">
         <v>3000</v>
@@ -23772,7 +23772,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G807" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H807" t="n">
         <v>2250</v>
@@ -23801,7 +23801,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H808" t="n">
         <v>750</v>
@@ -23830,7 +23830,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G810" t="n">
-        <v>1.67826235294342</v>
+        <v>1.67826223373413</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23917,7 +23917,7 @@
         <v>2.10999989509583</v>
       </c>
       <c r="G812" t="n">
-        <v>1.72738230228424</v>
+        <v>1.72738218307495</v>
       </c>
       <c r="H812" t="n">
         <v>3000</v>
@@ -23946,7 +23946,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650225162506</v>
       </c>
       <c r="H813" t="n">
         <v>5250</v>
@@ -24033,7 +24033,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842195510864</v>
+        <v>1.94842183589935</v>
       </c>
       <c r="H816" t="n">
         <v>13500</v>
@@ -24149,7 +24149,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H820" t="n">
         <v>11250</v>
@@ -24265,7 +24265,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660865306854</v>
       </c>
       <c r="H824" t="n">
         <v>65250</v>
@@ -24294,7 +24294,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660865306854</v>
       </c>
       <c r="H825" t="n">
         <v>78000</v>
@@ -24323,7 +24323,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>1.94023489952087</v>
+        <v>1.94023501873016</v>
       </c>
       <c r="H826" t="n">
         <v>27000</v>
@@ -24352,7 +24352,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G827" t="n">
-        <v>1.94023489952087</v>
+        <v>1.94023501873016</v>
       </c>
       <c r="H827" t="n">
         <v>60000</v>
@@ -24410,7 +24410,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660865306854</v>
       </c>
       <c r="H829" t="n">
         <v>36000</v>
@@ -24439,7 +24439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940769195557</v>
       </c>
       <c r="H830" t="n">
         <v>53250</v>
@@ -24468,7 +24468,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>2.09578108787537</v>
+        <v>2.09578132629395</v>
       </c>
       <c r="H831" t="n">
         <v>31500</v>
@@ -24497,7 +24497,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034106254578</v>
+        <v>2.12034130096436</v>
       </c>
       <c r="H832" t="n">
         <v>2250</v>
@@ -24555,7 +24555,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847503662109</v>
       </c>
       <c r="H834" t="n">
         <v>3000</v>
@@ -24613,7 +24613,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210164070129</v>
+        <v>2.02210116386414</v>
       </c>
       <c r="H836" t="n">
         <v>7500</v>
@@ -24642,7 +24642,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H837" t="n">
         <v>3750</v>
@@ -24671,7 +24671,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H838" t="n">
         <v>23250</v>
@@ -24700,7 +24700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210164070129</v>
+        <v>2.02210116386414</v>
       </c>
       <c r="H839" t="n">
         <v>27750</v>
@@ -24729,7 +24729,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G840" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H840" t="n">
         <v>3750</v>
@@ -24816,7 +24816,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>2.09578108787537</v>
+        <v>2.09578132629395</v>
       </c>
       <c r="H843" t="n">
         <v>2250</v>
@@ -24845,7 +24845,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>2.09578108787537</v>
+        <v>2.09578132629395</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940769195557</v>
       </c>
       <c r="H846" t="n">
         <v>175500</v>
@@ -24932,7 +24932,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>2.05484795570374</v>
+        <v>2.05484819412231</v>
       </c>
       <c r="H847" t="n">
         <v>41250</v>
@@ -24961,7 +24961,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.05484795570374</v>
+        <v>2.05484819412231</v>
       </c>
       <c r="H848" t="n">
         <v>2250</v>
@@ -24990,7 +24990,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G849" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847503662109</v>
       </c>
       <c r="H849" t="n">
         <v>8250</v>
@@ -25019,7 +25019,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G850" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H850" t="n">
         <v>15000</v>
@@ -25077,7 +25077,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25164,7 +25164,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>1.97298169136047</v>
+        <v>1.97298157215118</v>
       </c>
       <c r="H855" t="n">
         <v>7500</v>
@@ -25193,7 +25193,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H856" t="n">
         <v>2250</v>
@@ -25222,7 +25222,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660817623138</v>
+        <v>1.95660865306854</v>
       </c>
       <c r="H857" t="n">
         <v>9750</v>
@@ -25251,7 +25251,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G858" t="n">
-        <v>1.97298169136047</v>
+        <v>1.97298157215118</v>
       </c>
       <c r="H858" t="n">
         <v>750</v>
@@ -25280,7 +25280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935496807098</v>
+        <v>1.98935508728027</v>
       </c>
       <c r="H859" t="n">
         <v>53250</v>
@@ -25309,7 +25309,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03847479820251</v>
+        <v>2.03847503662109</v>
       </c>
       <c r="H860" t="n">
         <v>6750</v>
@@ -25338,7 +25338,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>2.0139148235321</v>
+        <v>2.01391458511353</v>
       </c>
       <c r="H861" t="n">
         <v>6000</v>
@@ -25367,7 +25367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204832077026</v>
+        <v>1.93204808235168</v>
       </c>
       <c r="H862" t="n">
         <v>27000</v>
@@ -25396,7 +25396,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479511260986</v>
+        <v>1.96479499340057</v>
       </c>
       <c r="H863" t="n">
         <v>4500</v>
@@ -25454,7 +25454,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930176734924</v>
       </c>
       <c r="H865" t="n">
         <v>6750</v>
@@ -25483,7 +25483,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930176734924</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H868" t="n">
         <v>11250</v>
@@ -25744,7 +25744,7 @@
         <v>2.5</v>
       </c>
       <c r="G875" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H875" t="n">
         <v>66750</v>
@@ -25773,7 +25773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>2.05484795570374</v>
+        <v>2.05484819412231</v>
       </c>
       <c r="H876" t="n">
         <v>54750</v>
@@ -25802,7 +25802,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G877" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H877" t="n">
         <v>15000</v>
@@ -25831,7 +25831,7 @@
         <v>2.5</v>
       </c>
       <c r="G878" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H878" t="n">
         <v>36000</v>
@@ -25860,7 +25860,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G879" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H879" t="n">
         <v>1500</v>
@@ -25889,7 +25889,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G880" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H880" t="n">
         <v>6750</v>
@@ -25947,7 +25947,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940769195557</v>
       </c>
       <c r="H882" t="n">
         <v>3000</v>
@@ -26034,7 +26034,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940769195557</v>
       </c>
       <c r="H885" t="n">
         <v>1500</v>
@@ -26063,7 +26063,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>2.07940816879272</v>
+        <v>2.07940769195557</v>
       </c>
       <c r="H886" t="n">
         <v>4500</v>
@@ -26092,7 +26092,7 @@
         <v>2.5</v>
       </c>
       <c r="G887" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H887" t="n">
         <v>4500</v>
@@ -26121,7 +26121,7 @@
         <v>2.5</v>
       </c>
       <c r="G888" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H888" t="n">
         <v>2250</v>
@@ -26150,7 +26150,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H889" t="n">
         <v>7500</v>
@@ -26179,7 +26179,7 @@
         <v>2.5</v>
       </c>
       <c r="G890" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H890" t="n">
         <v>46500</v>
@@ -26208,7 +26208,7 @@
         <v>2.5</v>
       </c>
       <c r="G891" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>2.5</v>
       </c>
       <c r="G892" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H892" t="n">
         <v>5250</v>
@@ -26266,7 +26266,7 @@
         <v>2.5</v>
       </c>
       <c r="G893" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26295,7 +26295,7 @@
         <v>2.5</v>
       </c>
       <c r="G894" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H894" t="n">
         <v>288750</v>
@@ -26324,7 +26324,7 @@
         <v>2.5</v>
       </c>
       <c r="G895" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H895" t="n">
         <v>3000</v>
@@ -26353,7 +26353,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G896" t="n">
-        <v>2.0302882194519</v>
+        <v>2.03028798103333</v>
       </c>
       <c r="H896" t="n">
         <v>4500</v>
@@ -26382,7 +26382,7 @@
         <v>2.5</v>
       </c>
       <c r="G897" t="n">
-        <v>2.04666137695312</v>
+        <v>2.0466616153717</v>
       </c>
       <c r="H897" t="n">
         <v>750</v>
@@ -26411,7 +26411,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116838932037</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H898" t="n">
         <v>10500</v>
@@ -26614,7 +26614,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26643,7 +26643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H906" t="n">
         <v>750</v>
@@ -26672,7 +26672,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H907" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91285216808319</v>
+        <v>1.9128520488739</v>
       </c>
       <c r="H908" t="n">
         <v>21000</v>
@@ -26817,7 +26817,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869393825531</v>
+        <v>1.87869381904602</v>
       </c>
       <c r="H912" t="n">
         <v>3000</v>
@@ -27078,7 +27078,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H921" t="n">
         <v>6750</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H925" t="n">
         <v>8250</v>
@@ -27252,7 +27252,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H927" t="n">
         <v>2250</v>
@@ -27310,7 +27310,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H929" t="n">
         <v>6750</v>
@@ -27426,7 +27426,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H933" t="n">
         <v>20250</v>
@@ -27455,7 +27455,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H934" t="n">
         <v>12000</v>
@@ -27571,7 +27571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H938" t="n">
         <v>14250</v>
@@ -27716,7 +27716,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H943" t="n">
         <v>2250</v>
@@ -27745,7 +27745,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H944" t="n">
         <v>750</v>
@@ -27774,7 +27774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H945" t="n">
         <v>1500</v>
@@ -27803,7 +27803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H948" t="n">
         <v>2250</v>
@@ -27890,7 +27890,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G949" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H949" t="n">
         <v>9000</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.91285216808319</v>
+        <v>1.9128520488739</v>
       </c>
       <c r="H951" t="n">
         <v>10500</v>
@@ -27977,7 +27977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H952" t="n">
         <v>9750</v>
@@ -28006,7 +28006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869393825531</v>
+        <v>1.87869381904602</v>
       </c>
       <c r="H953" t="n">
         <v>3000</v>
@@ -28209,7 +28209,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H960" t="n">
         <v>30750</v>
@@ -28238,7 +28238,7 @@
         <v>2</v>
       </c>
       <c r="G961" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H961" t="n">
         <v>28500</v>
@@ -28354,7 +28354,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H965" t="n">
         <v>3750</v>
@@ -28470,7 +28470,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H969" t="n">
         <v>3750</v>
@@ -28499,7 +28499,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.84453594684601</v>
+        <v>1.8445360660553</v>
       </c>
       <c r="H970" t="n">
         <v>2250</v>
@@ -28528,7 +28528,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H971" t="n">
         <v>2250</v>
@@ -28557,7 +28557,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28586,7 +28586,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -28760,7 +28760,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H979" t="n">
         <v>2250</v>
@@ -28847,7 +28847,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H982" t="n">
         <v>9000</v>
@@ -28876,7 +28876,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -28934,7 +28934,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H985" t="n">
         <v>4500</v>
@@ -28963,7 +28963,7 @@
         <v>2</v>
       </c>
       <c r="G986" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H986" t="n">
         <v>8250</v>
@@ -28992,7 +28992,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H987" t="n">
         <v>52500</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.58835029602051</v>
+        <v>1.5883504152298</v>
       </c>
       <c r="H989" t="n">
         <v>18000</v>
@@ -29108,7 +29108,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G991" t="n">
-        <v>1.40048098564148</v>
+        <v>1.40048086643219</v>
       </c>
       <c r="H991" t="n">
         <v>120750</v>
@@ -29369,7 +29369,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1000" t="n">
         <v>16500</v>
@@ -29746,7 +29746,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1013" t="n">
         <v>8250</v>
@@ -29949,7 +29949,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1020" t="n">
         <v>24750</v>
@@ -29978,7 +29978,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1021" t="n">
         <v>4500</v>
@@ -30297,7 +30297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1032" t="n">
         <v>4500</v>
@@ -30355,7 +30355,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.34070444107056</v>
+        <v>1.34070432186127</v>
       </c>
       <c r="H1034" t="n">
         <v>28500</v>
@@ -30442,7 +30442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.34070444107056</v>
+        <v>1.34070432186127</v>
       </c>
       <c r="H1037" t="n">
         <v>27000</v>
@@ -30471,7 +30471,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1038" t="n">
         <v>23250</v>
@@ -30500,7 +30500,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1039" t="n">
         <v>12000</v>
@@ -30529,7 +30529,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1040" t="n">
         <v>750</v>
@@ -30558,7 +30558,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1041" t="n">
         <v>6750</v>
@@ -30790,7 +30790,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1049" t="n">
         <v>9000</v>
@@ -30906,7 +30906,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1053" t="n">
         <v>3750</v>
@@ -30993,7 +30993,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1056" t="n">
         <v>18000</v>
@@ -31080,7 +31080,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1059" t="n">
         <v>99750</v>
@@ -31109,7 +31109,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1060" t="n">
         <v>4500</v>
@@ -31138,7 +31138,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1061" t="n">
         <v>5250</v>
@@ -31167,7 +31167,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.40048098564148</v>
+        <v>1.40048086643219</v>
       </c>
       <c r="H1064" t="n">
         <v>8250</v>
@@ -31631,7 +31631,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1078" t="n">
         <v>2250</v>
@@ -31660,7 +31660,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1079" t="n">
         <v>2250</v>
@@ -31689,7 +31689,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -31805,7 +31805,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1084" t="n">
         <v>19500</v>
@@ -31863,7 +31863,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1086" t="n">
         <v>3000</v>
@@ -31892,7 +31892,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1087" t="n">
         <v>6000</v>
@@ -31979,7 +31979,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1090" t="n">
         <v>15750</v>
@@ -32124,7 +32124,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.58835029602051</v>
+        <v>1.5883504152298</v>
       </c>
       <c r="H1095" t="n">
         <v>20250</v>
@@ -32153,7 +32153,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1096" t="n">
         <v>23250</v>
@@ -32182,7 +32182,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1097" t="n">
         <v>9750</v>
@@ -32211,7 +32211,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1098" t="n">
         <v>12750</v>
@@ -32356,7 +32356,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1103" t="n">
         <v>12000</v>
@@ -32472,7 +32472,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.51149475574493</v>
+        <v>1.51149463653564</v>
       </c>
       <c r="H1107" t="n">
         <v>6750</v>
@@ -32559,7 +32559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958728313446</v>
+        <v>1.63958740234375</v>
       </c>
       <c r="H1110" t="n">
         <v>45000</v>
@@ -32617,7 +32617,7 @@
         <v>2</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1112" t="n">
         <v>37500</v>
@@ -32646,7 +32646,7 @@
         <v>2</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1113" t="n">
         <v>2250</v>
@@ -32762,7 +32762,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H1117" t="n">
         <v>3000</v>
@@ -32791,7 +32791,7 @@
         <v>2</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1118" t="n">
         <v>32250</v>
@@ -32849,7 +32849,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H1120" t="n">
         <v>9750</v>
@@ -32878,7 +32878,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H1121" t="n">
         <v>3000</v>
@@ -32907,7 +32907,7 @@
         <v>2</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1122" t="n">
         <v>1500</v>
@@ -32936,7 +32936,7 @@
         <v>2</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1123" t="n">
         <v>750</v>
@@ -32965,7 +32965,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1124" t="n">
         <v>35250</v>
@@ -32994,7 +32994,7 @@
         <v>2</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1125" t="n">
         <v>27750</v>
@@ -33023,7 +33023,7 @@
         <v>2</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1126" t="n">
         <v>82500</v>
@@ -33052,7 +33052,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H1127" t="n">
         <v>1500</v>
@@ -33081,7 +33081,7 @@
         <v>2</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1128" t="n">
         <v>19500</v>
@@ -33110,7 +33110,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H1129" t="n">
         <v>3000</v>
@@ -33139,7 +33139,7 @@
         <v>2</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1130" t="n">
         <v>12750</v>
@@ -33255,7 +33255,7 @@
         <v>2</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1134" t="n">
         <v>2250</v>
@@ -33284,7 +33284,7 @@
         <v>2</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33313,7 +33313,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1136" t="n">
         <v>3750</v>
@@ -33342,7 +33342,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1137" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H1140" t="n">
         <v>8250</v>
@@ -33632,7 +33632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958728313446</v>
+        <v>1.63958740234375</v>
       </c>
       <c r="H1147" t="n">
         <v>9750</v>
@@ -33748,7 +33748,7 @@
         <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1151" t="n">
         <v>18000</v>
@@ -33777,7 +33777,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1152" t="n">
         <v>122250</v>
@@ -34705,7 +34705,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1184" t="n">
         <v>84000</v>
@@ -34792,7 +34792,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1187" t="n">
         <v>18000</v>
@@ -34879,7 +34879,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1190" t="n">
         <v>57000</v>
@@ -34908,7 +34908,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1191" t="n">
         <v>43500</v>
@@ -34937,7 +34937,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1192" t="n">
         <v>75750</v>
@@ -34966,7 +34966,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.06746244430542</v>
+        <v>2.06746220588684</v>
       </c>
       <c r="H1193" t="n">
         <v>28500</v>
@@ -34995,7 +34995,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.99555063247681</v>
+        <v>1.99555051326752</v>
       </c>
       <c r="H1194" t="n">
         <v>24000</v>
@@ -35024,7 +35024,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1195" t="n">
         <v>12000</v>
@@ -35053,7 +35053,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1196" t="n">
         <v>12000</v>
@@ -35082,7 +35082,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1197" t="n">
         <v>2250</v>
@@ -35111,7 +35111,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1198" t="n">
         <v>30000</v>
@@ -35140,7 +35140,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1199" t="n">
         <v>3750</v>
@@ -35169,7 +35169,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1200" t="n">
         <v>0</v>
@@ -35198,7 +35198,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1201" t="n">
         <v>750</v>
@@ -35227,7 +35227,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1202" t="n">
         <v>6000</v>
@@ -35256,7 +35256,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1203" t="n">
         <v>9000</v>
@@ -35314,7 +35314,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1205" t="n">
         <v>21000</v>
@@ -35343,7 +35343,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1206" t="n">
         <v>24750</v>
@@ -35372,7 +35372,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1207" t="n">
         <v>3750</v>
@@ -35401,7 +35401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1208" t="n">
         <v>3750</v>
@@ -35981,7 +35981,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1228" t="n">
         <v>12750</v>
@@ -36010,7 +36010,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1229" t="n">
         <v>9750</v>
@@ -36126,7 +36126,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1233" t="n">
         <v>1500</v>
@@ -36155,7 +36155,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1234" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1242" t="n">
         <v>27000</v>
@@ -36445,7 +36445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1244" t="n">
         <v>2250</v>
@@ -36561,7 +36561,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1248" t="n">
         <v>3000</v>
@@ -36764,7 +36764,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1255" t="n">
         <v>7500</v>
@@ -36793,7 +36793,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1256" t="n">
         <v>11250</v>
@@ -36851,7 +36851,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1258" t="n">
         <v>20250</v>
@@ -36938,7 +36938,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1261" t="n">
         <v>12750</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1263" t="n">
         <v>32250</v>
@@ -37402,7 +37402,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1277" t="n">
         <v>5250</v>
@@ -37431,7 +37431,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1278" t="n">
         <v>4500</v>
@@ -37518,7 +37518,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1281" t="n">
         <v>6000</v>
@@ -37576,7 +37576,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1283" t="n">
         <v>2250</v>
@@ -37605,7 +37605,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1284" t="n">
         <v>8250</v>
@@ -37779,7 +37779,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1290" t="n">
         <v>14250</v>
@@ -37837,7 +37837,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1292" t="n">
         <v>750</v>
@@ -37866,7 +37866,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1293" t="n">
         <v>750</v>
@@ -37895,7 +37895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1294" t="n">
         <v>0</v>
@@ -37953,7 +37953,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1296" t="n">
         <v>4500</v>
@@ -37982,7 +37982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1297" t="n">
         <v>3000</v>
@@ -38040,7 +38040,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1299" t="n">
         <v>7500</v>
@@ -38069,7 +38069,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1300" t="n">
         <v>3000</v>
@@ -38098,7 +38098,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1301" t="n">
         <v>6750</v>
@@ -38127,7 +38127,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1302" t="n">
         <v>6000</v>
@@ -38359,7 +38359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1310" t="n">
         <v>7500</v>
@@ -39229,7 +39229,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1340" t="n">
         <v>5250</v>
@@ -39258,7 +39258,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1341" t="n">
         <v>2250</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1342" t="n">
         <v>12000</v>
@@ -39316,7 +39316,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1343" t="n">
         <v>13500</v>
@@ -39345,7 +39345,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1344" t="n">
         <v>5250</v>
@@ -39403,7 +39403,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1346" t="n">
         <v>6000</v>
@@ -39432,7 +39432,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1347" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1367" t="n">
         <v>2250</v>
@@ -40041,7 +40041,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1368" t="n">
         <v>42750</v>
@@ -40070,7 +40070,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1369" t="n">
         <v>4500</v>
@@ -40099,7 +40099,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1370" t="n">
         <v>0</v>
@@ -40128,7 +40128,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1371" t="n">
         <v>1500</v>
@@ -40244,7 +40244,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1375" t="n">
         <v>750</v>
@@ -40273,7 +40273,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1376" t="n">
         <v>0</v>
@@ -40360,7 +40360,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1379" t="n">
         <v>5250</v>
@@ -40389,7 +40389,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.03150629997253</v>
+        <v>2.03150653839111</v>
       </c>
       <c r="H1380" t="n">
         <v>114750</v>
@@ -40418,7 +40418,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1381" t="n">
         <v>12750</v>
@@ -40447,7 +40447,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1382" t="n">
         <v>4500</v>
@@ -40476,7 +40476,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1383" t="n">
         <v>1500</v>
@@ -40505,7 +40505,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1384" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1386" t="n">
         <v>15000</v>
@@ -40592,7 +40592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1387" t="n">
         <v>3000</v>
@@ -40621,7 +40621,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1388" t="n">
         <v>2250</v>
@@ -40650,7 +40650,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1389" t="n">
         <v>1500</v>
@@ -40679,7 +40679,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1391" t="n">
         <v>1500</v>
@@ -40737,7 +40737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.03150629997253</v>
+        <v>2.03150653839111</v>
       </c>
       <c r="H1392" t="n">
         <v>60750</v>
@@ -40766,7 +40766,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.01352858543396</v>
+        <v>2.01352834701538</v>
       </c>
       <c r="H1393" t="n">
         <v>5250</v>
@@ -40795,7 +40795,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.01352858543396</v>
+        <v>2.01352834701538</v>
       </c>
       <c r="H1394" t="n">
         <v>13500</v>
@@ -40824,7 +40824,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1395" t="n">
         <v>11250</v>
@@ -40853,7 +40853,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1396" t="n">
         <v>21000</v>
@@ -40911,7 +40911,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1398" t="n">
         <v>15750</v>
@@ -40969,7 +40969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1400" t="n">
         <v>22500</v>
@@ -41027,7 +41027,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1402" t="n">
         <v>9000</v>
@@ -51937,6 +51937,35 @@
         <v>6000</v>
       </c>
       <c r="I1778" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1779">
+      <c r="A1779" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1779" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1779" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="D1779" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="E1779" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="F1779" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="G1779" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="H1779" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1779" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189401626587</v>
+        <v>2.73189449310303</v>
       </c>
       <c r="H2" t="n">
         <v>893250</v>
@@ -456,7 +456,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722803115845</v>
+        <v>2.86722779273987</v>
       </c>
       <c r="H3" t="n">
         <v>428250</v>
@@ -485,7 +485,7 @@
         <v>3.50550007820129</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80716872215271</v>
+        <v>2.80716848373413</v>
       </c>
       <c r="H4" t="n">
         <v>86250</v>
@@ -543,7 +543,7 @@
         <v>3.37899994850159</v>
       </c>
       <c r="G6" t="n">
-        <v>2.7058687210083</v>
+        <v>2.70586848258972</v>
       </c>
       <c r="H6" t="n">
         <v>35250</v>
@@ -601,7 +601,7 @@
         <v>3.38949990272522</v>
       </c>
       <c r="G8" t="n">
-        <v>2.71427655220032</v>
+        <v>2.7142767906189</v>
       </c>
       <c r="H8" t="n">
         <v>111000</v>
@@ -659,7 +659,7 @@
         <v>3.43650007247925</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75191426277161</v>
+        <v>2.75191402435303</v>
       </c>
       <c r="H10" t="n">
         <v>33750</v>
@@ -746,7 +746,7 @@
         <v>3.36450004577637</v>
       </c>
       <c r="G13" t="n">
-        <v>2.6942572593689</v>
+        <v>2.69425702095032</v>
       </c>
       <c r="H13" t="n">
         <v>14250</v>
@@ -804,7 +804,7 @@
         <v>3.37150001525879</v>
       </c>
       <c r="G15" t="n">
-        <v>2.69986271858215</v>
+        <v>2.69986295700073</v>
       </c>
       <c r="H15" t="n">
         <v>21750</v>
@@ -891,7 +891,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558530807495</v>
+        <v>3.63558506965637</v>
       </c>
       <c r="H18" t="n">
         <v>196500</v>
@@ -920,7 +920,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.9639093875885</v>
+        <v>3.96390867233276</v>
       </c>
       <c r="H19" t="n">
         <v>402000</v>
@@ -949,7 +949,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578300476074</v>
+        <v>3.83578324317932</v>
       </c>
       <c r="H20" t="n">
         <v>495750</v>
@@ -978,7 +978,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G21" t="n">
-        <v>3.60515570640564</v>
+        <v>3.60515546798706</v>
       </c>
       <c r="H21" t="n">
         <v>81000</v>
@@ -1065,7 +1065,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43698954582214</v>
+        <v>3.43698930740356</v>
       </c>
       <c r="H24" t="n">
         <v>24750</v>
@@ -1181,7 +1181,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329771995544</v>
+        <v>3.34329748153687</v>
       </c>
       <c r="H28" t="n">
         <v>18000</v>
@@ -1268,7 +1268,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048439025879</v>
+        <v>3.33048462867737</v>
       </c>
       <c r="H31" t="n">
         <v>6750</v>
@@ -1529,7 +1529,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H40" t="n">
         <v>3000</v>
@@ -1558,7 +1558,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H41" t="n">
         <v>9750</v>
@@ -1587,7 +1587,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1616,7 +1616,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G43" t="n">
-        <v>3.03499293327332</v>
+        <v>3.03499317169189</v>
       </c>
       <c r="H43" t="n">
         <v>3750</v>
@@ -1645,7 +1645,7 @@
         <v>3.78999996185303</v>
       </c>
       <c r="G44" t="n">
-        <v>3.03499293327332</v>
+        <v>3.03499317169189</v>
       </c>
       <c r="H44" t="n">
         <v>750</v>
@@ -1674,7 +1674,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694562911987</v>
+        <v>2.98694586753845</v>
       </c>
       <c r="H45" t="n">
         <v>13500</v>
@@ -1703,7 +1703,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694562911987</v>
+        <v>2.98694586753845</v>
       </c>
       <c r="H46" t="n">
         <v>3000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1819,7 +1819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H50" t="n">
         <v>4500</v>
@@ -1848,7 +1848,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H51" t="n">
         <v>750</v>
@@ -1906,7 +1906,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G53" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H53" t="n">
         <v>9000</v>
@@ -2080,7 +2080,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G59" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H59" t="n">
         <v>12000</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H65" t="n">
         <v>9750</v>
@@ -2341,7 +2341,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280347824097</v>
+        <v>2.84280371665955</v>
       </c>
       <c r="H68" t="n">
         <v>8250</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670910835266</v>
+        <v>2.74670886993408</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2486,7 +2486,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467709541321</v>
+        <v>2.71467757225037</v>
       </c>
       <c r="H73" t="n">
         <v>17250</v>
@@ -2515,7 +2515,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H74" t="n">
         <v>15000</v>
@@ -2544,7 +2544,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G75" t="n">
-        <v>2.83879947662354</v>
+        <v>2.83879971504211</v>
       </c>
       <c r="H75" t="n">
         <v>12750</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H76" t="n">
         <v>24000</v>
@@ -2718,7 +2718,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2747,7 +2747,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H82" t="n">
         <v>7500</v>
@@ -2863,7 +2863,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866132736206</v>
+        <v>2.69866156578064</v>
       </c>
       <c r="H86" t="n">
         <v>7500</v>
@@ -2921,7 +2921,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H88" t="n">
         <v>3750</v>
@@ -2950,7 +2950,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049612045288</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H90" t="n">
         <v>10500</v>
@@ -3008,7 +3008,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G91" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H91" t="n">
         <v>27750</v>
@@ -3037,7 +3037,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H92" t="n">
         <v>16500</v>
@@ -3066,7 +3066,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H93" t="n">
         <v>9750</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185572624207</v>
+        <v>1.88185596466064</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3153,7 +3153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H96" t="n">
         <v>14250</v>
@@ -3269,7 +3269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161896705627</v>
+        <v>1.64161884784698</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3327,7 +3327,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.677654504776</v>
+        <v>1.67765462398529</v>
       </c>
       <c r="H102" t="n">
         <v>11250</v>
@@ -3414,7 +3414,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173734664917</v>
       </c>
       <c r="H105" t="n">
         <v>6750</v>
@@ -3501,7 +3501,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.89787173271179</v>
+        <v>1.8978716135025</v>
       </c>
       <c r="H108" t="n">
         <v>15750</v>
@@ -3559,7 +3559,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049612045288</v>
       </c>
       <c r="H110" t="n">
         <v>16500</v>
@@ -3588,7 +3588,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H111" t="n">
         <v>28500</v>
@@ -3617,7 +3617,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>2.81878018379211</v>
+        <v>2.81877994537354</v>
       </c>
       <c r="H112" t="n">
         <v>15000</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H116" t="n">
         <v>6750</v>
@@ -3762,7 +3762,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H117" t="n">
         <v>3750</v>
@@ -3820,7 +3820,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H119" t="n">
         <v>8250</v>
@@ -3849,7 +3849,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664979934692</v>
+        <v>2.68664956092834</v>
       </c>
       <c r="H120" t="n">
         <v>11250</v>
@@ -3965,7 +3965,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467709541321</v>
+        <v>2.71467757225037</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -4023,7 +4023,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H126" t="n">
         <v>3750</v>
@@ -4052,7 +4052,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.7947564125061</v>
+        <v>2.79475617408752</v>
       </c>
       <c r="H127" t="n">
         <v>2250</v>
@@ -4081,7 +4081,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.78674817085266</v>
+        <v>2.78674840927124</v>
       </c>
       <c r="H128" t="n">
         <v>3000</v>
@@ -4110,7 +4110,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78674817085266</v>
+        <v>2.78674840927124</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4139,7 +4139,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H130" t="n">
         <v>3750</v>
@@ -4168,7 +4168,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H131" t="n">
         <v>750</v>
@@ -4226,7 +4226,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H133" t="n">
         <v>5250</v>
@@ -4255,7 +4255,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H134" t="n">
         <v>750</v>
@@ -4284,7 +4284,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H135" t="n">
         <v>750</v>
@@ -4313,7 +4313,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H137" t="n">
         <v>750</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856295585632</v>
+        <v>2.59856271743774</v>
       </c>
       <c r="H139" t="n">
         <v>1500</v>
@@ -4516,7 +4516,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4545,7 +4545,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H144" t="n">
         <v>1500</v>
@@ -4574,7 +4574,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H145" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4864,7 +4864,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H155" t="n">
         <v>8250</v>
@@ -4922,7 +4922,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>2.76272463798523</v>
+        <v>2.76272439956665</v>
       </c>
       <c r="H157" t="n">
         <v>11250</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H161" t="n">
         <v>14250</v>
@@ -5212,7 +5212,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G167" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H167" t="n">
         <v>15000</v>
@@ -5299,7 +5299,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H170" t="n">
         <v>18000</v>
@@ -5850,7 +5850,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G189" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H189" t="n">
         <v>3750</v>
@@ -5879,7 +5879,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G190" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H190" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.61858248710632</v>
+        <v>2.6185827255249</v>
       </c>
       <c r="H197" t="n">
         <v>139500</v>
@@ -6169,7 +6169,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.81878018379211</v>
+        <v>2.81877994537354</v>
       </c>
       <c r="H200" t="n">
         <v>47250</v>
@@ -6256,7 +6256,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264579772949</v>
+        <v>2.68264555931091</v>
       </c>
       <c r="H203" t="n">
         <v>9750</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256671905518</v>
+        <v>2.60256695747375</v>
       </c>
       <c r="H204" t="n">
         <v>12000</v>
@@ -6314,7 +6314,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451917648315</v>
+        <v>2.55451941490173</v>
       </c>
       <c r="H205" t="n">
         <v>13500</v>
@@ -6517,7 +6517,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H212" t="n">
         <v>2250</v>
@@ -6546,7 +6546,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H213" t="n">
         <v>10500</v>
@@ -6633,7 +6633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6662,7 +6662,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H217" t="n">
         <v>11250</v>
@@ -6691,7 +6691,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G218" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H218" t="n">
         <v>7500</v>
@@ -6749,7 +6749,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H220" t="n">
         <v>750</v>
@@ -6836,7 +6836,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651141166687</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H223" t="n">
         <v>5250</v>
@@ -6865,7 +6865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6894,7 +6894,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H225" t="n">
         <v>5250</v>
@@ -6981,7 +6981,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238903045654</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H228" t="n">
         <v>15750</v>
@@ -7010,7 +7010,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G229" t="n">
-        <v>2.35031771659851</v>
+        <v>2.35031795501709</v>
       </c>
       <c r="H229" t="n">
         <v>18750</v>
@@ -7039,7 +7039,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G230" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H230" t="n">
         <v>750</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H231" t="n">
         <v>3000</v>
@@ -7126,7 +7126,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G233" t="n">
-        <v>2.33029866218567</v>
+        <v>2.33029842376709</v>
       </c>
       <c r="H233" t="n">
         <v>3750</v>
@@ -7329,7 +7329,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G240" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H240" t="n">
         <v>3000</v>
@@ -7358,7 +7358,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G241" t="n">
-        <v>2.35832619667053</v>
+        <v>2.35832595825195</v>
       </c>
       <c r="H241" t="n">
         <v>0</v>
@@ -7445,7 +7445,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G244" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H244" t="n">
         <v>4500</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H257" t="n">
         <v>1500</v>
@@ -7851,7 +7851,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G258" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H258" t="n">
         <v>750</v>
@@ -7880,7 +7880,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G259" t="n">
-        <v>2.25021934509277</v>
+        <v>2.25021910667419</v>
       </c>
       <c r="H259" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H262" t="n">
         <v>2250</v>
@@ -8025,7 +8025,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.18615627288818</v>
+        <v>2.1861560344696</v>
       </c>
       <c r="H265" t="n">
         <v>1500</v>
@@ -8083,7 +8083,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H266" t="n">
         <v>2250</v>
@@ -8112,7 +8112,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820734024048</v>
+        <v>2.23820757865906</v>
       </c>
       <c r="H267" t="n">
         <v>2250</v>
@@ -8199,7 +8199,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H270" t="n">
         <v>750</v>
@@ -8228,7 +8228,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H271" t="n">
         <v>6000</v>
@@ -8257,7 +8257,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H272" t="n">
         <v>2250</v>
@@ -8286,7 +8286,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834548950195</v>
+        <v>2.37834596633911</v>
       </c>
       <c r="H274" t="n">
         <v>3750</v>
@@ -8373,7 +8373,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H276" t="n">
         <v>3000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037726402283</v>
+        <v>2.41037702560425</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H282" t="n">
         <v>3750</v>
@@ -8576,7 +8576,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8866,7 +8866,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H294" t="n">
         <v>750</v>
@@ -8924,7 +8924,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G295" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H295" t="n">
         <v>6000</v>
@@ -8982,7 +8982,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G297" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H297" t="n">
         <v>2250</v>
@@ -9011,7 +9011,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G298" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H298" t="n">
         <v>2250</v>
@@ -9098,7 +9098,7 @@
         <v>2.75</v>
       </c>
       <c r="G301" t="n">
-        <v>2.20217180252075</v>
+        <v>2.20217204093933</v>
       </c>
       <c r="H301" t="n">
         <v>9000</v>
@@ -9127,7 +9127,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H302" t="n">
         <v>3000</v>
@@ -9156,7 +9156,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9185,7 +9185,7 @@
         <v>3.41000008583069</v>
       </c>
       <c r="G304" t="n">
-        <v>2.73069357872009</v>
+        <v>2.73069334030151</v>
       </c>
       <c r="H304" t="n">
         <v>120750</v>
@@ -9214,7 +9214,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H305" t="n">
         <v>148500</v>
@@ -9272,7 +9272,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047587394714</v>
+        <v>2.51047611236572</v>
       </c>
       <c r="H307" t="n">
         <v>32250</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H308" t="n">
         <v>6750</v>
@@ -9417,7 +9417,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045610427856</v>
+        <v>2.49045634269714</v>
       </c>
       <c r="H312" t="n">
         <v>5250</v>
@@ -9533,7 +9533,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>2.36633372306824</v>
+        <v>2.36633348464966</v>
       </c>
       <c r="H316" t="n">
         <v>3750</v>
@@ -9620,7 +9620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H319" t="n">
         <v>3750</v>
@@ -9794,7 +9794,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H325" t="n">
         <v>13500</v>
@@ -9852,7 +9852,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G327" t="n">
-        <v>2.41438126564026</v>
+        <v>2.41438102722168</v>
       </c>
       <c r="H327" t="n">
         <v>2250</v>
@@ -9910,7 +9910,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H329" t="n">
         <v>2250</v>
@@ -9968,7 +9968,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G331" t="n">
-        <v>2.45842456817627</v>
+        <v>2.45842432975769</v>
       </c>
       <c r="H331" t="n">
         <v>7500</v>
@@ -10026,7 +10026,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H333" t="n">
         <v>9000</v>
@@ -10055,7 +10055,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238903045654</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H334" t="n">
         <v>2250</v>
@@ -10142,7 +10142,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.43840479850769</v>
+        <v>2.43840503692627</v>
       </c>
       <c r="H337" t="n">
         <v>3750</v>
@@ -10258,7 +10258,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238903045654</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H341" t="n">
         <v>20250</v>
@@ -10287,7 +10287,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H342" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H349" t="n">
         <v>3750</v>
@@ -10548,7 +10548,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G351" t="n">
-        <v>2.62659025192261</v>
+        <v>2.62659049034119</v>
       </c>
       <c r="H351" t="n">
         <v>3750</v>
@@ -10577,7 +10577,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451917648315</v>
+        <v>2.55451941490173</v>
       </c>
       <c r="H352" t="n">
         <v>4500</v>
@@ -10606,7 +10606,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.5304958820343</v>
+        <v>2.53049612045288</v>
       </c>
       <c r="H353" t="n">
         <v>750</v>
@@ -10635,7 +10635,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G354" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H354" t="n">
         <v>4500</v>
@@ -10664,7 +10664,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>2.6706337928772</v>
+        <v>2.67063403129578</v>
       </c>
       <c r="H355" t="n">
         <v>14250</v>
@@ -10693,7 +10693,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H356" t="n">
         <v>5250</v>
@@ -10751,7 +10751,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266556739807</v>
+        <v>2.70266532897949</v>
       </c>
       <c r="H358" t="n">
         <v>13500</v>
@@ -10780,7 +10780,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.61858248710632</v>
+        <v>2.6185827255249</v>
       </c>
       <c r="H359" t="n">
         <v>10500</v>
@@ -10809,7 +10809,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467709541321</v>
+        <v>2.71467757225037</v>
       </c>
       <c r="H360" t="n">
         <v>10500</v>
@@ -10896,7 +10896,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H363" t="n">
         <v>1500</v>
@@ -10925,7 +10925,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H364" t="n">
         <v>3000</v>
@@ -10954,7 +10954,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.65862202644348</v>
+        <v>2.6586217880249</v>
       </c>
       <c r="H365" t="n">
         <v>5250</v>
@@ -11012,7 +11012,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G367" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H367" t="n">
         <v>172500</v>
@@ -11099,7 +11099,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H370" t="n">
         <v>12750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11215,7 +11215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H374" t="n">
         <v>20250</v>
@@ -11273,7 +11273,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G376" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H376" t="n">
         <v>39000</v>
@@ -11302,7 +11302,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G377" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H377" t="n">
         <v>18000</v>
@@ -11360,7 +11360,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G379" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H379" t="n">
         <v>24000</v>
@@ -11389,7 +11389,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G380" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H380" t="n">
         <v>3000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11563,7 +11563,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G386" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H386" t="n">
         <v>3750</v>
@@ -11592,7 +11592,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G387" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H387" t="n">
         <v>3750</v>
@@ -11708,7 +11708,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G391" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11737,7 +11737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H392" t="n">
         <v>5250</v>
@@ -11911,7 +11911,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11940,7 +11940,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G399" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H399" t="n">
         <v>6000</v>
@@ -12085,7 +12085,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917510032654</v>
       </c>
       <c r="H404" t="n">
         <v>21000</v>
@@ -12143,7 +12143,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H406" t="n">
         <v>72750</v>
@@ -12172,7 +12172,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H407" t="n">
         <v>13500</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917510032654</v>
       </c>
       <c r="H409" t="n">
         <v>12750</v>
@@ -12288,7 +12288,7 @@
         <v>4</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H411" t="n">
         <v>8250</v>
@@ -12317,7 +12317,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917510032654</v>
       </c>
       <c r="H412" t="n">
         <v>3000</v>
@@ -12346,7 +12346,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>3.21917486190796</v>
+        <v>3.21917510032654</v>
       </c>
       <c r="H413" t="n">
         <v>5250</v>
@@ -12375,7 +12375,7 @@
         <v>4</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H414" t="n">
         <v>4500</v>
@@ -12404,7 +12404,7 @@
         <v>3.92000007629395</v>
       </c>
       <c r="G415" t="n">
-        <v>3.1390962600708</v>
+        <v>3.13909602165222</v>
       </c>
       <c r="H415" t="n">
         <v>2250</v>
@@ -12462,7 +12462,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G417" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H417" t="n">
         <v>3750</v>
@@ -12549,7 +12549,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G420" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H420" t="n">
         <v>2250</v>
@@ -12578,7 +12578,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G421" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H421" t="n">
         <v>3000</v>
@@ -12607,7 +12607,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G422" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H422" t="n">
         <v>0</v>
@@ -12665,7 +12665,7 @@
         <v>4</v>
       </c>
       <c r="G424" t="n">
-        <v>3.20315909385681</v>
+        <v>3.20315933227539</v>
       </c>
       <c r="H424" t="n">
         <v>6000</v>
@@ -12723,7 +12723,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G426" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H426" t="n">
         <v>5250</v>
@@ -12752,7 +12752,7 @@
         <v>3.90000009536743</v>
       </c>
       <c r="G427" t="n">
-        <v>3.1230800151825</v>
+        <v>3.12308025360107</v>
       </c>
       <c r="H427" t="n">
         <v>0</v>
@@ -12839,7 +12839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H430" t="n">
         <v>7500</v>
@@ -12868,7 +12868,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H431" t="n">
         <v>9000</v>
@@ -12926,7 +12926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H433" t="n">
         <v>1500</v>
@@ -12955,7 +12955,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G434" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H434" t="n">
         <v>750</v>
@@ -12984,7 +12984,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G435" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H435" t="n">
         <v>0</v>
@@ -13013,7 +13013,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901670455933</v>
       </c>
       <c r="H436" t="n">
         <v>4500</v>
@@ -13042,7 +13042,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G437" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H437" t="n">
         <v>750</v>
@@ -13187,7 +13187,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G442" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H442" t="n">
         <v>750</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13274,7 +13274,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13477,7 +13477,7 @@
         <v>3.79999995231628</v>
       </c>
       <c r="G452" t="n">
-        <v>3.04300093650818</v>
+        <v>3.04300117492676</v>
       </c>
       <c r="H452" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H453" t="n">
         <v>1500</v>
@@ -13564,7 +13564,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H455" t="n">
         <v>2250</v>
@@ -13593,7 +13593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G456" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H456" t="n">
         <v>3750</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H458" t="n">
         <v>3750</v>
@@ -13796,7 +13796,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H463" t="n">
         <v>3000</v>
@@ -13825,7 +13825,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H464" t="n">
         <v>4500</v>
@@ -13854,7 +13854,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13912,7 +13912,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H467" t="n">
         <v>750</v>
@@ -13941,7 +13941,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G468" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H469" t="n">
         <v>1500</v>
@@ -13999,7 +13999,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H470" t="n">
         <v>2250</v>
@@ -14028,7 +14028,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H471" t="n">
         <v>6750</v>
@@ -14057,7 +14057,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H472" t="n">
         <v>750</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14202,7 +14202,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H477" t="n">
         <v>6000</v>
@@ -14260,7 +14260,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H479" t="n">
         <v>6000</v>
@@ -14347,7 +14347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H482" t="n">
         <v>750</v>
@@ -14376,7 +14376,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H483" t="n">
         <v>1500</v>
@@ -14434,7 +14434,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H485" t="n">
         <v>750</v>
@@ -14463,7 +14463,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292233467102</v>
+        <v>2.96292209625244</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14579,7 +14579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G490" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H490" t="n">
         <v>750</v>
@@ -14608,7 +14608,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97893786430359</v>
+        <v>2.97893810272217</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14666,7 +14666,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G493" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H493" t="n">
         <v>1500</v>
@@ -14695,7 +14695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H494" t="n">
         <v>2250</v>
@@ -14724,7 +14724,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G495" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H495" t="n">
         <v>1500</v>
@@ -14811,7 +14811,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G498" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H498" t="n">
         <v>3750</v>
@@ -14840,7 +14840,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G499" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H503" t="n">
         <v>5250</v>
@@ -14985,7 +14985,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H504" t="n">
         <v>750</v>
@@ -15014,7 +15014,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G505" t="n">
-        <v>2.914874792099</v>
+        <v>2.91487503051758</v>
       </c>
       <c r="H505" t="n">
         <v>1500</v>
@@ -15043,7 +15043,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H506" t="n">
         <v>8250</v>
@@ -15072,7 +15072,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H508" t="n">
         <v>4500</v>
@@ -15275,7 +15275,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.89885878562927</v>
+        <v>2.89885902404785</v>
       </c>
       <c r="H514" t="n">
         <v>5250</v>
@@ -15304,7 +15304,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682724952698</v>
+        <v>2.86682748794556</v>
       </c>
       <c r="H515" t="n">
         <v>6750</v>
@@ -15391,7 +15391,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H518" t="n">
         <v>12750</v>
@@ -15420,7 +15420,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H519" t="n">
         <v>3750</v>
@@ -15449,7 +15449,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471687316895</v>
+        <v>2.75471711158752</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268533706665</v>
+        <v>2.72268509864807</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15623,7 +15623,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H526" t="n">
         <v>17250</v>
@@ -15652,7 +15652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.57854294776917</v>
+        <v>2.57854318618774</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15681,7 +15681,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846410751343</v>
+        <v>2.49846386909485</v>
       </c>
       <c r="H528" t="n">
         <v>5250</v>
@@ -15739,7 +15739,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>2.43440079689026</v>
+        <v>2.43440103530884</v>
       </c>
       <c r="H530" t="n">
         <v>5250</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15826,7 +15826,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H533" t="n">
         <v>15000</v>
@@ -15855,7 +15855,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G534" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H534" t="n">
         <v>8250</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16145,7 +16145,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H544" t="n">
         <v>750</v>
@@ -16174,7 +16174,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G545" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H545" t="n">
         <v>7500</v>
@@ -16203,7 +16203,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H546" t="n">
         <v>8250</v>
@@ -16232,7 +16232,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H547" t="n">
         <v>6750</v>
@@ -16290,7 +16290,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G549" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H549" t="n">
         <v>5250</v>
@@ -16319,7 +16319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16348,7 +16348,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G551" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H551" t="n">
         <v>102750</v>
@@ -16377,7 +16377,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G552" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H552" t="n">
         <v>3750</v>
@@ -16435,7 +16435,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H555" t="n">
         <v>6000</v>
@@ -16493,7 +16493,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830618858337</v>
+        <v>2.33830595016479</v>
       </c>
       <c r="H556" t="n">
         <v>3750</v>
@@ -16522,7 +16522,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G557" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H557" t="n">
         <v>5250</v>
@@ -16551,7 +16551,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G558" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H558" t="n">
         <v>6000</v>
@@ -16580,7 +16580,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G559" t="n">
-        <v>2.3062744140625</v>
+        <v>2.30627465248108</v>
       </c>
       <c r="H559" t="n">
         <v>750</v>
@@ -16609,7 +16609,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H560" t="n">
         <v>1500</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H568" t="n">
         <v>6750</v>
@@ -16870,7 +16870,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H570" t="n">
         <v>750</v>
@@ -16928,7 +16928,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H571" t="n">
         <v>7500</v>
@@ -16957,7 +16957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H572" t="n">
         <v>3000</v>
@@ -16986,7 +16986,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H573" t="n">
         <v>6750</v>
@@ -17015,7 +17015,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822710990906</v>
+        <v>2.25822687149048</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424311637878</v>
+        <v>2.27424263954163</v>
       </c>
       <c r="H576" t="n">
         <v>3000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H577" t="n">
         <v>12750</v>
@@ -17131,7 +17131,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221110343933</v>
       </c>
       <c r="H579" t="n">
         <v>6000</v>
@@ -17189,7 +17189,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21017980575562</v>
+        <v>2.21018004417419</v>
       </c>
       <c r="H580" t="n">
         <v>3750</v>
@@ -17334,7 +17334,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G585" t="n">
-        <v>2.11408495903015</v>
+        <v>2.11408519744873</v>
       </c>
       <c r="H585" t="n">
         <v>6000</v>
@@ -17363,7 +17363,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G586" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400588035583</v>
       </c>
       <c r="H586" t="n">
         <v>6000</v>
@@ -17392,7 +17392,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G587" t="n">
-        <v>2.11408495903015</v>
+        <v>2.11408519744873</v>
       </c>
       <c r="H587" t="n">
         <v>3000</v>
@@ -17421,7 +17421,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.17814826965332</v>
+        <v>2.1781485080719</v>
       </c>
       <c r="H588" t="n">
         <v>8250</v>
@@ -17479,7 +17479,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G590" t="n">
-        <v>2.11408495903015</v>
+        <v>2.11408519744873</v>
       </c>
       <c r="H590" t="n">
         <v>10500</v>
@@ -17508,7 +17508,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.05002188682556</v>
+        <v>2.05002164840698</v>
       </c>
       <c r="H591" t="n">
         <v>11250</v>
@@ -17537,7 +17537,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G592" t="n">
-        <v>2.03400564193726</v>
+        <v>2.03400588035583</v>
       </c>
       <c r="H592" t="n">
         <v>6000</v>
@@ -17624,7 +17624,7 @@
         <v>2.5</v>
       </c>
       <c r="G595" t="n">
-        <v>2.00197458267212</v>
+        <v>2.00197434425354</v>
       </c>
       <c r="H595" t="n">
         <v>4500</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986361026764</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17769,7 +17769,7 @@
         <v>2</v>
       </c>
       <c r="G600" t="n">
-        <v>1.60157954692841</v>
+        <v>1.6015796661377</v>
       </c>
       <c r="H600" t="n">
         <v>21750</v>
@@ -17856,7 +17856,7 @@
         <v>2</v>
       </c>
       <c r="G603" t="n">
-        <v>1.60157954692841</v>
+        <v>1.6015796661377</v>
       </c>
       <c r="H603" t="n">
         <v>9000</v>
@@ -17943,7 +17943,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G606" t="n">
-        <v>1.69767439365387</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H606" t="n">
         <v>14250</v>
@@ -17972,7 +17972,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G607" t="n">
-        <v>1.69767439365387</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H607" t="n">
         <v>3000</v>
@@ -18001,7 +18001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H608" t="n">
         <v>11250</v>
@@ -18059,7 +18059,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H610" t="n">
         <v>5250</v>
@@ -18146,7 +18146,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173734664917</v>
       </c>
       <c r="H613" t="n">
         <v>4500</v>
@@ -18175,7 +18175,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G614" t="n">
-        <v>1.69767439365387</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H614" t="n">
         <v>4500</v>
@@ -18204,7 +18204,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G615" t="n">
-        <v>1.69767439365387</v>
+        <v>1.69767427444458</v>
       </c>
       <c r="H615" t="n">
         <v>5250</v>
@@ -18262,7 +18262,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173734664917</v>
       </c>
       <c r="H617" t="n">
         <v>5250</v>
@@ -18291,7 +18291,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376900196075</v>
+        <v>1.79376912117004</v>
       </c>
       <c r="H618" t="n">
         <v>10500</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986361026764</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18378,7 +18378,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.95392715930939</v>
+        <v>1.9539270401001</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.80978488922119</v>
+        <v>1.80978500843048</v>
       </c>
       <c r="H622" t="n">
         <v>48750</v>
@@ -18436,7 +18436,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962685108185</v>
+        <v>1.64962673187256</v>
       </c>
       <c r="H623" t="n">
         <v>186750</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568227767944</v>
+        <v>1.70568215847015</v>
       </c>
       <c r="H625" t="n">
         <v>23250</v>
@@ -18523,7 +18523,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.7216979265213</v>
+        <v>1.72169804573059</v>
       </c>
       <c r="H626" t="n">
         <v>40500</v>
@@ -18552,7 +18552,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970604896545</v>
+        <v>1.72970592975616</v>
       </c>
       <c r="H627" t="n">
         <v>3750</v>
@@ -18581,7 +18581,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970604896545</v>
+        <v>1.72970592975616</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
@@ -18610,7 +18610,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376900196075</v>
+        <v>1.79376912117004</v>
       </c>
       <c r="H629" t="n">
         <v>18750</v>
@@ -18639,7 +18639,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173746585846</v>
+        <v>1.76173734664917</v>
       </c>
       <c r="H630" t="n">
         <v>14250</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.7216979265213</v>
+        <v>1.72169804573059</v>
       </c>
       <c r="H631" t="n">
         <v>5250</v>
@@ -18871,7 +18871,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165838718414</v>
+        <v>1.68165850639343</v>
       </c>
       <c r="H638" t="n">
         <v>18000</v>
@@ -18900,7 +18900,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568227767944</v>
+        <v>1.70568215847015</v>
       </c>
       <c r="H639" t="n">
         <v>15750</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779253482819</v>
       </c>
       <c r="H640" t="n">
         <v>17250</v>
@@ -18958,7 +18958,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779253482819</v>
       </c>
       <c r="H641" t="n">
         <v>167250</v>
@@ -19016,7 +19016,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H643" t="n">
         <v>15000</v>
@@ -19103,7 +19103,7 @@
         <v>2.25</v>
       </c>
       <c r="G646" t="n">
-        <v>1.8419953584671</v>
+        <v>1.84199523925781</v>
       </c>
       <c r="H646" t="n">
         <v>12750</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111518859863</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H648" t="n">
         <v>47250</v>
@@ -19190,7 +19190,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.85018193721771</v>
+        <v>1.850182056427</v>
       </c>
       <c r="H649" t="n">
         <v>5250</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H651" t="n">
         <v>33750</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H654" t="n">
         <v>9750</v>
@@ -19480,7 +19480,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H659" t="n">
         <v>7500</v>
@@ -19538,7 +19538,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G661" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H661" t="n">
         <v>1500</v>
@@ -19567,7 +19567,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H662" t="n">
         <v>7500</v>
@@ -19596,7 +19596,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.83380854129791</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H663" t="n">
         <v>21750</v>
@@ -19654,7 +19654,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.83380854129791</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H665" t="n">
         <v>15750</v>
@@ -19683,7 +19683,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.8256219625473</v>
+        <v>1.82562184333801</v>
       </c>
       <c r="H666" t="n">
         <v>4500</v>
@@ -19770,7 +19770,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G669" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H669" t="n">
         <v>6750</v>
@@ -19828,7 +19828,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G671" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H671" t="n">
         <v>3750</v>
@@ -19857,7 +19857,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G672" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H672" t="n">
         <v>2250</v>
@@ -19886,7 +19886,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G673" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H673" t="n">
         <v>3000</v>
@@ -19944,7 +19944,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G675" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H675" t="n">
         <v>3750</v>
@@ -20089,7 +20089,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H680" t="n">
         <v>750</v>
@@ -20147,7 +20147,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H682" t="n">
         <v>1500</v>
@@ -20176,7 +20176,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G683" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H683" t="n">
         <v>8250</v>
@@ -20205,7 +20205,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G684" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H684" t="n">
         <v>6000</v>
@@ -20234,7 +20234,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G685" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H685" t="n">
         <v>4500</v>
@@ -20321,7 +20321,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76012873649597</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H688" t="n">
         <v>19500</v>
@@ -20350,7 +20350,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H689" t="n">
         <v>6750</v>
@@ -20437,7 +20437,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G692" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H692" t="n">
         <v>6000</v>
@@ -20466,7 +20466,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G693" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H693" t="n">
         <v>0</v>
@@ -20495,7 +20495,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G694" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H694" t="n">
         <v>0</v>
@@ -20524,7 +20524,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H695" t="n">
         <v>750</v>
@@ -20553,7 +20553,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G696" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H696" t="n">
         <v>1500</v>
@@ -20872,7 +20872,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H707" t="n">
         <v>2250</v>
@@ -20901,7 +20901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H710" t="n">
         <v>15000</v>
@@ -20988,7 +20988,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -21162,7 +21162,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H717" t="n">
         <v>7500</v>
@@ -21191,7 +21191,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H718" t="n">
         <v>2250</v>
@@ -21220,7 +21220,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.76012873649597</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H720" t="n">
         <v>3000</v>
@@ -21278,7 +21278,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>1.76012873649597</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21452,7 +21452,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G727" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H727" t="n">
         <v>3750</v>
@@ -21481,7 +21481,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G728" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H728" t="n">
         <v>0</v>
@@ -21568,7 +21568,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H731" t="n">
         <v>3000</v>
@@ -21597,7 +21597,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G732" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H732" t="n">
         <v>2250</v>
@@ -21626,7 +21626,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G733" t="n">
-        <v>1.66188895702362</v>
+        <v>1.66188907623291</v>
       </c>
       <c r="H733" t="n">
         <v>0</v>
@@ -21655,7 +21655,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H734" t="n">
         <v>750</v>
@@ -21684,7 +21684,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095582485199</v>
+        <v>1.62095594406128</v>
       </c>
       <c r="H737" t="n">
         <v>2250</v>
@@ -21858,7 +21858,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H741" t="n">
         <v>2250</v>
@@ -21887,7 +21887,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H742" t="n">
         <v>7500</v>
@@ -21916,7 +21916,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -22090,7 +22090,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G749" t="n">
-        <v>1.56364941596985</v>
+        <v>1.56364929676056</v>
       </c>
       <c r="H749" t="n">
         <v>6750</v>
@@ -22119,7 +22119,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H751" t="n">
         <v>4500</v>
@@ -22177,7 +22177,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.50224947929382</v>
+        <v>1.50224959850311</v>
       </c>
       <c r="H752" t="n">
         <v>10500</v>
@@ -22293,7 +22293,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G756" t="n">
-        <v>1.48996949195862</v>
+        <v>1.48996961116791</v>
       </c>
       <c r="H756" t="n">
         <v>16500</v>
@@ -22438,7 +22438,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H761" t="n">
         <v>6000</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H763" t="n">
         <v>3750</v>
@@ -22525,7 +22525,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -22612,7 +22612,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G768" t="n">
-        <v>1.56364941596985</v>
+        <v>1.56364929676056</v>
       </c>
       <c r="H768" t="n">
         <v>1500</v>
@@ -22844,7 +22844,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H775" t="n">
         <v>4500</v>
@@ -22902,7 +22902,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H777" t="n">
         <v>16500</v>
@@ -22931,7 +22931,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.6373291015625</v>
+        <v>1.63732922077179</v>
       </c>
       <c r="H778" t="n">
         <v>3000</v>
@@ -22989,7 +22989,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.8256219625473</v>
+        <v>1.82562184333801</v>
       </c>
       <c r="H780" t="n">
         <v>60000</v>
@@ -23018,7 +23018,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H781" t="n">
         <v>11250</v>
@@ -23047,7 +23047,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>1.76012873649597</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H782" t="n">
         <v>7500</v>
@@ -23076,7 +23076,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>1.76012873649597</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H784" t="n">
         <v>2250</v>
@@ -23134,7 +23134,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G785" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H785" t="n">
         <v>750</v>
@@ -23163,7 +23163,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G786" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H786" t="n">
         <v>2250</v>
@@ -23192,7 +23192,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G787" t="n">
-        <v>1.70282232761383</v>
+        <v>1.70282220840454</v>
       </c>
       <c r="H787" t="n">
         <v>16500</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.80924868583679</v>
+        <v>1.8092485666275</v>
       </c>
       <c r="H793" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G794" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H794" t="n">
         <v>750</v>
@@ -23424,7 +23424,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G795" t="n">
-        <v>1.78468883037567</v>
+        <v>1.78468894958496</v>
       </c>
       <c r="H795" t="n">
         <v>750</v>
@@ -23453,7 +23453,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>1.76012873649597</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H796" t="n">
         <v>1500</v>
@@ -23482,7 +23482,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76012873649597</v>
+        <v>1.76012885570526</v>
       </c>
       <c r="H797" t="n">
         <v>2250</v>
@@ -23540,7 +23540,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H799" t="n">
         <v>3750</v>
@@ -23598,7 +23598,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H801" t="n">
         <v>12750</v>
@@ -23627,7 +23627,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G802" t="n">
-        <v>1.74375557899475</v>
+        <v>1.74375545978546</v>
       </c>
       <c r="H802" t="n">
         <v>3000</v>
@@ -23656,7 +23656,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644893169403</v>
+        <v>1.68644881248474</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -24149,7 +24149,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111518859863</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H820" t="n">
         <v>11250</v>
@@ -24265,7 +24265,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660865306854</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H824" t="n">
         <v>65250</v>
@@ -24294,7 +24294,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660865306854</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H825" t="n">
         <v>78000</v>
@@ -24323,7 +24323,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H826" t="n">
         <v>27000</v>
@@ -24352,7 +24352,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G827" t="n">
-        <v>1.94023501873016</v>
+        <v>1.94023489952087</v>
       </c>
       <c r="H827" t="n">
         <v>60000</v>
@@ -24410,7 +24410,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660865306854</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H829" t="n">
         <v>36000</v>
@@ -24439,7 +24439,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G830" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H830" t="n">
         <v>53250</v>
@@ -24468,7 +24468,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H831" t="n">
         <v>31500</v>
@@ -24497,7 +24497,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034130096436</v>
+        <v>2.12034106254578</v>
       </c>
       <c r="H832" t="n">
         <v>2250</v>
@@ -24555,7 +24555,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G834" t="n">
-        <v>2.03847503662109</v>
+        <v>2.03847479820251</v>
       </c>
       <c r="H834" t="n">
         <v>3000</v>
@@ -24613,7 +24613,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210116386414</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H836" t="n">
         <v>7500</v>
@@ -24642,7 +24642,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H837" t="n">
         <v>3750</v>
@@ -24671,7 +24671,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H838" t="n">
         <v>23250</v>
@@ -24700,7 +24700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210116386414</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H839" t="n">
         <v>27750</v>
@@ -24758,7 +24758,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H841" t="n">
         <v>33000</v>
@@ -24787,7 +24787,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H842" t="n">
         <v>26250</v>
@@ -24816,7 +24816,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H843" t="n">
         <v>2250</v>
@@ -24845,7 +24845,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>2.09578132629395</v>
+        <v>2.09578108787537</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -24903,7 +24903,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G846" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H846" t="n">
         <v>175500</v>
@@ -24990,7 +24990,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G849" t="n">
-        <v>2.03847503662109</v>
+        <v>2.03847479820251</v>
       </c>
       <c r="H849" t="n">
         <v>8250</v>
@@ -25048,7 +25048,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>2.08759450912476</v>
+        <v>2.08759474754333</v>
       </c>
       <c r="H851" t="n">
         <v>7500</v>
@@ -25077,7 +25077,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215448379517</v>
+        <v>2.11215472221375</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25164,7 +25164,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H855" t="n">
         <v>7500</v>
@@ -25193,7 +25193,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H856" t="n">
         <v>2250</v>
@@ -25222,7 +25222,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660865306854</v>
+        <v>1.95660841464996</v>
       </c>
       <c r="H857" t="n">
         <v>9750</v>
@@ -25251,7 +25251,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G858" t="n">
-        <v>1.97298157215118</v>
+        <v>1.97298169136047</v>
       </c>
       <c r="H858" t="n">
         <v>750</v>
@@ -25280,7 +25280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935508728027</v>
+        <v>1.98935496807098</v>
       </c>
       <c r="H859" t="n">
         <v>53250</v>
@@ -25309,7 +25309,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G860" t="n">
-        <v>2.03847503662109</v>
+        <v>2.03847479820251</v>
       </c>
       <c r="H860" t="n">
         <v>6750</v>
@@ -25338,7 +25338,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G861" t="n">
-        <v>2.01391458511353</v>
+        <v>2.0139148235321</v>
       </c>
       <c r="H861" t="n">
         <v>6000</v>
@@ -25367,7 +25367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204808235168</v>
+        <v>1.93204832077026</v>
       </c>
       <c r="H862" t="n">
         <v>27000</v>
@@ -25396,7 +25396,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479499340057</v>
+        <v>1.96479487419128</v>
       </c>
       <c r="H863" t="n">
         <v>4500</v>
@@ -25454,7 +25454,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930176734924</v>
+        <v>1.89930188655853</v>
       </c>
       <c r="H865" t="n">
         <v>6750</v>
@@ -25483,7 +25483,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930176734924</v>
+        <v>1.89930188655853</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111518859863</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H868" t="n">
         <v>11250</v>
@@ -25628,7 +25628,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.83380854129791</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H871" t="n">
         <v>3750</v>
@@ -25744,7 +25744,7 @@
         <v>2.5</v>
       </c>
       <c r="G875" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H875" t="n">
         <v>66750</v>
@@ -25831,7 +25831,7 @@
         <v>2.5</v>
       </c>
       <c r="G878" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H878" t="n">
         <v>36000</v>
@@ -25947,7 +25947,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G882" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H882" t="n">
         <v>3000</v>
@@ -26034,7 +26034,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G885" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H885" t="n">
         <v>1500</v>
@@ -26063,7 +26063,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G886" t="n">
-        <v>2.07940769195557</v>
+        <v>2.07940793037415</v>
       </c>
       <c r="H886" t="n">
         <v>4500</v>
@@ -26092,7 +26092,7 @@
         <v>2.5</v>
       </c>
       <c r="G887" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H887" t="n">
         <v>4500</v>
@@ -26121,7 +26121,7 @@
         <v>2.5</v>
       </c>
       <c r="G888" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H888" t="n">
         <v>2250</v>
@@ -26150,7 +26150,7 @@
         <v>2.5</v>
       </c>
       <c r="G889" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H889" t="n">
         <v>7500</v>
@@ -26179,7 +26179,7 @@
         <v>2.5</v>
       </c>
       <c r="G890" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H890" t="n">
         <v>46500</v>
@@ -26208,7 +26208,7 @@
         <v>2.5</v>
       </c>
       <c r="G891" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H891" t="n">
         <v>0</v>
@@ -26237,7 +26237,7 @@
         <v>2.5</v>
       </c>
       <c r="G892" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H892" t="n">
         <v>5250</v>
@@ -26266,7 +26266,7 @@
         <v>2.5</v>
       </c>
       <c r="G893" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H893" t="n">
         <v>0</v>
@@ -26295,7 +26295,7 @@
         <v>2.5</v>
       </c>
       <c r="G894" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H894" t="n">
         <v>288750</v>
@@ -26324,7 +26324,7 @@
         <v>2.5</v>
       </c>
       <c r="G895" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H895" t="n">
         <v>3000</v>
@@ -26382,7 +26382,7 @@
         <v>2.5</v>
       </c>
       <c r="G897" t="n">
-        <v>2.0466616153717</v>
+        <v>2.04666137695312</v>
       </c>
       <c r="H897" t="n">
         <v>750</v>
@@ -26411,7 +26411,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H898" t="n">
         <v>10500</v>
@@ -26614,7 +26614,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26643,7 +26643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H906" t="n">
         <v>750</v>
@@ -26672,7 +26672,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H907" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H908" t="n">
         <v>21000</v>
@@ -26817,7 +26817,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H912" t="n">
         <v>3000</v>
@@ -27078,7 +27078,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H921" t="n">
         <v>6750</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H925" t="n">
         <v>8250</v>
@@ -27252,7 +27252,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H927" t="n">
         <v>2250</v>
@@ -27310,7 +27310,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H929" t="n">
         <v>6750</v>
@@ -27426,7 +27426,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H933" t="n">
         <v>20250</v>
@@ -27455,7 +27455,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H934" t="n">
         <v>12000</v>
@@ -27571,7 +27571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H938" t="n">
         <v>14250</v>
@@ -27716,7 +27716,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H943" t="n">
         <v>2250</v>
@@ -27745,7 +27745,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H944" t="n">
         <v>750</v>
@@ -27774,7 +27774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H945" t="n">
         <v>1500</v>
@@ -27803,7 +27803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408903598785</v>
       </c>
       <c r="H948" t="n">
         <v>2250</v>
@@ -27890,7 +27890,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G949" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H949" t="n">
         <v>9000</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H951" t="n">
         <v>10500</v>
@@ -27977,7 +27977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993128299713</v>
       </c>
       <c r="H952" t="n">
         <v>9750</v>
@@ -28006,7 +28006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H953" t="n">
         <v>3000</v>
@@ -28209,7 +28209,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H960" t="n">
         <v>30750</v>
@@ -28238,7 +28238,7 @@
         <v>2</v>
       </c>
       <c r="G961" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H961" t="n">
         <v>28500</v>
@@ -28354,7 +28354,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H965" t="n">
         <v>3750</v>
@@ -28470,7 +28470,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H969" t="n">
         <v>3750</v>
@@ -28499,7 +28499,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.8445360660553</v>
+        <v>1.84453594684601</v>
       </c>
       <c r="H970" t="n">
         <v>2250</v>
@@ -28528,7 +28528,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H971" t="n">
         <v>2250</v>
@@ -28557,7 +28557,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28586,7 +28586,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -28760,7 +28760,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H979" t="n">
         <v>2250</v>
@@ -28847,7 +28847,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H982" t="n">
         <v>9000</v>
@@ -28876,7 +28876,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -28934,7 +28934,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H985" t="n">
         <v>4500</v>
@@ -28963,7 +28963,7 @@
         <v>2</v>
       </c>
       <c r="G986" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H986" t="n">
         <v>8250</v>
@@ -28992,7 +28992,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H987" t="n">
         <v>52500</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H989" t="n">
         <v>18000</v>
@@ -29108,7 +29108,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G991" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H991" t="n">
         <v>120750</v>
@@ -29369,7 +29369,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1000" t="n">
         <v>16500</v>
@@ -29746,7 +29746,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1013" t="n">
         <v>8250</v>
@@ -29949,7 +29949,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1020" t="n">
         <v>24750</v>
@@ -29978,7 +29978,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1021" t="n">
         <v>4500</v>
@@ -30297,7 +30297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1032" t="n">
         <v>4500</v>
@@ -30355,7 +30355,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.34070432186127</v>
+        <v>1.34070444107056</v>
       </c>
       <c r="H1034" t="n">
         <v>28500</v>
@@ -30442,7 +30442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.34070432186127</v>
+        <v>1.34070444107056</v>
       </c>
       <c r="H1037" t="n">
         <v>27000</v>
@@ -30471,7 +30471,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1038" t="n">
         <v>23250</v>
@@ -30500,7 +30500,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1039" t="n">
         <v>12000</v>
@@ -30529,7 +30529,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1040" t="n">
         <v>750</v>
@@ -30558,7 +30558,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1041" t="n">
         <v>6750</v>
@@ -30790,7 +30790,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1049" t="n">
         <v>9000</v>
@@ -30906,7 +30906,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1053" t="n">
         <v>3750</v>
@@ -30993,7 +30993,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1056" t="n">
         <v>18000</v>
@@ -31080,7 +31080,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1059" t="n">
         <v>99750</v>
@@ -31109,7 +31109,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1060" t="n">
         <v>4500</v>
@@ -31138,7 +31138,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1061" t="n">
         <v>5250</v>
@@ -31167,7 +31167,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H1064" t="n">
         <v>8250</v>
@@ -31631,7 +31631,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1078" t="n">
         <v>2250</v>
@@ -31660,7 +31660,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1079" t="n">
         <v>2250</v>
@@ -31689,7 +31689,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -31805,7 +31805,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1084" t="n">
         <v>19500</v>
@@ -31863,7 +31863,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1086" t="n">
         <v>3000</v>
@@ -31892,7 +31892,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1087" t="n">
         <v>6000</v>
@@ -31979,7 +31979,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1090" t="n">
         <v>15750</v>
@@ -32124,7 +32124,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H1095" t="n">
         <v>20250</v>
@@ -32153,7 +32153,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1096" t="n">
         <v>23250</v>
@@ -32182,7 +32182,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1097" t="n">
         <v>9750</v>
@@ -32211,7 +32211,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1098" t="n">
         <v>12750</v>
@@ -32356,7 +32356,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.52003419399261</v>
+        <v>1.5200343132019</v>
       </c>
       <c r="H1103" t="n">
         <v>12000</v>
@@ -32472,7 +32472,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.51149463653564</v>
+        <v>1.51149475574493</v>
       </c>
       <c r="H1107" t="n">
         <v>6750</v>
@@ -32559,7 +32559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958728313446</v>
       </c>
       <c r="H1110" t="n">
         <v>45000</v>
@@ -32617,7 +32617,7 @@
         <v>2</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1112" t="n">
         <v>37500</v>
@@ -32646,7 +32646,7 @@
         <v>2</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1113" t="n">
         <v>2250</v>
@@ -32762,7 +32762,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1117" t="n">
         <v>3000</v>
@@ -32791,7 +32791,7 @@
         <v>2</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1118" t="n">
         <v>32250</v>
@@ -32849,7 +32849,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329860210419</v>
+        <v>1.79329872131348</v>
       </c>
       <c r="H1120" t="n">
         <v>9750</v>
@@ -32878,7 +32878,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1121" t="n">
         <v>3000</v>
@@ -32907,7 +32907,7 @@
         <v>2</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1122" t="n">
         <v>1500</v>
@@ -32936,7 +32936,7 @@
         <v>2</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1123" t="n">
         <v>750</v>
@@ -32965,7 +32965,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1124" t="n">
         <v>35250</v>
@@ -32994,7 +32994,7 @@
         <v>2</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1125" t="n">
         <v>27750</v>
@@ -33023,7 +33023,7 @@
         <v>2</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1126" t="n">
         <v>82500</v>
@@ -33052,7 +33052,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1127" t="n">
         <v>1500</v>
@@ -33081,7 +33081,7 @@
         <v>2</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1128" t="n">
         <v>19500</v>
@@ -33110,7 +33110,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1129" t="n">
         <v>3000</v>
@@ -33139,7 +33139,7 @@
         <v>2</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1130" t="n">
         <v>12750</v>
@@ -33255,7 +33255,7 @@
         <v>2</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1134" t="n">
         <v>2250</v>
@@ -33284,7 +33284,7 @@
         <v>2</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33313,7 +33313,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1136" t="n">
         <v>3750</v>
@@ -33342,7 +33342,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.72498261928558</v>
+        <v>1.72498250007629</v>
       </c>
       <c r="H1137" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812695980072</v>
+        <v>1.64812684059143</v>
       </c>
       <c r="H1140" t="n">
         <v>8250</v>
@@ -33632,7 +33632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958740234375</v>
+        <v>1.63958728313446</v>
       </c>
       <c r="H1147" t="n">
         <v>9750</v>
@@ -33748,7 +33748,7 @@
         <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1151" t="n">
         <v>18000</v>
@@ -33777,7 +33777,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1152" t="n">
         <v>122250</v>
@@ -34705,7 +34705,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1184" t="n">
         <v>84000</v>
@@ -34792,7 +34792,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1187" t="n">
         <v>18000</v>
@@ -34879,7 +34879,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1190" t="n">
         <v>57000</v>
@@ -34908,7 +34908,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1191" t="n">
         <v>43500</v>
@@ -34937,7 +34937,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1192" t="n">
         <v>75750</v>
@@ -34966,7 +34966,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.06746220588684</v>
+        <v>2.06746244430542</v>
       </c>
       <c r="H1193" t="n">
         <v>28500</v>
@@ -34995,7 +34995,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.99555051326752</v>
+        <v>1.99555063247681</v>
       </c>
       <c r="H1194" t="n">
         <v>24000</v>
@@ -35024,7 +35024,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1195" t="n">
         <v>12000</v>
@@ -35053,7 +35053,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1196" t="n">
         <v>12000</v>
@@ -35082,7 +35082,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1197" t="n">
         <v>2250</v>
@@ -35111,7 +35111,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1198" t="n">
         <v>30000</v>
@@ -35140,7 +35140,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1199" t="n">
         <v>3750</v>
@@ -35169,7 +35169,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1200" t="n">
         <v>0</v>
@@ -35198,7 +35198,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1201" t="n">
         <v>750</v>
@@ -35227,7 +35227,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1202" t="n">
         <v>6000</v>
@@ -35256,7 +35256,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1203" t="n">
         <v>9000</v>
@@ -35314,7 +35314,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1205" t="n">
         <v>21000</v>
@@ -35343,7 +35343,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1206" t="n">
         <v>24750</v>
@@ -35372,7 +35372,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1207" t="n">
         <v>3750</v>
@@ -35401,7 +35401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1208" t="n">
         <v>3750</v>
@@ -35981,7 +35981,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1228" t="n">
         <v>12750</v>
@@ -36010,7 +36010,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1229" t="n">
         <v>9750</v>
@@ -36126,7 +36126,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1233" t="n">
         <v>1500</v>
@@ -36155,7 +36155,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1234" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1242" t="n">
         <v>27000</v>
@@ -36445,7 +36445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1244" t="n">
         <v>2250</v>
@@ -36561,7 +36561,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1248" t="n">
         <v>3000</v>
@@ -36764,7 +36764,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1255" t="n">
         <v>7500</v>
@@ -36793,7 +36793,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1256" t="n">
         <v>11250</v>
@@ -36851,7 +36851,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1258" t="n">
         <v>20250</v>
@@ -36938,7 +36938,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1261" t="n">
         <v>12750</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1263" t="n">
         <v>32250</v>
@@ -37402,7 +37402,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1277" t="n">
         <v>5250</v>
@@ -37431,7 +37431,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1278" t="n">
         <v>4500</v>
@@ -37518,7 +37518,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1281" t="n">
         <v>6000</v>
@@ -37576,7 +37576,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1283" t="n">
         <v>2250</v>
@@ -37605,7 +37605,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1284" t="n">
         <v>8250</v>
@@ -37779,7 +37779,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1290" t="n">
         <v>14250</v>
@@ -37837,7 +37837,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1292" t="n">
         <v>750</v>
@@ -37866,7 +37866,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1293" t="n">
         <v>750</v>
@@ -37895,7 +37895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1294" t="n">
         <v>0</v>
@@ -37953,7 +37953,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1296" t="n">
         <v>4500</v>
@@ -37982,7 +37982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1297" t="n">
         <v>3000</v>
@@ -38040,7 +38040,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1299" t="n">
         <v>7500</v>
@@ -38069,7 +38069,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1300" t="n">
         <v>3000</v>
@@ -38098,7 +38098,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1301" t="n">
         <v>6750</v>
@@ -38127,7 +38127,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1302" t="n">
         <v>6000</v>
@@ -38359,7 +38359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1310" t="n">
         <v>7500</v>
@@ -39229,7 +39229,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1340" t="n">
         <v>5250</v>
@@ -39258,7 +39258,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1341" t="n">
         <v>2250</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1342" t="n">
         <v>12000</v>
@@ -39316,7 +39316,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1343" t="n">
         <v>13500</v>
@@ -39345,7 +39345,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1344" t="n">
         <v>5250</v>
@@ -39403,7 +39403,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1346" t="n">
         <v>6000</v>
@@ -39432,7 +39432,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1347" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1367" t="n">
         <v>2250</v>
@@ -40041,7 +40041,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1368" t="n">
         <v>42750</v>
@@ -40070,7 +40070,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1369" t="n">
         <v>4500</v>
@@ -40099,7 +40099,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1370" t="n">
         <v>0</v>
@@ -40128,7 +40128,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1371" t="n">
         <v>1500</v>
@@ -40244,7 +40244,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1375" t="n">
         <v>750</v>
@@ -40273,7 +40273,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1376" t="n">
         <v>0</v>
@@ -40360,7 +40360,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1379" t="n">
         <v>5250</v>
@@ -40389,7 +40389,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1380" t="n">
         <v>114750</v>
@@ -40418,7 +40418,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1381" t="n">
         <v>12750</v>
@@ -40447,7 +40447,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1382" t="n">
         <v>4500</v>
@@ -40476,7 +40476,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1383" t="n">
         <v>1500</v>
@@ -40505,7 +40505,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1384" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1386" t="n">
         <v>15000</v>
@@ -40592,7 +40592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1387" t="n">
         <v>3000</v>
@@ -40621,7 +40621,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1388" t="n">
         <v>2250</v>
@@ -40650,7 +40650,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1389" t="n">
         <v>1500</v>
@@ -40679,7 +40679,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1391" t="n">
         <v>1500</v>
@@ -40737,7 +40737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1392" t="n">
         <v>60750</v>
@@ -40766,7 +40766,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1393" t="n">
         <v>5250</v>
@@ -40795,7 +40795,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1394" t="n">
         <v>13500</v>
@@ -40824,7 +40824,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1395" t="n">
         <v>11250</v>
@@ -40853,7 +40853,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1396" t="n">
         <v>21000</v>
@@ -40911,7 +40911,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1398" t="n">
         <v>15750</v>
@@ -40969,7 +40969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1400" t="n">
         <v>22500</v>
@@ -41027,7 +41027,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1402" t="n">
         <v>9000</v>
@@ -51966,6 +51966,64 @@
         <v>0</v>
       </c>
       <c r="I1779" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1780">
+      <c r="A1780" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1780" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1780" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="D1780" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="E1780" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="F1780" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="G1780" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="H1780" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1780" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1781">
+      <c r="A1781" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1781" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1781" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="D1781" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="E1781" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F1781" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G1781" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H1781" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1781" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189449310303</v>
+        <v>2.73189401626587</v>
       </c>
       <c r="H2" t="n">
         <v>893250</v>
@@ -630,7 +630,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75111317634583</v>
+        <v>2.75111293792725</v>
       </c>
       <c r="H9" t="n">
         <v>62250</v>
@@ -659,7 +659,7 @@
         <v>3.43650007247925</v>
       </c>
       <c r="G10" t="n">
-        <v>2.75191402435303</v>
+        <v>2.75191426277161</v>
       </c>
       <c r="H10" t="n">
         <v>33750</v>
@@ -891,7 +891,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558506965637</v>
+        <v>3.63558530807495</v>
       </c>
       <c r="H18" t="n">
         <v>196500</v>
@@ -920,7 +920,7 @@
         <v>4.94999980926514</v>
       </c>
       <c r="G19" t="n">
-        <v>3.96390867233276</v>
+        <v>3.9639093875885</v>
       </c>
       <c r="H19" t="n">
         <v>402000</v>
@@ -949,7 +949,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578324317932</v>
+        <v>3.83578276634216</v>
       </c>
       <c r="H20" t="n">
         <v>495750</v>
@@ -1036,7 +1036,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51226401329041</v>
+        <v>3.51226377487183</v>
       </c>
       <c r="H23" t="n">
         <v>94500</v>
@@ -1065,7 +1065,7 @@
         <v>4.29199981689453</v>
       </c>
       <c r="G24" t="n">
-        <v>3.43698930740356</v>
+        <v>3.43698954582214</v>
       </c>
       <c r="H24" t="n">
         <v>24750</v>
@@ -1094,7 +1094,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.4914436340332</v>
+        <v>3.49144387245178</v>
       </c>
       <c r="H25" t="n">
         <v>20250</v>
@@ -1123,7 +1123,7 @@
         <v>4.38350009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>3.51026225090027</v>
+        <v>3.51026248931885</v>
       </c>
       <c r="H26" t="n">
         <v>24750</v>
@@ -1181,7 +1181,7 @@
         <v>4.17500019073486</v>
       </c>
       <c r="G28" t="n">
-        <v>3.34329748153687</v>
+        <v>3.34329771995544</v>
       </c>
       <c r="H28" t="n">
         <v>18000</v>
@@ -1297,7 +1297,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.28724217414856</v>
+        <v>3.28724193572998</v>
       </c>
       <c r="H32" t="n">
         <v>2250</v>
@@ -1384,7 +1384,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G35" t="n">
-        <v>3.03098940849304</v>
+        <v>3.03098964691162</v>
       </c>
       <c r="H35" t="n">
         <v>10500</v>
@@ -1442,7 +1442,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H37" t="n">
         <v>750</v>
@@ -1471,7 +1471,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G38" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H38" t="n">
         <v>27000</v>
@@ -1500,7 +1500,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G39" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H39" t="n">
         <v>15000</v>
@@ -1558,7 +1558,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G41" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H41" t="n">
         <v>9750</v>
@@ -1587,7 +1587,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G42" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H42" t="n">
         <v>0</v>
@@ -1674,7 +1674,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G45" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H45" t="n">
         <v>13500</v>
@@ -1703,7 +1703,7 @@
         <v>3.73000001907349</v>
       </c>
       <c r="G46" t="n">
-        <v>2.98694586753845</v>
+        <v>2.98694562911987</v>
       </c>
       <c r="H46" t="n">
         <v>3000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1935,7 +1935,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.07903671264648</v>
+        <v>3.07903647422791</v>
       </c>
       <c r="H54" t="n">
         <v>13500</v>
@@ -1964,7 +1964,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G55" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H55" t="n">
         <v>2250</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507225036621</v>
+        <v>3.11507248878479</v>
       </c>
       <c r="H56" t="n">
         <v>18750</v>
@@ -2022,7 +2022,7 @@
         <v>3.82999992370605</v>
       </c>
       <c r="G57" t="n">
-        <v>3.06702494621277</v>
+        <v>3.06702470779419</v>
       </c>
       <c r="H57" t="n">
         <v>18750</v>
@@ -2051,7 +2051,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H58" t="n">
         <v>3000</v>
@@ -2109,7 +2109,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.00296187400818</v>
+        <v>3.0029616355896</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507225036621</v>
+        <v>3.11507248878479</v>
       </c>
       <c r="H61" t="n">
         <v>5250</v>
@@ -2196,7 +2196,7 @@
         <v>3.78500008583069</v>
       </c>
       <c r="G63" t="n">
-        <v>3.03098940849304</v>
+        <v>3.03098964691162</v>
       </c>
       <c r="H63" t="n">
         <v>3000</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087079048157</v>
       </c>
       <c r="H65" t="n">
         <v>9750</v>
@@ -2283,7 +2283,7 @@
         <v>3.63000011444092</v>
       </c>
       <c r="G66" t="n">
-        <v>2.90686702728271</v>
+        <v>2.90686726570129</v>
       </c>
       <c r="H66" t="n">
         <v>3750</v>
@@ -2312,7 +2312,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G67" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H67" t="n">
         <v>7500</v>
@@ -2341,7 +2341,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280371665955</v>
+        <v>2.84280395507812</v>
       </c>
       <c r="H68" t="n">
         <v>8250</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670886993408</v>
+        <v>2.74670910835266</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2486,7 +2486,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G73" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H73" t="n">
         <v>17250</v>
@@ -2573,7 +2573,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G76" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H76" t="n">
         <v>24000</v>
@@ -2602,7 +2602,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>3.07903671264648</v>
+        <v>3.07903647422791</v>
       </c>
       <c r="H77" t="n">
         <v>26250</v>
@@ -2660,7 +2660,7 @@
         <v>3.76999998092651</v>
       </c>
       <c r="G79" t="n">
-        <v>3.01897764205933</v>
+        <v>3.01897740364075</v>
       </c>
       <c r="H79" t="n">
         <v>7500</v>
@@ -2747,7 +2747,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087102890015</v>
+        <v>2.91087079048157</v>
       </c>
       <c r="H82" t="n">
         <v>7500</v>
@@ -2834,7 +2834,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G85" t="n">
-        <v>2.80676817893982</v>
+        <v>2.8067684173584</v>
       </c>
       <c r="H85" t="n">
         <v>1500</v>
@@ -2892,7 +2892,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.59055495262146</v>
+        <v>2.59055471420288</v>
       </c>
       <c r="H87" t="n">
         <v>14250</v>
@@ -2921,7 +2921,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H88" t="n">
         <v>3750</v>
@@ -2950,7 +2950,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G89" t="n">
-        <v>2.53049612045288</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H89" t="n">
         <v>4500</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H90" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.0099823474884</v>
+        <v>2.00998258590698</v>
       </c>
       <c r="H92" t="n">
         <v>16500</v>
@@ -3066,7 +3066,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.0099823474884</v>
+        <v>2.00998258590698</v>
       </c>
       <c r="H93" t="n">
         <v>9750</v>
@@ -3124,7 +3124,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.57755589485168</v>
+        <v>1.57755601406097</v>
       </c>
       <c r="H95" t="n">
         <v>9000</v>
@@ -3240,7 +3240,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556377887726</v>
+        <v>1.58556365966797</v>
       </c>
       <c r="H99" t="n">
         <v>14250</v>
@@ -3327,7 +3327,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.67765462398529</v>
+        <v>1.677654504776</v>
       </c>
       <c r="H102" t="n">
         <v>11250</v>
@@ -3501,7 +3501,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.8978716135025</v>
+        <v>1.89787149429321</v>
       </c>
       <c r="H108" t="n">
         <v>15750</v>
@@ -3559,7 +3559,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G110" t="n">
-        <v>2.53049612045288</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H110" t="n">
         <v>16500</v>
@@ -3588,7 +3588,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H111" t="n">
         <v>28500</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3733,7 +3733,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G116" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H116" t="n">
         <v>6750</v>
@@ -3762,7 +3762,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G117" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H117" t="n">
         <v>3750</v>
@@ -3849,7 +3849,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664956092834</v>
+        <v>2.68664979934692</v>
       </c>
       <c r="H120" t="n">
         <v>11250</v>
@@ -3965,7 +3965,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G124" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H124" t="n">
         <v>2250</v>
@@ -4023,7 +4023,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G126" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H126" t="n">
         <v>3750</v>
@@ -4139,7 +4139,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G130" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H130" t="n">
         <v>3750</v>
@@ -4168,7 +4168,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G131" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H131" t="n">
         <v>750</v>
@@ -4226,7 +4226,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G133" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H133" t="n">
         <v>5250</v>
@@ -4255,7 +4255,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G134" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H134" t="n">
         <v>750</v>
@@ -4284,7 +4284,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G135" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H135" t="n">
         <v>750</v>
@@ -4313,7 +4313,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G136" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H136" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H137" t="n">
         <v>750</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856271743774</v>
+        <v>2.59856295585632</v>
       </c>
       <c r="H139" t="n">
         <v>1500</v>
@@ -4516,7 +4516,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4574,7 +4574,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651117324829</v>
       </c>
       <c r="H145" t="n">
         <v>3000</v>
@@ -4603,7 +4603,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.71868109703064</v>
+        <v>2.7186815738678</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4835,7 +4835,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.63459825515747</v>
+        <v>2.63459849357605</v>
       </c>
       <c r="H154" t="n">
         <v>9000</v>
@@ -4864,7 +4864,7 @@
         <v>3.25</v>
       </c>
       <c r="G155" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H155" t="n">
         <v>8250</v>
@@ -4922,7 +4922,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>2.76272439956665</v>
+        <v>2.76272463798523</v>
       </c>
       <c r="H157" t="n">
         <v>11250</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651117324829</v>
       </c>
       <c r="H161" t="n">
         <v>14250</v>
@@ -5299,7 +5299,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H170" t="n">
         <v>18000</v>
@@ -5647,7 +5647,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H182" t="n">
         <v>750</v>
@@ -6082,7 +6082,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H197" t="n">
         <v>139500</v>
@@ -6111,7 +6111,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.05100917816162</v>
+        <v>3.0510094165802</v>
       </c>
       <c r="H198" t="n">
         <v>203250</v>
@@ -6256,7 +6256,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G203" t="n">
-        <v>2.68264555931091</v>
+        <v>2.68264579772949</v>
       </c>
       <c r="H203" t="n">
         <v>9750</v>
@@ -6285,7 +6285,7 @@
         <v>3.25</v>
       </c>
       <c r="G204" t="n">
-        <v>2.60256695747375</v>
+        <v>2.60256671905518</v>
       </c>
       <c r="H204" t="n">
         <v>12000</v>
@@ -6314,7 +6314,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451941490173</v>
+        <v>2.55451917648315</v>
       </c>
       <c r="H205" t="n">
         <v>13500</v>
@@ -6343,7 +6343,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258696556091</v>
       </c>
       <c r="H206" t="n">
         <v>8250</v>
@@ -6372,7 +6372,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258672714233</v>
+        <v>2.62258696556091</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6546,7 +6546,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H213" t="n">
         <v>10500</v>
@@ -6604,7 +6604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34631395339966</v>
+        <v>2.34631419181824</v>
       </c>
       <c r="H215" t="n">
         <v>5250</v>
@@ -6662,7 +6662,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H217" t="n">
         <v>11250</v>
@@ -6749,7 +6749,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H220" t="n">
         <v>750</v>
@@ -6836,7 +6836,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651165008545</v>
+        <v>2.54651117324829</v>
       </c>
       <c r="H223" t="n">
         <v>5250</v>
@@ -6865,7 +6865,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G224" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H224" t="n">
         <v>5250</v>
@@ -6981,7 +6981,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238879203796</v>
       </c>
       <c r="H228" t="n">
         <v>15750</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H231" t="n">
         <v>3000</v>
@@ -7097,7 +7097,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>2.34631395339966</v>
+        <v>2.34631419181824</v>
       </c>
       <c r="H232" t="n">
         <v>6000</v>
@@ -7213,7 +7213,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G236" t="n">
-        <v>2.29025840759277</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H236" t="n">
         <v>2250</v>
@@ -7242,7 +7242,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G237" t="n">
-        <v>2.29025840759277</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -7532,7 +7532,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H247" t="n">
         <v>1500</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7822,7 +7822,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H257" t="n">
         <v>1500</v>
@@ -7909,7 +7909,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G260" t="n">
-        <v>2.21418380737305</v>
+        <v>2.21418356895447</v>
       </c>
       <c r="H260" t="n">
         <v>3000</v>
@@ -7938,7 +7938,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21418380737305</v>
+        <v>2.21418356895447</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7967,7 +7967,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G262" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H262" t="n">
         <v>2250</v>
@@ -8025,7 +8025,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21018004417419</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8083,7 +8083,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G266" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H266" t="n">
         <v>2250</v>
@@ -8112,7 +8112,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820757865906</v>
+        <v>2.23820734024048</v>
       </c>
       <c r="H267" t="n">
         <v>2250</v>
@@ -8199,7 +8199,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H270" t="n">
         <v>750</v>
@@ -8228,7 +8228,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H271" t="n">
         <v>6000</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834596633911</v>
+        <v>2.37834572792053</v>
       </c>
       <c r="H274" t="n">
         <v>3750</v>
@@ -8344,7 +8344,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H275" t="n">
         <v>12000</v>
@@ -8373,7 +8373,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H276" t="n">
         <v>3000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037702560425</v>
+        <v>2.41037750244141</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H282" t="n">
         <v>3750</v>
@@ -8576,7 +8576,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8634,7 +8634,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G285" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H285" t="n">
         <v>3000</v>
@@ -8721,7 +8721,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G288" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H288" t="n">
         <v>1500</v>
@@ -8837,7 +8837,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.2862548828125</v>
+        <v>2.28625512123108</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8866,7 +8866,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G293" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H293" t="n">
         <v>1500</v>
@@ -8895,7 +8895,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21018004417419</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H294" t="n">
         <v>750</v>
@@ -9127,7 +9127,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G302" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H302" t="n">
         <v>3000</v>
@@ -9156,7 +9156,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G303" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H303" t="n">
         <v>0</v>
@@ -9214,7 +9214,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G305" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H305" t="n">
         <v>148500</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H308" t="n">
         <v>6750</v>
@@ -9533,7 +9533,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G316" t="n">
-        <v>2.36633348464966</v>
+        <v>2.36633372306824</v>
       </c>
       <c r="H316" t="n">
         <v>3750</v>
@@ -9562,7 +9562,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H317" t="n">
         <v>3750</v>
@@ -9591,7 +9591,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.36232995986938</v>
+        <v>2.36232972145081</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9649,7 +9649,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430218696594</v>
+        <v>2.33430194854736</v>
       </c>
       <c r="H320" t="n">
         <v>750</v>
@@ -9794,7 +9794,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G325" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H325" t="n">
         <v>13500</v>
@@ -9852,7 +9852,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G327" t="n">
-        <v>2.41438102722168</v>
+        <v>2.41438126564026</v>
       </c>
       <c r="H327" t="n">
         <v>2250</v>
@@ -9910,7 +9910,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>2.46643257141113</v>
+        <v>2.46643233299255</v>
       </c>
       <c r="H329" t="n">
         <v>2250</v>
@@ -10026,7 +10026,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G333" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H333" t="n">
         <v>9000</v>
@@ -10055,7 +10055,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238879203796</v>
       </c>
       <c r="H334" t="n">
         <v>2250</v>
@@ -10258,7 +10258,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238926887512</v>
+        <v>2.42238879203796</v>
       </c>
       <c r="H341" t="n">
         <v>20250</v>
@@ -10287,7 +10287,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.4263927936554</v>
+        <v>2.42639303207397</v>
       </c>
       <c r="H342" t="n">
         <v>1500</v>
@@ -10490,7 +10490,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G349" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H349" t="n">
         <v>3750</v>
@@ -10577,7 +10577,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451941490173</v>
+        <v>2.55451917648315</v>
       </c>
       <c r="H352" t="n">
         <v>4500</v>
@@ -10606,7 +10606,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G353" t="n">
-        <v>2.53049612045288</v>
+        <v>2.5304958820343</v>
       </c>
       <c r="H353" t="n">
         <v>750</v>
@@ -10664,7 +10664,7 @@
         <v>3.33500003814697</v>
       </c>
       <c r="G355" t="n">
-        <v>2.67063403129578</v>
+        <v>2.6706337928772</v>
       </c>
       <c r="H355" t="n">
         <v>14250</v>
@@ -10693,7 +10693,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H356" t="n">
         <v>5250</v>
@@ -10751,7 +10751,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266532897949</v>
+        <v>2.70266556739807</v>
       </c>
       <c r="H358" t="n">
         <v>13500</v>
@@ -10780,7 +10780,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.6185827255249</v>
+        <v>2.61858248710632</v>
       </c>
       <c r="H359" t="n">
         <v>10500</v>
@@ -10809,7 +10809,7 @@
         <v>3.39000010490417</v>
       </c>
       <c r="G360" t="n">
-        <v>2.71467757225037</v>
+        <v>2.71467733383179</v>
       </c>
       <c r="H360" t="n">
         <v>10500</v>
@@ -10896,7 +10896,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G363" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H363" t="n">
         <v>1500</v>
@@ -10925,7 +10925,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G364" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H364" t="n">
         <v>3000</v>
@@ -10954,7 +10954,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G365" t="n">
-        <v>2.6586217880249</v>
+        <v>2.65862202644348</v>
       </c>
       <c r="H365" t="n">
         <v>5250</v>
@@ -11041,7 +11041,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H368" t="n">
         <v>210750</v>
@@ -11099,7 +11099,7 @@
         <v>4</v>
       </c>
       <c r="G370" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H370" t="n">
         <v>12750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11244,7 +11244,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H375" t="n">
         <v>3750</v>
@@ -11331,7 +11331,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H378" t="n">
         <v>6000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11505,7 +11505,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H384" t="n">
         <v>19500</v>
@@ -11534,7 +11534,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H385" t="n">
         <v>22500</v>
@@ -11708,7 +11708,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G391" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H391" t="n">
         <v>9000</v>
@@ -11766,7 +11766,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.17112755775452</v>
+        <v>3.17112731933594</v>
       </c>
       <c r="H393" t="n">
         <v>23250</v>
@@ -11795,7 +11795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H394" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -11853,7 +11853,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H397" t="n">
         <v>750</v>
@@ -11911,7 +11911,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11998,7 +11998,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H401" t="n">
         <v>8250</v>
@@ -12056,7 +12056,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.2672221660614</v>
+        <v>3.26722240447998</v>
       </c>
       <c r="H403" t="n">
         <v>38250</v>
@@ -12143,7 +12143,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>3.31526970863342</v>
+        <v>3.31526947021484</v>
       </c>
       <c r="H406" t="n">
         <v>72750</v>
@@ -12172,7 +12172,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>3.31526970863342</v>
+        <v>3.31526947021484</v>
       </c>
       <c r="H407" t="n">
         <v>13500</v>
@@ -12259,7 +12259,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511202812195</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12288,7 +12288,7 @@
         <v>4</v>
       </c>
       <c r="G411" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H411" t="n">
         <v>8250</v>
@@ -12375,7 +12375,7 @@
         <v>4</v>
       </c>
       <c r="G414" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H414" t="n">
         <v>4500</v>
@@ -12433,7 +12433,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511202812195</v>
       </c>
       <c r="H416" t="n">
         <v>3750</v>
@@ -12491,7 +12491,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706448554993</v>
+        <v>3.10706424713135</v>
       </c>
       <c r="H418" t="n">
         <v>8250</v>
@@ -12665,7 +12665,7 @@
         <v>4</v>
       </c>
       <c r="G424" t="n">
-        <v>3.20315933227539</v>
+        <v>3.20315909385681</v>
       </c>
       <c r="H424" t="n">
         <v>6000</v>
@@ -12694,7 +12694,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>3.15511178970337</v>
+        <v>3.15511202812195</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12839,7 +12839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H430" t="n">
         <v>7500</v>
@@ -12926,7 +12926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H433" t="n">
         <v>1500</v>
@@ -13013,7 +13013,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901670455933</v>
+        <v>3.05901718139648</v>
       </c>
       <c r="H436" t="n">
         <v>4500</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13419,7 +13419,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G450" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H450" t="n">
         <v>1500</v>
@@ -13506,7 +13506,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G453" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H453" t="n">
         <v>1500</v>
@@ -13593,7 +13593,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G456" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H456" t="n">
         <v>3750</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13651,7 +13651,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G458" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H458" t="n">
         <v>3750</v>
@@ -13738,7 +13738,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G461" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H461" t="n">
         <v>1500</v>
@@ -13767,7 +13767,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G462" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H462" t="n">
         <v>0</v>
@@ -13796,7 +13796,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G463" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H463" t="n">
         <v>3000</v>
@@ -13883,7 +13883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H466" t="n">
         <v>9750</v>
@@ -13912,7 +13912,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G467" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H467" t="n">
         <v>750</v>
@@ -13941,7 +13941,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G468" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H468" t="n">
         <v>0</v>
@@ -13970,7 +13970,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G469" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H469" t="n">
         <v>1500</v>
@@ -13999,7 +13999,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G470" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H470" t="n">
         <v>2250</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14260,7 +14260,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G479" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H479" t="n">
         <v>6000</v>
@@ -14376,7 +14376,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G483" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H483" t="n">
         <v>1500</v>
@@ -14405,7 +14405,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G484" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H484" t="n">
         <v>2250</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698540687561</v>
+        <v>3.02698516845703</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14579,7 +14579,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G490" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H490" t="n">
         <v>750</v>
@@ -14608,7 +14608,7 @@
         <v>3.72000002861023</v>
       </c>
       <c r="G491" t="n">
-        <v>2.97893810272217</v>
+        <v>2.97893786430359</v>
       </c>
       <c r="H491" t="n">
         <v>0</v>
@@ -14637,7 +14637,7 @@
         <v>3.6800000667572</v>
       </c>
       <c r="G492" t="n">
-        <v>2.94690632820129</v>
+        <v>2.94690656661987</v>
       </c>
       <c r="H492" t="n">
         <v>750</v>
@@ -14666,7 +14666,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G493" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H493" t="n">
         <v>1500</v>
@@ -14724,7 +14724,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G495" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H495" t="n">
         <v>1500</v>
@@ -14753,7 +14753,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G496" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H496" t="n">
         <v>4500</v>
@@ -14782,7 +14782,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G497" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H497" t="n">
         <v>750</v>
@@ -14811,7 +14811,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G498" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H498" t="n">
         <v>3750</v>
@@ -14840,7 +14840,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G499" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H499" t="n">
         <v>0</v>
@@ -14869,7 +14869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H500" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089056015015</v>
+        <v>2.93089079856873</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -14927,7 +14927,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G502" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H502" t="n">
         <v>3750</v>
@@ -14956,7 +14956,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G503" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H503" t="n">
         <v>5250</v>
@@ -14985,7 +14985,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G504" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H504" t="n">
         <v>750</v>
@@ -15014,7 +15014,7 @@
         <v>3.64000010490417</v>
       </c>
       <c r="G505" t="n">
-        <v>2.91487503051758</v>
+        <v>2.914874792099</v>
       </c>
       <c r="H505" t="n">
         <v>1500</v>
@@ -15043,7 +15043,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G506" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H506" t="n">
         <v>8250</v>
@@ -15130,7 +15130,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G509" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H509" t="n">
         <v>4500</v>
@@ -15159,7 +15159,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G510" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H510" t="n">
         <v>9000</v>
@@ -15188,7 +15188,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G511" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H511" t="n">
         <v>0</v>
@@ -15217,7 +15217,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G512" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H512" t="n">
         <v>0</v>
@@ -15246,7 +15246,7 @@
         <v>3.59999990463257</v>
       </c>
       <c r="G513" t="n">
-        <v>2.8828432559967</v>
+        <v>2.88284301757812</v>
       </c>
       <c r="H513" t="n">
         <v>0</v>
@@ -15304,7 +15304,7 @@
         <v>3.57999992370605</v>
       </c>
       <c r="G515" t="n">
-        <v>2.86682748794556</v>
+        <v>2.86682724952698</v>
       </c>
       <c r="H515" t="n">
         <v>6750</v>
@@ -15391,7 +15391,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G518" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H518" t="n">
         <v>12750</v>
@@ -15420,7 +15420,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G519" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H519" t="n">
         <v>3750</v>
@@ -15449,7 +15449,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G520" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H520" t="n">
         <v>1500</v>
@@ -15478,7 +15478,7 @@
         <v>3.44000005722046</v>
       </c>
       <c r="G521" t="n">
-        <v>2.75471711158752</v>
+        <v>2.75471687316895</v>
       </c>
       <c r="H521" t="n">
         <v>0</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268509864807</v>
+        <v>2.72268557548523</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15623,7 +15623,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59455895423889</v>
+        <v>2.59455919265747</v>
       </c>
       <c r="H526" t="n">
         <v>17250</v>
@@ -15681,7 +15681,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G528" t="n">
-        <v>2.49846386909485</v>
+        <v>2.49846410751343</v>
       </c>
       <c r="H528" t="n">
         <v>5250</v>
@@ -15739,7 +15739,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G530" t="n">
-        <v>2.43440103530884</v>
+        <v>2.43440079689026</v>
       </c>
       <c r="H530" t="n">
         <v>5250</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -15826,7 +15826,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G533" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H533" t="n">
         <v>15000</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16203,7 +16203,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G546" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H546" t="n">
         <v>8250</v>
@@ -16232,7 +16232,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H547" t="n">
         <v>6750</v>
@@ -16261,7 +16261,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G548" t="n">
-        <v>2.29025840759277</v>
+        <v>2.29025864601135</v>
       </c>
       <c r="H548" t="n">
         <v>6750</v>
@@ -16319,7 +16319,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G550" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H550" t="n">
         <v>1500</v>
@@ -16435,7 +16435,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H555" t="n">
         <v>6000</v>
@@ -16609,7 +16609,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H560" t="n">
         <v>1500</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.38635349273682</v>
+        <v>2.3863537311554</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H568" t="n">
         <v>6750</v>
@@ -16870,7 +16870,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>2.32229042053223</v>
+        <v>2.32229065895081</v>
       </c>
       <c r="H570" t="n">
         <v>750</v>
@@ -16928,7 +16928,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G571" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H571" t="n">
         <v>7500</v>
@@ -16957,7 +16957,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G572" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H572" t="n">
         <v>3000</v>
@@ -16986,7 +16986,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G573" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H573" t="n">
         <v>6750</v>
@@ -17015,7 +17015,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G574" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H574" t="n">
         <v>0</v>
@@ -17044,7 +17044,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G575" t="n">
-        <v>2.25822687149048</v>
+        <v>2.25822710990906</v>
       </c>
       <c r="H575" t="n">
         <v>0</v>
@@ -17073,7 +17073,7 @@
         <v>2.83999991416931</v>
       </c>
       <c r="G576" t="n">
-        <v>2.27424263954163</v>
+        <v>2.27424287796021</v>
       </c>
       <c r="H576" t="n">
         <v>3000</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H577" t="n">
         <v>12750</v>
@@ -17131,7 +17131,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221110343933</v>
+        <v>2.24221134185791</v>
       </c>
       <c r="H579" t="n">
         <v>6000</v>
@@ -17189,7 +17189,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21018004417419</v>
+        <v>2.21017956733704</v>
       </c>
       <c r="H580" t="n">
         <v>3750</v>
@@ -17218,7 +17218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213250160217</v>
+        <v>2.16213274002075</v>
       </c>
       <c r="H581" t="n">
         <v>15750</v>
@@ -17247,7 +17247,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H582" t="n">
         <v>18000</v>
@@ -17276,7 +17276,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G583" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H583" t="n">
         <v>15750</v>
@@ -17305,7 +17305,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.098069190979</v>
+        <v>2.09806895256042</v>
       </c>
       <c r="H584" t="n">
         <v>4500</v>
@@ -17450,7 +17450,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G589" t="n">
-        <v>2.13010096549988</v>
+        <v>2.1301007270813</v>
       </c>
       <c r="H589" t="n">
         <v>3000</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986361026764</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17682,7 +17682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587985515594</v>
+        <v>1.90587961673737</v>
       </c>
       <c r="H597" t="n">
         <v>7500</v>
@@ -17769,7 +17769,7 @@
         <v>2</v>
       </c>
       <c r="G600" t="n">
-        <v>1.6015796661377</v>
+        <v>1.60157954692841</v>
       </c>
       <c r="H600" t="n">
         <v>21750</v>
@@ -17856,7 +17856,7 @@
         <v>2</v>
       </c>
       <c r="G603" t="n">
-        <v>1.6015796661377</v>
+        <v>1.60157954692841</v>
       </c>
       <c r="H603" t="n">
         <v>9000</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.6336110830307</v>
+        <v>1.63361120223999</v>
       </c>
       <c r="H604" t="n">
         <v>1500</v>
@@ -18117,7 +18117,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18320,7 +18320,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587985515594</v>
+        <v>1.90587961673737</v>
       </c>
       <c r="H619" t="n">
         <v>75000</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986384868622</v>
+        <v>1.88986361026764</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18378,7 +18378,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G621" t="n">
-        <v>1.9539270401001</v>
+        <v>1.95392715930939</v>
       </c>
       <c r="H621" t="n">
         <v>34500</v>
@@ -18407,7 +18407,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.80978500843048</v>
+        <v>1.80978488922119</v>
       </c>
       <c r="H622" t="n">
         <v>48750</v>
@@ -18436,7 +18436,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G623" t="n">
-        <v>1.64962673187256</v>
+        <v>1.64962685108185</v>
       </c>
       <c r="H623" t="n">
         <v>186750</v>
@@ -18523,7 +18523,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.72169804573059</v>
+        <v>1.7216979265213</v>
       </c>
       <c r="H626" t="n">
         <v>40500</v>
@@ -18552,7 +18552,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G627" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H627" t="n">
         <v>3750</v>
@@ -18581,7 +18581,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G628" t="n">
-        <v>1.72970592975616</v>
+        <v>1.72970604896545</v>
       </c>
       <c r="H628" t="n">
         <v>0</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.72169804573059</v>
+        <v>1.7216979265213</v>
       </c>
       <c r="H631" t="n">
         <v>5250</v>
@@ -18697,7 +18697,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H632" t="n">
         <v>2250</v>
@@ -18726,7 +18726,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H633" t="n">
         <v>750</v>
@@ -18755,7 +18755,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.7457218170166</v>
+        <v>1.74572193622589</v>
       </c>
       <c r="H635" t="n">
         <v>5250</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779253482819</v>
+        <v>1.81779265403748</v>
       </c>
       <c r="H640" t="n">
         <v>17250</v>
@@ -18958,7 +18958,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779253482819</v>
+        <v>1.81779265403748</v>
       </c>
       <c r="H641" t="n">
         <v>167250</v>
@@ -18987,7 +18987,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G642" t="n">
-        <v>1.75372970104218</v>
+        <v>1.75372958183289</v>
       </c>
       <c r="H642" t="n">
         <v>8250</v>
@@ -19016,7 +19016,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.83380854129791</v>
+        <v>1.8338086605072</v>
       </c>
       <c r="H643" t="n">
         <v>15000</v>
@@ -19103,7 +19103,7 @@
         <v>2.25</v>
       </c>
       <c r="G646" t="n">
-        <v>1.84199523925781</v>
+        <v>1.8419953584671</v>
       </c>
       <c r="H646" t="n">
         <v>12750</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H648" t="n">
         <v>47250</v>
@@ -19190,7 +19190,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.850182056427</v>
+        <v>1.85018193721771</v>
       </c>
       <c r="H649" t="n">
         <v>5250</v>
@@ -19219,7 +19219,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.80106198787689</v>
+        <v>1.8010618686676</v>
       </c>
       <c r="H650" t="n">
         <v>12000</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474191188812</v>
       </c>
       <c r="H651" t="n">
         <v>33750</v>
@@ -19277,7 +19277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836827754974</v>
       </c>
       <c r="H652" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836839675903</v>
+        <v>1.85836827754974</v>
       </c>
       <c r="H653" t="n">
         <v>4500</v>
@@ -19335,7 +19335,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G654" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H654" t="n">
         <v>9750</v>
@@ -19393,7 +19393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19567,7 +19567,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474179267883</v>
+        <v>1.87474191188812</v>
       </c>
       <c r="H662" t="n">
         <v>7500</v>
@@ -19683,7 +19683,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H666" t="n">
         <v>4500</v>
@@ -19770,7 +19770,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G669" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H669" t="n">
         <v>6750</v>
@@ -19799,7 +19799,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H670" t="n">
         <v>15750</v>
@@ -20118,7 +20118,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H681" t="n">
         <v>750</v>
@@ -20147,7 +20147,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H682" t="n">
         <v>1500</v>
@@ -20524,7 +20524,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H695" t="n">
         <v>750</v>
@@ -20872,7 +20872,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H707" t="n">
         <v>2250</v>
@@ -20901,7 +20901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H710" t="n">
         <v>15000</v>
@@ -20988,7 +20988,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21162,7 +21162,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H717" t="n">
         <v>7500</v>
@@ -21191,7 +21191,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H718" t="n">
         <v>2250</v>
@@ -21220,7 +21220,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21568,7 +21568,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63732922077179</v>
+        <v>1.63732898235321</v>
       </c>
       <c r="H731" t="n">
         <v>3000</v>
@@ -21655,7 +21655,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G734" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H734" t="n">
         <v>750</v>
@@ -21684,7 +21684,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G735" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H735" t="n">
         <v>0</v>
@@ -21713,7 +21713,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G736" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H736" t="n">
         <v>0</v>
@@ -21742,7 +21742,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G737" t="n">
-        <v>1.62095594406128</v>
+        <v>1.62095582485199</v>
       </c>
       <c r="H737" t="n">
         <v>2250</v>
@@ -21858,7 +21858,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H741" t="n">
         <v>2250</v>
@@ -21887,7 +21887,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H742" t="n">
         <v>7500</v>
@@ -21916,7 +21916,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -22119,7 +22119,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H751" t="n">
         <v>4500</v>
@@ -22177,7 +22177,7 @@
         <v>1.83500003814697</v>
       </c>
       <c r="G752" t="n">
-        <v>1.50224959850311</v>
+        <v>1.50224947929382</v>
       </c>
       <c r="H752" t="n">
         <v>10500</v>
@@ -22264,7 +22264,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G755" t="n">
-        <v>1.47359621524811</v>
+        <v>1.47359609603882</v>
       </c>
       <c r="H755" t="n">
         <v>6000</v>
@@ -22293,7 +22293,7 @@
         <v>1.82000005245209</v>
       </c>
       <c r="G756" t="n">
-        <v>1.48996961116791</v>
+        <v>1.48996949195862</v>
       </c>
       <c r="H756" t="n">
         <v>16500</v>
@@ -22438,7 +22438,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H761" t="n">
         <v>6000</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H763" t="n">
         <v>3750</v>
@@ -22525,7 +22525,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -22612,7 +22612,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908932209015</v>
+        <v>1.53908944129944</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22670,7 +22670,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G769" t="n">
-        <v>1.52271604537964</v>
+        <v>1.52271616458893</v>
       </c>
       <c r="H769" t="n">
         <v>3750</v>
@@ -22699,7 +22699,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G770" t="n">
-        <v>1.52271604537964</v>
+        <v>1.52271616458893</v>
       </c>
       <c r="H770" t="n">
         <v>3750</v>
@@ -22844,7 +22844,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727602005005</v>
+        <v>1.54727590084076</v>
       </c>
       <c r="H775" t="n">
         <v>4500</v>
@@ -22902,7 +22902,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.63732922077179</v>
+        <v>1.63732898235321</v>
       </c>
       <c r="H777" t="n">
         <v>16500</v>
@@ -22931,7 +22931,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.63732922077179</v>
+        <v>1.63732898235321</v>
       </c>
       <c r="H778" t="n">
         <v>3000</v>
@@ -22989,7 +22989,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.82562184333801</v>
+        <v>1.8256219625473</v>
       </c>
       <c r="H780" t="n">
         <v>60000</v>
@@ -23018,7 +23018,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H781" t="n">
         <v>11250</v>
@@ -23105,7 +23105,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H784" t="n">
         <v>2250</v>
@@ -23221,7 +23221,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>1.80106198787689</v>
+        <v>1.8010618686676</v>
       </c>
       <c r="H788" t="n">
         <v>35250</v>
@@ -23279,7 +23279,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.8092485666275</v>
+        <v>1.80924868583679</v>
       </c>
       <c r="H793" t="n">
         <v>7500</v>
@@ -23395,7 +23395,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G794" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H794" t="n">
         <v>750</v>
@@ -23424,7 +23424,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G795" t="n">
-        <v>1.78468894958496</v>
+        <v>1.78468883037567</v>
       </c>
       <c r="H795" t="n">
         <v>750</v>
@@ -23598,7 +23598,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556876182556</v>
+        <v>1.73556888103485</v>
       </c>
       <c r="H801" t="n">
         <v>12750</v>
@@ -23656,7 +23656,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644881248474</v>
+        <v>1.68644905090332</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23714,7 +23714,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H805" t="n">
         <v>45750</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919548511505</v>
+        <v>1.71919536590576</v>
       </c>
       <c r="H806" t="n">
         <v>3000</v>
@@ -23946,7 +23946,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650225162506</v>
+        <v>1.77650213241577</v>
       </c>
       <c r="H813" t="n">
         <v>5250</v>
@@ -23975,7 +23975,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.80106198787689</v>
+        <v>1.8010618686676</v>
       </c>
       <c r="H814" t="n">
         <v>9000</v>
@@ -24033,7 +24033,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842183589935</v>
+        <v>1.94842171669006</v>
       </c>
       <c r="H816" t="n">
         <v>13500</v>
@@ -24062,7 +24062,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748822689056</v>
       </c>
       <c r="H817" t="n">
         <v>76500</v>
@@ -24149,7 +24149,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H820" t="n">
         <v>11250</v>
@@ -24178,7 +24178,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748822689056</v>
       </c>
       <c r="H821" t="n">
         <v>2250</v>
@@ -24265,7 +24265,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660853385925</v>
       </c>
       <c r="H824" t="n">
         <v>65250</v>
@@ -24294,7 +24294,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660853385925</v>
       </c>
       <c r="H825" t="n">
         <v>78000</v>
@@ -24381,7 +24381,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748834609985</v>
+        <v>1.90748822689056</v>
       </c>
       <c r="H828" t="n">
         <v>11250</v>
@@ -24410,7 +24410,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660853385925</v>
       </c>
       <c r="H829" t="n">
         <v>36000</v>
@@ -24497,7 +24497,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034106254578</v>
+        <v>2.12034130096436</v>
       </c>
       <c r="H832" t="n">
         <v>2250</v>
@@ -24584,7 +24584,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.99754166603088</v>
+        <v>1.99754154682159</v>
       </c>
       <c r="H835" t="n">
         <v>6000</v>
@@ -24613,7 +24613,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210164070129</v>
+        <v>2.02210140228271</v>
       </c>
       <c r="H836" t="n">
         <v>7500</v>
@@ -24642,7 +24642,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H837" t="n">
         <v>3750</v>
@@ -24671,7 +24671,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G838" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H838" t="n">
         <v>23250</v>
@@ -24700,7 +24700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210164070129</v>
+        <v>2.02210140228271</v>
       </c>
       <c r="H839" t="n">
         <v>27750</v>
@@ -24758,7 +24758,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H841" t="n">
         <v>33000</v>
@@ -24787,7 +24787,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852764129639</v>
+        <v>2.12852787971497</v>
       </c>
       <c r="H842" t="n">
         <v>26250</v>
@@ -24932,7 +24932,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G847" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H847" t="n">
         <v>41250</v>
@@ -24961,7 +24961,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G848" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H848" t="n">
         <v>2250</v>
@@ -25048,7 +25048,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>2.08759474754333</v>
+        <v>2.08759450912476</v>
       </c>
       <c r="H851" t="n">
         <v>7500</v>
@@ -25077,7 +25077,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G852" t="n">
-        <v>2.11215472221375</v>
+        <v>2.11215448379517</v>
       </c>
       <c r="H852" t="n">
         <v>10500</v>
@@ -25193,7 +25193,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H856" t="n">
         <v>2250</v>
@@ -25222,7 +25222,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660841464996</v>
+        <v>1.95660853385925</v>
       </c>
       <c r="H857" t="n">
         <v>9750</v>
@@ -25280,7 +25280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935496807098</v>
+        <v>1.98935508728027</v>
       </c>
       <c r="H859" t="n">
         <v>53250</v>
@@ -25367,7 +25367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204832077026</v>
+        <v>1.93204808235168</v>
       </c>
       <c r="H862" t="n">
         <v>27000</v>
@@ -25396,7 +25396,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G863" t="n">
-        <v>1.96479487419128</v>
+        <v>1.96479511260986</v>
       </c>
       <c r="H863" t="n">
         <v>4500</v>
@@ -25541,7 +25541,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111506938934</v>
+        <v>1.89111518859863</v>
       </c>
       <c r="H868" t="n">
         <v>11250</v>
@@ -25773,7 +25773,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G876" t="n">
-        <v>2.05484819412231</v>
+        <v>2.05484795570374</v>
       </c>
       <c r="H876" t="n">
         <v>54750</v>
@@ -26411,7 +26411,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H898" t="n">
         <v>10500</v>
@@ -26614,7 +26614,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26643,7 +26643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H906" t="n">
         <v>750</v>
@@ -26672,7 +26672,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H907" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.91285216808319</v>
+        <v>1.9128520488739</v>
       </c>
       <c r="H908" t="n">
         <v>21000</v>
@@ -26817,7 +26817,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869393825531</v>
+        <v>1.87869381904602</v>
       </c>
       <c r="H912" t="n">
         <v>3000</v>
@@ -27078,7 +27078,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H921" t="n">
         <v>6750</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H925" t="n">
         <v>8250</v>
@@ -27252,7 +27252,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G927" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H927" t="n">
         <v>2250</v>
@@ -27310,7 +27310,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H929" t="n">
         <v>6750</v>
@@ -27426,7 +27426,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H933" t="n">
         <v>20250</v>
@@ -27455,7 +27455,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H934" t="n">
         <v>12000</v>
@@ -27571,7 +27571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H938" t="n">
         <v>14250</v>
@@ -27716,7 +27716,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H943" t="n">
         <v>2250</v>
@@ -27745,7 +27745,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H944" t="n">
         <v>750</v>
@@ -27774,7 +27774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H945" t="n">
         <v>1500</v>
@@ -27803,7 +27803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408903598785</v>
+        <v>1.96408915519714</v>
       </c>
       <c r="H948" t="n">
         <v>2250</v>
@@ -27890,7 +27890,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G949" t="n">
-        <v>1.98116815090179</v>
+        <v>1.98116827011108</v>
       </c>
       <c r="H949" t="n">
         <v>9000</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.91285216808319</v>
+        <v>1.9128520488739</v>
       </c>
       <c r="H951" t="n">
         <v>10500</v>
@@ -27977,7 +27977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993128299713</v>
+        <v>1.92993116378784</v>
       </c>
       <c r="H952" t="n">
         <v>9750</v>
@@ -28006,7 +28006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869393825531</v>
+        <v>1.87869381904602</v>
       </c>
       <c r="H953" t="n">
         <v>3000</v>
@@ -28209,7 +28209,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H960" t="n">
         <v>30750</v>
@@ -28238,7 +28238,7 @@
         <v>2</v>
       </c>
       <c r="G961" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H961" t="n">
         <v>28500</v>
@@ -28354,7 +28354,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H965" t="n">
         <v>3750</v>
@@ -28470,7 +28470,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H969" t="n">
         <v>3750</v>
@@ -28499,7 +28499,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.84453594684601</v>
+        <v>1.8445360660553</v>
       </c>
       <c r="H970" t="n">
         <v>2250</v>
@@ -28528,7 +28528,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G971" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H971" t="n">
         <v>2250</v>
@@ -28557,7 +28557,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G972" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H972" t="n">
         <v>0</v>
@@ -28586,7 +28586,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G973" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H973" t="n">
         <v>0</v>
@@ -28760,7 +28760,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H979" t="n">
         <v>2250</v>
@@ -28847,7 +28847,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G982" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H982" t="n">
         <v>9000</v>
@@ -28876,7 +28876,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -28934,7 +28934,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G985" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H985" t="n">
         <v>4500</v>
@@ -28963,7 +28963,7 @@
         <v>2</v>
       </c>
       <c r="G986" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H986" t="n">
         <v>8250</v>
@@ -28992,7 +28992,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G987" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H987" t="n">
         <v>52500</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.58835029602051</v>
+        <v>1.5883504152298</v>
       </c>
       <c r="H989" t="n">
         <v>18000</v>
@@ -29108,7 +29108,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G991" t="n">
-        <v>1.40048098564148</v>
+        <v>1.40048086643219</v>
       </c>
       <c r="H991" t="n">
         <v>120750</v>
@@ -29369,7 +29369,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1000" t="n">
         <v>16500</v>
@@ -29746,7 +29746,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1013" t="n">
         <v>8250</v>
@@ -29949,7 +29949,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1020" t="n">
         <v>24750</v>
@@ -29978,7 +29978,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1021" t="n">
         <v>4500</v>
@@ -30297,7 +30297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1032" t="n">
         <v>4500</v>
@@ -30355,7 +30355,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1034" t="n">
-        <v>1.34070444107056</v>
+        <v>1.34070432186127</v>
       </c>
       <c r="H1034" t="n">
         <v>28500</v>
@@ -30442,7 +30442,7 @@
         <v>1.57000005245209</v>
       </c>
       <c r="G1037" t="n">
-        <v>1.34070444107056</v>
+        <v>1.34070432186127</v>
       </c>
       <c r="H1037" t="n">
         <v>27000</v>
@@ -30471,7 +30471,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1038" t="n">
         <v>23250</v>
@@ -30500,7 +30500,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1039" t="n">
         <v>12000</v>
@@ -30529,7 +30529,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1040" t="n">
         <v>750</v>
@@ -30558,7 +30558,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.31508576869965</v>
+        <v>1.31508564949036</v>
       </c>
       <c r="H1041" t="n">
         <v>6750</v>
@@ -30790,7 +30790,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1049" t="n">
         <v>9000</v>
@@ -30906,7 +30906,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1053" t="n">
         <v>3750</v>
@@ -30993,7 +30993,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1056" t="n">
         <v>18000</v>
@@ -31080,7 +31080,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1059" t="n">
         <v>99750</v>
@@ -31109,7 +31109,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1060" t="n">
         <v>4500</v>
@@ -31138,7 +31138,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1061" t="n">
         <v>5250</v>
@@ -31167,7 +31167,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.40048098564148</v>
+        <v>1.40048086643219</v>
       </c>
       <c r="H1064" t="n">
         <v>8250</v>
@@ -31631,7 +31631,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1078" t="n">
         <v>2250</v>
@@ -31660,7 +31660,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1079" t="n">
         <v>2250</v>
@@ -31689,7 +31689,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.43463909626007</v>
+        <v>1.43463897705078</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -31805,7 +31805,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1084" t="n">
         <v>19500</v>
@@ -31863,7 +31863,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1086" t="n">
         <v>3000</v>
@@ -31892,7 +31892,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.36632287502289</v>
+        <v>1.36632299423218</v>
       </c>
       <c r="H1087" t="n">
         <v>6000</v>
@@ -31979,7 +31979,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.4260995388031</v>
+        <v>1.42609941959381</v>
       </c>
       <c r="H1090" t="n">
         <v>15750</v>
@@ -32124,7 +32124,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.58835029602051</v>
+        <v>1.5883504152298</v>
       </c>
       <c r="H1095" t="n">
         <v>20250</v>
@@ -32153,7 +32153,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1096" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1096" t="n">
         <v>23250</v>
@@ -32182,7 +32182,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.48587620258331</v>
+        <v>1.48587608337402</v>
       </c>
       <c r="H1097" t="n">
         <v>9750</v>
@@ -32211,7 +32211,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1098" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1098" t="n">
         <v>12750</v>
@@ -32356,7 +32356,7 @@
         <v>1.77999997138977</v>
       </c>
       <c r="G1103" t="n">
-        <v>1.5200343132019</v>
+        <v>1.52003419399261</v>
       </c>
       <c r="H1103" t="n">
         <v>12000</v>
@@ -32472,7 +32472,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G1107" t="n">
-        <v>1.51149475574493</v>
+        <v>1.51149463653564</v>
       </c>
       <c r="H1107" t="n">
         <v>6750</v>
@@ -32559,7 +32559,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1110" t="n">
-        <v>1.63958728313446</v>
+        <v>1.63958740234375</v>
       </c>
       <c r="H1110" t="n">
         <v>45000</v>
@@ -32617,7 +32617,7 @@
         <v>2</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1112" t="n">
         <v>37500</v>
@@ -32646,7 +32646,7 @@
         <v>2</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1113" t="n">
         <v>2250</v>
@@ -32762,7 +32762,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H1117" t="n">
         <v>3000</v>
@@ -32791,7 +32791,7 @@
         <v>2</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1118" t="n">
         <v>32250</v>
@@ -32849,7 +32849,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1120" t="n">
-        <v>1.79329872131348</v>
+        <v>1.79329860210419</v>
       </c>
       <c r="H1120" t="n">
         <v>9750</v>
@@ -32878,7 +32878,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H1121" t="n">
         <v>3000</v>
@@ -32907,7 +32907,7 @@
         <v>2</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1122" t="n">
         <v>1500</v>
@@ -32936,7 +32936,7 @@
         <v>2</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1123" t="n">
         <v>750</v>
@@ -32965,7 +32965,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1124" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1124" t="n">
         <v>35250</v>
@@ -32994,7 +32994,7 @@
         <v>2</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1125" t="n">
         <v>27750</v>
@@ -33023,7 +33023,7 @@
         <v>2</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1126" t="n">
         <v>82500</v>
@@ -33052,7 +33052,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.67374551296234</v>
+        <v>1.67374563217163</v>
       </c>
       <c r="H1127" t="n">
         <v>1500</v>
@@ -33081,7 +33081,7 @@
         <v>2</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1128" t="n">
         <v>19500</v>
@@ -33110,7 +33110,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.75914061069489</v>
+        <v>1.75914072990417</v>
       </c>
       <c r="H1129" t="n">
         <v>3000</v>
@@ -33139,7 +33139,7 @@
         <v>2</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1130" t="n">
         <v>12750</v>
@@ -33255,7 +33255,7 @@
         <v>2</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1134" t="n">
         <v>2250</v>
@@ -33284,7 +33284,7 @@
         <v>2</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33313,7 +33313,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1136" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1136" t="n">
         <v>3750</v>
@@ -33342,7 +33342,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G1137" t="n">
-        <v>1.72498250007629</v>
+        <v>1.72498261928558</v>
       </c>
       <c r="H1137" t="n">
         <v>0</v>
@@ -33429,7 +33429,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1140" t="n">
-        <v>1.64812684059143</v>
+        <v>1.64812695980072</v>
       </c>
       <c r="H1140" t="n">
         <v>8250</v>
@@ -33632,7 +33632,7 @@
         <v>1.91999995708466</v>
       </c>
       <c r="G1147" t="n">
-        <v>1.63958728313446</v>
+        <v>1.63958740234375</v>
       </c>
       <c r="H1147" t="n">
         <v>9750</v>
@@ -33748,7 +33748,7 @@
         <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1151" t="n">
         <v>18000</v>
@@ -33777,7 +33777,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1152" t="n">
         <v>122250</v>
@@ -34705,7 +34705,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1184" t="n">
         <v>84000</v>
@@ -34792,7 +34792,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1187" t="n">
         <v>18000</v>
@@ -34879,7 +34879,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1190" t="n">
         <v>57000</v>
@@ -34908,7 +34908,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1191" t="n">
         <v>43500</v>
@@ -34937,7 +34937,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1192" t="n">
         <v>75750</v>
@@ -34966,7 +34966,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.06746244430542</v>
+        <v>2.06746220588684</v>
       </c>
       <c r="H1193" t="n">
         <v>28500</v>
@@ -34995,7 +34995,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.99555063247681</v>
+        <v>1.99555051326752</v>
       </c>
       <c r="H1194" t="n">
         <v>24000</v>
@@ -35024,7 +35024,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1195" t="n">
         <v>12000</v>
@@ -35053,7 +35053,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1196" t="n">
         <v>12000</v>
@@ -35082,7 +35082,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1197" t="n">
         <v>2250</v>
@@ -35111,7 +35111,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1198" t="n">
         <v>30000</v>
@@ -35140,7 +35140,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1199" t="n">
         <v>3750</v>
@@ -35169,7 +35169,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.97757256031036</v>
+        <v>1.97757267951965</v>
       </c>
       <c r="H1200" t="n">
         <v>0</v>
@@ -35198,7 +35198,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1201" t="n">
         <v>750</v>
@@ -35227,7 +35227,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1202" t="n">
         <v>6000</v>
@@ -35256,7 +35256,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1203" t="n">
         <v>9000</v>
@@ -35314,7 +35314,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1205" t="n">
         <v>21000</v>
@@ -35343,7 +35343,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1206" t="n">
         <v>24750</v>
@@ -35372,7 +35372,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1207" t="n">
         <v>3750</v>
@@ -35401,7 +35401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1208" t="n">
         <v>3750</v>
@@ -35981,7 +35981,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1228" t="n">
         <v>12750</v>
@@ -36010,7 +36010,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1229" t="n">
         <v>9750</v>
@@ -36126,7 +36126,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1233" t="n">
         <v>1500</v>
@@ -36155,7 +36155,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1234" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1242" t="n">
         <v>27000</v>
@@ -36445,7 +36445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1244" t="n">
         <v>2250</v>
@@ -36561,7 +36561,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1248" t="n">
         <v>3000</v>
@@ -36764,7 +36764,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1255" t="n">
         <v>7500</v>
@@ -36793,7 +36793,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1256" t="n">
         <v>11250</v>
@@ -36851,7 +36851,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1258" t="n">
         <v>20250</v>
@@ -36938,7 +36938,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1261" t="n">
         <v>12750</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1263" t="n">
         <v>32250</v>
@@ -37402,7 +37402,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1277" t="n">
         <v>5250</v>
@@ -37431,7 +37431,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1278" t="n">
         <v>4500</v>
@@ -37518,7 +37518,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1281" t="n">
         <v>6000</v>
@@ -37576,7 +37576,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1283" t="n">
         <v>2250</v>
@@ -37605,7 +37605,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1284" t="n">
         <v>8250</v>
@@ -37779,7 +37779,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1290" t="n">
         <v>14250</v>
@@ -37837,7 +37837,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1292" t="n">
         <v>750</v>
@@ -37866,7 +37866,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1293" t="n">
         <v>750</v>
@@ -37895,7 +37895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1294" t="n">
         <v>0</v>
@@ -37953,7 +37953,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1296" t="n">
         <v>4500</v>
@@ -37982,7 +37982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1297" t="n">
         <v>3000</v>
@@ -38040,7 +38040,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1299" t="n">
         <v>7500</v>
@@ -38069,7 +38069,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1300" t="n">
         <v>3000</v>
@@ -38098,7 +38098,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1301" t="n">
         <v>6750</v>
@@ -38127,7 +38127,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.70790362358093</v>
+        <v>1.70790350437164</v>
       </c>
       <c r="H1302" t="n">
         <v>6000</v>
@@ -38359,7 +38359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.78880429267883</v>
+        <v>1.78880441188812</v>
       </c>
       <c r="H1310" t="n">
         <v>7500</v>
@@ -39229,7 +39229,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1340" t="n">
         <v>5250</v>
@@ -39258,7 +39258,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1341" t="n">
         <v>2250</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1342" t="n">
         <v>12000</v>
@@ -39316,7 +39316,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1343" t="n">
         <v>13500</v>
@@ -39345,7 +39345,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.73487055301666</v>
+        <v>1.73487043380737</v>
       </c>
       <c r="H1344" t="n">
         <v>5250</v>
@@ -39403,7 +39403,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1346" t="n">
         <v>6000</v>
@@ -39432,7 +39432,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.71689248085022</v>
+        <v>1.71689260005951</v>
       </c>
       <c r="H1347" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1367" t="n">
         <v>2250</v>
@@ -40041,7 +40041,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1368" t="n">
         <v>42750</v>
@@ -40070,7 +40070,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1369" t="n">
         <v>4500</v>
@@ -40099,7 +40099,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1370" t="n">
         <v>0</v>
@@ -40128,7 +40128,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1371" t="n">
         <v>1500</v>
@@ -40244,7 +40244,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1375" t="n">
         <v>750</v>
@@ -40273,7 +40273,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1376" t="n">
         <v>0</v>
@@ -40360,7 +40360,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1379" t="n">
         <v>5250</v>
@@ -40389,7 +40389,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.03150629997253</v>
+        <v>2.03150653839111</v>
       </c>
       <c r="H1380" t="n">
         <v>114750</v>
@@ -40418,7 +40418,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1381" t="n">
         <v>12750</v>
@@ -40447,7 +40447,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1382" t="n">
         <v>4500</v>
@@ -40476,7 +40476,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1383" t="n">
         <v>1500</v>
@@ -40505,7 +40505,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1384" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1386" t="n">
         <v>15000</v>
@@ -40592,7 +40592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.94161677360535</v>
+        <v>1.94161689281464</v>
       </c>
       <c r="H1387" t="n">
         <v>3000</v>
@@ -40621,7 +40621,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.8876827955246</v>
+        <v>1.88768291473389</v>
       </c>
       <c r="H1388" t="n">
         <v>2250</v>
@@ -40650,7 +40650,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1389" t="n">
         <v>1500</v>
@@ -40679,7 +40679,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.92363882064819</v>
+        <v>1.92363905906677</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.90566086769104</v>
+        <v>1.90566062927246</v>
       </c>
       <c r="H1391" t="n">
         <v>1500</v>
@@ -40737,7 +40737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.03150629997253</v>
+        <v>2.03150653839111</v>
       </c>
       <c r="H1392" t="n">
         <v>60750</v>
@@ -40766,7 +40766,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.01352858543396</v>
+        <v>2.01352834701538</v>
       </c>
       <c r="H1393" t="n">
         <v>5250</v>
@@ -40795,7 +40795,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.01352858543396</v>
+        <v>2.01352834701538</v>
       </c>
       <c r="H1394" t="n">
         <v>13500</v>
@@ -40824,7 +40824,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1395" t="n">
         <v>11250</v>
@@ -40853,7 +40853,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.04948425292969</v>
+        <v>2.04948449134827</v>
       </c>
       <c r="H1396" t="n">
         <v>21000</v>
@@ -40911,7 +40911,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1398" t="n">
         <v>15750</v>
@@ -40969,7 +40969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1400" t="n">
         <v>22500</v>
@@ -41027,7 +41027,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.1213960647583</v>
+        <v>2.12139582633972</v>
       </c>
       <c r="H1402" t="n">
         <v>9000</v>
@@ -52024,6 +52024,35 @@
         <v>4500</v>
       </c>
       <c r="I1781" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1782">
+      <c r="A1782" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1782" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1782" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="D1782" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="E1782" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="F1782" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="G1782" t="n">
+        <v>2.98000001907349</v>
+      </c>
+      <c r="H1782" t="n">
+        <v>3750</v>
+      </c>
+      <c r="I1782" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/ARBS.MI.xlsx
+++ b/data/ARBS.MI.xlsx
@@ -427,7 +427,7 @@
         <v>3.41149997711182</v>
       </c>
       <c r="G2" t="n">
-        <v>2.73189401626587</v>
+        <v>2.73189425468445</v>
       </c>
       <c r="H2" t="n">
         <v>893250</v>
@@ -456,7 +456,7 @@
         <v>3.58049988746643</v>
       </c>
       <c r="G3" t="n">
-        <v>2.86722779273987</v>
+        <v>2.86722755432129</v>
       </c>
       <c r="H3" t="n">
         <v>428250</v>
@@ -485,7 +485,7 @@
         <v>3.50550007820129</v>
       </c>
       <c r="G4" t="n">
-        <v>2.80716848373413</v>
+        <v>2.80716872215271</v>
       </c>
       <c r="H4" t="n">
         <v>86250</v>
@@ -630,7 +630,7 @@
         <v>3.43549990653992</v>
       </c>
       <c r="G9" t="n">
-        <v>2.75111293792725</v>
+        <v>2.75111317634583</v>
       </c>
       <c r="H9" t="n">
         <v>62250</v>
@@ -746,7 +746,7 @@
         <v>3.36450004577637</v>
       </c>
       <c r="G13" t="n">
-        <v>2.69425702095032</v>
+        <v>2.6942572593689</v>
       </c>
       <c r="H13" t="n">
         <v>14250</v>
@@ -775,7 +775,7 @@
         <v>3.39949989318848</v>
       </c>
       <c r="G14" t="n">
-        <v>2.72228455543518</v>
+        <v>2.72228479385376</v>
       </c>
       <c r="H14" t="n">
         <v>7500</v>
@@ -804,7 +804,7 @@
         <v>3.37150001525879</v>
       </c>
       <c r="G15" t="n">
-        <v>2.69986295700073</v>
+        <v>2.69986271858215</v>
       </c>
       <c r="H15" t="n">
         <v>21750</v>
@@ -833,7 +833,7 @@
         <v>3.43449997901917</v>
       </c>
       <c r="G16" t="n">
-        <v>2.7503125667572</v>
+        <v>2.75031232833862</v>
       </c>
       <c r="H16" t="n">
         <v>44250</v>
@@ -891,7 +891,7 @@
         <v>4.53999996185303</v>
       </c>
       <c r="G18" t="n">
-        <v>3.63558530807495</v>
+        <v>3.63558578491211</v>
       </c>
       <c r="H18" t="n">
         <v>196500</v>
@@ -949,7 +949,7 @@
         <v>4.78999996185303</v>
       </c>
       <c r="G20" t="n">
-        <v>3.83578276634216</v>
+        <v>3.83578300476074</v>
       </c>
       <c r="H20" t="n">
         <v>495750</v>
@@ -978,7 +978,7 @@
         <v>4.5019998550415</v>
       </c>
       <c r="G21" t="n">
-        <v>3.60515546798706</v>
+        <v>3.60515570640564</v>
       </c>
       <c r="H21" t="n">
         <v>81000</v>
@@ -1036,7 +1036,7 @@
         <v>4.38600015640259</v>
       </c>
       <c r="G23" t="n">
-        <v>3.51226377487183</v>
+        <v>3.51226425170898</v>
       </c>
       <c r="H23" t="n">
         <v>94500</v>
@@ -1094,7 +1094,7 @@
         <v>4.3600001335144</v>
       </c>
       <c r="G25" t="n">
-        <v>3.49144387245178</v>
+        <v>3.4914436340332</v>
       </c>
       <c r="H25" t="n">
         <v>20250</v>
@@ -1123,7 +1123,7 @@
         <v>4.38350009918213</v>
       </c>
       <c r="G26" t="n">
-        <v>3.51026248931885</v>
+        <v>3.51026225090027</v>
       </c>
       <c r="H26" t="n">
         <v>24750</v>
@@ -1152,7 +1152,7 @@
         <v>4.24350023269653</v>
       </c>
       <c r="G27" t="n">
-        <v>3.39815187454224</v>
+        <v>3.39815163612366</v>
       </c>
       <c r="H27" t="n">
         <v>19500</v>
@@ -1210,7 +1210,7 @@
         <v>4.20050001144409</v>
       </c>
       <c r="G29" t="n">
-        <v>3.36371755599976</v>
+        <v>3.36371731758118</v>
       </c>
       <c r="H29" t="n">
         <v>12750</v>
@@ -1239,7 +1239,7 @@
         <v>4.15999984741211</v>
       </c>
       <c r="G30" t="n">
-        <v>3.33128547668457</v>
+        <v>3.33128523826599</v>
       </c>
       <c r="H30" t="n">
         <v>9000</v>
@@ -1268,7 +1268,7 @@
         <v>4.15899991989136</v>
       </c>
       <c r="G31" t="n">
-        <v>3.33048462867737</v>
+        <v>3.33048439025879</v>
       </c>
       <c r="H31" t="n">
         <v>6750</v>
@@ -1297,7 +1297,7 @@
         <v>4.10500001907349</v>
       </c>
       <c r="G32" t="n">
-        <v>3.28724193572998</v>
+        <v>3.28724217414856</v>
       </c>
       <c r="H32" t="n">
         <v>2250</v>
@@ -1413,7 +1413,7 @@
         <v>3.71000003814697</v>
       </c>
       <c r="G36" t="n">
-        <v>2.9709300994873</v>
+        <v>2.97093033790588</v>
       </c>
       <c r="H36" t="n">
         <v>16500</v>
@@ -1442,7 +1442,7 @@
         <v>3.75</v>
       </c>
       <c r="G37" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H37" t="n">
         <v>750</v>
@@ -1529,7 +1529,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G40" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H40" t="n">
         <v>3000</v>
@@ -1790,7 +1790,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G49" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H49" t="n">
         <v>7500</v>
@@ -1819,7 +1819,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G50" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H50" t="n">
         <v>4500</v>
@@ -1848,7 +1848,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G51" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H51" t="n">
         <v>750</v>
@@ -1877,7 +1877,7 @@
         <v>3.84999990463257</v>
       </c>
       <c r="G52" t="n">
-        <v>3.08304047584534</v>
+        <v>3.08304071426392</v>
       </c>
       <c r="H52" t="n">
         <v>29250</v>
@@ -1935,7 +1935,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G54" t="n">
-        <v>3.07903647422791</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H54" t="n">
         <v>13500</v>
@@ -1993,7 +1993,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G56" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H56" t="n">
         <v>18750</v>
@@ -2051,7 +2051,7 @@
         <v>3.75</v>
       </c>
       <c r="G58" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H58" t="n">
         <v>3000</v>
@@ -2109,7 +2109,7 @@
         <v>3.75</v>
       </c>
       <c r="G60" t="n">
-        <v>3.0029616355896</v>
+        <v>3.00296187400818</v>
       </c>
       <c r="H60" t="n">
         <v>1500</v>
@@ -2138,7 +2138,7 @@
         <v>3.89000010490417</v>
       </c>
       <c r="G61" t="n">
-        <v>3.11507248878479</v>
+        <v>3.11507225036621</v>
       </c>
       <c r="H61" t="n">
         <v>5250</v>
@@ -2167,7 +2167,7 @@
         <v>3.86500000953674</v>
       </c>
       <c r="G62" t="n">
-        <v>3.09505271911621</v>
+        <v>3.09505248069763</v>
       </c>
       <c r="H62" t="n">
         <v>4500</v>
@@ -2225,7 +2225,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G64" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H64" t="n">
         <v>1500</v>
@@ -2254,7 +2254,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G65" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H65" t="n">
         <v>9750</v>
@@ -2341,7 +2341,7 @@
         <v>3.54999995231628</v>
       </c>
       <c r="G68" t="n">
-        <v>2.84280395507812</v>
+        <v>2.84280347824097</v>
       </c>
       <c r="H68" t="n">
         <v>8250</v>
@@ -2370,7 +2370,7 @@
         <v>3.5</v>
       </c>
       <c r="G69" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H69" t="n">
         <v>9000</v>
@@ -2428,7 +2428,7 @@
         <v>3.5</v>
       </c>
       <c r="G71" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H71" t="n">
         <v>750</v>
@@ -2457,7 +2457,7 @@
         <v>3.4300000667572</v>
       </c>
       <c r="G72" t="n">
-        <v>2.74670910835266</v>
+        <v>2.74670886993408</v>
       </c>
       <c r="H72" t="n">
         <v>6750</v>
@@ -2515,7 +2515,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G74" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H74" t="n">
         <v>15000</v>
@@ -2602,7 +2602,7 @@
         <v>3.84500002861023</v>
       </c>
       <c r="G77" t="n">
-        <v>3.07903647422791</v>
+        <v>3.07903671264648</v>
       </c>
       <c r="H77" t="n">
         <v>26250</v>
@@ -2689,7 +2689,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G80" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H80" t="n">
         <v>9750</v>
@@ -2718,7 +2718,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G81" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H81" t="n">
         <v>3000</v>
@@ -2747,7 +2747,7 @@
         <v>3.63499999046326</v>
       </c>
       <c r="G82" t="n">
-        <v>2.91087079048157</v>
+        <v>2.91087102890015</v>
       </c>
       <c r="H82" t="n">
         <v>7500</v>
@@ -2863,7 +2863,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G86" t="n">
-        <v>2.69866156578064</v>
+        <v>2.69866132736206</v>
       </c>
       <c r="H86" t="n">
         <v>7500</v>
@@ -2892,7 +2892,7 @@
         <v>3.23499989509583</v>
       </c>
       <c r="G87" t="n">
-        <v>2.59055471420288</v>
+        <v>2.59055495262146</v>
       </c>
       <c r="H87" t="n">
         <v>14250</v>
@@ -2921,7 +2921,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G88" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H88" t="n">
         <v>3750</v>
@@ -2979,7 +2979,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G90" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H90" t="n">
         <v>10500</v>
@@ -3037,7 +3037,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G92" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H92" t="n">
         <v>16500</v>
@@ -3066,7 +3066,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G93" t="n">
-        <v>2.00998258590698</v>
+        <v>2.0099823474884</v>
       </c>
       <c r="H93" t="n">
         <v>9750</v>
@@ -3095,7 +3095,7 @@
         <v>2.34999990463257</v>
       </c>
       <c r="G94" t="n">
-        <v>1.88185596466064</v>
+        <v>1.88185584545135</v>
       </c>
       <c r="H94" t="n">
         <v>4500</v>
@@ -3124,7 +3124,7 @@
         <v>1.97000002861023</v>
       </c>
       <c r="G95" t="n">
-        <v>1.57755601406097</v>
+        <v>1.57755589485168</v>
       </c>
       <c r="H95" t="n">
         <v>9000</v>
@@ -3153,7 +3153,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G96" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H96" t="n">
         <v>14250</v>
@@ -3240,7 +3240,7 @@
         <v>1.98000001907349</v>
       </c>
       <c r="G99" t="n">
-        <v>1.58556365966797</v>
+        <v>1.58556377887726</v>
       </c>
       <c r="H99" t="n">
         <v>14250</v>
@@ -3269,7 +3269,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G100" t="n">
-        <v>1.64161884784698</v>
+        <v>1.64161908626556</v>
       </c>
       <c r="H100" t="n">
         <v>3000</v>
@@ -3327,7 +3327,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G102" t="n">
-        <v>1.677654504776</v>
+        <v>1.67765462398529</v>
       </c>
       <c r="H102" t="n">
         <v>11250</v>
@@ -3356,7 +3356,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G103" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H103" t="n">
         <v>12000</v>
@@ -3414,7 +3414,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G105" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H105" t="n">
         <v>6750</v>
@@ -3472,7 +3472,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G107" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H107" t="n">
         <v>750</v>
@@ -3501,7 +3501,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G108" t="n">
-        <v>1.89787149429321</v>
+        <v>1.89787185192108</v>
       </c>
       <c r="H108" t="n">
         <v>15750</v>
@@ -3530,7 +3530,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G109" t="n">
-        <v>2.08205342292786</v>
+        <v>2.08205318450928</v>
       </c>
       <c r="H109" t="n">
         <v>8250</v>
@@ -3588,7 +3588,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G111" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H111" t="n">
         <v>28500</v>
@@ -3617,7 +3617,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G112" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H112" t="n">
         <v>15000</v>
@@ -3646,7 +3646,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G113" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H113" t="n">
         <v>28500</v>
@@ -3675,7 +3675,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G114" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H114" t="n">
         <v>10500</v>
@@ -3704,7 +3704,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G115" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H115" t="n">
         <v>9000</v>
@@ -3791,7 +3791,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G118" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H118" t="n">
         <v>6000</v>
@@ -3820,7 +3820,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G119" t="n">
-        <v>2.79475617408752</v>
+        <v>2.79475665092468</v>
       </c>
       <c r="H119" t="n">
         <v>8250</v>
@@ -3849,7 +3849,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G120" t="n">
-        <v>2.68664979934692</v>
+        <v>2.68664956092834</v>
       </c>
       <c r="H120" t="n">
         <v>11250</v>
@@ -3994,7 +3994,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G125" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H125" t="n">
         <v>4500</v>
@@ -4052,7 +4052,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G127" t="n">
-        <v>2.79475617408752</v>
+        <v>2.79475665092468</v>
       </c>
       <c r="H127" t="n">
         <v>2250</v>
@@ -4081,7 +4081,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G128" t="n">
-        <v>2.78674840927124</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H128" t="n">
         <v>3000</v>
@@ -4110,7 +4110,7 @@
         <v>3.48000001907349</v>
       </c>
       <c r="G129" t="n">
-        <v>2.78674840927124</v>
+        <v>2.78674817085266</v>
       </c>
       <c r="H129" t="n">
         <v>0</v>
@@ -4342,7 +4342,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G137" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H137" t="n">
         <v>750</v>
@@ -4371,7 +4371,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G138" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H138" t="n">
         <v>0</v>
@@ -4400,7 +4400,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G139" t="n">
-        <v>2.59856295585632</v>
+        <v>2.59856271743774</v>
       </c>
       <c r="H139" t="n">
         <v>1500</v>
@@ -4429,7 +4429,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G140" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H140" t="n">
         <v>3750</v>
@@ -4458,7 +4458,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G141" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H141" t="n">
         <v>2250</v>
@@ -4487,7 +4487,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G142" t="n">
-        <v>2.44240856170654</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H142" t="n">
         <v>750</v>
@@ -4516,7 +4516,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G143" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H143" t="n">
         <v>1500</v>
@@ -4545,7 +4545,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G144" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H144" t="n">
         <v>1500</v>
@@ -4574,7 +4574,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G145" t="n">
-        <v>2.54651117324829</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H145" t="n">
         <v>3000</v>
@@ -4603,7 +4603,7 @@
         <v>3.39499998092651</v>
       </c>
       <c r="G146" t="n">
-        <v>2.7186815738678</v>
+        <v>2.71868109703064</v>
       </c>
       <c r="H146" t="n">
         <v>3000</v>
@@ -4632,7 +4632,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G147" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H147" t="n">
         <v>5250</v>
@@ -4777,7 +4777,7 @@
         <v>3.38499999046326</v>
       </c>
       <c r="G152" t="n">
-        <v>2.71067333221436</v>
+        <v>2.71067357063293</v>
       </c>
       <c r="H152" t="n">
         <v>750</v>
@@ -4835,7 +4835,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G154" t="n">
-        <v>2.63459849357605</v>
+        <v>2.63459801673889</v>
       </c>
       <c r="H154" t="n">
         <v>9000</v>
@@ -4922,7 +4922,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G157" t="n">
-        <v>2.76272463798523</v>
+        <v>2.76272487640381</v>
       </c>
       <c r="H157" t="n">
         <v>11250</v>
@@ -4951,7 +4951,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G158" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H158" t="n">
         <v>7500</v>
@@ -4980,7 +4980,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G159" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H159" t="n">
         <v>0</v>
@@ -5009,7 +5009,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G160" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H160" t="n">
         <v>0</v>
@@ -5038,7 +5038,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G161" t="n">
-        <v>2.54651117324829</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H161" t="n">
         <v>14250</v>
@@ -5067,7 +5067,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G162" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H162" t="n">
         <v>6750</v>
@@ -5096,7 +5096,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G163" t="n">
-        <v>2.50647211074829</v>
+        <v>2.50647234916687</v>
       </c>
       <c r="H163" t="n">
         <v>6750</v>
@@ -5125,7 +5125,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G164" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H164" t="n">
         <v>750</v>
@@ -5154,7 +5154,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G165" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H165" t="n">
         <v>0</v>
@@ -5183,7 +5183,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G166" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H166" t="n">
         <v>6750</v>
@@ -5299,7 +5299,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G170" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H170" t="n">
         <v>18000</v>
@@ -5328,7 +5328,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G171" t="n">
-        <v>2.37434148788452</v>
+        <v>2.37434124946594</v>
       </c>
       <c r="H171" t="n">
         <v>3000</v>
@@ -5386,7 +5386,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G173" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H173" t="n">
         <v>2250</v>
@@ -5415,7 +5415,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G174" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H174" t="n">
         <v>0</v>
@@ -5444,7 +5444,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G175" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -5473,7 +5473,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G176" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5502,7 +5502,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G177" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H177" t="n">
         <v>3750</v>
@@ -5531,7 +5531,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G178" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5560,7 +5560,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G179" t="n">
-        <v>2.44240856170654</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H179" t="n">
         <v>2250</v>
@@ -5647,7 +5647,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G182" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H182" t="n">
         <v>750</v>
@@ -5937,7 +5937,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G192" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826688766479</v>
       </c>
       <c r="H192" t="n">
         <v>3000</v>
@@ -5966,7 +5966,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G193" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826688766479</v>
       </c>
       <c r="H193" t="n">
         <v>0</v>
@@ -5995,7 +5995,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G194" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826688766479</v>
       </c>
       <c r="H194" t="n">
         <v>0</v>
@@ -6024,7 +6024,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G195" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826688766479</v>
       </c>
       <c r="H195" t="n">
         <v>0</v>
@@ -6082,7 +6082,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G197" t="n">
-        <v>2.61858248710632</v>
+        <v>2.6185827255249</v>
       </c>
       <c r="H197" t="n">
         <v>139500</v>
@@ -6111,7 +6111,7 @@
         <v>3.80999994277954</v>
       </c>
       <c r="G198" t="n">
-        <v>3.0510094165802</v>
+        <v>3.05100917816162</v>
       </c>
       <c r="H198" t="n">
         <v>203250</v>
@@ -6140,7 +6140,7 @@
         <v>3.5</v>
       </c>
       <c r="G199" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H199" t="n">
         <v>148500</v>
@@ -6169,7 +6169,7 @@
         <v>3.51999998092651</v>
       </c>
       <c r="G200" t="n">
-        <v>2.81877994537354</v>
+        <v>2.81878018379211</v>
       </c>
       <c r="H200" t="n">
         <v>47250</v>
@@ -6314,7 +6314,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G205" t="n">
-        <v>2.55451917648315</v>
+        <v>2.55451941490173</v>
       </c>
       <c r="H205" t="n">
         <v>13500</v>
@@ -6343,7 +6343,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G206" t="n">
-        <v>2.62258696556091</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H206" t="n">
         <v>8250</v>
@@ -6372,7 +6372,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G207" t="n">
-        <v>2.62258696556091</v>
+        <v>2.62258648872375</v>
       </c>
       <c r="H207" t="n">
         <v>0</v>
@@ -6401,7 +6401,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G208" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H208" t="n">
         <v>18000</v>
@@ -6430,7 +6430,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G209" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H209" t="n">
         <v>2250</v>
@@ -6459,7 +6459,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G210" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H210" t="n">
         <v>3750</v>
@@ -6488,7 +6488,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G211" t="n">
-        <v>2.48244833946228</v>
+        <v>2.4824481010437</v>
       </c>
       <c r="H211" t="n">
         <v>2250</v>
@@ -6517,7 +6517,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G212" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H212" t="n">
         <v>2250</v>
@@ -6546,7 +6546,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G213" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H213" t="n">
         <v>10500</v>
@@ -6575,7 +6575,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G214" t="n">
-        <v>2.44240856170654</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H214" t="n">
         <v>8250</v>
@@ -6604,7 +6604,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G215" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H215" t="n">
         <v>5250</v>
@@ -6633,7 +6633,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G216" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H216" t="n">
         <v>9000</v>
@@ -6662,7 +6662,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G217" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H217" t="n">
         <v>11250</v>
@@ -6749,7 +6749,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G220" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H220" t="n">
         <v>750</v>
@@ -6778,7 +6778,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G221" t="n">
-        <v>2.44240856170654</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H221" t="n">
         <v>1500</v>
@@ -6807,7 +6807,7 @@
         <v>3.11500000953674</v>
       </c>
       <c r="G222" t="n">
-        <v>2.494460105896</v>
+        <v>2.49445986747742</v>
       </c>
       <c r="H222" t="n">
         <v>6750</v>
@@ -6836,7 +6836,7 @@
         <v>3.1800000667572</v>
       </c>
       <c r="G223" t="n">
-        <v>2.54651117324829</v>
+        <v>2.54651165008545</v>
       </c>
       <c r="H223" t="n">
         <v>5250</v>
@@ -6894,7 +6894,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G225" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H225" t="n">
         <v>5250</v>
@@ -6923,7 +6923,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G226" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H226" t="n">
         <v>3000</v>
@@ -6952,7 +6952,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G227" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H227" t="n">
         <v>0</v>
@@ -6981,7 +6981,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G228" t="n">
-        <v>2.42238879203796</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H228" t="n">
         <v>15750</v>
@@ -7068,7 +7068,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G231" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H231" t="n">
         <v>3000</v>
@@ -7097,7 +7097,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G232" t="n">
-        <v>2.34631419181824</v>
+        <v>2.34631395339966</v>
       </c>
       <c r="H232" t="n">
         <v>6000</v>
@@ -7155,7 +7155,7 @@
         <v>2.96499991416931</v>
       </c>
       <c r="G234" t="n">
-        <v>2.37434148788452</v>
+        <v>2.37434124946594</v>
       </c>
       <c r="H234" t="n">
         <v>2250</v>
@@ -7184,7 +7184,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G235" t="n">
-        <v>2.31428241729736</v>
+        <v>2.31428217887878</v>
       </c>
       <c r="H235" t="n">
         <v>4500</v>
@@ -7532,7 +7532,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G247" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H247" t="n">
         <v>1500</v>
@@ -7561,7 +7561,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G248" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826688766479</v>
       </c>
       <c r="H248" t="n">
         <v>1500</v>
@@ -7590,7 +7590,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G249" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826688766479</v>
       </c>
       <c r="H249" t="n">
         <v>0</v>
@@ -7619,7 +7619,7 @@
         <v>2.99499988555908</v>
       </c>
       <c r="G250" t="n">
-        <v>2.39836525917053</v>
+        <v>2.39836502075195</v>
       </c>
       <c r="H250" t="n">
         <v>3000</v>
@@ -7648,7 +7648,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G251" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H251" t="n">
         <v>750</v>
@@ -7677,7 +7677,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G252" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H252" t="n">
         <v>0</v>
@@ -7793,7 +7793,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G256" t="n">
-        <v>2.29826641082764</v>
+        <v>2.29826688766479</v>
       </c>
       <c r="H256" t="n">
         <v>7500</v>
@@ -7822,7 +7822,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G257" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H257" t="n">
         <v>1500</v>
@@ -7909,7 +7909,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G260" t="n">
-        <v>2.21418356895447</v>
+        <v>2.21418404579163</v>
       </c>
       <c r="H260" t="n">
         <v>3000</v>
@@ -7938,7 +7938,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G261" t="n">
-        <v>2.21418356895447</v>
+        <v>2.21418404579163</v>
       </c>
       <c r="H261" t="n">
         <v>0</v>
@@ -7996,7 +7996,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G263" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H263" t="n">
         <v>750</v>
@@ -8025,7 +8025,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G264" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21017980575562</v>
       </c>
       <c r="H264" t="n">
         <v>3000</v>
@@ -8054,7 +8054,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G265" t="n">
-        <v>2.1861560344696</v>
+        <v>2.18615627288818</v>
       </c>
       <c r="H265" t="n">
         <v>1500</v>
@@ -8112,7 +8112,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G267" t="n">
-        <v>2.23820734024048</v>
+        <v>2.23820757865906</v>
       </c>
       <c r="H267" t="n">
         <v>2250</v>
@@ -8141,7 +8141,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G268" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H268" t="n">
         <v>4500</v>
@@ -8199,7 +8199,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G270" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H270" t="n">
         <v>750</v>
@@ -8228,7 +8228,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G271" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H271" t="n">
         <v>6000</v>
@@ -8257,7 +8257,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G272" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H272" t="n">
         <v>2250</v>
@@ -8286,7 +8286,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G273" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H273" t="n">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G274" t="n">
-        <v>2.37834572792053</v>
+        <v>2.37834548950195</v>
       </c>
       <c r="H274" t="n">
         <v>3750</v>
@@ -8344,7 +8344,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G275" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H275" t="n">
         <v>12000</v>
@@ -8373,7 +8373,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G276" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H276" t="n">
         <v>3000</v>
@@ -8402,7 +8402,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G277" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H277" t="n">
         <v>0</v>
@@ -8431,7 +8431,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G278" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H278" t="n">
         <v>3000</v>
@@ -8460,7 +8460,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G279" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H279" t="n">
         <v>0</v>
@@ -8489,7 +8489,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G280" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H280" t="n">
         <v>0</v>
@@ -8518,7 +8518,7 @@
         <v>3.00999999046326</v>
       </c>
       <c r="G281" t="n">
-        <v>2.41037750244141</v>
+        <v>2.41037726402283</v>
       </c>
       <c r="H281" t="n">
         <v>0</v>
@@ -8547,7 +8547,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G282" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H282" t="n">
         <v>3750</v>
@@ -8576,7 +8576,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G283" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H283" t="n">
         <v>0</v>
@@ -8605,7 +8605,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G284" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H284" t="n">
         <v>0</v>
@@ -8750,7 +8750,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G289" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H289" t="n">
         <v>750</v>
@@ -8779,7 +8779,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G290" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H290" t="n">
         <v>750</v>
@@ -8808,7 +8808,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G291" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H291" t="n">
         <v>0</v>
@@ -8837,7 +8837,7 @@
         <v>2.85500001907349</v>
       </c>
       <c r="G292" t="n">
-        <v>2.28625512123108</v>
+        <v>2.28625464439392</v>
       </c>
       <c r="H292" t="n">
         <v>3000</v>
@@ -8895,7 +8895,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G294" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21017980575562</v>
       </c>
       <c r="H294" t="n">
         <v>750</v>
@@ -9040,7 +9040,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G299" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H299" t="n">
         <v>3000</v>
@@ -9069,7 +9069,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G300" t="n">
-        <v>2.28225088119507</v>
+        <v>2.28225064277649</v>
       </c>
       <c r="H300" t="n">
         <v>750</v>
@@ -9098,7 +9098,7 @@
         <v>2.75</v>
       </c>
       <c r="G301" t="n">
-        <v>2.20217204093933</v>
+        <v>2.20217180252075</v>
       </c>
       <c r="H301" t="n">
         <v>9000</v>
@@ -9243,7 +9243,7 @@
         <v>3.25500011444092</v>
       </c>
       <c r="G306" t="n">
-        <v>2.60657095909119</v>
+        <v>2.60657072067261</v>
       </c>
       <c r="H306" t="n">
         <v>45000</v>
@@ -9272,7 +9272,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G307" t="n">
-        <v>2.51047611236572</v>
+        <v>2.51047587394714</v>
       </c>
       <c r="H307" t="n">
         <v>32250</v>
@@ -9301,7 +9301,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G308" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H308" t="n">
         <v>6750</v>
@@ -9330,7 +9330,7 @@
         <v>3.03500008583069</v>
       </c>
       <c r="G309" t="n">
-        <v>2.43039679527283</v>
+        <v>2.43039703369141</v>
       </c>
       <c r="H309" t="n">
         <v>17250</v>
@@ -9388,7 +9388,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G311" t="n">
-        <v>2.44240856170654</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H311" t="n">
         <v>5250</v>
@@ -9417,7 +9417,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G312" t="n">
-        <v>2.49045634269714</v>
+        <v>2.49045610427856</v>
       </c>
       <c r="H312" t="n">
         <v>5250</v>
@@ -9475,7 +9475,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G314" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H314" t="n">
         <v>1500</v>
@@ -9504,7 +9504,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G315" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H315" t="n">
         <v>0</v>
@@ -9562,7 +9562,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G317" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H317" t="n">
         <v>3750</v>
@@ -9591,7 +9591,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G318" t="n">
-        <v>2.36232972145081</v>
+        <v>2.36232995986938</v>
       </c>
       <c r="H318" t="n">
         <v>0</v>
@@ -9620,7 +9620,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G319" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H319" t="n">
         <v>3750</v>
@@ -9649,7 +9649,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G320" t="n">
-        <v>2.33430194854736</v>
+        <v>2.33430218696594</v>
       </c>
       <c r="H320" t="n">
         <v>750</v>
@@ -9852,7 +9852,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G327" t="n">
-        <v>2.41438126564026</v>
+        <v>2.41438150405884</v>
       </c>
       <c r="H327" t="n">
         <v>2250</v>
@@ -9881,7 +9881,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G328" t="n">
-        <v>2.44240856170654</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H328" t="n">
         <v>9750</v>
@@ -9910,7 +9910,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G329" t="n">
-        <v>2.46643233299255</v>
+        <v>2.46643257141113</v>
       </c>
       <c r="H329" t="n">
         <v>2250</v>
@@ -9939,7 +9939,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G330" t="n">
-        <v>2.52248787879944</v>
+        <v>2.52248764038086</v>
       </c>
       <c r="H330" t="n">
         <v>18750</v>
@@ -9997,7 +9997,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G332" t="n">
-        <v>2.44240856170654</v>
+        <v>2.4424090385437</v>
       </c>
       <c r="H332" t="n">
         <v>4500</v>
@@ -10055,7 +10055,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G334" t="n">
-        <v>2.42238879203796</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H334" t="n">
         <v>2250</v>
@@ -10142,7 +10142,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G337" t="n">
-        <v>2.43840503692627</v>
+        <v>2.43840479850769</v>
       </c>
       <c r="H337" t="n">
         <v>3750</v>
@@ -10171,7 +10171,7 @@
         <v>3.00500011444092</v>
       </c>
       <c r="G338" t="n">
-        <v>2.40637350082397</v>
+        <v>2.4063732624054</v>
       </c>
       <c r="H338" t="n">
         <v>1500</v>
@@ -10229,7 +10229,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G340" t="n">
-        <v>2.50647211074829</v>
+        <v>2.50647234916687</v>
       </c>
       <c r="H340" t="n">
         <v>29250</v>
@@ -10258,7 +10258,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G341" t="n">
-        <v>2.42238879203796</v>
+        <v>2.42238926887512</v>
       </c>
       <c r="H341" t="n">
         <v>20250</v>
@@ -10287,7 +10287,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G342" t="n">
-        <v>2.42639303207397</v>
+        <v>2.4263927936554</v>
       </c>
       <c r="H342" t="n">
         <v>1500</v>
@@ -10374,7 +10374,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G345" t="n">
-        <v>2.5505154132843</v>
+        <v>2.55051493644714</v>
       </c>
       <c r="H345" t="n">
         <v>26250</v>
@@ -10403,7 +10403,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G346" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H346" t="n">
         <v>54000</v>
@@ -10577,7 +10577,7 @@
         <v>3.19000005722046</v>
       </c>
       <c r="G352" t="n">
-        <v>2.55451917648315</v>
+        <v>2.55451941490173</v>
       </c>
       <c r="H352" t="n">
         <v>4500</v>
@@ -10635,7 +10635,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G354" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H354" t="n">
         <v>4500</v>
@@ -10693,7 +10693,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G356" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H356" t="n">
         <v>5250</v>
@@ -10751,7 +10751,7 @@
         <v>3.375</v>
       </c>
       <c r="G358" t="n">
-        <v>2.70266556739807</v>
+        <v>2.70266580581665</v>
       </c>
       <c r="H358" t="n">
         <v>13500</v>
@@ -10780,7 +10780,7 @@
         <v>3.26999998092651</v>
       </c>
       <c r="G359" t="n">
-        <v>2.61858248710632</v>
+        <v>2.6185827255249</v>
       </c>
       <c r="H359" t="n">
         <v>10500</v>
@@ -10838,7 +10838,7 @@
         <v>3.46499991416931</v>
       </c>
       <c r="G361" t="n">
-        <v>2.77473664283752</v>
+        <v>2.77473640441895</v>
       </c>
       <c r="H361" t="n">
         <v>13500</v>
@@ -10867,7 +10867,7 @@
         <v>3.38000011444092</v>
       </c>
       <c r="G362" t="n">
-        <v>2.70666933059692</v>
+        <v>2.7066695690155</v>
       </c>
       <c r="H362" t="n">
         <v>15750</v>
@@ -10983,7 +10983,7 @@
         <v>3.5</v>
       </c>
       <c r="G366" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H366" t="n">
         <v>25500</v>
@@ -11041,7 +11041,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G368" t="n">
-        <v>3.26722240447998</v>
+        <v>3.2672221660614</v>
       </c>
       <c r="H368" t="n">
         <v>210750</v>
@@ -11157,7 +11157,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G372" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H372" t="n">
         <v>36000</v>
@@ -11215,7 +11215,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G374" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H374" t="n">
         <v>20250</v>
@@ -11244,7 +11244,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G375" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H375" t="n">
         <v>3750</v>
@@ -11331,7 +11331,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G378" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H378" t="n">
         <v>6000</v>
@@ -11418,7 +11418,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G381" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H381" t="n">
         <v>5250</v>
@@ -11447,7 +11447,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G382" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H382" t="n">
         <v>1500</v>
@@ -11505,7 +11505,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G384" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H384" t="n">
         <v>19500</v>
@@ -11534,7 +11534,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G385" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H385" t="n">
         <v>22500</v>
@@ -11737,7 +11737,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G392" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H392" t="n">
         <v>5250</v>
@@ -11766,7 +11766,7 @@
         <v>3.96000003814697</v>
       </c>
       <c r="G393" t="n">
-        <v>3.17112731933594</v>
+        <v>3.17112755775452</v>
       </c>
       <c r="H393" t="n">
         <v>23250</v>
@@ -11795,7 +11795,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G394" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H394" t="n">
         <v>5250</v>
@@ -11824,7 +11824,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G395" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H395" t="n">
         <v>3000</v>
@@ -11853,7 +11853,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G396" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H396" t="n">
         <v>0</v>
@@ -11882,7 +11882,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G397" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H397" t="n">
         <v>750</v>
@@ -11911,7 +11911,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G398" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H398" t="n">
         <v>10500</v>
@@ -11998,7 +11998,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G401" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H401" t="n">
         <v>8250</v>
@@ -12056,7 +12056,7 @@
         <v>4.07999992370605</v>
       </c>
       <c r="G403" t="n">
-        <v>3.26722240447998</v>
+        <v>3.2672221660614</v>
       </c>
       <c r="H403" t="n">
         <v>38250</v>
@@ -12085,7 +12085,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G404" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H404" t="n">
         <v>21000</v>
@@ -12143,7 +12143,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G406" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H406" t="n">
         <v>72750</v>
@@ -12172,7 +12172,7 @@
         <v>4.1399998664856</v>
       </c>
       <c r="G407" t="n">
-        <v>3.31526947021484</v>
+        <v>3.31526970863342</v>
       </c>
       <c r="H407" t="n">
         <v>13500</v>
@@ -12201,7 +12201,7 @@
         <v>4.17999982833862</v>
       </c>
       <c r="G408" t="n">
-        <v>3.34730100631714</v>
+        <v>3.34730124473572</v>
       </c>
       <c r="H408" t="n">
         <v>10500</v>
@@ -12230,7 +12230,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G409" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H409" t="n">
         <v>12750</v>
@@ -12259,7 +12259,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G410" t="n">
-        <v>3.15511202812195</v>
+        <v>3.15511178970337</v>
       </c>
       <c r="H410" t="n">
         <v>10500</v>
@@ -12317,7 +12317,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G412" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H412" t="n">
         <v>3000</v>
@@ -12346,7 +12346,7 @@
         <v>4.01999998092651</v>
       </c>
       <c r="G413" t="n">
-        <v>3.21917510032654</v>
+        <v>3.21917486190796</v>
       </c>
       <c r="H413" t="n">
         <v>5250</v>
@@ -12433,7 +12433,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G416" t="n">
-        <v>3.15511202812195</v>
+        <v>3.15511178970337</v>
       </c>
       <c r="H416" t="n">
         <v>3750</v>
@@ -12491,7 +12491,7 @@
         <v>3.88000011444092</v>
       </c>
       <c r="G418" t="n">
-        <v>3.10706424713135</v>
+        <v>3.10706448554993</v>
       </c>
       <c r="H418" t="n">
         <v>8250</v>
@@ -12694,7 +12694,7 @@
         <v>3.94000005722046</v>
       </c>
       <c r="G425" t="n">
-        <v>3.15511202812195</v>
+        <v>3.15511178970337</v>
       </c>
       <c r="H425" t="n">
         <v>1500</v>
@@ -12839,7 +12839,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G430" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H430" t="n">
         <v>7500</v>
@@ -12868,7 +12868,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G431" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H431" t="n">
         <v>9000</v>
@@ -12926,7 +12926,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G433" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H433" t="n">
         <v>1500</v>
@@ -13013,7 +13013,7 @@
         <v>3.8199999332428</v>
       </c>
       <c r="G436" t="n">
-        <v>3.05901718139648</v>
+        <v>3.05901694297791</v>
       </c>
       <c r="H436" t="n">
         <v>4500</v>
@@ -13216,7 +13216,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G443" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H443" t="n">
         <v>3000</v>
@@ -13245,7 +13245,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G444" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H444" t="n">
         <v>4500</v>
@@ -13274,7 +13274,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G445" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H445" t="n">
         <v>3000</v>
@@ -13303,7 +13303,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G446" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H446" t="n">
         <v>0</v>
@@ -13332,7 +13332,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G447" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H447" t="n">
         <v>750</v>
@@ -13361,7 +13361,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G448" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H448" t="n">
         <v>0</v>
@@ -13390,7 +13390,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G449" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H449" t="n">
         <v>2250</v>
@@ -13535,7 +13535,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G454" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H454" t="n">
         <v>1500</v>
@@ -13564,7 +13564,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G455" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H455" t="n">
         <v>2250</v>
@@ -13622,7 +13622,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G457" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H457" t="n">
         <v>3000</v>
@@ -13680,7 +13680,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G459" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H459" t="n">
         <v>750</v>
@@ -13825,7 +13825,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G464" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H464" t="n">
         <v>4500</v>
@@ -13854,7 +13854,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G465" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H465" t="n">
         <v>0</v>
@@ -13883,7 +13883,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G466" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H466" t="n">
         <v>9750</v>
@@ -14028,7 +14028,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G471" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H471" t="n">
         <v>6750</v>
@@ -14057,7 +14057,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G472" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H472" t="n">
         <v>750</v>
@@ -14115,7 +14115,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G474" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H474" t="n">
         <v>6750</v>
@@ -14144,7 +14144,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G475" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H475" t="n">
         <v>3000</v>
@@ -14173,7 +14173,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G476" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H476" t="n">
         <v>1500</v>
@@ -14202,7 +14202,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G477" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H477" t="n">
         <v>6000</v>
@@ -14231,7 +14231,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G478" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H478" t="n">
         <v>2250</v>
@@ -14347,7 +14347,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G482" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H482" t="n">
         <v>750</v>
@@ -14434,7 +14434,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G485" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H485" t="n">
         <v>750</v>
@@ -14463,7 +14463,7 @@
         <v>3.70000004768372</v>
       </c>
       <c r="G486" t="n">
-        <v>2.96292209625244</v>
+        <v>2.96292233467102</v>
       </c>
       <c r="H486" t="n">
         <v>0</v>
@@ -14521,7 +14521,7 @@
         <v>3.77999997138977</v>
       </c>
       <c r="G488" t="n">
-        <v>3.02698516845703</v>
+        <v>3.02698540687561</v>
       </c>
       <c r="H488" t="n">
         <v>750</v>
@@ -14550,7 +14550,7 @@
         <v>3.75999999046326</v>
       </c>
       <c r="G489" t="n">
-        <v>3.01096963882446</v>
+        <v>3.01096940040588</v>
       </c>
       <c r="H489" t="n">
         <v>3750</v>
@@ -14695,7 +14695,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G494" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H494" t="n">
         <v>2250</v>
@@ -14869,7 +14869,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G500" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H500" t="n">
         <v>1500</v>
@@ -14898,7 +14898,7 @@
         <v>3.66000008583069</v>
       </c>
       <c r="G501" t="n">
-        <v>2.93089079856873</v>
+        <v>2.93089056015015</v>
       </c>
       <c r="H501" t="n">
         <v>0</v>
@@ -15072,7 +15072,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G507" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H507" t="n">
         <v>3000</v>
@@ -15101,7 +15101,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G508" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H508" t="n">
         <v>4500</v>
@@ -15275,7 +15275,7 @@
         <v>3.61999988555908</v>
       </c>
       <c r="G514" t="n">
-        <v>2.89885902404785</v>
+        <v>2.89885878562927</v>
       </c>
       <c r="H514" t="n">
         <v>5250</v>
@@ -15362,7 +15362,7 @@
         <v>3.5</v>
       </c>
       <c r="G517" t="n">
-        <v>2.80276441574097</v>
+        <v>2.80276417732239</v>
       </c>
       <c r="H517" t="n">
         <v>6750</v>
@@ -15507,7 +15507,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G522" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H522" t="n">
         <v>9750</v>
@@ -15536,7 +15536,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G523" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H523" t="n">
         <v>6000</v>
@@ -15565,7 +15565,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G524" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H524" t="n">
         <v>0</v>
@@ -15594,7 +15594,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G525" t="n">
-        <v>2.72268557548523</v>
+        <v>2.72268533706665</v>
       </c>
       <c r="H525" t="n">
         <v>8250</v>
@@ -15623,7 +15623,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G526" t="n">
-        <v>2.59455919265747</v>
+        <v>2.59455895423889</v>
       </c>
       <c r="H526" t="n">
         <v>17250</v>
@@ -15652,7 +15652,7 @@
         <v>3.22000002861023</v>
       </c>
       <c r="G527" t="n">
-        <v>2.57854318618774</v>
+        <v>2.57854294776917</v>
       </c>
       <c r="H527" t="n">
         <v>12000</v>
@@ -15768,7 +15768,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G531" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H531" t="n">
         <v>3000</v>
@@ -15797,7 +15797,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G532" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H532" t="n">
         <v>4500</v>
@@ -16000,7 +16000,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G539" t="n">
-        <v>2.45041656494141</v>
+        <v>2.45041680335999</v>
       </c>
       <c r="H539" t="n">
         <v>24750</v>
@@ -16058,7 +16058,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G541" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H541" t="n">
         <v>3750</v>
@@ -16145,7 +16145,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G544" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H544" t="n">
         <v>750</v>
@@ -16232,7 +16232,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G547" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H547" t="n">
         <v>6750</v>
@@ -16435,7 +16435,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G554" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H554" t="n">
         <v>1500</v>
@@ -16464,7 +16464,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G555" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H555" t="n">
         <v>6000</v>
@@ -16493,7 +16493,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G556" t="n">
-        <v>2.33830595016479</v>
+        <v>2.33830618858337</v>
       </c>
       <c r="H556" t="n">
         <v>3750</v>
@@ -16609,7 +16609,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G560" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H560" t="n">
         <v>1500</v>
@@ -16696,7 +16696,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G563" t="n">
-        <v>2.3863537311554</v>
+        <v>2.38635349273682</v>
       </c>
       <c r="H563" t="n">
         <v>3000</v>
@@ -16841,7 +16841,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G568" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H568" t="n">
         <v>6750</v>
@@ -16870,7 +16870,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G569" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H569" t="n">
         <v>7500</v>
@@ -16899,7 +16899,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G570" t="n">
-        <v>2.32229065895081</v>
+        <v>2.32229042053223</v>
       </c>
       <c r="H570" t="n">
         <v>750</v>
@@ -17102,7 +17102,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G577" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H577" t="n">
         <v>12750</v>
@@ -17131,7 +17131,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G578" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H578" t="n">
         <v>1500</v>
@@ -17160,7 +17160,7 @@
         <v>2.79999995231628</v>
       </c>
       <c r="G579" t="n">
-        <v>2.24221134185791</v>
+        <v>2.24221158027649</v>
       </c>
       <c r="H579" t="n">
         <v>6000</v>
@@ -17189,7 +17189,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G580" t="n">
-        <v>2.21017956733704</v>
+        <v>2.21017980575562</v>
       </c>
       <c r="H580" t="n">
         <v>3750</v>
@@ -17218,7 +17218,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G581" t="n">
-        <v>2.16213274002075</v>
+        <v>2.16213226318359</v>
       </c>
       <c r="H581" t="n">
         <v>15750</v>
@@ -17247,7 +17247,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G582" t="n">
-        <v>2.09806895256042</v>
+        <v>2.098069190979</v>
       </c>
       <c r="H582" t="n">
         <v>18000</v>
@@ -17276,7 +17276,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G583" t="n">
-        <v>2.09806895256042</v>
+        <v>2.098069190979</v>
       </c>
       <c r="H583" t="n">
         <v>15750</v>
@@ -17305,7 +17305,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G584" t="n">
-        <v>2.09806895256042</v>
+        <v>2.098069190979</v>
       </c>
       <c r="H584" t="n">
         <v>4500</v>
@@ -17334,7 +17334,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G585" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H585" t="n">
         <v>6000</v>
@@ -17392,7 +17392,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G587" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H587" t="n">
         <v>3000</v>
@@ -17421,7 +17421,7 @@
         <v>2.72000002861023</v>
       </c>
       <c r="G588" t="n">
-        <v>2.1781485080719</v>
+        <v>2.17814803123474</v>
       </c>
       <c r="H588" t="n">
         <v>8250</v>
@@ -17450,7 +17450,7 @@
         <v>2.66000008583069</v>
       </c>
       <c r="G589" t="n">
-        <v>2.1301007270813</v>
+        <v>2.13010096549988</v>
       </c>
       <c r="H589" t="n">
         <v>3000</v>
@@ -17479,7 +17479,7 @@
         <v>2.64000010490417</v>
       </c>
       <c r="G590" t="n">
-        <v>2.11408519744873</v>
+        <v>2.11408495903015</v>
       </c>
       <c r="H590" t="n">
         <v>10500</v>
@@ -17508,7 +17508,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G591" t="n">
-        <v>2.05002164840698</v>
+        <v>2.05002188682556</v>
       </c>
       <c r="H591" t="n">
         <v>11250</v>
@@ -17653,7 +17653,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G596" t="n">
-        <v>1.88986361026764</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H596" t="n">
         <v>6000</v>
@@ -17682,7 +17682,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G597" t="n">
-        <v>1.90587961673737</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H597" t="n">
         <v>7500</v>
@@ -17885,7 +17885,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G604" t="n">
-        <v>1.63361120223999</v>
+        <v>1.6336110830307</v>
       </c>
       <c r="H604" t="n">
         <v>1500</v>
@@ -17914,7 +17914,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G605" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H605" t="n">
         <v>3750</v>
@@ -18001,7 +18001,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G608" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H608" t="n">
         <v>11250</v>
@@ -18059,7 +18059,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G610" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H610" t="n">
         <v>5250</v>
@@ -18117,7 +18117,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G612" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H612" t="n">
         <v>1500</v>
@@ -18146,7 +18146,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G613" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H613" t="n">
         <v>4500</v>
@@ -18262,7 +18262,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G617" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H617" t="n">
         <v>5250</v>
@@ -18291,7 +18291,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G618" t="n">
-        <v>1.79376912117004</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H618" t="n">
         <v>10500</v>
@@ -18320,7 +18320,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G619" t="n">
-        <v>1.90587961673737</v>
+        <v>1.90587985515594</v>
       </c>
       <c r="H619" t="n">
         <v>75000</v>
@@ -18349,7 +18349,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G620" t="n">
-        <v>1.88986361026764</v>
+        <v>1.88986384868622</v>
       </c>
       <c r="H620" t="n">
         <v>8250</v>
@@ -18407,7 +18407,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G622" t="n">
-        <v>1.80978488922119</v>
+        <v>1.8097847700119</v>
       </c>
       <c r="H622" t="n">
         <v>48750</v>
@@ -18465,7 +18465,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G624" t="n">
-        <v>1.66564273834229</v>
+        <v>1.665642619133</v>
       </c>
       <c r="H624" t="n">
         <v>174750</v>
@@ -18494,7 +18494,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G625" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H625" t="n">
         <v>23250</v>
@@ -18523,7 +18523,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G626" t="n">
-        <v>1.7216979265213</v>
+        <v>1.72169816493988</v>
       </c>
       <c r="H626" t="n">
         <v>40500</v>
@@ -18610,7 +18610,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G629" t="n">
-        <v>1.79376912117004</v>
+        <v>1.79376924037933</v>
       </c>
       <c r="H629" t="n">
         <v>18750</v>
@@ -18639,7 +18639,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G630" t="n">
-        <v>1.76173734664917</v>
+        <v>1.76173758506775</v>
       </c>
       <c r="H630" t="n">
         <v>14250</v>
@@ -18668,7 +18668,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G631" t="n">
-        <v>1.7216979265213</v>
+        <v>1.72169816493988</v>
       </c>
       <c r="H631" t="n">
         <v>5250</v>
@@ -18697,7 +18697,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G632" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H632" t="n">
         <v>2250</v>
@@ -18726,7 +18726,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G633" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H633" t="n">
         <v>750</v>
@@ -18755,7 +18755,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G634" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H634" t="n">
         <v>0</v>
@@ -18784,7 +18784,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G635" t="n">
-        <v>1.74572193622589</v>
+        <v>1.7457218170166</v>
       </c>
       <c r="H635" t="n">
         <v>5250</v>
@@ -18842,7 +18842,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G637" t="n">
-        <v>1.73771393299103</v>
+        <v>1.73771369457245</v>
       </c>
       <c r="H637" t="n">
         <v>7500</v>
@@ -18871,7 +18871,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G638" t="n">
-        <v>1.68165850639343</v>
+        <v>1.68165838718414</v>
       </c>
       <c r="H638" t="n">
         <v>18000</v>
@@ -18900,7 +18900,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G639" t="n">
-        <v>1.70568215847015</v>
+        <v>1.70568227767944</v>
       </c>
       <c r="H639" t="n">
         <v>15750</v>
@@ -18929,7 +18929,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G640" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779289245605</v>
       </c>
       <c r="H640" t="n">
         <v>17250</v>
@@ -18958,7 +18958,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G641" t="n">
-        <v>1.81779265403748</v>
+        <v>1.81779289245605</v>
       </c>
       <c r="H641" t="n">
         <v>167250</v>
@@ -19016,7 +19016,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G643" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380854129791</v>
       </c>
       <c r="H643" t="n">
         <v>15000</v>
@@ -19103,7 +19103,7 @@
         <v>2.25</v>
       </c>
       <c r="G646" t="n">
-        <v>1.8419953584671</v>
+        <v>1.84199523925781</v>
       </c>
       <c r="H646" t="n">
         <v>12750</v>
@@ -19132,7 +19132,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G647" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H647" t="n">
         <v>11250</v>
@@ -19161,7 +19161,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G648" t="n">
-        <v>1.89111518859863</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H648" t="n">
         <v>47250</v>
@@ -19190,7 +19190,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G649" t="n">
-        <v>1.85018193721771</v>
+        <v>1.85018181800842</v>
       </c>
       <c r="H649" t="n">
         <v>5250</v>
@@ -19219,7 +19219,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G650" t="n">
-        <v>1.8010618686676</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H650" t="n">
         <v>12000</v>
@@ -19248,7 +19248,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G651" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H651" t="n">
         <v>33750</v>
@@ -19277,7 +19277,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G652" t="n">
-        <v>1.85836827754974</v>
+        <v>1.85836863517761</v>
       </c>
       <c r="H652" t="n">
         <v>3000</v>
@@ -19306,7 +19306,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G653" t="n">
-        <v>1.85836827754974</v>
+        <v>1.85836863517761</v>
       </c>
       <c r="H653" t="n">
         <v>4500</v>
@@ -19364,7 +19364,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G655" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H655" t="n">
         <v>1500</v>
@@ -19393,7 +19393,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G656" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H656" t="n">
         <v>3000</v>
@@ -19422,7 +19422,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G657" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H657" t="n">
         <v>0</v>
@@ -19480,7 +19480,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G659" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H659" t="n">
         <v>7500</v>
@@ -19538,7 +19538,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G661" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H661" t="n">
         <v>1500</v>
@@ -19567,7 +19567,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G662" t="n">
-        <v>1.87474191188812</v>
+        <v>1.87474179267883</v>
       </c>
       <c r="H662" t="n">
         <v>7500</v>
@@ -19596,7 +19596,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G663" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H663" t="n">
         <v>21750</v>
@@ -19625,7 +19625,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G664" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H664" t="n">
         <v>6750</v>
@@ -19654,7 +19654,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G665" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H665" t="n">
         <v>15750</v>
@@ -19683,7 +19683,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G666" t="n">
-        <v>1.8256219625473</v>
+        <v>1.82562172412872</v>
       </c>
       <c r="H666" t="n">
         <v>4500</v>
@@ -19712,7 +19712,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G667" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H667" t="n">
         <v>5250</v>
@@ -19741,7 +19741,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G668" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H668" t="n">
         <v>10500</v>
@@ -19799,7 +19799,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G670" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H670" t="n">
         <v>15750</v>
@@ -19828,7 +19828,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G671" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H671" t="n">
         <v>3750</v>
@@ -19973,7 +19973,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G676" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H676" t="n">
         <v>750</v>
@@ -20002,7 +20002,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G677" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H677" t="n">
         <v>0</v>
@@ -20031,7 +20031,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G678" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H678" t="n">
         <v>0</v>
@@ -20089,7 +20089,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G680" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H680" t="n">
         <v>750</v>
@@ -20118,7 +20118,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G681" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H681" t="n">
         <v>750</v>
@@ -20147,7 +20147,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G682" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H682" t="n">
         <v>1500</v>
@@ -20321,7 +20321,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G688" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H688" t="n">
         <v>19500</v>
@@ -20350,7 +20350,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G689" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H689" t="n">
         <v>6750</v>
@@ -20524,7 +20524,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G695" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H695" t="n">
         <v>750</v>
@@ -20582,7 +20582,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G697" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H697" t="n">
         <v>4500</v>
@@ -20611,7 +20611,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G698" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H698" t="n">
         <v>0</v>
@@ -20640,7 +20640,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G699" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H699" t="n">
         <v>1500</v>
@@ -20669,7 +20669,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G700" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H700" t="n">
         <v>0</v>
@@ -20698,7 +20698,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G701" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H701" t="n">
         <v>750</v>
@@ -20756,7 +20756,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G703" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H703" t="n">
         <v>2250</v>
@@ -20814,7 +20814,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G705" t="n">
-        <v>1.71100878715515</v>
+        <v>1.71100890636444</v>
       </c>
       <c r="H705" t="n">
         <v>750</v>
@@ -20843,7 +20843,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G706" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H706" t="n">
         <v>750</v>
@@ -20872,7 +20872,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G707" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H707" t="n">
         <v>2250</v>
@@ -20901,7 +20901,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G708" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H708" t="n">
         <v>0</v>
@@ -20930,7 +20930,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G709" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H709" t="n">
         <v>0</v>
@@ -20959,7 +20959,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G710" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H710" t="n">
         <v>15000</v>
@@ -20988,7 +20988,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G711" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H711" t="n">
         <v>0</v>
@@ -21075,7 +21075,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G714" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H714" t="n">
         <v>4500</v>
@@ -21104,7 +21104,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G715" t="n">
-        <v>1.79287552833557</v>
+        <v>1.79287540912628</v>
       </c>
       <c r="H715" t="n">
         <v>3000</v>
@@ -21162,7 +21162,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G717" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H717" t="n">
         <v>7500</v>
@@ -21191,7 +21191,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G718" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H718" t="n">
         <v>2250</v>
@@ -21220,7 +21220,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G719" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H719" t="n">
         <v>0</v>
@@ -21249,7 +21249,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G720" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H720" t="n">
         <v>3000</v>
@@ -21278,7 +21278,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G721" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H721" t="n">
         <v>0</v>
@@ -21365,7 +21365,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G724" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H724" t="n">
         <v>1500</v>
@@ -21568,7 +21568,7 @@
         <v>2</v>
       </c>
       <c r="G731" t="n">
-        <v>1.63732898235321</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H731" t="n">
         <v>3000</v>
@@ -21771,7 +21771,7 @@
         <v>1.88499999046326</v>
       </c>
       <c r="G738" t="n">
-        <v>1.54318273067474</v>
+        <v>1.54318261146545</v>
       </c>
       <c r="H738" t="n">
         <v>12750</v>
@@ -21800,7 +21800,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G739" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H739" t="n">
         <v>11250</v>
@@ -21858,7 +21858,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G741" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H741" t="n">
         <v>2250</v>
@@ -21887,7 +21887,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G742" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H742" t="n">
         <v>7500</v>
@@ -21916,7 +21916,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G743" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H743" t="n">
         <v>0</v>
@@ -22003,7 +22003,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G746" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H746" t="n">
         <v>6000</v>
@@ -22061,7 +22061,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G748" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H748" t="n">
         <v>10500</v>
@@ -22119,7 +22119,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G750" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H750" t="n">
         <v>750</v>
@@ -22148,7 +22148,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G751" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H751" t="n">
         <v>4500</v>
@@ -22206,7 +22206,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G753" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H753" t="n">
         <v>2250</v>
@@ -22235,7 +22235,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G754" t="n">
-        <v>1.50634276866913</v>
+        <v>1.50634288787842</v>
       </c>
       <c r="H754" t="n">
         <v>0</v>
@@ -22322,7 +22322,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G757" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H757" t="n">
         <v>79500</v>
@@ -22409,7 +22409,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G760" t="n">
-        <v>1.60458266735077</v>
+        <v>1.60458254814148</v>
       </c>
       <c r="H760" t="n">
         <v>3750</v>
@@ -22438,7 +22438,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G761" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H761" t="n">
         <v>6000</v>
@@ -22467,7 +22467,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G762" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H762" t="n">
         <v>0</v>
@@ -22496,7 +22496,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G763" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H763" t="n">
         <v>3750</v>
@@ -22525,7 +22525,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G764" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H764" t="n">
         <v>0</v>
@@ -22554,7 +22554,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G765" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H765" t="n">
         <v>0</v>
@@ -22583,7 +22583,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G766" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H766" t="n">
         <v>0</v>
@@ -22612,7 +22612,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G767" t="n">
-        <v>1.53908944129944</v>
+        <v>1.53908932209015</v>
       </c>
       <c r="H767" t="n">
         <v>0</v>
@@ -22670,7 +22670,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G769" t="n">
-        <v>1.52271616458893</v>
+        <v>1.52271604537964</v>
       </c>
       <c r="H769" t="n">
         <v>3750</v>
@@ -22699,7 +22699,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G770" t="n">
-        <v>1.52271616458893</v>
+        <v>1.52271604537964</v>
       </c>
       <c r="H770" t="n">
         <v>3750</v>
@@ -22815,7 +22815,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G774" t="n">
-        <v>1.55546259880066</v>
+        <v>1.55546271800995</v>
       </c>
       <c r="H774" t="n">
         <v>2250</v>
@@ -22844,7 +22844,7 @@
         <v>1.88999998569489</v>
       </c>
       <c r="G775" t="n">
-        <v>1.54727590084076</v>
+        <v>1.54727602005005</v>
       </c>
       <c r="H775" t="n">
         <v>4500</v>
@@ -22873,7 +22873,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G776" t="n">
-        <v>1.60458266735077</v>
+        <v>1.60458254814148</v>
       </c>
       <c r="H776" t="n">
         <v>28500</v>
@@ -22902,7 +22902,7 @@
         <v>2</v>
       </c>
       <c r="G777" t="n">
-        <v>1.63732898235321</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H777" t="n">
         <v>16500</v>
@@ -22931,7 +22931,7 @@
         <v>2</v>
       </c>
       <c r="G778" t="n">
-        <v>1.63732898235321</v>
+        <v>1.6373291015625</v>
       </c>
       <c r="H778" t="n">
         <v>3000</v>
@@ -22989,7 +22989,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G780" t="n">
-        <v>1.8256219625473</v>
+        <v>1.82562172412872</v>
       </c>
       <c r="H780" t="n">
         <v>60000</v>
@@ -23018,7 +23018,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G781" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H781" t="n">
         <v>11250</v>
@@ -23047,7 +23047,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G782" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H782" t="n">
         <v>7500</v>
@@ -23076,7 +23076,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G783" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H783" t="n">
         <v>6750</v>
@@ -23105,7 +23105,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G784" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H784" t="n">
         <v>2250</v>
@@ -23221,7 +23221,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G788" t="n">
-        <v>1.8010618686676</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H788" t="n">
         <v>35250</v>
@@ -23279,7 +23279,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G790" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H790" t="n">
         <v>4500</v>
@@ -23366,7 +23366,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G793" t="n">
-        <v>1.80924868583679</v>
+        <v>1.80924880504608</v>
       </c>
       <c r="H793" t="n">
         <v>7500</v>
@@ -23453,7 +23453,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G796" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H796" t="n">
         <v>1500</v>
@@ -23482,7 +23482,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G797" t="n">
-        <v>1.76012885570526</v>
+        <v>1.76012897491455</v>
       </c>
       <c r="H797" t="n">
         <v>2250</v>
@@ -23540,7 +23540,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G799" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H799" t="n">
         <v>3750</v>
@@ -23598,7 +23598,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G801" t="n">
-        <v>1.73556888103485</v>
+        <v>1.73556876182556</v>
       </c>
       <c r="H801" t="n">
         <v>12750</v>
@@ -23627,7 +23627,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G802" t="n">
-        <v>1.74375545978546</v>
+        <v>1.74375557899475</v>
       </c>
       <c r="H802" t="n">
         <v>3000</v>
@@ -23656,7 +23656,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G803" t="n">
-        <v>1.68644905090332</v>
+        <v>1.68644893169403</v>
       </c>
       <c r="H803" t="n">
         <v>73500</v>
@@ -23685,7 +23685,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G804" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H804" t="n">
         <v>9750</v>
@@ -23714,7 +23714,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G805" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H805" t="n">
         <v>45750</v>
@@ -23743,7 +23743,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G806" t="n">
-        <v>1.71919536590576</v>
+        <v>1.71919548511505</v>
       </c>
       <c r="H806" t="n">
         <v>3000</v>
@@ -23772,7 +23772,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G807" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H807" t="n">
         <v>2250</v>
@@ -23801,7 +23801,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G808" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H808" t="n">
         <v>750</v>
@@ -23830,7 +23830,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G809" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H809" t="n">
         <v>0</v>
@@ -23859,7 +23859,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G810" t="n">
-        <v>1.67826223373413</v>
+        <v>1.67826235294342</v>
       </c>
       <c r="H810" t="n">
         <v>0</v>
@@ -23946,7 +23946,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G813" t="n">
-        <v>1.77650213241577</v>
+        <v>1.77650201320648</v>
       </c>
       <c r="H813" t="n">
         <v>5250</v>
@@ -23975,7 +23975,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G814" t="n">
-        <v>1.8010618686676</v>
+        <v>1.80106210708618</v>
       </c>
       <c r="H814" t="n">
         <v>9000</v>
@@ -24004,7 +24004,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G815" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H815" t="n">
         <v>11250</v>
@@ -24033,7 +24033,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G816" t="n">
-        <v>1.94842171669006</v>
+        <v>1.94842183589935</v>
       </c>
       <c r="H816" t="n">
         <v>13500</v>
@@ -24062,7 +24062,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G817" t="n">
-        <v>1.90748822689056</v>
+        <v>1.90748858451843</v>
       </c>
       <c r="H817" t="n">
         <v>76500</v>
@@ -24149,7 +24149,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G820" t="n">
-        <v>1.89111518859863</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H820" t="n">
         <v>11250</v>
@@ -24178,7 +24178,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G821" t="n">
-        <v>1.90748822689056</v>
+        <v>1.90748858451843</v>
       </c>
       <c r="H821" t="n">
         <v>2250</v>
@@ -24236,7 +24236,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G823" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H823" t="n">
         <v>3750</v>
@@ -24265,7 +24265,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G824" t="n">
-        <v>1.95660853385925</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H824" t="n">
         <v>65250</v>
@@ -24294,7 +24294,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G825" t="n">
-        <v>1.95660853385925</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H825" t="n">
         <v>78000</v>
@@ -24323,7 +24323,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G826" t="n">
-        <v>1.94023489952087</v>
+        <v>1.94023513793945</v>
       </c>
       <c r="H826" t="n">
         <v>27000</v>
@@ -24352,7 +24352,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G827" t="n">
-        <v>1.94023489952087</v>
+        <v>1.94023513793945</v>
       </c>
       <c r="H827" t="n">
         <v>60000</v>
@@ -24381,7 +24381,7 @@
         <v>2.32999992370605</v>
       </c>
       <c r="G828" t="n">
-        <v>1.90748822689056</v>
+        <v>1.90748858451843</v>
       </c>
       <c r="H828" t="n">
         <v>11250</v>
@@ -24410,7 +24410,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G829" t="n">
-        <v>1.95660853385925</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H829" t="n">
         <v>36000</v>
@@ -24468,7 +24468,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G831" t="n">
-        <v>2.09578108787537</v>
+        <v>2.09578132629395</v>
       </c>
       <c r="H831" t="n">
         <v>31500</v>
@@ -24497,7 +24497,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G832" t="n">
-        <v>2.12034130096436</v>
+        <v>2.12034106254578</v>
       </c>
       <c r="H832" t="n">
         <v>2250</v>
@@ -24584,7 +24584,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G835" t="n">
-        <v>1.99754154682159</v>
+        <v>1.99754166603088</v>
       </c>
       <c r="H835" t="n">
         <v>6000</v>
@@ -24613,7 +24613,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G836" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H836" t="n">
         <v>7500</v>
@@ -24642,7 +24642,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G837" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H837" t="n">
         <v>3750</v>
@@ -24700,7 +24700,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G839" t="n">
-        <v>2.02210140228271</v>
+        <v>2.02210164070129</v>
       </c>
       <c r="H839" t="n">
         <v>27750</v>
@@ -24758,7 +24758,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G841" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H841" t="n">
         <v>33000</v>
@@ -24787,7 +24787,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G842" t="n">
-        <v>2.12852787971497</v>
+        <v>2.12852764129639</v>
       </c>
       <c r="H842" t="n">
         <v>26250</v>
@@ -24816,7 +24816,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G843" t="n">
-        <v>2.09578108787537</v>
+        <v>2.09578132629395</v>
       </c>
       <c r="H843" t="n">
         <v>2250</v>
@@ -24845,7 +24845,7 @@
         <v>2.55999994277954</v>
       </c>
       <c r="G844" t="n">
-        <v>2.09578108787537</v>
+        <v>2.09578132629395</v>
       </c>
       <c r="H844" t="n">
         <v>0</v>
@@ -25048,7 +25048,7 @@
         <v>2.54999995231628</v>
       </c>
       <c r="G851" t="n">
-        <v>2.08759450912476</v>
+        <v>2.08759474754333</v>
       </c>
       <c r="H851" t="n">
         <v>7500</v>
@@ -25164,7 +25164,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G855" t="n">
-        <v>1.97298169136047</v>
+        <v>1.97298145294189</v>
       </c>
       <c r="H855" t="n">
         <v>7500</v>
@@ -25193,7 +25193,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G856" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H856" t="n">
         <v>2250</v>
@@ -25222,7 +25222,7 @@
         <v>2.39000010490417</v>
       </c>
       <c r="G857" t="n">
-        <v>1.95660853385925</v>
+        <v>1.95660817623138</v>
       </c>
       <c r="H857" t="n">
         <v>9750</v>
@@ -25251,7 +25251,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G858" t="n">
-        <v>1.97298169136047</v>
+        <v>1.97298145294189</v>
       </c>
       <c r="H858" t="n">
         <v>750</v>
@@ -25280,7 +25280,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G859" t="n">
-        <v>1.98935508728027</v>
+        <v>1.98935496807098</v>
       </c>
       <c r="H859" t="n">
         <v>53250</v>
@@ -25367,7 +25367,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G862" t="n">
-        <v>1.93204808235168</v>
+        <v>1.93204832077026</v>
       </c>
       <c r="H862" t="n">
         <v>27000</v>
@@ -25454,7 +25454,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G865" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H865" t="n">
         <v>6750</v>
@@ -25483,7 +25483,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G866" t="n">
-        <v>1.89930188655853</v>
+        <v>1.89930164813995</v>
       </c>
       <c r="H866" t="n">
         <v>0</v>
@@ -25541,7 +25541,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G868" t="n">
-        <v>1.89111518859863</v>
+        <v>1.89111506938934</v>
       </c>
       <c r="H868" t="n">
         <v>11250</v>
@@ -25570,7 +25570,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G869" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H869" t="n">
         <v>23250</v>
@@ -25599,7 +25599,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G870" t="n">
-        <v>1.86655521392822</v>
+        <v>1.86655509471893</v>
       </c>
       <c r="H870" t="n">
         <v>0</v>
@@ -25628,7 +25628,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G871" t="n">
-        <v>1.8338086605072</v>
+        <v>1.83380877971649</v>
       </c>
       <c r="H871" t="n">
         <v>3750</v>
@@ -26411,7 +26411,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G898" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116838932037</v>
       </c>
       <c r="H898" t="n">
         <v>10500</v>
@@ -26469,7 +26469,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G900" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H900" t="n">
         <v>1500</v>
@@ -26556,7 +26556,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G903" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H903" t="n">
         <v>11250</v>
@@ -26585,7 +26585,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G904" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H904" t="n">
         <v>2250</v>
@@ -26614,7 +26614,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G905" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H905" t="n">
         <v>3000</v>
@@ -26643,7 +26643,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G906" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993104457855</v>
       </c>
       <c r="H906" t="n">
         <v>750</v>
@@ -26672,7 +26672,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G907" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993104457855</v>
       </c>
       <c r="H907" t="n">
         <v>3000</v>
@@ -26701,7 +26701,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G908" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H908" t="n">
         <v>21000</v>
@@ -26730,7 +26730,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G909" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H909" t="n">
         <v>12750</v>
@@ -26817,7 +26817,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G912" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H912" t="n">
         <v>3000</v>
@@ -27049,7 +27049,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G920" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H920" t="n">
         <v>5250</v>
@@ -27078,7 +27078,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G921" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H921" t="n">
         <v>6750</v>
@@ -27107,7 +27107,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G922" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H922" t="n">
         <v>0</v>
@@ -27194,7 +27194,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G925" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H925" t="n">
         <v>8250</v>
@@ -27281,7 +27281,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G928" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H928" t="n">
         <v>3000</v>
@@ -27310,7 +27310,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G929" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H929" t="n">
         <v>6750</v>
@@ -27339,7 +27339,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G930" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H930" t="n">
         <v>750</v>
@@ -27368,7 +27368,7 @@
         <v>2.33999991416931</v>
       </c>
       <c r="G931" t="n">
-        <v>1.99824702739716</v>
+        <v>1.99824726581573</v>
       </c>
       <c r="H931" t="n">
         <v>0</v>
@@ -27397,7 +27397,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G932" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H932" t="n">
         <v>2250</v>
@@ -27426,7 +27426,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G933" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H933" t="n">
         <v>20250</v>
@@ -27455,7 +27455,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G934" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H934" t="n">
         <v>12000</v>
@@ -27484,7 +27484,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G935" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H935" t="n">
         <v>5250</v>
@@ -27571,7 +27571,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G938" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H938" t="n">
         <v>14250</v>
@@ -27716,7 +27716,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G943" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H943" t="n">
         <v>2250</v>
@@ -27745,7 +27745,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G944" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H944" t="n">
         <v>750</v>
@@ -27774,7 +27774,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G945" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H945" t="n">
         <v>1500</v>
@@ -27803,7 +27803,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G946" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H946" t="n">
         <v>0</v>
@@ -27832,7 +27832,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G947" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H947" t="n">
         <v>0</v>
@@ -27861,7 +27861,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G948" t="n">
-        <v>1.96408915519714</v>
+        <v>1.96408927440643</v>
       </c>
       <c r="H948" t="n">
         <v>2250</v>
@@ -27890,7 +27890,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G949" t="n">
-        <v>1.98116827011108</v>
+        <v>1.98116815090179</v>
       </c>
       <c r="H949" t="n">
         <v>9000</v>
@@ -27948,7 +27948,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G951" t="n">
-        <v>1.9128520488739</v>
+        <v>1.91285216808319</v>
       </c>
       <c r="H951" t="n">
         <v>10500</v>
@@ -27977,7 +27977,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G952" t="n">
-        <v>1.92993116378784</v>
+        <v>1.92993104457855</v>
       </c>
       <c r="H952" t="n">
         <v>9750</v>
@@ -28006,7 +28006,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G953" t="n">
-        <v>1.87869381904602</v>
+        <v>1.87869393825531</v>
       </c>
       <c r="H953" t="n">
         <v>3000</v>
@@ -28035,7 +28035,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G954" t="n">
-        <v>2.01532602310181</v>
+        <v>2.01532626152039</v>
       </c>
       <c r="H954" t="n">
         <v>6750</v>
@@ -28209,7 +28209,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G960" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H960" t="n">
         <v>30750</v>
@@ -28238,7 +28238,7 @@
         <v>2</v>
       </c>
       <c r="G961" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H961" t="n">
         <v>28500</v>
@@ -28354,7 +28354,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G965" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H965" t="n">
         <v>3750</v>
@@ -28412,7 +28412,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G967" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H967" t="n">
         <v>6750</v>
@@ -28441,7 +28441,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G968" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H968" t="n">
         <v>2250</v>
@@ -28470,7 +28470,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G969" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H969" t="n">
         <v>3750</v>
@@ -28499,7 +28499,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G970" t="n">
-        <v>1.8445360660553</v>
+        <v>1.84453594684601</v>
       </c>
       <c r="H970" t="n">
         <v>2250</v>
@@ -28615,7 +28615,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G974" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H974" t="n">
         <v>750</v>
@@ -28644,7 +28644,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G975" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H975" t="n">
         <v>0</v>
@@ -28673,7 +28673,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G976" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H976" t="n">
         <v>0</v>
@@ -28702,7 +28702,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G977" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H977" t="n">
         <v>0</v>
@@ -28731,7 +28731,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G978" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037771701813</v>
       </c>
       <c r="H978" t="n">
         <v>3000</v>
@@ -28760,7 +28760,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G979" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H979" t="n">
         <v>2250</v>
@@ -28789,7 +28789,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G980" t="n">
-        <v>1.77621972560883</v>
+        <v>1.77621960639954</v>
       </c>
       <c r="H980" t="n">
         <v>11250</v>
@@ -28818,7 +28818,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G981" t="n">
-        <v>1.81037783622742</v>
+        <v>1.81037771701813</v>
       </c>
       <c r="H981" t="n">
         <v>27000</v>
@@ -28876,7 +28876,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G983" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H983" t="n">
         <v>1500</v>
@@ -28963,7 +28963,7 @@
         <v>2</v>
       </c>
       <c r="G986" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H986" t="n">
         <v>8250</v>
@@ -29050,7 +29050,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G989" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H989" t="n">
         <v>18000</v>
@@ -29108,7 +29108,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G991" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H991" t="n">
         <v>120750</v>
@@ -29311,7 +29311,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G998" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H998" t="n">
         <v>750</v>
@@ -29340,7 +29340,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G999" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H999" t="n">
         <v>0</v>
@@ -29369,7 +29369,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1000" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1000" t="n">
         <v>16500</v>
@@ -29398,7 +29398,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1001" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1001" t="n">
         <v>8250</v>
@@ -29456,7 +29456,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1003" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1003" t="n">
         <v>39000</v>
@@ -29485,7 +29485,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1004" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1004" t="n">
         <v>81000</v>
@@ -29514,7 +29514,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1005" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1005" t="n">
         <v>9000</v>
@@ -29543,7 +29543,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1006" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1006" t="n">
         <v>10500</v>
@@ -29572,7 +29572,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1007" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1007" t="n">
         <v>18750</v>
@@ -29601,7 +29601,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1008" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1008" t="n">
         <v>9000</v>
@@ -29630,7 +29630,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1009" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1009" t="n">
         <v>0</v>
@@ -29659,7 +29659,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1010" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1010" t="n">
         <v>12000</v>
@@ -29688,7 +29688,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1011" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1011" t="n">
         <v>6000</v>
@@ -29717,7 +29717,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1012" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1012" t="n">
         <v>6000</v>
@@ -29746,7 +29746,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1013" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1013" t="n">
         <v>8250</v>
@@ -29775,7 +29775,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1014" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1014" t="n">
         <v>9000</v>
@@ -29804,7 +29804,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1015" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1015" t="n">
         <v>0</v>
@@ -29949,7 +29949,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1020" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1020" t="n">
         <v>24750</v>
@@ -29978,7 +29978,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1021" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1021" t="n">
         <v>4500</v>
@@ -30152,7 +30152,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1027" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1027" t="n">
         <v>1500</v>
@@ -30181,7 +30181,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1028" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1028" t="n">
         <v>1500</v>
@@ -30210,7 +30210,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1029" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1029" t="n">
         <v>0</v>
@@ -30297,7 +30297,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1032" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1032" t="n">
         <v>4500</v>
@@ -30384,7 +30384,7 @@
         <v>1.54999995231628</v>
       </c>
       <c r="G1035" t="n">
-        <v>1.32362532615662</v>
+        <v>1.32362520694733</v>
       </c>
       <c r="H1035" t="n">
         <v>6000</v>
@@ -30413,7 +30413,7 @@
         <v>1.48000001907349</v>
       </c>
       <c r="G1036" t="n">
-        <v>1.2638486623764</v>
+        <v>1.26384878158569</v>
       </c>
       <c r="H1036" t="n">
         <v>95250</v>
@@ -30471,7 +30471,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1038" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1038" t="n">
         <v>23250</v>
@@ -30500,7 +30500,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1039" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1039" t="n">
         <v>12000</v>
@@ -30529,7 +30529,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1040" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1040" t="n">
         <v>750</v>
@@ -30558,7 +30558,7 @@
         <v>1.53999996185303</v>
       </c>
       <c r="G1041" t="n">
-        <v>1.31508564949036</v>
+        <v>1.31508576869965</v>
       </c>
       <c r="H1041" t="n">
         <v>6750</v>
@@ -30587,7 +30587,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1042" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1042" t="n">
         <v>5250</v>
@@ -30616,7 +30616,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1043" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1043" t="n">
         <v>0</v>
@@ -30645,7 +30645,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1044" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1044" t="n">
         <v>1500</v>
@@ -30790,7 +30790,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1049" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1049" t="n">
         <v>9000</v>
@@ -30819,7 +30819,7 @@
         <v>1.5900000333786</v>
       </c>
       <c r="G1050" t="n">
-        <v>1.35778331756592</v>
+        <v>1.35778343677521</v>
       </c>
       <c r="H1050" t="n">
         <v>2250</v>
@@ -30906,7 +30906,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1053" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1053" t="n">
         <v>3750</v>
@@ -30935,7 +30935,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1054" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1054" t="n">
         <v>31500</v>
@@ -30964,7 +30964,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1055" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1055" t="n">
         <v>21000</v>
@@ -30993,7 +30993,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1056" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1056" t="n">
         <v>18000</v>
@@ -31051,7 +31051,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1058" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1058" t="n">
         <v>2250</v>
@@ -31080,7 +31080,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1059" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1059" t="n">
         <v>99750</v>
@@ -31109,7 +31109,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1060" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1060" t="n">
         <v>4500</v>
@@ -31138,7 +31138,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1061" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1061" t="n">
         <v>5250</v>
@@ -31167,7 +31167,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1062" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1062" t="n">
         <v>0</v>
@@ -31225,7 +31225,7 @@
         <v>1.63999998569489</v>
       </c>
       <c r="G1064" t="n">
-        <v>1.40048086643219</v>
+        <v>1.40048098564148</v>
       </c>
       <c r="H1064" t="n">
         <v>8250</v>
@@ -31399,7 +31399,7 @@
         <v>1.70000004768372</v>
       </c>
       <c r="G1070" t="n">
-        <v>1.45171809196472</v>
+        <v>1.45171821117401</v>
       </c>
       <c r="H1070" t="n">
         <v>3750</v>
@@ -31428,7 +31428,7 @@
         <v>1.73000001907349</v>
       </c>
       <c r="G1071" t="n">
-        <v>1.47733664512634</v>
+        <v>1.47733676433563</v>
       </c>
       <c r="H1071" t="n">
         <v>750</v>
@@ -31486,7 +31486,7 @@
         <v>1.69000005722046</v>
       </c>
       <c r="G1073" t="n">
-        <v>1.44317853450775</v>
+        <v>1.44317865371704</v>
       </c>
       <c r="H1073" t="n">
         <v>15750</v>
@@ -31631,7 +31631,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1078" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1078" t="n">
         <v>2250</v>
@@ -31660,7 +31660,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1079" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1079" t="n">
         <v>2250</v>
@@ -31689,7 +31689,7 @@
         <v>1.67999994754791</v>
       </c>
       <c r="G1080" t="n">
-        <v>1.43463897705078</v>
+        <v>1.43463909626007</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -31805,7 +31805,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1084" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1084" t="n">
         <v>19500</v>
@@ -31863,7 +31863,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1086" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1086" t="n">
         <v>3000</v>
@@ -31892,7 +31892,7 @@
         <v>1.60000002384186</v>
       </c>
       <c r="G1087" t="n">
-        <v>1.36632299423218</v>
+        <v>1.36632287502289</v>
       </c>
       <c r="H1087" t="n">
         <v>6000</v>
@@ -31979,7 +31979,7 @@
         <v>1.66999995708466</v>
       </c>
       <c r="G1090" t="n">
-        <v>1.42609941959381</v>
+        <v>1.4260995388031</v>
       </c>
       <c r="H1090" t="n">
         <v>15750</v>
@@ -32124,7 +32124,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G1095" t="n">
-        <v>1.5883504152298</v>
+        <v>1.58835029602051</v>
       </c>
       <c r="H1095" t="n">
         <v>20250</v>
@@ -32182,7 +32182,7 @@
         <v>1.74000000953674</v>
       </c>
       <c r="G1097" t="n">
-        <v>1.48587608337402</v>
+        <v>1.48587620258331</v>
       </c>
       <c r="H1097" t="n">
         <v>9750</v>
@@ -32617,7 +32617,7 @@
         <v>2</v>
       </c>
       <c r="G1112" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1112" t="n">
         <v>37500</v>
@@ -32646,7 +32646,7 @@
         <v>2</v>
       </c>
       <c r="G1113" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1113" t="n">
         <v>2250</v>
@@ -32762,7 +32762,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1117" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1117" t="n">
         <v>3000</v>
@@ -32791,7 +32791,7 @@
         <v>2</v>
       </c>
       <c r="G1118" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1118" t="n">
         <v>32250</v>
@@ -32878,7 +32878,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1121" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1121" t="n">
         <v>3000</v>
@@ -32907,7 +32907,7 @@
         <v>2</v>
       </c>
       <c r="G1122" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1122" t="n">
         <v>1500</v>
@@ -32936,7 +32936,7 @@
         <v>2</v>
       </c>
       <c r="G1123" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1123" t="n">
         <v>750</v>
@@ -32994,7 +32994,7 @@
         <v>2</v>
       </c>
       <c r="G1125" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1125" t="n">
         <v>27750</v>
@@ -33023,7 +33023,7 @@
         <v>2</v>
       </c>
       <c r="G1126" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1126" t="n">
         <v>82500</v>
@@ -33052,7 +33052,7 @@
         <v>1.96000003814697</v>
       </c>
       <c r="G1127" t="n">
-        <v>1.67374563217163</v>
+        <v>1.67374551296234</v>
       </c>
       <c r="H1127" t="n">
         <v>1500</v>
@@ -33081,7 +33081,7 @@
         <v>2</v>
       </c>
       <c r="G1128" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1128" t="n">
         <v>19500</v>
@@ -33110,7 +33110,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1129" t="n">
-        <v>1.75914072990417</v>
+        <v>1.75914061069489</v>
       </c>
       <c r="H1129" t="n">
         <v>3000</v>
@@ -33139,7 +33139,7 @@
         <v>2</v>
       </c>
       <c r="G1130" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1130" t="n">
         <v>12750</v>
@@ -33255,7 +33255,7 @@
         <v>2</v>
       </c>
       <c r="G1134" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1134" t="n">
         <v>2250</v>
@@ -33284,7 +33284,7 @@
         <v>2</v>
       </c>
       <c r="G1135" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1135" t="n">
         <v>0</v>
@@ -33748,7 +33748,7 @@
         <v>2</v>
       </c>
       <c r="G1151" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1151" t="n">
         <v>18000</v>
@@ -33777,7 +33777,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1152" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1152" t="n">
         <v>122250</v>
@@ -34705,7 +34705,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1184" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1184" t="n">
         <v>84000</v>
@@ -34792,7 +34792,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1187" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1187" t="n">
         <v>18000</v>
@@ -34879,7 +34879,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1190" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1190" t="n">
         <v>57000</v>
@@ -34908,7 +34908,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1191" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1191" t="n">
         <v>43500</v>
@@ -34937,7 +34937,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1192" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1192" t="n">
         <v>75750</v>
@@ -34966,7 +34966,7 @@
         <v>2.29999995231628</v>
       </c>
       <c r="G1193" t="n">
-        <v>2.06746220588684</v>
+        <v>2.06746244430542</v>
       </c>
       <c r="H1193" t="n">
         <v>28500</v>
@@ -34995,7 +34995,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1194" t="n">
-        <v>1.99555051326752</v>
+        <v>1.99555063247681</v>
       </c>
       <c r="H1194" t="n">
         <v>24000</v>
@@ -35024,7 +35024,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1195" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1195" t="n">
         <v>12000</v>
@@ -35053,7 +35053,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1196" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1196" t="n">
         <v>12000</v>
@@ -35082,7 +35082,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1197" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1197" t="n">
         <v>2250</v>
@@ -35111,7 +35111,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1198" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1198" t="n">
         <v>30000</v>
@@ -35140,7 +35140,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1199" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1199" t="n">
         <v>3750</v>
@@ -35169,7 +35169,7 @@
         <v>2.20000004768372</v>
       </c>
       <c r="G1200" t="n">
-        <v>1.97757267951965</v>
+        <v>1.97757256031036</v>
       </c>
       <c r="H1200" t="n">
         <v>0</v>
@@ -35198,7 +35198,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1201" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1201" t="n">
         <v>750</v>
@@ -35227,7 +35227,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1202" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1202" t="n">
         <v>6000</v>
@@ -35256,7 +35256,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1203" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1203" t="n">
         <v>9000</v>
@@ -35314,7 +35314,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1205" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1205" t="n">
         <v>21000</v>
@@ -35343,7 +35343,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1206" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1206" t="n">
         <v>24750</v>
@@ -35372,7 +35372,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1207" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1207" t="n">
         <v>3750</v>
@@ -35401,7 +35401,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1208" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1208" t="n">
         <v>3750</v>
@@ -35981,7 +35981,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1228" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1228" t="n">
         <v>12750</v>
@@ -36010,7 +36010,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1229" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1229" t="n">
         <v>9750</v>
@@ -36126,7 +36126,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1233" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1233" t="n">
         <v>1500</v>
@@ -36155,7 +36155,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1234" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1234" t="n">
         <v>0</v>
@@ -36387,7 +36387,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1242" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1242" t="n">
         <v>27000</v>
@@ -36445,7 +36445,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1244" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1244" t="n">
         <v>2250</v>
@@ -36561,7 +36561,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1248" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1248" t="n">
         <v>3000</v>
@@ -36764,7 +36764,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1255" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1255" t="n">
         <v>7500</v>
@@ -36793,7 +36793,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1256" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1256" t="n">
         <v>11250</v>
@@ -36851,7 +36851,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1258" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1258" t="n">
         <v>20250</v>
@@ -36938,7 +36938,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1261" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1261" t="n">
         <v>12750</v>
@@ -36996,7 +36996,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1263" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1263" t="n">
         <v>32250</v>
@@ -37402,7 +37402,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1277" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1277" t="n">
         <v>5250</v>
@@ -37431,7 +37431,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1278" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1278" t="n">
         <v>4500</v>
@@ -37518,7 +37518,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1281" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1281" t="n">
         <v>6000</v>
@@ -37576,7 +37576,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1283" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1283" t="n">
         <v>2250</v>
@@ -37605,7 +37605,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1284" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1284" t="n">
         <v>8250</v>
@@ -37779,7 +37779,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1290" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1290" t="n">
         <v>14250</v>
@@ -37837,7 +37837,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1292" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1292" t="n">
         <v>750</v>
@@ -37866,7 +37866,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1293" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1293" t="n">
         <v>750</v>
@@ -37895,7 +37895,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1294" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1294" t="n">
         <v>0</v>
@@ -37953,7 +37953,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1296" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1296" t="n">
         <v>4500</v>
@@ -37982,7 +37982,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1297" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1297" t="n">
         <v>3000</v>
@@ -38040,7 +38040,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1299" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1299" t="n">
         <v>7500</v>
@@ -38069,7 +38069,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1300" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1300" t="n">
         <v>3000</v>
@@ -38098,7 +38098,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1301" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1301" t="n">
         <v>6750</v>
@@ -38127,7 +38127,7 @@
         <v>1.89999997615814</v>
       </c>
       <c r="G1302" t="n">
-        <v>1.70790350437164</v>
+        <v>1.70790362358093</v>
       </c>
       <c r="H1302" t="n">
         <v>6000</v>
@@ -38359,7 +38359,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1310" t="n">
-        <v>1.78880441188812</v>
+        <v>1.78880429267883</v>
       </c>
       <c r="H1310" t="n">
         <v>7500</v>
@@ -39229,7 +39229,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1340" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1340" t="n">
         <v>5250</v>
@@ -39258,7 +39258,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1341" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1341" t="n">
         <v>2250</v>
@@ -39287,7 +39287,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1342" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1342" t="n">
         <v>12000</v>
@@ -39316,7 +39316,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1343" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1343" t="n">
         <v>13500</v>
@@ -39345,7 +39345,7 @@
         <v>1.92999994754791</v>
       </c>
       <c r="G1344" t="n">
-        <v>1.73487043380737</v>
+        <v>1.73487055301666</v>
       </c>
       <c r="H1344" t="n">
         <v>5250</v>
@@ -39403,7 +39403,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1346" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1346" t="n">
         <v>6000</v>
@@ -39432,7 +39432,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G1347" t="n">
-        <v>1.71689260005951</v>
+        <v>1.71689248085022</v>
       </c>
       <c r="H1347" t="n">
         <v>0</v>
@@ -40012,7 +40012,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1367" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1367" t="n">
         <v>2250</v>
@@ -40041,7 +40041,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1368" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1368" t="n">
         <v>42750</v>
@@ -40070,7 +40070,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1369" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1369" t="n">
         <v>4500</v>
@@ -40099,7 +40099,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1370" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1370" t="n">
         <v>0</v>
@@ -40128,7 +40128,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1371" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1371" t="n">
         <v>1500</v>
@@ -40244,7 +40244,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1375" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1375" t="n">
         <v>750</v>
@@ -40273,7 +40273,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1376" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1376" t="n">
         <v>0</v>
@@ -40360,7 +40360,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1379" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1379" t="n">
         <v>5250</v>
@@ -40389,7 +40389,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1380" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1380" t="n">
         <v>114750</v>
@@ -40418,7 +40418,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1381" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1381" t="n">
         <v>12750</v>
@@ -40447,7 +40447,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1382" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1382" t="n">
         <v>4500</v>
@@ -40476,7 +40476,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1383" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1383" t="n">
         <v>1500</v>
@@ -40505,7 +40505,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1384" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1384" t="n">
         <v>0</v>
@@ -40563,7 +40563,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1386" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1386" t="n">
         <v>15000</v>
@@ -40592,7 +40592,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1387" t="n">
-        <v>1.94161689281464</v>
+        <v>1.94161677360535</v>
       </c>
       <c r="H1387" t="n">
         <v>3000</v>
@@ -40621,7 +40621,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G1388" t="n">
-        <v>1.88768291473389</v>
+        <v>1.8876827955246</v>
       </c>
       <c r="H1388" t="n">
         <v>2250</v>
@@ -40650,7 +40650,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1389" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1389" t="n">
         <v>1500</v>
@@ -40679,7 +40679,7 @@
         <v>2.14000010490417</v>
       </c>
       <c r="G1390" t="n">
-        <v>1.92363905906677</v>
+        <v>1.92363882064819</v>
       </c>
       <c r="H1390" t="n">
         <v>0</v>
@@ -40708,7 +40708,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1391" t="n">
-        <v>1.90566062927246</v>
+        <v>1.90566086769104</v>
       </c>
       <c r="H1391" t="n">
         <v>1500</v>
@@ -40737,7 +40737,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G1392" t="n">
-        <v>2.03150653839111</v>
+        <v>2.03150629997253</v>
       </c>
       <c r="H1392" t="n">
         <v>60750</v>
@@ -40766,7 +40766,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1393" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1393" t="n">
         <v>5250</v>
@@ -40795,7 +40795,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G1394" t="n">
-        <v>2.01352834701538</v>
+        <v>2.01352858543396</v>
       </c>
       <c r="H1394" t="n">
         <v>13500</v>
@@ -40824,7 +40824,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1395" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1395" t="n">
         <v>11250</v>
@@ -40853,7 +40853,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1396" t="n">
-        <v>2.04948449134827</v>
+        <v>2.04948425292969</v>
       </c>
       <c r="H1396" t="n">
         <v>21000</v>
@@ -40911,7 +40911,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1398" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1398" t="n">
         <v>15750</v>
@@ -40969,7 +40969,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1400" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1400" t="n">
         <v>22500</v>
@@ -41027,7 +41027,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G1402" t="n">
-        <v>2.12139582633972</v>
+        <v>2.1213960647583</v>
       </c>
       <c r="H1402" t="n">
         <v>9000</v>
@@ -52053,6 +52053,35 @@
         <v>3750</v>
       </c>
       <c r="I1782" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1783">
+      <c r="A1783" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1783" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1783" t="n">
+        <v>3.02999997138977</v>
+      </c>
+      <c r="D1783" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="E1783" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="F1783" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="G1783" t="n">
+        <v>2.99000000953674</v>
+      </c>
+      <c r="H1783" t="n">
+        <v>4500</v>
+      </c>
+      <c r="I1783" t="s">
         <v>9</v>
       </c>
     </row>
